--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$Q$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$R$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
     <author>C</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="2">
+    <comment ref="J1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="1">
+    <comment ref="L1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -124,7 +124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1">
+    <comment ref="M1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -139,7 +139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -151,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="2">
+    <comment ref="O1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="2">
+    <comment ref="P1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -197,7 +197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2">
+    <comment ref="Q1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -221,7 +221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -244,7 +244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="2">
+    <comment ref="T1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -267,12 +267,58 @@
         </r>
       </text>
     </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+触发金额_多语言ID
+单局游戏获得金额大于此值时，添加至跑马灯列表播放
+当值小于等于0时，不播</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+道具ID_数量</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="75">
   <si>
     <t>游戏ID</t>
   </si>
@@ -280,6 +326,9 @@
     <t>游戏名称</t>
   </si>
   <si>
+    <t>多语言表ID</t>
+  </si>
+  <si>
     <t>机器人加入房间间隔（毫秒）</t>
   </si>
   <si>
@@ -322,6 +371,12 @@
     <t>历史记录清除方式</t>
   </si>
   <si>
+    <t>跑马触发金额</t>
+  </si>
+  <si>
+    <t>上庄最低金额</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -331,12 +386,21 @@
     <t>list&lt;list&lt;int&gt;{:}&gt;{|}</t>
   </si>
   <si>
+    <t>List&lt;long&gt;{_}</t>
+  </si>
+  <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>gameID</t>
   </si>
   <si>
+    <t>nameid</t>
+  </si>
+  <si>
     <t>IntervalTime</t>
   </si>
   <si>
@@ -379,6 +443,12 @@
     <t>RecordDeleteType</t>
   </si>
   <si>
+    <t>marqueeTrigger</t>
+  </si>
+  <si>
+    <t>minBankerAmount</t>
+  </si>
+  <si>
     <t>红黑大战</t>
   </si>
   <si>
@@ -397,10 +467,13 @@
     <t>组合</t>
   </si>
   <si>
-    <t>2000,14000,11000,0</t>
-  </si>
-  <si>
-    <t>覆盖</t>
+    <t>3000,14000,11000,0</t>
+  </si>
+  <si>
+    <t>500000_17001</t>
+  </si>
+  <si>
+    <t>1030002_1000</t>
   </si>
   <si>
     <t>中级场</t>
@@ -409,52 +482,52 @@
     <t>10000,20000,50000,100000,200000,500000,1000000</t>
   </si>
   <si>
+    <t>50000000_17001</t>
+  </si>
+  <si>
     <t>高级场</t>
   </si>
   <si>
     <t>1000000,2000000,5000000,10000000,20000000,50000000,100000000</t>
   </si>
   <si>
+    <t>5000000000_17001</t>
+  </si>
+  <si>
     <t>龙虎斗</t>
   </si>
   <si>
     <t>直接</t>
   </si>
   <si>
-    <t>2000,14000,13000,0</t>
+    <t>3000,14000,13000,0</t>
   </si>
   <si>
     <t>飞禽走兽</t>
   </si>
   <si>
-    <t>0,16000,17000,0</t>
+    <t>2000,16000,17000,0</t>
   </si>
   <si>
     <t>豪车俱乐部</t>
   </si>
   <si>
-    <t>0,16000,12000,0</t>
+    <t>2000,16000,12000,0</t>
   </si>
   <si>
     <t>百家乐</t>
   </si>
   <si>
-    <t>0,16000,14000,0</t>
+    <t>2000,16000,14000,0</t>
   </si>
   <si>
     <t>三个骰子</t>
   </si>
   <si>
-    <t>5000,14000,11000,0</t>
+    <t>4000,14000,11000,0</t>
   </si>
   <si>
     <t>色碟</t>
-  </si>
-  <si>
-    <t>3000,14000,11000,0</t>
-  </si>
-  <si>
-    <t>清空</t>
   </si>
   <si>
     <t>大小骰子</t>
@@ -482,7 +555,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,6 +577,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1034,156 +1113,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1215,6 +1294,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1238,80 +1320,83 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1658,28 +1743,30 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3"/>
     <col min="2" max="2" width="12" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="8.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.1416666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="28.2333333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="8.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="65" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="5.125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="24.75" style="3" customWidth="1"/>
-    <col min="12" max="17" width="9.81666666666667" style="3" customWidth="1"/>
-    <col min="18" max="18" width="17.2166666666667" style="4" customWidth="1"/>
-    <col min="19" max="19" width="19.5" style="5" customWidth="1"/>
-    <col min="20" max="20" width="8.96666666666667" style="4" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="3" max="4" width="20.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.1416666666667" style="3" customWidth="1"/>
+    <col min="7" max="7" width="28.2333333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="65" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="5.125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="24.75" style="3" customWidth="1"/>
+    <col min="13" max="18" width="9.81666666666667" style="3" customWidth="1"/>
+    <col min="19" max="19" width="17.2166666666667" style="4" customWidth="1"/>
+    <col min="20" max="21" width="19.5" style="5" customWidth="1"/>
+    <col min="22" max="22" width="19.125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="9.25" style="2"/>
+    <col min="24" max="24" width="20.125" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:22">
       <c r="A1" s="6"/>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -1687,245 +1774,276 @@
       <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="27"/>
-      <c r="K1" s="28" t="s">
+      <c r="J1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="K1" s="25"/>
+      <c r="L1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="M1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="31" t="s">
+      <c r="O1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="32" t="s">
+      <c r="P1" s="29" t="s">
         <v>12</v>
       </c>
       <c r="Q1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="38" t="s">
         <v>14</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="4"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:20">
+      <c r="T1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:22">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>16</v>
+      <c r="D2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="T2" s="4"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:20">
+        <v>19</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:22">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>23</v>
+      <c r="D3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="T3" s="4"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="2:20">
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="2:21">
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="4"/>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="3">
-        <f t="shared" ref="A5:A34" si="0">B5*10+G5</f>
+        <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="14">
         <v>200100</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="C5" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="14">
+        <v>200100038</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="14">
         <v>1</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="3">
+      <c r="I5" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="3">
         <v>1</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="3">
+      <c r="K5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="3">
         <v>9700</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>300</v>
       </c>
-      <c r="N5" s="3">
-        <v>60000</v>
-      </c>
       <c r="O5" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P5" s="3">
         <v>16000</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>15000</v>
       </c>
-      <c r="Q5" s="38">
+      <c r="R5" s="40">
         <v>16008</v>
       </c>
-      <c r="R5" s="4">
+      <c r="S5" s="4">
         <v>48</v>
       </c>
-      <c r="S5" s="39">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="T5" s="41">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>2001002</v>
@@ -1934,187 +2052,205 @@
         <v>200100</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="17">
+      <c r="D6" s="17">
+        <v>200100038</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="17">
         <v>2</v>
       </c>
-      <c r="H6" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="3">
+      <c r="I6" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="3">
         <v>1</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="3">
+      <c r="K6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="3">
         <v>9700</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>300</v>
       </c>
-      <c r="N6" s="3">
-        <v>60000</v>
-      </c>
       <c r="O6" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P6" s="3">
         <v>16000</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>15000</v>
       </c>
-      <c r="Q6" s="38">
+      <c r="R6" s="40">
         <v>16008</v>
       </c>
-      <c r="R6" s="4">
+      <c r="S6" s="4">
         <v>48</v>
       </c>
-      <c r="S6" s="39">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:20">
+      <c r="T6" s="41">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>54</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:22">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>2001003</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="14">
         <v>200100</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="C7" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="14">
+        <v>200100038</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="G7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="14">
         <v>3</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="3">
+      <c r="I7" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" s="3">
         <v>1</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="3">
+      <c r="K7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="3">
         <v>9700</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>300</v>
       </c>
-      <c r="N7" s="3">
-        <v>60000</v>
-      </c>
       <c r="O7" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P7" s="3">
         <v>16000</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>15000</v>
       </c>
-      <c r="Q7" s="38">
+      <c r="R7" s="40">
         <v>16008</v>
       </c>
-      <c r="R7" s="4">
+      <c r="S7" s="4">
         <v>48</v>
       </c>
-      <c r="S7" s="39">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:20">
+      <c r="T7" s="41">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>57</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:22">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>2001011</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <v>200101</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="14">
+        <v>200101001</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="14">
+        <v>1</v>
+      </c>
+      <c r="I8" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="13">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N8" s="3">
+        <v>300</v>
+      </c>
+      <c r="O8" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P8" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R8" s="40">
+        <v>16008</v>
+      </c>
+      <c r="S8" s="4">
         <v>48</v>
       </c>
-      <c r="K8" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M8" s="3">
-        <v>300</v>
-      </c>
-      <c r="N8" s="3">
-        <v>60000</v>
-      </c>
-      <c r="O8" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>15000</v>
-      </c>
-      <c r="Q8" s="38">
-        <v>16008</v>
-      </c>
-      <c r="R8" s="4">
-        <v>48</v>
-      </c>
-      <c r="S8" s="39">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="T8" s="41">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>50</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>2001012</v>
@@ -2123,187 +2259,205 @@
         <v>200101</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="17">
+        <v>58</v>
+      </c>
+      <c r="D9" s="17">
+        <v>200101001</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="17">
         <v>2</v>
       </c>
-      <c r="H9" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="I9" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N9" s="3">
+        <v>300</v>
+      </c>
+      <c r="O9" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P9" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R9" s="40">
+        <v>16008</v>
+      </c>
+      <c r="S9" s="4">
         <v>48</v>
       </c>
-      <c r="K9" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M9" s="3">
-        <v>300</v>
-      </c>
-      <c r="N9" s="3">
-        <v>60000</v>
-      </c>
-      <c r="O9" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P9" s="3">
-        <v>15000</v>
-      </c>
-      <c r="Q9" s="38">
-        <v>16008</v>
-      </c>
-      <c r="R9" s="4">
-        <v>48</v>
-      </c>
-      <c r="S9" s="39">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+      <c r="T9" s="41">
+        <v>0</v>
+      </c>
+      <c r="U9" t="s">
+        <v>54</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>2001013</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="14">
         <v>200101</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="C10" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="14">
+        <v>200101001</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="13">
+      <c r="G10" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="14">
         <v>3</v>
       </c>
-      <c r="H10" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="s">
+      <c r="I10" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N10" s="3">
+        <v>300</v>
+      </c>
+      <c r="O10" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P10" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R10" s="40">
+        <v>16008</v>
+      </c>
+      <c r="S10" s="4">
         <v>48</v>
       </c>
-      <c r="K10" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M10" s="3">
-        <v>300</v>
-      </c>
-      <c r="N10" s="3">
-        <v>60000</v>
-      </c>
-      <c r="O10" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>15000</v>
-      </c>
-      <c r="Q10" s="38">
-        <v>16008</v>
-      </c>
-      <c r="R10" s="4">
-        <v>48</v>
-      </c>
-      <c r="S10" s="39">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="T10" s="41">
+        <v>0</v>
+      </c>
+      <c r="U10" t="s">
+        <v>57</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>2003001</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="14">
         <v>200300</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="14">
+        <v>200300001</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="14">
+        <v>1</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N11" s="3">
+        <v>300</v>
+      </c>
+      <c r="O11" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P11" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R11" s="40">
+        <v>16008</v>
+      </c>
+      <c r="S11" s="4">
         <v>50</v>
       </c>
-      <c r="D11" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="13">
-        <v>1</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="35" t="s">
+      <c r="T11" s="41">
+        <v>0</v>
+      </c>
+      <c r="U11" t="s">
+        <v>50</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M11" s="3">
-        <v>300</v>
-      </c>
-      <c r="N11" s="3">
-        <v>180000</v>
-      </c>
-      <c r="O11" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P11" s="3">
-        <v>15000</v>
-      </c>
-      <c r="Q11" s="38">
-        <v>16008</v>
-      </c>
-      <c r="R11" s="4">
-        <v>50</v>
-      </c>
-      <c r="S11" s="39">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:20">
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:22">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>2003002</v>
@@ -2312,187 +2466,205 @@
         <v>200300</v>
       </c>
       <c r="C12" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="17">
+        <v>200300001</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="17">
+        <v>2</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N12" s="3">
+        <v>300</v>
+      </c>
+      <c r="O12" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P12" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R12" s="40">
+        <v>16008</v>
+      </c>
+      <c r="S12" s="4">
         <v>50</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="17">
-        <v>2</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K12" s="35" t="s">
+      <c r="T12" s="41">
+        <v>0</v>
+      </c>
+      <c r="U12" t="s">
+        <v>54</v>
+      </c>
+      <c r="V12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L12" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M12" s="3">
-        <v>300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>180000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>15000</v>
-      </c>
-      <c r="Q12" s="38">
-        <v>16008</v>
-      </c>
-      <c r="R12" s="4">
-        <v>50</v>
-      </c>
-      <c r="S12" s="39">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>2003003</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="14">
         <v>200300</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="14">
+        <v>200300001</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="14">
+        <v>3</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N13" s="3">
+        <v>300</v>
+      </c>
+      <c r="O13" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P13" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R13" s="40">
+        <v>16008</v>
+      </c>
+      <c r="S13" s="4">
         <v>50</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="13">
-        <v>3</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" s="35" t="s">
+      <c r="T13" s="41">
+        <v>0</v>
+      </c>
+      <c r="U13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L13" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M13" s="3">
-        <v>300</v>
-      </c>
-      <c r="N13" s="3">
-        <v>180000</v>
-      </c>
-      <c r="O13" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P13" s="3">
-        <v>15000</v>
-      </c>
-      <c r="Q13" s="38">
-        <v>16008</v>
-      </c>
-      <c r="R13" s="4">
-        <v>50</v>
-      </c>
-      <c r="S13" s="39">
-        <v>0</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>2004001</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <v>200400</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="13">
+      <c r="C14" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="14">
+        <v>200400009</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="14">
         <v>1</v>
       </c>
-      <c r="H14" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K14" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="I14" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14" s="3">
         <v>9700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>180000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>16000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>15000</v>
       </c>
-      <c r="Q14" s="38">
+      <c r="R14" s="40">
         <v>16008</v>
       </c>
-      <c r="R14" s="4">
+      <c r="S14" s="4">
         <v>50</v>
       </c>
-      <c r="S14" s="39">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="T14" s="41">
+        <v>0</v>
+      </c>
+      <c r="U14" t="s">
+        <v>50</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>2004002</v>
@@ -2501,187 +2673,205 @@
         <v>200400</v>
       </c>
       <c r="C15" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="17">
+        <v>200400009</v>
+      </c>
+      <c r="E15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="17">
+      <c r="F15" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="17">
         <v>2</v>
       </c>
-      <c r="H15" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K15" s="35" t="s">
+      <c r="I15" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="3">
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="3">
         <v>9700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>180000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>15000</v>
       </c>
-      <c r="Q15" s="38">
+      <c r="R15" s="40">
         <v>16008</v>
       </c>
-      <c r="R15" s="4">
+      <c r="S15" s="4">
         <v>50</v>
       </c>
-      <c r="S15" s="39">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:20">
+      <c r="T15" s="41">
+        <v>0</v>
+      </c>
+      <c r="U15" t="s">
+        <v>54</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:22">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>2004003</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <v>200400</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="14">
+        <v>200400009</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="13">
+      <c r="G16" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="14">
         <v>3</v>
       </c>
-      <c r="H16" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K16" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" s="3">
+      <c r="I16" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="3">
         <v>9700</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>300</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>180000</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <v>16000</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <v>15000</v>
       </c>
-      <c r="Q16" s="38">
+      <c r="R16" s="40">
         <v>16008</v>
       </c>
-      <c r="R16" s="4">
+      <c r="S16" s="4">
         <v>50</v>
       </c>
-      <c r="S16" s="39">
-        <v>0</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:20">
+      <c r="T16" s="41">
+        <v>0</v>
+      </c>
+      <c r="U16" t="s">
+        <v>57</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:22">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>2005001</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="14">
         <v>200500</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="13">
+      <c r="C17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="14">
+        <v>200500025</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="14">
         <v>1</v>
       </c>
-      <c r="H17" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="3">
         <v>1</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K17" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17" s="3">
         <v>9700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>180000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15000</v>
       </c>
-      <c r="Q17" s="38">
+      <c r="R17" s="40">
         <v>16008</v>
       </c>
-      <c r="R17" s="4">
+      <c r="S17" s="4">
         <v>48</v>
       </c>
-      <c r="S17" s="39">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+      <c r="T17" s="41">
+        <v>0</v>
+      </c>
+      <c r="U17" t="s">
+        <v>50</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>2005002</v>
@@ -2690,187 +2880,205 @@
         <v>200500</v>
       </c>
       <c r="C18" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="17">
+        <v>200500025</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="17">
+        <v>2</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="M18" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N18" s="3">
+        <v>300</v>
+      </c>
+      <c r="O18" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R18" s="40">
+        <v>16008</v>
+      </c>
+      <c r="S18" s="4">
+        <v>48</v>
+      </c>
+      <c r="T18" s="41">
+        <v>0</v>
+      </c>
+      <c r="U18" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="17">
-        <v>2</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K18" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M18" s="3">
-        <v>300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>180000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>15000</v>
-      </c>
-      <c r="Q18" s="38">
-        <v>16008</v>
-      </c>
-      <c r="R18" s="4">
-        <v>48</v>
-      </c>
-      <c r="S18" s="39">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="V18" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>2005003</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="14">
         <v>200500</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="13" t="s">
+      <c r="C19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="14">
+        <v>200500025</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="13">
+      <c r="G19" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="14">
         <v>3</v>
       </c>
-      <c r="H19" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="3">
+      <c r="I19" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="3">
         <v>1</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K19" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="L19" s="3">
+      <c r="K19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="3">
         <v>9700</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>300</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="3">
         <v>180000</v>
       </c>
-      <c r="O19" s="3">
+      <c r="P19" s="3">
         <v>16000</v>
       </c>
-      <c r="P19" s="3">
+      <c r="Q19" s="3">
         <v>15000</v>
       </c>
-      <c r="Q19" s="38">
+      <c r="R19" s="40">
         <v>16008</v>
       </c>
-      <c r="R19" s="4">
+      <c r="S19" s="4">
         <v>48</v>
       </c>
-      <c r="S19" s="39">
-        <v>0</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="T19" s="41">
+        <v>0</v>
+      </c>
+      <c r="U19" t="s">
+        <v>57</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>2006001</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="14">
         <v>200600</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="13">
+      <c r="C20" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="14">
+        <v>200600001</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="14">
         <v>1</v>
       </c>
-      <c r="H20" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K20" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="I20" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20" s="3">
         <v>9700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>180000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>16000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15000</v>
       </c>
-      <c r="Q20" s="38">
+      <c r="R20" s="40">
         <v>16008</v>
       </c>
-      <c r="R20" s="4">
+      <c r="S20" s="4">
         <v>500</v>
       </c>
-      <c r="S20" s="39">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:20">
+      <c r="T20" s="41">
+        <v>0</v>
+      </c>
+      <c r="U20" t="s">
+        <v>50</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:22">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>2006002</v>
@@ -2879,187 +3087,205 @@
         <v>200600</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="17">
+        <v>67</v>
+      </c>
+      <c r="D21" s="17">
+        <v>200600001</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="17">
         <v>2</v>
       </c>
-      <c r="H21" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K21" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="I21" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" s="3">
         <v>9700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>180000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>16000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15000</v>
       </c>
-      <c r="Q21" s="38">
+      <c r="R21" s="40">
         <v>16008</v>
       </c>
-      <c r="R21" s="4">
+      <c r="S21" s="4">
         <v>500</v>
       </c>
-      <c r="S21" s="39">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+      <c r="T21" s="41">
+        <v>0</v>
+      </c>
+      <c r="U21" t="s">
+        <v>54</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>2006003</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="14">
         <v>200600</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="14">
+        <v>200600001</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="14">
+        <v>3</v>
+      </c>
+      <c r="I22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="13">
-        <v>3</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K22" s="35" t="s">
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N22" s="3">
+        <v>300</v>
+      </c>
+      <c r="O22" s="3">
+        <v>180000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="R22" s="40">
+        <v>16008</v>
+      </c>
+      <c r="S22" s="4">
+        <v>500</v>
+      </c>
+      <c r="T22" s="41">
+        <v>0</v>
+      </c>
+      <c r="U22" t="s">
         <v>57</v>
       </c>
-      <c r="L22" s="3">
-        <v>9700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>180000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>15000</v>
-      </c>
-      <c r="Q22" s="38">
-        <v>16008</v>
-      </c>
-      <c r="R22" s="4">
-        <v>500</v>
-      </c>
-      <c r="S22" s="39">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+      <c r="V22" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>2007001</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="14">
         <v>200700</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="13">
+      <c r="C23" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="14">
+        <v>200700001</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="14">
         <v>1</v>
       </c>
-      <c r="H23" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J23" s="3">
         <v>1</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K23" s="35" t="s">
+      <c r="K23" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M23" s="3">
         <v>9700</v>
       </c>
-      <c r="M23" s="3">
-        <v>300</v>
-      </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>180000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15000</v>
       </c>
-      <c r="Q23" s="38">
+      <c r="R23" s="40">
         <v>16008</v>
       </c>
-      <c r="R23" s="4">
+      <c r="S23" s="4">
         <v>30</v>
       </c>
-      <c r="S23" s="39">
+      <c r="T23" s="41">
         <v>1</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+      <c r="U23" t="s">
+        <v>50</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>2007002</v>
@@ -3068,850 +3294,917 @@
         <v>200700</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="17">
+        <v>69</v>
+      </c>
+      <c r="D24" s="17">
+        <v>200700001</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="17">
         <v>2</v>
       </c>
-      <c r="H24" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="3">
         <v>1</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K24" s="35" t="s">
+      <c r="K24" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M24" s="3">
         <v>9700</v>
       </c>
-      <c r="M24" s="3">
-        <v>300</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>180000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15000</v>
       </c>
-      <c r="Q24" s="38">
+      <c r="R24" s="40">
         <v>16008</v>
       </c>
-      <c r="R24" s="4">
+      <c r="S24" s="4">
         <v>30</v>
       </c>
-      <c r="S24" s="39">
+      <c r="T24" s="41">
         <v>1</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:20">
+      <c r="U24" t="s">
+        <v>54</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:22">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>2007003</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="14">
         <v>200700</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="13" t="s">
+      <c r="C25" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="14">
+        <v>200700001</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="13">
+      <c r="G25" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="14">
         <v>3</v>
       </c>
-      <c r="H25" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="3">
+      <c r="I25" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J25" s="3">
         <v>1</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K25" s="35" t="s">
+      <c r="K25" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M25" s="3">
         <v>9700</v>
       </c>
-      <c r="M25" s="3">
-        <v>300</v>
-      </c>
       <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
         <v>180000</v>
       </c>
-      <c r="O25" s="3">
+      <c r="P25" s="3">
         <v>16000</v>
       </c>
-      <c r="P25" s="3">
+      <c r="Q25" s="3">
         <v>15000</v>
       </c>
-      <c r="Q25" s="38">
+      <c r="R25" s="40">
         <v>16008</v>
       </c>
-      <c r="R25" s="4">
+      <c r="S25" s="4">
         <v>30</v>
       </c>
-      <c r="S25" s="39">
+      <c r="T25" s="41">
         <v>1</v>
       </c>
-      <c r="T25" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:20">
+      <c r="U25" t="s">
+        <v>57</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:22">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>2008001</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <v>200800</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="13">
+      <c r="C26" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="14">
+        <v>200800001</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" s="14">
         <v>1</v>
       </c>
-      <c r="H26" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K26" s="35" t="s">
+      <c r="I26" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" s="3">
         <v>9700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>180000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15000</v>
       </c>
-      <c r="Q26" s="38">
+      <c r="R26" s="40">
         <v>16008</v>
       </c>
-      <c r="R26" s="4">
+      <c r="S26" s="4">
         <v>500</v>
       </c>
-      <c r="S26" s="39">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:20">
+      <c r="T26" s="41">
+        <v>0</v>
+      </c>
+      <c r="U26" t="s">
+        <v>50</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="1:22">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>2008002</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <v>200800</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" s="17">
+      <c r="C27" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="14">
+        <v>200800001</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" s="17">
         <v>2</v>
       </c>
-      <c r="H27" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K27" s="35" t="s">
+      <c r="I27" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M27" s="3">
         <v>9700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>180000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15000</v>
       </c>
-      <c r="Q27" s="38">
+      <c r="R27" s="40">
         <v>16008</v>
       </c>
-      <c r="R27" s="4">
+      <c r="S27" s="4">
         <v>500</v>
       </c>
-      <c r="S27" s="39">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:20">
+      <c r="T27" s="41">
+        <v>0</v>
+      </c>
+      <c r="U27" t="s">
+        <v>54</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="1:22">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>2008003</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="14">
         <v>200800</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="13" t="s">
+      <c r="C28" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="14">
+        <v>200800001</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="13">
+      <c r="G28" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H28" s="14">
         <v>3</v>
       </c>
-      <c r="H28" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K28" s="35" t="s">
+      <c r="I28" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L28" s="3">
+      <c r="L28" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M28" s="3">
         <v>9700</v>
       </c>
-      <c r="M28" s="3">
+      <c r="N28" s="3">
         <v>300</v>
       </c>
-      <c r="N28" s="3">
+      <c r="O28" s="3">
         <v>180000</v>
       </c>
-      <c r="O28" s="3">
+      <c r="P28" s="3">
         <v>16000</v>
       </c>
-      <c r="P28" s="3">
+      <c r="Q28" s="3">
         <v>15000</v>
       </c>
-      <c r="Q28" s="38">
+      <c r="R28" s="40">
         <v>16008</v>
       </c>
-      <c r="R28" s="4">
+      <c r="S28" s="4">
         <v>500</v>
       </c>
-      <c r="S28" s="39">
-        <v>0</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:20">
+      <c r="T28" s="41">
+        <v>0</v>
+      </c>
+      <c r="U28" t="s">
+        <v>57</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="1:22">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="20">
         <v>200900</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" s="13">
+      <c r="C29" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="14">
+        <v>200900001</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="14">
         <v>1</v>
       </c>
-      <c r="H29" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I29" s="36">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K29" s="35" t="s">
+      <c r="I29" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J29" s="35">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M29" s="3">
         <v>9700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>180000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>16000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>15000</v>
       </c>
-      <c r="Q29" s="38">
+      <c r="R29" s="40">
         <v>16008</v>
       </c>
-      <c r="R29" s="4">
+      <c r="S29" s="4">
         <v>500</v>
       </c>
-      <c r="S29" s="39">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+      <c r="T29" s="41">
+        <v>0</v>
+      </c>
+      <c r="U29" t="s">
+        <v>50</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="21">
         <v>200900</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" s="17">
+        <v>71</v>
+      </c>
+      <c r="D30" s="17">
+        <v>200900001</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H30" s="17">
         <v>2</v>
       </c>
-      <c r="H30" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I30" s="36">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K30" s="35" t="s">
+      <c r="I30" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" s="35">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L30" s="3">
+      <c r="L30" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" s="3">
         <v>9700</v>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <v>300</v>
       </c>
-      <c r="N30" s="3">
+      <c r="O30" s="3">
         <v>180000</v>
       </c>
-      <c r="O30" s="3">
+      <c r="P30" s="3">
         <v>16000</v>
       </c>
-      <c r="P30" s="3">
+      <c r="Q30" s="3">
         <v>15000</v>
       </c>
-      <c r="Q30" s="38">
+      <c r="R30" s="40">
         <v>16008</v>
       </c>
-      <c r="R30" s="4">
+      <c r="S30" s="4">
         <v>500</v>
       </c>
-      <c r="S30" s="39">
-        <v>0</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+      <c r="T30" s="41">
+        <v>0</v>
+      </c>
+      <c r="U30" t="s">
+        <v>54</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="22">
         <v>200900</v>
       </c>
-      <c r="C31" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="24" t="s">
+      <c r="C31" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="23">
+        <v>200900001</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" s="13">
+      <c r="G31" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H31" s="14">
         <v>3</v>
       </c>
-      <c r="H31" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I31" s="36">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K31" s="35" t="s">
+      <c r="I31" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J31" s="35">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L31" s="3">
+      <c r="L31" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M31" s="3">
         <v>9700</v>
       </c>
-      <c r="M31" s="3">
+      <c r="N31" s="3">
         <v>300</v>
       </c>
-      <c r="N31" s="3">
+      <c r="O31" s="3">
         <v>180000</v>
       </c>
-      <c r="O31" s="3">
+      <c r="P31" s="3">
         <v>16000</v>
       </c>
-      <c r="P31" s="3">
+      <c r="Q31" s="3">
         <v>15000</v>
       </c>
-      <c r="Q31" s="38">
+      <c r="R31" s="40">
         <v>16008</v>
       </c>
-      <c r="R31" s="4">
+      <c r="S31" s="4">
         <v>500</v>
       </c>
-      <c r="S31" s="39">
-        <v>0</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+      <c r="T31" s="41">
+        <v>0</v>
+      </c>
+      <c r="U31" t="s">
+        <v>57</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>2010001</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="24">
         <v>201000</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F32" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G32" s="13">
+        <v>72</v>
+      </c>
+      <c r="D32" s="3">
+        <v>101000006</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="H32" s="14">
         <v>1</v>
       </c>
-      <c r="H32" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I32" s="36">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K32" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="I32" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J32" s="35">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L32" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="M32" s="3">
         <v>9700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>180000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>16000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15000</v>
       </c>
-      <c r="Q32" s="38">
+      <c r="R32" s="40">
         <v>16008</v>
       </c>
-      <c r="R32" s="4">
+      <c r="S32" s="4">
         <v>50</v>
       </c>
-      <c r="S32" s="39">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20">
+      <c r="T32" s="41">
+        <v>0</v>
+      </c>
+      <c r="U32" t="s">
+        <v>50</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>2010002</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="24">
         <v>201000</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33" s="17">
+        <v>72</v>
+      </c>
+      <c r="D33" s="3">
+        <v>101000006</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="H33" s="17">
         <v>2</v>
       </c>
-      <c r="H33" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I33" s="36">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K33" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="I33" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J33" s="35">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="M33" s="3">
         <v>9700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>180000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15000</v>
       </c>
-      <c r="Q33" s="38">
+      <c r="R33" s="40">
         <v>16008</v>
       </c>
-      <c r="R33" s="4">
+      <c r="S33" s="4">
         <v>50</v>
       </c>
-      <c r="S33" s="39">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+      <c r="T33" s="41">
+        <v>0</v>
+      </c>
+      <c r="U33" t="s">
+        <v>54</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>2010003</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="24">
         <v>201000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="3">
+        <v>101000006</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F34" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G34" s="13">
+      <c r="G34" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" s="14">
         <v>3</v>
       </c>
-      <c r="H34" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I34" s="36">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K34" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="L34" s="3">
+      <c r="I34" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J34" s="35">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="M34" s="3">
         <v>9700</v>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="3">
         <v>300</v>
       </c>
-      <c r="N34" s="3">
+      <c r="O34" s="3">
         <v>180000</v>
       </c>
-      <c r="O34" s="3">
+      <c r="P34" s="3">
         <v>16000</v>
       </c>
-      <c r="P34" s="3">
+      <c r="Q34" s="3">
         <v>15000</v>
       </c>
-      <c r="Q34" s="38">
+      <c r="R34" s="40">
         <v>16008</v>
       </c>
-      <c r="R34" s="4">
+      <c r="S34" s="4">
         <v>50</v>
       </c>
-      <c r="S34" s="39">
-        <v>0</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="19:20">
-      <c r="S35" s="39"/>
-      <c r="T35" s="3"/>
-    </row>
-    <row r="36" spans="3:20">
+      <c r="T34" s="41">
+        <v>0</v>
+      </c>
+      <c r="U34" t="s">
+        <v>57</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="20:21">
+      <c r="T35" s="41"/>
+      <c r="U35" s="41"/>
+    </row>
+    <row r="36" spans="3:21">
       <c r="C36"/>
-      <c r="S36" s="39"/>
-      <c r="T36" s="3"/>
-    </row>
-    <row r="37" spans="19:20">
-      <c r="S37" s="39"/>
-      <c r="T37" s="3"/>
-    </row>
-    <row r="38" spans="18:20">
-      <c r="R38" s="5"/>
-      <c r="S38" s="39"/>
-      <c r="T38" s="3"/>
-    </row>
-    <row r="39" spans="18:20">
-      <c r="R39" s="5"/>
-      <c r="S39" s="39"/>
-      <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="18:20">
-      <c r="R40" s="5"/>
-      <c r="S40" s="39"/>
-      <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="18:20">
-      <c r="R41" s="5"/>
-      <c r="S41" s="39"/>
-      <c r="T41" s="3"/>
-    </row>
-    <row r="42" spans="18:20">
-      <c r="R42" s="5"/>
-      <c r="S42" s="39"/>
-      <c r="T42" s="3"/>
-    </row>
-    <row r="43" spans="8:20">
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="26"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="39"/>
-      <c r="T43" s="3"/>
-    </row>
-    <row r="44" spans="8:20">
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="26"/>
-      <c r="O44" s="26"/>
-      <c r="P44" s="26"/>
-      <c r="Q44" s="26"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="39"/>
-      <c r="T44" s="3"/>
-    </row>
-    <row r="45" spans="8:20">
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="26"/>
-      <c r="M45" s="26"/>
-      <c r="N45" s="26"/>
-      <c r="O45" s="26"/>
-      <c r="P45" s="26"/>
-      <c r="Q45" s="26"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="39"/>
-      <c r="T45" s="3"/>
-    </row>
-    <row r="46" spans="8:20">
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="26"/>
-      <c r="L46" s="26"/>
-      <c r="M46" s="26"/>
-      <c r="N46" s="26"/>
-      <c r="O46" s="26"/>
-      <c r="P46" s="26"/>
-      <c r="Q46" s="26"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="39"/>
-      <c r="T46" s="3"/>
-    </row>
-    <row r="47" spans="8:17">
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
-      <c r="P47" s="26"/>
-      <c r="Q47" s="26"/>
-    </row>
-    <row r="48" spans="8:17">
-      <c r="H48" s="26"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26"/>
-      <c r="L48" s="26"/>
-      <c r="M48" s="26"/>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-      <c r="P48" s="26"/>
-      <c r="Q48" s="26"/>
-    </row>
-    <row r="49" spans="8:17">
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
-      <c r="M49" s="26"/>
-      <c r="N49" s="26"/>
-      <c r="O49" s="26"/>
-      <c r="P49" s="26"/>
-      <c r="Q49" s="26"/>
-    </row>
-    <row r="50" spans="8:17">
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="26"/>
-      <c r="M50" s="26"/>
-      <c r="N50" s="26"/>
-      <c r="O50" s="26"/>
-      <c r="P50" s="26"/>
-      <c r="Q50" s="26"/>
-    </row>
-    <row r="51" spans="8:17">
-      <c r="H51" s="26"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
-      <c r="N51" s="26"/>
-      <c r="O51" s="26"/>
-      <c r="P51" s="26"/>
-      <c r="Q51" s="26"/>
+      <c r="D36"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="41"/>
+    </row>
+    <row r="37" spans="20:21">
+      <c r="T37" s="41"/>
+      <c r="U37" s="41"/>
+    </row>
+    <row r="38" spans="19:21">
+      <c r="S38" s="5"/>
+      <c r="T38" s="41"/>
+      <c r="U38" s="41"/>
+    </row>
+    <row r="39" spans="19:21">
+      <c r="S39" s="5"/>
+      <c r="T39" s="41"/>
+      <c r="U39" s="41"/>
+    </row>
+    <row r="40" spans="19:21">
+      <c r="S40" s="5"/>
+      <c r="T40" s="41"/>
+      <c r="U40" s="41"/>
+    </row>
+    <row r="41" spans="19:21">
+      <c r="S41" s="5"/>
+      <c r="T41" s="41"/>
+      <c r="U41" s="41"/>
+    </row>
+    <row r="42" spans="19:21">
+      <c r="S42" s="5"/>
+      <c r="T42" s="41"/>
+      <c r="U42" s="41"/>
+    </row>
+    <row r="43" spans="9:21">
+      <c r="I43" s="36"/>
+      <c r="J43" s="36"/>
+      <c r="K43" s="36"/>
+      <c r="L43" s="36"/>
+      <c r="M43" s="36"/>
+      <c r="N43" s="36"/>
+      <c r="O43" s="36"/>
+      <c r="P43" s="36"/>
+      <c r="Q43" s="36"/>
+      <c r="R43" s="36"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="41"/>
+      <c r="U43" s="41"/>
+    </row>
+    <row r="44" spans="9:21">
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="36"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="41"/>
+      <c r="U44" s="41"/>
+    </row>
+    <row r="45" spans="9:21">
+      <c r="I45" s="36"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="36"/>
+      <c r="M45" s="36"/>
+      <c r="N45" s="36"/>
+      <c r="O45" s="36"/>
+      <c r="P45" s="36"/>
+      <c r="Q45" s="36"/>
+      <c r="R45" s="36"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="41"/>
+      <c r="U45" s="41"/>
+    </row>
+    <row r="46" spans="9:21">
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="36"/>
+      <c r="M46" s="36"/>
+      <c r="N46" s="36"/>
+      <c r="O46" s="36"/>
+      <c r="P46" s="36"/>
+      <c r="Q46" s="36"/>
+      <c r="R46" s="36"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="41"/>
+      <c r="U46" s="41"/>
+    </row>
+    <row r="47" spans="9:18">
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="36"/>
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="36"/>
+      <c r="P47" s="36"/>
+      <c r="Q47" s="36"/>
+      <c r="R47" s="36"/>
+    </row>
+    <row r="48" spans="9:18">
+      <c r="I48" s="36"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="36"/>
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="36"/>
+      <c r="P48" s="36"/>
+      <c r="Q48" s="36"/>
+      <c r="R48" s="36"/>
+    </row>
+    <row r="49" spans="9:18">
+      <c r="I49" s="36"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="36"/>
+      <c r="L49" s="36"/>
+      <c r="M49" s="36"/>
+      <c r="N49" s="36"/>
+      <c r="O49" s="36"/>
+      <c r="P49" s="36"/>
+      <c r="Q49" s="36"/>
+      <c r="R49" s="36"/>
+    </row>
+    <row r="50" spans="9:18">
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="36"/>
+      <c r="O50" s="36"/>
+      <c r="P50" s="36"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="36"/>
+    </row>
+    <row r="51" spans="9:18">
+      <c r="I51" s="36"/>
+      <c r="J51" s="36"/>
+      <c r="K51" s="36"/>
+      <c r="L51" s="36"/>
+      <c r="M51" s="36"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="36"/>
+      <c r="P51" s="36"/>
+      <c r="Q51" s="36"/>
+      <c r="R51" s="36"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q51" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:R51" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$R$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="2">
+    <comment ref="K1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1">
+    <comment ref="M1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -124,7 +124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -139,7 +139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -151,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="2">
+    <comment ref="P1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2">
+    <comment ref="Q1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -197,7 +197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="2">
+    <comment ref="R1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -221,7 +221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0">
+    <comment ref="S1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -244,7 +244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="2">
+    <comment ref="U1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -267,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0">
+    <comment ref="V1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -291,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0">
+    <comment ref="W1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="85">
   <si>
     <t>游戏ID</t>
   </si>
@@ -338,6 +338,9 @@
     <t>倍场ID</t>
   </si>
   <si>
+    <t>交易项目ID</t>
+  </si>
+  <si>
     <t>押分筹码列表</t>
   </si>
   <si>
@@ -386,12 +389,12 @@
     <t>list&lt;list&lt;int&gt;{:}&gt;{|}</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>List&lt;long&gt;{_}</t>
   </si>
   <si>
-    <t>list&lt;int&gt;{_}</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -410,6 +413,9 @@
     <t>roomID</t>
   </si>
   <si>
+    <t>transactionItemId</t>
+  </si>
+  <si>
     <t>betList</t>
   </si>
   <si>
@@ -461,7 +467,7 @@
     <t>0:6:28|6:12:36|12:18:45|18:24:43</t>
   </si>
   <si>
-    <t>100,200,500,1000,2000,5000,10000</t>
+    <t>100_200_500_1000_2000_5000_10000</t>
   </si>
   <si>
     <t>组合</t>
@@ -473,27 +479,33 @@
     <t>500000_17001</t>
   </si>
   <si>
-    <t>1030002_1000</t>
+    <t>1990000_100000</t>
   </si>
   <si>
     <t>中级场</t>
   </si>
   <si>
-    <t>10000,20000,50000,100000,200000,500000,1000000</t>
+    <t>10000_20000_50000_100000_200000_500000_1000000</t>
   </si>
   <si>
     <t>50000000_17001</t>
   </si>
   <si>
+    <t>1990000_10000000</t>
+  </si>
+  <si>
     <t>高级场</t>
   </si>
   <si>
-    <t>1000000,2000000,5000000,10000000,20000000,50000000,100000000</t>
+    <t>1000000_2000000_5000000_10000000_20000000_50000000_100000000</t>
   </si>
   <si>
     <t>5000000000_17001</t>
   </si>
   <si>
+    <t>1990000_100000000</t>
+  </si>
+  <si>
     <t>龙虎斗</t>
   </si>
   <si>
@@ -543,6 +555,24 @@
   </si>
   <si>
     <t>0,15000,10000,4000</t>
+  </si>
+  <si>
+    <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
+  </si>
+  <si>
+    <t>1_2_5_10_20_50_100</t>
+  </si>
+  <si>
+    <t>5000_17001</t>
+  </si>
+  <si>
+    <t>1980000_1000</t>
+  </si>
+  <si>
+    <t>1980000_100000</t>
+  </si>
+  <si>
+    <t>1980000_10000000</t>
   </si>
 </sst>
 </file>
@@ -759,7 +789,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -799,6 +829,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1119,7 +1161,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1143,16 +1185,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1161,85 +1203,85 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
@@ -1262,7 +1304,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1351,6 +1393,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1363,14 +1408,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1386,9 +1432,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1402,6 +1455,10 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
@@ -1410,6 +1467,9 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="60">
@@ -1743,7 +1803,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3"/>
@@ -1753,20 +1813,22 @@
     <col min="6" max="6" width="15.1416666666667" style="3" customWidth="1"/>
     <col min="7" max="7" width="28.2333333333333" style="3" customWidth="1"/>
     <col min="8" max="8" width="8.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="65" style="3" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="5.125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="24.75" style="3" customWidth="1"/>
-    <col min="13" max="18" width="9.81666666666667" style="3" customWidth="1"/>
-    <col min="19" max="19" width="17.2166666666667" style="4" customWidth="1"/>
-    <col min="20" max="21" width="19.5" style="5" customWidth="1"/>
-    <col min="22" max="22" width="19.125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="9.25" style="2"/>
-    <col min="24" max="24" width="20.125" style="2" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="21.025" style="3" customWidth="1"/>
+    <col min="10" max="10" width="65" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="24.75" style="3" customWidth="1"/>
+    <col min="14" max="15" width="16.3166666666667" style="3" customWidth="1"/>
+    <col min="16" max="19" width="9.81666666666667" style="3" customWidth="1"/>
+    <col min="20" max="20" width="17.2166666666667" style="4" customWidth="1"/>
+    <col min="21" max="22" width="19.5" style="5" customWidth="1"/>
+    <col min="23" max="23" width="19.125" style="2" customWidth="1"/>
+    <col min="24" max="24" width="9.25" style="2"/>
+    <col min="25" max="25" width="20.125" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:22">
+    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:23">
       <c r="A1" s="6"/>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -1787,20 +1849,20 @@
       <c r="H1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="26" t="s">
+      <c r="K1" s="26" t="s">
         <v>8</v>
       </c>
+      <c r="L1" s="26"/>
       <c r="M1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="28" t="s">
         <v>10</v>
       </c>
       <c r="O1" s="28" t="s">
@@ -1809,150 +1871,159 @@
       <c r="P1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="38" t="s">
+      <c r="R1" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="41" t="s">
         <v>15</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>18</v>
       </c>
+      <c r="W1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:22">
+    <row r="2" s="1" customFormat="1" spans="1:23">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="V2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V2" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:22">
+    <row r="3" s="1" customFormat="1" spans="1:23">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="K3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="S3" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="S3" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="U3" t="s">
         <v>41</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="U3" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="2:21">
+    <row r="4" s="1" customFormat="1" spans="2:22">
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -1960,21 +2031,22 @@
       <c r="F4" s="13"/>
       <c r="G4" s="4"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
-      <c r="L4" s="30"/>
+      <c r="L4" s="12"/>
       <c r="M4" s="30"/>
       <c r="N4" s="30"/>
-      <c r="O4" s="31"/>
+      <c r="O4" s="30"/>
       <c r="P4" s="31"/>
       <c r="Q4" s="31"/>
       <c r="R4" s="31"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="5"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="4"/>
       <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:23">
       <c r="A5" s="3">
         <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
@@ -1983,67 +2055,70 @@
         <v>200100</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" s="14">
         <v>200100038</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" s="14">
         <v>1</v>
       </c>
-      <c r="I5" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="I5" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="3">
         <v>1</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" s="3">
+      <c r="L5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" s="3">
         <v>9700</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>300</v>
       </c>
-      <c r="O5" s="3">
+      <c r="P5" s="3">
         <v>180000</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>16000</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <v>15000</v>
       </c>
-      <c r="R5" s="40">
+      <c r="S5" s="43">
         <v>16008</v>
       </c>
-      <c r="S5" s="4">
-        <v>48</v>
-      </c>
-      <c r="T5" s="41">
-        <v>0</v>
-      </c>
-      <c r="U5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>51</v>
+      <c r="T5" s="4">
+        <v>48</v>
+      </c>
+      <c r="U5" s="44">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>52</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:23">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>2001002</v>
@@ -2052,67 +2127,70 @@
         <v>200100</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>200100038</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H6" s="17">
         <v>2</v>
       </c>
-      <c r="I6" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="I6" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="3">
         <v>1</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L6" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="M6" s="3">
+      <c r="L6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" s="3">
         <v>9700</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>300</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <v>180000</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>16000</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="3">
         <v>15000</v>
       </c>
-      <c r="R6" s="40">
+      <c r="S6" s="43">
         <v>16008</v>
       </c>
-      <c r="S6" s="4">
-        <v>48</v>
-      </c>
-      <c r="T6" s="41">
-        <v>0</v>
-      </c>
-      <c r="U6" t="s">
-        <v>54</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>51</v>
+      <c r="T6" s="4">
+        <v>48</v>
+      </c>
+      <c r="U6" s="44">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:22">
+    <row r="7" s="2" customFormat="1" spans="1:23">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -2121,67 +2199,70 @@
         <v>200100</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" s="14">
         <v>200100038</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H7" s="14">
         <v>3</v>
       </c>
-      <c r="I7" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="I7" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="3">
         <v>1</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L7" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7" s="3">
+      <c r="L7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="3">
         <v>9700</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>300</v>
       </c>
-      <c r="O7" s="3">
+      <c r="P7" s="3">
         <v>180000</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>16000</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <v>15000</v>
       </c>
-      <c r="R7" s="40">
+      <c r="S7" s="43">
         <v>16008</v>
       </c>
-      <c r="S7" s="4">
-        <v>48</v>
-      </c>
-      <c r="T7" s="41">
-        <v>0</v>
-      </c>
-      <c r="U7" t="s">
-        <v>57</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>51</v>
+      <c r="T7" s="4">
+        <v>48</v>
+      </c>
+      <c r="U7" s="44">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
+        <v>60</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:22">
+    <row r="8" s="2" customFormat="1" spans="1:23">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -2190,67 +2271,70 @@
         <v>200101</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D8" s="14">
         <v>200101001</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H8" s="14">
         <v>1</v>
       </c>
-      <c r="I8" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="I8" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" s="3">
         <v>9700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>180000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15000</v>
       </c>
-      <c r="R8" s="40">
+      <c r="S8" s="43">
         <v>16008</v>
       </c>
-      <c r="S8" s="4">
-        <v>48</v>
-      </c>
-      <c r="T8" s="41">
-        <v>0</v>
-      </c>
-      <c r="U8" t="s">
-        <v>50</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>51</v>
+      <c r="T8" s="4">
+        <v>48</v>
+      </c>
+      <c r="U8" s="44">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
+        <v>52</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:23">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>2001012</v>
@@ -2259,67 +2343,70 @@
         <v>200101</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D9" s="17">
         <v>200101001</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H9" s="17">
         <v>2</v>
       </c>
-      <c r="I9" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="I9" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J9" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" s="3">
         <v>9700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>180000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15000</v>
       </c>
-      <c r="R9" s="40">
+      <c r="S9" s="43">
         <v>16008</v>
       </c>
-      <c r="S9" s="4">
-        <v>48</v>
-      </c>
-      <c r="T9" s="41">
-        <v>0</v>
-      </c>
-      <c r="U9" t="s">
-        <v>54</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>51</v>
+      <c r="T9" s="4">
+        <v>48</v>
+      </c>
+      <c r="U9" s="44">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
+        <v>56</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>2001013</v>
@@ -2328,67 +2415,70 @@
         <v>200101</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D10" s="14">
         <v>200101001</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="42" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H10" s="14">
         <v>3</v>
       </c>
-      <c r="I10" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="I10" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J10" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33" t="s">
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O10" s="3">
+        <v>300</v>
+      </c>
+      <c r="P10" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R10" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S10" s="43">
+        <v>16008</v>
+      </c>
+      <c r="T10" s="4">
+        <v>48</v>
+      </c>
+      <c r="U10" s="44">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>60</v>
       </c>
-      <c r="M10" s="3">
-        <v>9700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>300</v>
-      </c>
-      <c r="O10" s="3">
-        <v>180000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>16000</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>15000</v>
-      </c>
-      <c r="R10" s="40">
-        <v>16008</v>
-      </c>
-      <c r="S10" s="4">
-        <v>48</v>
-      </c>
-      <c r="T10" s="41">
-        <v>0</v>
-      </c>
-      <c r="U10" t="s">
-        <v>57</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>51</v>
+      <c r="W10" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>2003001</v>
@@ -2397,67 +2487,70 @@
         <v>200300</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D11" s="14">
         <v>200300001</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H11" s="14">
         <v>1</v>
       </c>
-      <c r="I11" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" s="3">
+      <c r="I11" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="3">
         <v>9700</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="3">
         <v>300</v>
       </c>
-      <c r="O11" s="3">
+      <c r="P11" s="3">
         <v>180000</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>16000</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="3">
         <v>15000</v>
       </c>
-      <c r="R11" s="40">
+      <c r="S11" s="43">
         <v>16008</v>
       </c>
-      <c r="S11" s="4">
+      <c r="T11" s="4">
         <v>50</v>
       </c>
-      <c r="T11" s="41">
-        <v>0</v>
-      </c>
-      <c r="U11" t="s">
-        <v>50</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>51</v>
+      <c r="U11" s="44">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
+        <v>52</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:22">
+    <row r="12" s="2" customFormat="1" spans="1:23">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>2003002</v>
@@ -2466,67 +2559,70 @@
         <v>200300</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D12" s="17">
         <v>200300001</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="42" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H12" s="17">
         <v>2</v>
       </c>
-      <c r="I12" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="M12" s="3">
+      <c r="I12" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J12" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="3">
         <v>9700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>180000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15000</v>
       </c>
-      <c r="R12" s="40">
+      <c r="S12" s="43">
         <v>16008</v>
       </c>
-      <c r="S12" s="4">
+      <c r="T12" s="4">
         <v>50</v>
       </c>
-      <c r="T12" s="41">
-        <v>0</v>
-      </c>
-      <c r="U12" t="s">
-        <v>54</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>51</v>
+      <c r="U12" s="44">
+        <v>0</v>
+      </c>
+      <c r="V12" t="s">
+        <v>56</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:23">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>2003003</v>
@@ -2535,67 +2631,70 @@
         <v>200300</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D13" s="14">
         <v>200300001</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="42" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H13" s="14">
         <v>3</v>
       </c>
-      <c r="I13" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="s">
+      <c r="I13" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J13" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="M13" s="3">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="3">
         <v>9700</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>300</v>
       </c>
-      <c r="O13" s="3">
+      <c r="P13" s="3">
         <v>180000</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3">
         <v>16000</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="R13" s="3">
         <v>15000</v>
       </c>
-      <c r="R13" s="40">
+      <c r="S13" s="43">
         <v>16008</v>
       </c>
-      <c r="S13" s="4">
+      <c r="T13" s="4">
         <v>50</v>
       </c>
-      <c r="T13" s="41">
-        <v>0</v>
-      </c>
-      <c r="U13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>51</v>
+      <c r="U13" s="44">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
+        <v>60</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:23">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>2004001</v>
@@ -2604,67 +2703,70 @@
         <v>200400</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D14" s="14">
         <v>200400009</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H14" s="14">
         <v>1</v>
       </c>
-      <c r="I14" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L14" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="I14" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="3">
         <v>9700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>180000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>15000</v>
       </c>
-      <c r="R14" s="40">
+      <c r="S14" s="43">
         <v>16008</v>
       </c>
-      <c r="S14" s="4">
+      <c r="T14" s="4">
         <v>50</v>
       </c>
-      <c r="T14" s="41">
-        <v>0</v>
-      </c>
-      <c r="U14" t="s">
-        <v>50</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>51</v>
+      <c r="U14" s="44">
+        <v>0</v>
+      </c>
+      <c r="V14" t="s">
+        <v>52</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:23">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>2004002</v>
@@ -2673,67 +2775,70 @@
         <v>200400</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D15" s="17">
         <v>200400009</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="42" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H15" s="17">
         <v>2</v>
       </c>
-      <c r="I15" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="I15" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J15" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="N15" s="3">
         <v>9700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>180000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>15000</v>
       </c>
-      <c r="R15" s="40">
+      <c r="S15" s="43">
         <v>16008</v>
       </c>
-      <c r="S15" s="4">
+      <c r="T15" s="4">
         <v>50</v>
       </c>
-      <c r="T15" s="41">
-        <v>0</v>
-      </c>
-      <c r="U15" t="s">
-        <v>54</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>51</v>
+      <c r="U15" s="44">
+        <v>0</v>
+      </c>
+      <c r="V15" t="s">
+        <v>56</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:22">
+    <row r="16" s="2" customFormat="1" spans="1:23">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -2742,67 +2847,70 @@
         <v>200400</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D16" s="14">
         <v>200400009</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="42" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H16" s="14">
         <v>3</v>
       </c>
-      <c r="I16" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="3">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3" t="s">
+      <c r="I16" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J16" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="L16" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="M16" s="3">
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="N16" s="3">
         <v>9700</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>300</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <v>180000</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <v>16000</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="R16" s="3">
         <v>15000</v>
       </c>
-      <c r="R16" s="40">
+      <c r="S16" s="43">
         <v>16008</v>
       </c>
-      <c r="S16" s="4">
+      <c r="T16" s="4">
         <v>50</v>
       </c>
-      <c r="T16" s="41">
-        <v>0</v>
-      </c>
-      <c r="U16" t="s">
-        <v>57</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>51</v>
+      <c r="U16" s="44">
+        <v>0</v>
+      </c>
+      <c r="V16" t="s">
+        <v>60</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:22">
+    <row r="17" s="2" customFormat="1" spans="1:23">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -2811,67 +2919,70 @@
         <v>200500</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D17" s="14">
         <v>200500025</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H17" s="14">
         <v>1</v>
       </c>
-      <c r="I17" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="I17" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="3">
         <v>1</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L17" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="N17" s="3">
         <v>9700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>180000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15000</v>
       </c>
-      <c r="R17" s="40">
+      <c r="S17" s="43">
         <v>16008</v>
       </c>
-      <c r="S17" s="4">
-        <v>48</v>
-      </c>
-      <c r="T17" s="41">
-        <v>0</v>
-      </c>
-      <c r="U17" t="s">
-        <v>50</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>51</v>
+      <c r="T17" s="4">
+        <v>48</v>
+      </c>
+      <c r="U17" s="44">
+        <v>0</v>
+      </c>
+      <c r="V17" t="s">
+        <v>52</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:23">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>2005002</v>
@@ -2880,67 +2991,70 @@
         <v>200500</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D18" s="17">
         <v>200500025</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="42" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H18" s="17">
         <v>2</v>
       </c>
-      <c r="I18" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="I18" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K18" s="3">
         <v>1</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L18" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="3">
         <v>9700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>180000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15000</v>
       </c>
-      <c r="R18" s="40">
+      <c r="S18" s="43">
         <v>16008</v>
       </c>
-      <c r="S18" s="4">
-        <v>48</v>
-      </c>
-      <c r="T18" s="41">
-        <v>0</v>
-      </c>
-      <c r="U18" t="s">
-        <v>54</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>51</v>
+      <c r="T18" s="4">
+        <v>48</v>
+      </c>
+      <c r="U18" s="44">
+        <v>0</v>
+      </c>
+      <c r="V18" t="s">
+        <v>56</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:23">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>2005003</v>
@@ -2949,67 +3063,70 @@
         <v>200500</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D19" s="14">
         <v>200500025</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="42" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H19" s="14">
         <v>3</v>
       </c>
-      <c r="I19" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J19" s="3">
+      <c r="I19" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J19" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="K19" s="3">
         <v>1</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L19" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="M19" s="3">
+      <c r="L19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="N19" s="3">
         <v>9700</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="3">
         <v>300</v>
       </c>
-      <c r="O19" s="3">
+      <c r="P19" s="3">
         <v>180000</v>
       </c>
-      <c r="P19" s="3">
+      <c r="Q19" s="3">
         <v>16000</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="R19" s="3">
         <v>15000</v>
       </c>
-      <c r="R19" s="40">
+      <c r="S19" s="43">
         <v>16008</v>
       </c>
-      <c r="S19" s="4">
-        <v>48</v>
-      </c>
-      <c r="T19" s="41">
-        <v>0</v>
-      </c>
-      <c r="U19" t="s">
-        <v>57</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>51</v>
+      <c r="T19" s="4">
+        <v>48</v>
+      </c>
+      <c r="U19" s="44">
+        <v>0</v>
+      </c>
+      <c r="V19" t="s">
+        <v>60</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:23">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>2006001</v>
@@ -3018,67 +3135,70 @@
         <v>200600</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D20" s="14">
         <v>200600001</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H20" s="14">
         <v>1</v>
       </c>
-      <c r="I20" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L20" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="I20" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J20" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N20" s="3">
         <v>9700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>180000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>16000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>15000</v>
       </c>
-      <c r="R20" s="40">
+      <c r="S20" s="43">
         <v>16008</v>
       </c>
-      <c r="S20" s="4">
-        <v>500</v>
-      </c>
-      <c r="T20" s="41">
-        <v>0</v>
-      </c>
-      <c r="U20" t="s">
-        <v>50</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>51</v>
+      <c r="T20" s="4">
+        <v>3</v>
+      </c>
+      <c r="U20" s="44">
+        <v>0</v>
+      </c>
+      <c r="V20" t="s">
+        <v>52</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:22">
+    <row r="21" s="2" customFormat="1" spans="1:23">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>2006002</v>
@@ -3087,67 +3207,70 @@
         <v>200600</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D21" s="17">
         <v>200600001</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="42" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H21" s="17">
         <v>2</v>
       </c>
-      <c r="I21" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L21" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="I21" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J21" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N21" s="3">
         <v>9700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>180000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>16000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15000</v>
       </c>
-      <c r="R21" s="40">
+      <c r="S21" s="43">
         <v>16008</v>
       </c>
-      <c r="S21" s="4">
-        <v>500</v>
-      </c>
-      <c r="T21" s="41">
-        <v>0</v>
-      </c>
-      <c r="U21" t="s">
-        <v>54</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>51</v>
+      <c r="T21" s="4">
+        <v>3</v>
+      </c>
+      <c r="U21" s="44">
+        <v>0</v>
+      </c>
+      <c r="V21" t="s">
+        <v>56</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:23">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>2006003</v>
@@ -3156,67 +3279,70 @@
         <v>200600</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D22" s="14">
         <v>200600001</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F22" s="42" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F22" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H22" s="14">
         <v>3</v>
       </c>
-      <c r="I22" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
+      <c r="I22" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J22" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="L22" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N22" s="3">
         <v>9700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>180000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15000</v>
       </c>
-      <c r="R22" s="40">
+      <c r="S22" s="43">
         <v>16008</v>
       </c>
-      <c r="S22" s="4">
-        <v>500</v>
-      </c>
-      <c r="T22" s="41">
-        <v>0</v>
-      </c>
-      <c r="U22" t="s">
-        <v>57</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>51</v>
+      <c r="T22" s="4">
+        <v>3</v>
+      </c>
+      <c r="U22" s="44">
+        <v>0</v>
+      </c>
+      <c r="V22" t="s">
+        <v>60</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:23">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>2007001</v>
@@ -3225,67 +3351,70 @@
         <v>200700</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D23" s="14">
         <v>200700001</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H23" s="14">
         <v>1</v>
       </c>
-      <c r="I23" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="I23" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J23" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="3">
         <v>1</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L23" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M23" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N23" s="3">
         <v>9700</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>180000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>16000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>15000</v>
       </c>
-      <c r="R23" s="40">
+      <c r="S23" s="43">
         <v>16008</v>
       </c>
-      <c r="S23" s="4">
+      <c r="T23" s="4">
         <v>30</v>
       </c>
-      <c r="T23" s="41">
+      <c r="U23" s="44">
         <v>1</v>
       </c>
-      <c r="U23" t="s">
-        <v>50</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>51</v>
+      <c r="V23" t="s">
+        <v>52</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:23">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>2007002</v>
@@ -3294,67 +3423,70 @@
         <v>200700</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D24" s="17">
         <v>200700001</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="42" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H24" s="17">
         <v>2</v>
       </c>
-      <c r="I24" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="I24" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J24" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K24" s="3">
         <v>1</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L24" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M24" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N24" s="3">
         <v>9700</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>180000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>16000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15000</v>
       </c>
-      <c r="R24" s="40">
+      <c r="S24" s="43">
         <v>16008</v>
       </c>
-      <c r="S24" s="4">
+      <c r="T24" s="4">
         <v>30</v>
       </c>
-      <c r="T24" s="41">
+      <c r="U24" s="44">
         <v>1</v>
       </c>
-      <c r="U24" t="s">
-        <v>54</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>51</v>
+      <c r="V24" t="s">
+        <v>56</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:22">
+    <row r="25" s="2" customFormat="1" spans="1:23">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -3363,67 +3495,70 @@
         <v>200700</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D25" s="14">
         <v>200700001</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" s="42" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H25" s="14">
         <v>3</v>
       </c>
-      <c r="I25" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J25" s="3">
+      <c r="I25" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J25" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="K25" s="3">
         <v>1</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L25" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M25" s="3">
+      <c r="L25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M25" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N25" s="3">
         <v>9700</v>
       </c>
-      <c r="N25" s="3">
-        <v>0</v>
-      </c>
       <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
         <v>180000</v>
       </c>
-      <c r="P25" s="3">
+      <c r="Q25" s="3">
         <v>16000</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="R25" s="3">
         <v>15000</v>
       </c>
-      <c r="R25" s="40">
+      <c r="S25" s="43">
         <v>16008</v>
       </c>
-      <c r="S25" s="4">
+      <c r="T25" s="4">
         <v>30</v>
       </c>
-      <c r="T25" s="41">
+      <c r="U25" s="44">
         <v>1</v>
       </c>
-      <c r="U25" t="s">
-        <v>57</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>51</v>
+      <c r="V25" t="s">
+        <v>60</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:22">
+    <row r="26" s="2" customFormat="1" spans="1:23">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -3432,67 +3567,70 @@
         <v>200800</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D26" s="14">
         <v>200800001</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H26" s="14">
         <v>1</v>
       </c>
-      <c r="I26" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L26" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="I26" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J26" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N26" s="3">
         <v>9700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>180000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15000</v>
       </c>
-      <c r="R26" s="40">
+      <c r="S26" s="43">
         <v>16008</v>
       </c>
-      <c r="S26" s="4">
-        <v>500</v>
-      </c>
-      <c r="T26" s="41">
-        <v>0</v>
-      </c>
-      <c r="U26" t="s">
-        <v>50</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>51</v>
+      <c r="T26" s="4">
+        <v>3</v>
+      </c>
+      <c r="U26" s="44">
+        <v>0</v>
+      </c>
+      <c r="V26" t="s">
+        <v>52</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:22">
+    <row r="27" s="2" customFormat="1" spans="1:23">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -3501,67 +3639,70 @@
         <v>200800</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D27" s="14">
         <v>200800001</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H27" s="17">
         <v>2</v>
       </c>
-      <c r="I27" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L27" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="I27" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J27" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M27" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N27" s="3">
         <v>9700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>180000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15000</v>
       </c>
-      <c r="R27" s="40">
+      <c r="S27" s="43">
         <v>16008</v>
       </c>
-      <c r="S27" s="4">
-        <v>500</v>
-      </c>
-      <c r="T27" s="41">
-        <v>0</v>
-      </c>
-      <c r="U27" t="s">
-        <v>54</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>51</v>
+      <c r="T27" s="4">
+        <v>3</v>
+      </c>
+      <c r="U27" s="44">
+        <v>0</v>
+      </c>
+      <c r="V27" t="s">
+        <v>56</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:22">
+    <row r="28" s="2" customFormat="1" spans="1:23">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -3570,67 +3711,70 @@
         <v>200800</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D28" s="14">
         <v>200800001</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="42" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F28" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H28" s="14">
         <v>3</v>
       </c>
-      <c r="I28" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3" t="s">
+      <c r="I28" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J28" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="L28" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M28" s="3">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M28" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N28" s="3">
         <v>9700</v>
       </c>
-      <c r="N28" s="3">
+      <c r="O28" s="3">
         <v>300</v>
       </c>
-      <c r="O28" s="3">
+      <c r="P28" s="3">
         <v>180000</v>
       </c>
-      <c r="P28" s="3">
+      <c r="Q28" s="3">
         <v>16000</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="R28" s="3">
         <v>15000</v>
       </c>
-      <c r="R28" s="40">
+      <c r="S28" s="43">
         <v>16008</v>
       </c>
-      <c r="S28" s="4">
-        <v>500</v>
-      </c>
-      <c r="T28" s="41">
-        <v>0</v>
-      </c>
-      <c r="U28" t="s">
-        <v>57</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>51</v>
+      <c r="T28" s="4">
+        <v>3</v>
+      </c>
+      <c r="U28" s="44">
+        <v>0</v>
+      </c>
+      <c r="V28" t="s">
+        <v>60</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:22">
+    <row r="29" s="2" customFormat="1" spans="1:23">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>2009001</v>
@@ -3639,67 +3783,70 @@
         <v>200900</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D29" s="14">
         <v>200900001</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="42" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F29" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H29" s="14">
         <v>1</v>
       </c>
-      <c r="I29" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J29" s="35">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L29" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="I29" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K29" s="36">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N29" s="3">
         <v>9700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>180000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>16000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>15000</v>
       </c>
-      <c r="R29" s="40">
+      <c r="S29" s="43">
         <v>16008</v>
       </c>
-      <c r="S29" s="4">
-        <v>500</v>
-      </c>
-      <c r="T29" s="41">
-        <v>0</v>
-      </c>
-      <c r="U29" t="s">
-        <v>50</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>51</v>
+      <c r="T29" s="4">
+        <v>3</v>
+      </c>
+      <c r="U29" s="44">
+        <v>0</v>
+      </c>
+      <c r="V29" t="s">
+        <v>52</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:23">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>2009002</v>
@@ -3708,67 +3855,70 @@
         <v>200900</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D30" s="17">
         <v>200900001</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F30" s="42" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H30" s="17">
         <v>2</v>
       </c>
-      <c r="I30" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J30" s="35">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L30" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M30" s="3">
+      <c r="I30" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J30" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K30" s="36">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M30" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N30" s="3">
         <v>9700</v>
       </c>
-      <c r="N30" s="3">
+      <c r="O30" s="3">
         <v>300</v>
       </c>
-      <c r="O30" s="3">
+      <c r="P30" s="3">
         <v>180000</v>
       </c>
-      <c r="P30" s="3">
+      <c r="Q30" s="3">
         <v>16000</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="R30" s="3">
         <v>15000</v>
       </c>
-      <c r="R30" s="40">
+      <c r="S30" s="43">
         <v>16008</v>
       </c>
-      <c r="S30" s="4">
-        <v>500</v>
-      </c>
-      <c r="T30" s="41">
-        <v>0</v>
-      </c>
-      <c r="U30" t="s">
-        <v>54</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>51</v>
+      <c r="T30" s="4">
+        <v>3</v>
+      </c>
+      <c r="U30" s="44">
+        <v>0</v>
+      </c>
+      <c r="V30" t="s">
+        <v>56</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:23">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>2009003</v>
@@ -3777,67 +3927,70 @@
         <v>200900</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D31" s="23">
         <v>200900001</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="42" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F31" s="47" t="s">
+        <v>47</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H31" s="14">
         <v>3</v>
       </c>
-      <c r="I31" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="J31" s="35">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3" t="s">
+      <c r="I31" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J31" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="L31" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="M31" s="3">
+      <c r="K31" s="36">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M31" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N31" s="3">
         <v>9700</v>
       </c>
-      <c r="N31" s="3">
+      <c r="O31" s="3">
         <v>300</v>
       </c>
-      <c r="O31" s="3">
+      <c r="P31" s="3">
         <v>180000</v>
       </c>
-      <c r="P31" s="3">
+      <c r="Q31" s="3">
         <v>16000</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="R31" s="3">
         <v>15000</v>
       </c>
-      <c r="R31" s="40">
+      <c r="S31" s="43">
         <v>16008</v>
       </c>
-      <c r="S31" s="4">
-        <v>500</v>
-      </c>
-      <c r="T31" s="41">
-        <v>0</v>
-      </c>
-      <c r="U31" t="s">
-        <v>57</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>51</v>
+      <c r="T31" s="4">
+        <v>3</v>
+      </c>
+      <c r="U31" s="44">
+        <v>0</v>
+      </c>
+      <c r="V31" t="s">
+        <v>60</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:23">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>2010001</v>
@@ -3846,67 +3999,70 @@
         <v>201000</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D32" s="3">
         <v>101000006</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="G32" s="43" t="s">
-        <v>73</v>
+        <v>46</v>
+      </c>
+      <c r="F32" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="G32" s="48" t="s">
+        <v>77</v>
       </c>
       <c r="H32" s="14">
         <v>1</v>
       </c>
-      <c r="I32" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J32" s="35">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L32" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="I32" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J32" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K32" s="36">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="N32" s="3">
         <v>9700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>180000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>16000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="R32" s="40">
+      <c r="S32" s="43">
         <v>16008</v>
       </c>
-      <c r="S32" s="4">
+      <c r="T32" s="4">
         <v>50</v>
       </c>
-      <c r="T32" s="41">
-        <v>0</v>
-      </c>
-      <c r="U32" t="s">
-        <v>50</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>51</v>
+      <c r="U32" s="44">
+        <v>0</v>
+      </c>
+      <c r="V32" t="s">
+        <v>52</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:23">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>2010002</v>
@@ -3915,67 +4071,70 @@
         <v>201000</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D33" s="3">
         <v>101000006</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F33" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="43" t="s">
-        <v>73</v>
+        <v>54</v>
+      </c>
+      <c r="F33" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="48" t="s">
+        <v>77</v>
       </c>
       <c r="H33" s="17">
         <v>2</v>
       </c>
-      <c r="I33" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J33" s="35">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L33" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="I33" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J33" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K33" s="36">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M33" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="N33" s="3">
         <v>9700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>180000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15000</v>
       </c>
-      <c r="R33" s="40">
+      <c r="S33" s="43">
         <v>16008</v>
       </c>
-      <c r="S33" s="4">
+      <c r="T33" s="4">
         <v>50</v>
       </c>
-      <c r="T33" s="41">
-        <v>0</v>
-      </c>
-      <c r="U33" t="s">
-        <v>54</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>51</v>
+      <c r="U33" s="44">
+        <v>0</v>
+      </c>
+      <c r="V33" t="s">
+        <v>56</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:23">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>2010003</v>
@@ -3984,227 +4143,1988 @@
         <v>201000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D34" s="3">
         <v>101000006</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="G34" s="43" t="s">
-        <v>73</v>
+        <v>58</v>
+      </c>
+      <c r="F34" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" s="48" t="s">
+        <v>77</v>
       </c>
       <c r="H34" s="14">
         <v>3</v>
       </c>
-      <c r="I34" s="32" t="s">
+      <c r="I34" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J34" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="K34" s="36">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M34" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="N34" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O34" s="3">
+        <v>300</v>
+      </c>
+      <c r="P34" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R34" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S34" s="43">
+        <v>16008</v>
+      </c>
+      <c r="T34" s="4">
+        <v>50</v>
+      </c>
+      <c r="U34" s="44">
+        <v>0</v>
+      </c>
+      <c r="V34" t="s">
+        <v>60</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="A35" s="4">
+        <v>20010010</v>
+      </c>
+      <c r="B35" s="25">
+        <v>200100</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="14">
+        <v>200100038</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H35" s="14">
+        <v>1</v>
+      </c>
+      <c r="I35" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J35" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="K35" s="3">
+        <v>1</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O35" s="3">
+        <v>300</v>
+      </c>
+      <c r="P35" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R35" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S35" s="43">
+        <v>16008</v>
+      </c>
+      <c r="T35" s="4">
+        <v>48</v>
+      </c>
+      <c r="U35" s="44">
+        <v>0</v>
+      </c>
+      <c r="V35" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="W35" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23">
+      <c r="A36" s="4">
+        <v>20010011</v>
+      </c>
+      <c r="B36" s="25">
+        <v>200100</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="17">
+        <v>200100038</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" s="17">
+        <v>2</v>
+      </c>
+      <c r="I36" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J36" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" s="3">
+        <v>1</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O36" s="3">
+        <v>300</v>
+      </c>
+      <c r="P36" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R36" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S36" s="43">
+        <v>16008</v>
+      </c>
+      <c r="T36" s="4">
+        <v>48</v>
+      </c>
+      <c r="U36" s="44">
+        <v>0</v>
+      </c>
+      <c r="V36" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="W36" s="46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37" s="4">
+        <v>20010012</v>
+      </c>
+      <c r="B37" s="25">
+        <v>200100</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="14">
+        <v>200100038</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H37" s="14">
+        <v>3</v>
+      </c>
+      <c r="I37" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J37" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K37" s="3">
+        <v>1</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O37" s="3">
+        <v>300</v>
+      </c>
+      <c r="P37" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R37" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S37" s="43">
+        <v>16008</v>
+      </c>
+      <c r="T37" s="4">
+        <v>48</v>
+      </c>
+      <c r="U37" s="44">
+        <v>0</v>
+      </c>
+      <c r="V37" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="J34" s="35">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L34" s="33" t="s">
+      <c r="W37" s="46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23">
+      <c r="A38" s="4">
+        <v>20010110</v>
+      </c>
+      <c r="B38" s="25">
+        <v>200101</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="3">
+        <v>200101001</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J38" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N38" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O38" s="3">
+        <v>300</v>
+      </c>
+      <c r="P38" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R38" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S38" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T38" s="5">
+        <v>48</v>
+      </c>
+      <c r="U38" s="44">
+        <v>0</v>
+      </c>
+      <c r="V38" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="W38" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="4">
+        <v>20010111</v>
+      </c>
+      <c r="B39" s="25">
+        <v>200101</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="3">
+        <v>200101001</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2</v>
+      </c>
+      <c r="I39" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J39" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K39" s="3">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N39" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O39" s="3">
+        <v>300</v>
+      </c>
+      <c r="P39" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R39" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S39" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T39" s="5">
+        <v>48</v>
+      </c>
+      <c r="U39" s="44">
+        <v>0</v>
+      </c>
+      <c r="V39" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="W39" s="46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="4">
+        <v>20010112</v>
+      </c>
+      <c r="B40" s="25">
+        <v>200101</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" s="3">
+        <v>200101001</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H40" s="3">
+        <v>3</v>
+      </c>
+      <c r="I40" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J40" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N40" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O40" s="3">
+        <v>300</v>
+      </c>
+      <c r="P40" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R40" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S40" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T40" s="5">
+        <v>48</v>
+      </c>
+      <c r="U40" s="44">
+        <v>0</v>
+      </c>
+      <c r="V40" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="W40" s="46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23">
+      <c r="A41" s="4">
+        <v>20030010</v>
+      </c>
+      <c r="B41" s="25">
+        <v>200300</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="3">
+        <v>200300001</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1</v>
+      </c>
+      <c r="I41" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J41" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N41" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O41" s="3">
+        <v>300</v>
+      </c>
+      <c r="P41" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R41" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S41" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T41" s="5">
+        <v>50</v>
+      </c>
+      <c r="U41" s="44">
+        <v>0</v>
+      </c>
+      <c r="V41" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="W41" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="4">
+        <v>20030011</v>
+      </c>
+      <c r="B42" s="25">
+        <v>200300</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="3">
+        <v>200300001</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H42" s="3">
+        <v>2</v>
+      </c>
+      <c r="I42" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J42" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N42" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O42" s="3">
+        <v>300</v>
+      </c>
+      <c r="P42" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R42" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S42" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T42" s="5">
+        <v>50</v>
+      </c>
+      <c r="U42" s="44">
+        <v>0</v>
+      </c>
+      <c r="V42" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="W42" s="46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="4">
+        <v>20030012</v>
+      </c>
+      <c r="B43" s="25">
+        <v>200300</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="3">
+        <v>200300001</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H43" s="3">
+        <v>3</v>
+      </c>
+      <c r="I43" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J43" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K43" s="38">
+        <v>0</v>
+      </c>
+      <c r="L43" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="M43" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="N43" s="38">
+        <v>9700</v>
+      </c>
+      <c r="O43" s="38">
+        <v>300</v>
+      </c>
+      <c r="P43" s="38">
+        <v>180000</v>
+      </c>
+      <c r="Q43" s="38">
+        <v>16000</v>
+      </c>
+      <c r="R43" s="38">
+        <v>15000</v>
+      </c>
+      <c r="S43" s="38">
+        <v>16008</v>
+      </c>
+      <c r="T43" s="5">
+        <v>50</v>
+      </c>
+      <c r="U43" s="44">
+        <v>0</v>
+      </c>
+      <c r="V43" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="W43" s="46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="4">
+        <v>20040010</v>
+      </c>
+      <c r="B44" s="25">
+        <v>200400</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="3">
+        <v>200400009</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F44" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1</v>
+      </c>
+      <c r="I44" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J44" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="K44" s="38">
+        <v>0</v>
+      </c>
+      <c r="L44" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="M44" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="N44" s="38">
+        <v>9700</v>
+      </c>
+      <c r="O44" s="38">
+        <v>300</v>
+      </c>
+      <c r="P44" s="38">
+        <v>180000</v>
+      </c>
+      <c r="Q44" s="38">
+        <v>16000</v>
+      </c>
+      <c r="R44" s="38">
+        <v>15000</v>
+      </c>
+      <c r="S44" s="38">
+        <v>16008</v>
+      </c>
+      <c r="T44" s="5">
+        <v>50</v>
+      </c>
+      <c r="U44" s="44">
+        <v>0</v>
+      </c>
+      <c r="V44" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="W44" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="4">
+        <v>20040011</v>
+      </c>
+      <c r="B45" s="25">
+        <v>200400</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="3">
+        <v>200400009</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2</v>
+      </c>
+      <c r="I45" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J45" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K45" s="38">
+        <v>0</v>
+      </c>
+      <c r="L45" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="M45" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="N45" s="38">
+        <v>9700</v>
+      </c>
+      <c r="O45" s="38">
+        <v>300</v>
+      </c>
+      <c r="P45" s="38">
+        <v>180000</v>
+      </c>
+      <c r="Q45" s="38">
+        <v>16000</v>
+      </c>
+      <c r="R45" s="38">
+        <v>15000</v>
+      </c>
+      <c r="S45" s="38">
+        <v>16008</v>
+      </c>
+      <c r="T45" s="5">
+        <v>50</v>
+      </c>
+      <c r="U45" s="44">
+        <v>0</v>
+      </c>
+      <c r="V45" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="W45" s="46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23">
+      <c r="A46" s="4">
+        <v>20040012</v>
+      </c>
+      <c r="B46" s="25">
+        <v>200400</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="3">
+        <v>200400009</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H46" s="3">
+        <v>3</v>
+      </c>
+      <c r="I46" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J46" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K46" s="38">
+        <v>0</v>
+      </c>
+      <c r="L46" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="M46" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="N46" s="38">
+        <v>9700</v>
+      </c>
+      <c r="O46" s="38">
+        <v>300</v>
+      </c>
+      <c r="P46" s="38">
+        <v>180000</v>
+      </c>
+      <c r="Q46" s="38">
+        <v>16000</v>
+      </c>
+      <c r="R46" s="38">
+        <v>15000</v>
+      </c>
+      <c r="S46" s="38">
+        <v>16008</v>
+      </c>
+      <c r="T46" s="5">
+        <v>50</v>
+      </c>
+      <c r="U46" s="44">
+        <v>0</v>
+      </c>
+      <c r="V46" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="W46" s="46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23">
+      <c r="A47" s="4">
+        <v>20050010</v>
+      </c>
+      <c r="B47" s="25">
+        <v>200500</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="3">
+        <v>200500025</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1</v>
+      </c>
+      <c r="I47" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J47" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="K47" s="38">
+        <v>1</v>
+      </c>
+      <c r="L47" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="N47" s="38">
+        <v>9700</v>
+      </c>
+      <c r="O47" s="38">
+        <v>300</v>
+      </c>
+      <c r="P47" s="38">
+        <v>180000</v>
+      </c>
+      <c r="Q47" s="38">
+        <v>16000</v>
+      </c>
+      <c r="R47" s="38">
+        <v>15000</v>
+      </c>
+      <c r="S47" s="38">
+        <v>16008</v>
+      </c>
+      <c r="T47" s="4">
+        <v>48</v>
+      </c>
+      <c r="U47" s="5">
+        <v>0</v>
+      </c>
+      <c r="V47" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="W47" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23">
+      <c r="A48" s="4">
+        <v>20050011</v>
+      </c>
+      <c r="B48" s="25">
+        <v>200500</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" s="3">
+        <v>200500025</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F48" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H48" s="3">
+        <v>2</v>
+      </c>
+      <c r="I48" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J48" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K48" s="38">
+        <v>1</v>
+      </c>
+      <c r="L48" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="N48" s="38">
+        <v>9700</v>
+      </c>
+      <c r="O48" s="38">
+        <v>300</v>
+      </c>
+      <c r="P48" s="38">
+        <v>180000</v>
+      </c>
+      <c r="Q48" s="38">
+        <v>16000</v>
+      </c>
+      <c r="R48" s="38">
+        <v>15000</v>
+      </c>
+      <c r="S48" s="38">
+        <v>16008</v>
+      </c>
+      <c r="T48" s="4">
+        <v>48</v>
+      </c>
+      <c r="U48" s="5">
+        <v>0</v>
+      </c>
+      <c r="V48" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="W48" s="46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23">
+      <c r="A49" s="4">
+        <v>20050012</v>
+      </c>
+      <c r="B49" s="25">
+        <v>200500</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="3">
+        <v>200500025</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H49" s="3">
+        <v>3</v>
+      </c>
+      <c r="I49" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J49" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K49" s="38">
+        <v>1</v>
+      </c>
+      <c r="L49" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="N49" s="38">
+        <v>9700</v>
+      </c>
+      <c r="O49" s="38">
+        <v>300</v>
+      </c>
+      <c r="P49" s="38">
+        <v>180000</v>
+      </c>
+      <c r="Q49" s="38">
+        <v>16000</v>
+      </c>
+      <c r="R49" s="38">
+        <v>15000</v>
+      </c>
+      <c r="S49" s="38">
+        <v>16008</v>
+      </c>
+      <c r="T49" s="4">
+        <v>48</v>
+      </c>
+      <c r="U49" s="5">
+        <v>0</v>
+      </c>
+      <c r="V49" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="W49" s="46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23">
+      <c r="A50" s="4">
+        <v>20060010</v>
+      </c>
+      <c r="B50" s="25">
+        <v>200600</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="3">
+        <v>200600001</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F50" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="I50" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J50" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="K50" s="38">
+        <v>0</v>
+      </c>
+      <c r="L50" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="M50" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="N50" s="38">
+        <v>9700</v>
+      </c>
+      <c r="O50" s="38">
+        <v>300</v>
+      </c>
+      <c r="P50" s="38">
+        <v>180000</v>
+      </c>
+      <c r="Q50" s="38">
+        <v>16000</v>
+      </c>
+      <c r="R50" s="38">
+        <v>15000</v>
+      </c>
+      <c r="S50" s="38">
+        <v>16008</v>
+      </c>
+      <c r="T50" s="4">
+        <v>3</v>
+      </c>
+      <c r="U50" s="5">
+        <v>0</v>
+      </c>
+      <c r="V50" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="W50" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23">
+      <c r="A51" s="4">
+        <v>20060011</v>
+      </c>
+      <c r="B51" s="25">
+        <v>200600</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" s="3">
+        <v>200600001</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H51" s="3">
+        <v>2</v>
+      </c>
+      <c r="I51" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J51" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K51" s="38">
+        <v>0</v>
+      </c>
+      <c r="L51" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="M51" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="N51" s="38">
+        <v>9700</v>
+      </c>
+      <c r="O51" s="38">
+        <v>300</v>
+      </c>
+      <c r="P51" s="38">
+        <v>180000</v>
+      </c>
+      <c r="Q51" s="38">
+        <v>16000</v>
+      </c>
+      <c r="R51" s="38">
+        <v>15000</v>
+      </c>
+      <c r="S51" s="38">
+        <v>16008</v>
+      </c>
+      <c r="T51" s="4">
+        <v>3</v>
+      </c>
+      <c r="U51" s="5">
+        <v>0</v>
+      </c>
+      <c r="V51" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="W51" s="46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23">
+      <c r="A52" s="4">
+        <v>20060012</v>
+      </c>
+      <c r="B52" s="25">
+        <v>200600</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D52" s="3">
+        <v>200600001</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H52" s="3">
+        <v>3</v>
+      </c>
+      <c r="I52" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J52" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N52" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O52" s="3">
+        <v>300</v>
+      </c>
+      <c r="P52" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R52" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S52" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T52" s="4">
+        <v>3</v>
+      </c>
+      <c r="U52" s="5">
+        <v>0</v>
+      </c>
+      <c r="V52" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="W52" s="46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23">
+      <c r="A53" s="4">
+        <v>20070010</v>
+      </c>
+      <c r="B53" s="25">
+        <v>200700</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" s="3">
+        <v>200700001</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J53" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="K53" s="3">
+        <v>1</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N53" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R53" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S53" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T53" s="4">
+        <v>30</v>
+      </c>
+      <c r="U53" s="5">
+        <v>1</v>
+      </c>
+      <c r="V53" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="W53" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23">
+      <c r="A54" s="4">
+        <v>20070011</v>
+      </c>
+      <c r="B54" s="25">
+        <v>200700</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="3">
+        <v>200700001</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H54" s="3">
+        <v>2</v>
+      </c>
+      <c r="I54" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J54" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K54" s="3">
+        <v>1</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N54" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O54" s="3">
+        <v>0</v>
+      </c>
+      <c r="P54" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R54" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S54" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T54" s="4">
+        <v>30</v>
+      </c>
+      <c r="U54" s="5">
+        <v>1</v>
+      </c>
+      <c r="V54" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="W54" s="46" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23">
+      <c r="A55" s="4">
+        <v>20070012</v>
+      </c>
+      <c r="B55" s="25">
+        <v>200700</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="3">
+        <v>200700001</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F55" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H55" s="3">
+        <v>3</v>
+      </c>
+      <c r="I55" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J55" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K55" s="3">
+        <v>1</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N55" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O55" s="3">
+        <v>0</v>
+      </c>
+      <c r="P55" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R55" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S55" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T55" s="4">
+        <v>30</v>
+      </c>
+      <c r="U55" s="5">
+        <v>1</v>
+      </c>
+      <c r="V55" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="W55" s="46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23">
+      <c r="A56" s="4">
+        <v>20080010</v>
+      </c>
+      <c r="B56" s="25">
+        <v>200800</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="M34" s="3">
+      <c r="D56" s="3">
+        <v>200800001</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J56" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="K56" s="3">
+        <v>0</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N56" s="3">
         <v>9700</v>
       </c>
-      <c r="N34" s="3">
+      <c r="O56" s="3">
         <v>300</v>
       </c>
-      <c r="O34" s="3">
+      <c r="P56" s="3">
         <v>180000</v>
       </c>
-      <c r="P34" s="3">
+      <c r="Q56" s="3">
         <v>16000</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="R56" s="3">
         <v>15000</v>
       </c>
-      <c r="R34" s="40">
+      <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="S34" s="4">
-        <v>50</v>
-      </c>
-      <c r="T34" s="41">
-        <v>0</v>
-      </c>
-      <c r="U34" t="s">
-        <v>57</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>51</v>
+      <c r="T56" s="4">
+        <v>3</v>
+      </c>
+      <c r="U56" s="5">
+        <v>0</v>
+      </c>
+      <c r="V56" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="W56" s="46" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="35" spans="20:21">
-      <c r="T35" s="41"/>
-      <c r="U35" s="41"/>
+    <row r="57" spans="1:23">
+      <c r="A57" s="4">
+        <v>20080011</v>
+      </c>
+      <c r="B57" s="25">
+        <v>200800</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" s="3">
+        <v>200800001</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F57" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2</v>
+      </c>
+      <c r="I57" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J57" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N57" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O57" s="3">
+        <v>300</v>
+      </c>
+      <c r="P57" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R57" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S57" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T57" s="4">
+        <v>3</v>
+      </c>
+      <c r="U57" s="5">
+        <v>0</v>
+      </c>
+      <c r="V57" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="W57" s="46" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="36" spans="3:21">
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
+    <row r="58" spans="1:23">
+      <c r="A58" s="4">
+        <v>20080012</v>
+      </c>
+      <c r="B58" s="25">
+        <v>200800</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D58" s="3">
+        <v>200800001</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F58" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H58" s="3">
+        <v>3</v>
+      </c>
+      <c r="I58" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J58" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O58" s="3">
+        <v>300</v>
+      </c>
+      <c r="P58" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S58" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T58" s="4">
+        <v>3</v>
+      </c>
+      <c r="U58" s="5">
+        <v>0</v>
+      </c>
+      <c r="V58" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="W58" s="46" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="37" spans="20:21">
-      <c r="T37" s="41"/>
-      <c r="U37" s="41"/>
+    <row r="59" spans="1:23">
+      <c r="A59" s="4">
+        <v>20090010</v>
+      </c>
+      <c r="B59" s="25">
+        <v>200900</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D59" s="3">
+        <v>200900001</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1</v>
+      </c>
+      <c r="I59" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J59" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O59" s="3">
+        <v>300</v>
+      </c>
+      <c r="P59" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R59" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S59" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T59" s="4">
+        <v>3</v>
+      </c>
+      <c r="U59" s="5">
+        <v>0</v>
+      </c>
+      <c r="V59" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="W59" s="46" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="38" spans="19:21">
-      <c r="S38" s="5"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
+    <row r="60" spans="1:23">
+      <c r="A60" s="4">
+        <v>20090011</v>
+      </c>
+      <c r="B60" s="25">
+        <v>200900</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" s="3">
+        <v>200900001</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F60" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H60" s="3">
+        <v>2</v>
+      </c>
+      <c r="I60" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J60" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K60" s="3">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N60" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O60" s="3">
+        <v>300</v>
+      </c>
+      <c r="P60" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R60" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S60" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T60" s="4">
+        <v>3</v>
+      </c>
+      <c r="U60" s="5">
+        <v>0</v>
+      </c>
+      <c r="V60" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="W60" s="46" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="39" spans="19:21">
-      <c r="S39" s="5"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="41"/>
-    </row>
-    <row r="40" spans="19:21">
-      <c r="S40" s="5"/>
-      <c r="T40" s="41"/>
-      <c r="U40" s="41"/>
-    </row>
-    <row r="41" spans="19:21">
-      <c r="S41" s="5"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="41"/>
-    </row>
-    <row r="42" spans="19:21">
-      <c r="S42" s="5"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-    </row>
-    <row r="43" spans="9:21">
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
-      <c r="K43" s="36"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="36"/>
-      <c r="N43" s="36"/>
-      <c r="O43" s="36"/>
-      <c r="P43" s="36"/>
-      <c r="Q43" s="36"/>
-      <c r="R43" s="36"/>
-      <c r="S43" s="5"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-    </row>
-    <row r="44" spans="9:21">
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="36"/>
-      <c r="M44" s="36"/>
-      <c r="N44" s="36"/>
-      <c r="O44" s="36"/>
-      <c r="P44" s="36"/>
-      <c r="Q44" s="36"/>
-      <c r="R44" s="36"/>
-      <c r="S44" s="5"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-    </row>
-    <row r="45" spans="9:21">
-      <c r="I45" s="36"/>
-      <c r="J45" s="36"/>
-      <c r="K45" s="36"/>
-      <c r="L45" s="36"/>
-      <c r="M45" s="36"/>
-      <c r="N45" s="36"/>
-      <c r="O45" s="36"/>
-      <c r="P45" s="36"/>
-      <c r="Q45" s="36"/>
-      <c r="R45" s="36"/>
-      <c r="S45" s="5"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-    </row>
-    <row r="46" spans="9:21">
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="36"/>
-      <c r="M46" s="36"/>
-      <c r="N46" s="36"/>
-      <c r="O46" s="36"/>
-      <c r="P46" s="36"/>
-      <c r="Q46" s="36"/>
-      <c r="R46" s="36"/>
-      <c r="S46" s="5"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-    </row>
-    <row r="47" spans="9:18">
-      <c r="I47" s="36"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
-      <c r="L47" s="36"/>
-      <c r="M47" s="36"/>
-      <c r="N47" s="36"/>
-      <c r="O47" s="36"/>
-      <c r="P47" s="36"/>
-      <c r="Q47" s="36"/>
-      <c r="R47" s="36"/>
-    </row>
-    <row r="48" spans="9:18">
-      <c r="I48" s="36"/>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="36"/>
-      <c r="M48" s="36"/>
-      <c r="N48" s="36"/>
-      <c r="O48" s="36"/>
-      <c r="P48" s="36"/>
-      <c r="Q48" s="36"/>
-      <c r="R48" s="36"/>
-    </row>
-    <row r="49" spans="9:18">
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="36"/>
-      <c r="L49" s="36"/>
-      <c r="M49" s="36"/>
-      <c r="N49" s="36"/>
-      <c r="O49" s="36"/>
-      <c r="P49" s="36"/>
-      <c r="Q49" s="36"/>
-      <c r="R49" s="36"/>
-    </row>
-    <row r="50" spans="9:18">
-      <c r="I50" s="36"/>
-      <c r="J50" s="36"/>
-      <c r="K50" s="36"/>
-      <c r="L50" s="36"/>
-      <c r="M50" s="36"/>
-      <c r="N50" s="36"/>
-      <c r="O50" s="36"/>
-      <c r="P50" s="36"/>
-      <c r="Q50" s="36"/>
-      <c r="R50" s="36"/>
-    </row>
-    <row r="51" spans="9:18">
-      <c r="I51" s="36"/>
-      <c r="J51" s="36"/>
-      <c r="K51" s="36"/>
-      <c r="L51" s="36"/>
-      <c r="M51" s="36"/>
-      <c r="N51" s="36"/>
-      <c r="O51" s="36"/>
-      <c r="P51" s="36"/>
-      <c r="Q51" s="36"/>
-      <c r="R51" s="36"/>
+    <row r="61" spans="1:23">
+      <c r="A61" s="4">
+        <v>20090012</v>
+      </c>
+      <c r="B61" s="25">
+        <v>200900</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="3">
+        <v>200900001</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H61" s="3">
+        <v>3</v>
+      </c>
+      <c r="I61" s="37">
+        <v>1980000</v>
+      </c>
+      <c r="J61" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N61" s="3">
+        <v>9700</v>
+      </c>
+      <c r="O61" s="3">
+        <v>300</v>
+      </c>
+      <c r="P61" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S61" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T61" s="4">
+        <v>3</v>
+      </c>
+      <c r="U61" s="5">
+        <v>0</v>
+      </c>
+      <c r="V61" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="W61" s="46" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:R51" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S61" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="87">
   <si>
     <t>游戏ID</t>
   </si>
@@ -380,6 +380,9 @@
     <t>上庄最低金额</t>
   </si>
   <si>
+    <t>是否允许庄家参与游戏</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -453,6 +456,9 @@
   </si>
   <si>
     <t>minBankerAmount</t>
+  </si>
+  <si>
+    <t>bankerBets</t>
   </si>
   <si>
     <t>红黑大战</t>
@@ -1803,7 +1809,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:W61"/>
+  <dimension ref="A1:X61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3"/>
@@ -1823,12 +1829,12 @@
     <col min="20" max="20" width="17.2166666666667" style="4" customWidth="1"/>
     <col min="21" max="22" width="19.5" style="5" customWidth="1"/>
     <col min="23" max="23" width="19.125" style="2" customWidth="1"/>
-    <col min="24" max="24" width="9.25" style="2"/>
+    <col min="24" max="24" width="12.875" style="2" customWidth="1"/>
     <col min="25" max="25" width="20.125" style="2" customWidth="1"/>
     <col min="26" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:23">
+    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:24">
       <c r="A1" s="6"/>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -1892,135 +1898,144 @@
       <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="X1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:23">
+    <row r="2" s="1" customFormat="1" spans="1:24">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="O2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V2" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="4" t="s">
-        <v>23</v>
+      <c r="X2" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:23">
+    <row r="3" s="1" customFormat="1" spans="1:24">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:22">
@@ -2055,19 +2070,19 @@
         <v>200100</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" s="14">
         <v>200100038</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H5" s="14">
         <v>1</v>
@@ -2076,16 +2091,16 @@
         <v>1990000</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K5" s="3">
         <v>1</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N5" s="3">
         <v>9700</v>
@@ -2112,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -2127,19 +2142,19 @@
         <v>200100</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" s="17">
         <v>200100038</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="17">
         <v>2</v>
@@ -2148,16 +2163,16 @@
         <v>1990000</v>
       </c>
       <c r="J6" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K6" s="3">
         <v>1</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M6" s="34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N6" s="3">
         <v>9700</v>
@@ -2184,10 +2199,10 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:23">
@@ -2199,19 +2214,19 @@
         <v>200100</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" s="14">
         <v>200100038</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H7" s="14">
         <v>3</v>
@@ -2220,16 +2235,16 @@
         <v>1990000</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K7" s="3">
         <v>1</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M7" s="34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N7" s="3">
         <v>9700</v>
@@ -2256,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:23">
@@ -2271,19 +2286,19 @@
         <v>200101</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" s="14">
         <v>200101001</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H8" s="14">
         <v>1</v>
@@ -2292,16 +2307,16 @@
         <v>1990000</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N8" s="3">
         <v>9700</v>
@@ -2328,10 +2343,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -2343,19 +2358,19 @@
         <v>200101</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" s="17">
         <v>200101001</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H9" s="17">
         <v>2</v>
@@ -2364,16 +2379,16 @@
         <v>1990000</v>
       </c>
       <c r="J9" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N9" s="3">
         <v>9700</v>
@@ -2400,10 +2415,10 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -2415,19 +2430,19 @@
         <v>200101</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" s="14">
         <v>200101001</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H10" s="14">
         <v>3</v>
@@ -2436,16 +2451,16 @@
         <v>1990000</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N10" s="3">
         <v>9700</v>
@@ -2472,10 +2487,10 @@
         <v>0</v>
       </c>
       <c r="V10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -2487,19 +2502,19 @@
         <v>200300</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D11" s="14">
         <v>200300001</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H11" s="14">
         <v>1</v>
@@ -2508,16 +2523,16 @@
         <v>1990000</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N11" s="3">
         <v>9700</v>
@@ -2544,10 +2559,10 @@
         <v>0</v>
       </c>
       <c r="V11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:23">
@@ -2559,19 +2574,19 @@
         <v>200300</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D12" s="17">
         <v>200300001</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H12" s="17">
         <v>2</v>
@@ -2580,16 +2595,16 @@
         <v>1990000</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M12" s="34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N12" s="3">
         <v>9700</v>
@@ -2616,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="V12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -2631,19 +2646,19 @@
         <v>200300</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" s="14">
         <v>200300001</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H13" s="14">
         <v>3</v>
@@ -2652,16 +2667,16 @@
         <v>1990000</v>
       </c>
       <c r="J13" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M13" s="34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N13" s="3">
         <v>9700</v>
@@ -2688,10 +2703,10 @@
         <v>0</v>
       </c>
       <c r="V13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -2703,19 +2718,19 @@
         <v>200400</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" s="14">
         <v>200400009</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H14" s="14">
         <v>1</v>
@@ -2724,16 +2739,16 @@
         <v>1990000</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M14" s="34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N14" s="3">
         <v>9700</v>
@@ -2760,10 +2775,10 @@
         <v>0</v>
       </c>
       <c r="V14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -2775,19 +2790,19 @@
         <v>200400</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15" s="17">
         <v>200400009</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H15" s="17">
         <v>2</v>
@@ -2796,16 +2811,16 @@
         <v>1990000</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M15" s="34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N15" s="3">
         <v>9700</v>
@@ -2832,10 +2847,10 @@
         <v>0</v>
       </c>
       <c r="V15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:23">
@@ -2847,19 +2862,19 @@
         <v>200400</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" s="14">
         <v>200400009</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H16" s="14">
         <v>3</v>
@@ -2868,16 +2883,16 @@
         <v>1990000</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K16" s="3">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M16" s="34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N16" s="3">
         <v>9700</v>
@@ -2904,13 +2919,13 @@
         <v>0</v>
       </c>
       <c r="V16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:23">
+    <row r="17" s="2" customFormat="1" spans="1:24">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -2919,19 +2934,19 @@
         <v>200500</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D17" s="14">
         <v>200500025</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H17" s="14">
         <v>1</v>
@@ -2940,16 +2955,16 @@
         <v>1990000</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K17" s="3">
         <v>1</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N17" s="3">
         <v>9700</v>
@@ -2976,13 +2991,16 @@
         <v>0</v>
       </c>
       <c r="V17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:24">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>2005002</v>
@@ -2991,19 +3009,19 @@
         <v>200500</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D18" s="17">
         <v>200500025</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F18" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H18" s="17">
         <v>2</v>
@@ -3012,16 +3030,16 @@
         <v>1990000</v>
       </c>
       <c r="J18" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K18" s="3">
         <v>1</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M18" s="34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N18" s="3">
         <v>9700</v>
@@ -3048,13 +3066,16 @@
         <v>0</v>
       </c>
       <c r="V18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:24">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>2005003</v>
@@ -3063,19 +3084,19 @@
         <v>200500</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D19" s="14">
         <v>200500025</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F19" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H19" s="14">
         <v>3</v>
@@ -3084,16 +3105,16 @@
         <v>1990000</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K19" s="3">
         <v>1</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M19" s="34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N19" s="3">
         <v>9700</v>
@@ -3120,13 +3141,16 @@
         <v>0</v>
       </c>
       <c r="V19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:24">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>2006001</v>
@@ -3135,19 +3159,19 @@
         <v>200600</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D20" s="14">
         <v>200600001</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H20" s="14">
         <v>1</v>
@@ -3156,16 +3180,16 @@
         <v>1990000</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M20" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N20" s="3">
         <v>9700</v>
@@ -3186,19 +3210,22 @@
         <v>16008</v>
       </c>
       <c r="T20" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U20" s="44">
         <v>0</v>
       </c>
       <c r="V20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:23">
+    <row r="21" s="2" customFormat="1" spans="1:24">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>2006002</v>
@@ -3207,19 +3234,19 @@
         <v>200600</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D21" s="17">
         <v>200600001</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F21" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H21" s="17">
         <v>2</v>
@@ -3228,16 +3255,16 @@
         <v>1990000</v>
       </c>
       <c r="J21" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M21" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N21" s="3">
         <v>9700</v>
@@ -3258,19 +3285,22 @@
         <v>16008</v>
       </c>
       <c r="T21" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U21" s="44">
         <v>0</v>
       </c>
       <c r="V21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:24">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>2006003</v>
@@ -3279,19 +3309,19 @@
         <v>200600</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D22" s="14">
         <v>200600001</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F22" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H22" s="14">
         <v>3</v>
@@ -3300,16 +3330,16 @@
         <v>1990000</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N22" s="3">
         <v>9700</v>
@@ -3330,19 +3360,22 @@
         <v>16008</v>
       </c>
       <c r="T22" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U22" s="44">
         <v>0</v>
       </c>
       <c r="V22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:24">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>2007001</v>
@@ -3351,19 +3384,19 @@
         <v>200700</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D23" s="14">
         <v>200700001</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F23" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H23" s="14">
         <v>1</v>
@@ -3372,16 +3405,16 @@
         <v>1990000</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K23" s="3">
         <v>1</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M23" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N23" s="3">
         <v>9700</v>
@@ -3408,13 +3441,16 @@
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="X23" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:24">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>2007002</v>
@@ -3423,19 +3459,19 @@
         <v>200700</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D24" s="17">
         <v>200700001</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F24" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H24" s="17">
         <v>2</v>
@@ -3444,16 +3480,16 @@
         <v>1990000</v>
       </c>
       <c r="J24" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K24" s="3">
         <v>1</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N24" s="3">
         <v>9700</v>
@@ -3480,13 +3516,16 @@
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="X24" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:23">
+    <row r="25" s="2" customFormat="1" spans="1:24">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -3495,19 +3534,19 @@
         <v>200700</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D25" s="14">
         <v>200700001</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H25" s="14">
         <v>3</v>
@@ -3516,16 +3555,16 @@
         <v>1990000</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K25" s="3">
         <v>1</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M25" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N25" s="3">
         <v>9700</v>
@@ -3552,13 +3591,16 @@
         <v>1</v>
       </c>
       <c r="V25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="X25" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:23">
+    <row r="26" s="2" customFormat="1" spans="1:24">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -3567,19 +3609,19 @@
         <v>200800</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D26" s="14">
         <v>200800001</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H26" s="14">
         <v>1</v>
@@ -3588,16 +3630,16 @@
         <v>1990000</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M26" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N26" s="3">
         <v>9700</v>
@@ -3618,19 +3660,22 @@
         <v>16008</v>
       </c>
       <c r="T26" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U26" s="44">
         <v>0</v>
       </c>
       <c r="V26" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="X26" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:23">
+    <row r="27" s="2" customFormat="1" spans="1:24">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -3639,19 +3684,19 @@
         <v>200800</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D27" s="14">
         <v>200800001</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H27" s="17">
         <v>2</v>
@@ -3660,16 +3705,16 @@
         <v>1990000</v>
       </c>
       <c r="J27" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M27" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N27" s="3">
         <v>9700</v>
@@ -3690,19 +3735,22 @@
         <v>16008</v>
       </c>
       <c r="T27" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U27" s="44">
         <v>0</v>
       </c>
       <c r="V27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="X27" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:23">
+    <row r="28" s="2" customFormat="1" spans="1:24">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -3711,19 +3759,19 @@
         <v>200800</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D28" s="14">
         <v>200800001</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H28" s="14">
         <v>3</v>
@@ -3732,16 +3780,16 @@
         <v>1990000</v>
       </c>
       <c r="J28" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M28" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N28" s="3">
         <v>9700</v>
@@ -3762,19 +3810,22 @@
         <v>16008</v>
       </c>
       <c r="T28" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U28" s="44">
         <v>0</v>
       </c>
       <c r="V28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="X28" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:23">
+    <row r="29" s="2" customFormat="1" spans="1:24">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>2009001</v>
@@ -3783,19 +3834,19 @@
         <v>200900</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D29" s="14">
         <v>200900001</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F29" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H29" s="14">
         <v>1</v>
@@ -3804,16 +3855,16 @@
         <v>1990000</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K29" s="36">
         <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M29" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N29" s="3">
         <v>9700</v>
@@ -3834,19 +3885,22 @@
         <v>16008</v>
       </c>
       <c r="T29" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U29" s="44">
         <v>0</v>
       </c>
       <c r="V29" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="X29" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:24">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>2009002</v>
@@ -3855,19 +3909,19 @@
         <v>200900</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D30" s="17">
         <v>200900001</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F30" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H30" s="17">
         <v>2</v>
@@ -3876,16 +3930,16 @@
         <v>1990000</v>
       </c>
       <c r="J30" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K30" s="36">
         <v>0</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N30" s="3">
         <v>9700</v>
@@ -3906,19 +3960,22 @@
         <v>16008</v>
       </c>
       <c r="T30" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U30" s="44">
         <v>0</v>
       </c>
       <c r="V30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="X30" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>2009003</v>
@@ -3927,19 +3984,19 @@
         <v>200900</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D31" s="23">
         <v>200900001</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F31" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H31" s="14">
         <v>3</v>
@@ -3948,16 +4005,16 @@
         <v>1990000</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K31" s="36">
         <v>0</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M31" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N31" s="3">
         <v>9700</v>
@@ -3978,19 +4035,22 @@
         <v>16008</v>
       </c>
       <c r="T31" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U31" s="44">
         <v>0</v>
       </c>
       <c r="V31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="X31" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>2010001</v>
@@ -3999,19 +4059,19 @@
         <v>201000</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D32" s="3">
         <v>101000006</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F32" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G32" s="48" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H32" s="14">
         <v>1</v>
@@ -4020,16 +4080,16 @@
         <v>1990000</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K32" s="36">
         <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M32" s="34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N32" s="3">
         <v>9700</v>
@@ -4056,13 +4116,16 @@
         <v>0</v>
       </c>
       <c r="V32" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="X32" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:24">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>2010002</v>
@@ -4071,19 +4134,19 @@
         <v>201000</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D33" s="3">
         <v>101000006</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F33" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G33" s="48" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H33" s="17">
         <v>2</v>
@@ -4092,16 +4155,16 @@
         <v>1990000</v>
       </c>
       <c r="J33" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K33" s="36">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M33" s="34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N33" s="3">
         <v>9700</v>
@@ -4128,13 +4191,16 @@
         <v>0</v>
       </c>
       <c r="V33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="X33" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:24">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>2010003</v>
@@ -4143,19 +4209,19 @@
         <v>201000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D34" s="3">
         <v>101000006</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G34" s="48" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H34" s="14">
         <v>3</v>
@@ -4164,16 +4230,16 @@
         <v>1990000</v>
       </c>
       <c r="J34" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K34" s="36">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M34" s="34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N34" s="3">
         <v>9700</v>
@@ -4200,13 +4266,16 @@
         <v>0</v>
       </c>
       <c r="V34" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="X34" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:24">
       <c r="A35" s="4">
         <v>20010010</v>
       </c>
@@ -4214,19 +4283,19 @@
         <v>200100</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D35" s="14">
         <v>200100038</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F35" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H35" s="14">
         <v>1</v>
@@ -4235,16 +4304,16 @@
         <v>1980000</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K35" s="3">
         <v>1</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M35" s="34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N35" s="3">
         <v>9700</v>
@@ -4271,13 +4340,16 @@
         <v>0</v>
       </c>
       <c r="V35" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W35" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="X35" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:24">
       <c r="A36" s="4">
         <v>20010011</v>
       </c>
@@ -4285,19 +4357,19 @@
         <v>200100</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D36" s="17">
         <v>200100038</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F36" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H36" s="17">
         <v>2</v>
@@ -4306,16 +4378,16 @@
         <v>1980000</v>
       </c>
       <c r="J36" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K36" s="3">
         <v>1</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M36" s="34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N36" s="3">
         <v>9700</v>
@@ -4342,13 +4414,16 @@
         <v>0</v>
       </c>
       <c r="V36" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W36" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="X36" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:24">
       <c r="A37" s="4">
         <v>20010012</v>
       </c>
@@ -4356,19 +4431,19 @@
         <v>200100</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D37" s="14">
         <v>200100038</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F37" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H37" s="14">
         <v>3</v>
@@ -4377,16 +4452,16 @@
         <v>1980000</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K37" s="3">
         <v>1</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M37" s="34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N37" s="3">
         <v>9700</v>
@@ -4413,13 +4488,16 @@
         <v>0</v>
       </c>
       <c r="V37" s="45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W37" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X37" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:24">
       <c r="A38" s="4">
         <v>20010110</v>
       </c>
@@ -4427,19 +4505,19 @@
         <v>200101</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D38" s="3">
         <v>200101001</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F38" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
@@ -4448,16 +4526,16 @@
         <v>1980000</v>
       </c>
       <c r="J38" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K38" s="3">
         <v>0</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N38" s="3">
         <v>9700</v>
@@ -4484,13 +4562,16 @@
         <v>0</v>
       </c>
       <c r="V38" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W38" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="X38" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:24">
       <c r="A39" s="4">
         <v>20010111</v>
       </c>
@@ -4498,19 +4579,19 @@
         <v>200101</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D39" s="3">
         <v>200101001</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F39" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
@@ -4519,16 +4600,16 @@
         <v>1980000</v>
       </c>
       <c r="J39" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N39" s="3">
         <v>9700</v>
@@ -4555,13 +4636,16 @@
         <v>0</v>
       </c>
       <c r="V39" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W39" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="X39" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:24">
       <c r="A40" s="4">
         <v>20010112</v>
       </c>
@@ -4569,19 +4653,19 @@
         <v>200101</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D40" s="3">
         <v>200101001</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F40" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H40" s="3">
         <v>3</v>
@@ -4590,16 +4674,16 @@
         <v>1980000</v>
       </c>
       <c r="J40" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K40" s="3">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N40" s="3">
         <v>9700</v>
@@ -4626,13 +4710,16 @@
         <v>0</v>
       </c>
       <c r="V40" s="45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W40" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X40" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:24">
       <c r="A41" s="4">
         <v>20030010</v>
       </c>
@@ -4640,19 +4727,19 @@
         <v>200300</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D41" s="3">
         <v>200300001</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F41" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
@@ -4661,16 +4748,16 @@
         <v>1980000</v>
       </c>
       <c r="J41" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N41" s="3">
         <v>9700</v>
@@ -4697,13 +4784,16 @@
         <v>0</v>
       </c>
       <c r="V41" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W41" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="X41" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:24">
       <c r="A42" s="4">
         <v>20030011</v>
       </c>
@@ -4711,19 +4801,19 @@
         <v>200300</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D42" s="3">
         <v>200300001</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F42" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
@@ -4732,16 +4822,16 @@
         <v>1980000</v>
       </c>
       <c r="J42" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N42" s="3">
         <v>9700</v>
@@ -4768,13 +4858,16 @@
         <v>0</v>
       </c>
       <c r="V42" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W42" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="X42" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:24">
       <c r="A43" s="4">
         <v>20030012</v>
       </c>
@@ -4782,19 +4875,19 @@
         <v>200300</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D43" s="3">
         <v>200300001</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F43" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H43" s="3">
         <v>3</v>
@@ -4803,16 +4896,16 @@
         <v>1980000</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K43" s="38">
         <v>0</v>
       </c>
       <c r="L43" s="38" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M43" s="38" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N43" s="38">
         <v>9700</v>
@@ -4839,13 +4932,16 @@
         <v>0</v>
       </c>
       <c r="V43" s="45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W43" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X43" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:24">
       <c r="A44" s="4">
         <v>20040010</v>
       </c>
@@ -4853,19 +4949,19 @@
         <v>200400</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D44" s="3">
         <v>200400009</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F44" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
@@ -4874,16 +4970,16 @@
         <v>1980000</v>
       </c>
       <c r="J44" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K44" s="38">
         <v>0</v>
       </c>
       <c r="L44" s="38" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M44" s="38" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N44" s="38">
         <v>9700</v>
@@ -4910,13 +5006,16 @@
         <v>0</v>
       </c>
       <c r="V44" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W44" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="X44" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:24">
       <c r="A45" s="4">
         <v>20040011</v>
       </c>
@@ -4924,19 +5023,19 @@
         <v>200400</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D45" s="3">
         <v>200400009</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F45" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
@@ -4945,16 +5044,16 @@
         <v>1980000</v>
       </c>
       <c r="J45" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K45" s="38">
         <v>0</v>
       </c>
       <c r="L45" s="38" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N45" s="38">
         <v>9700</v>
@@ -4981,13 +5080,16 @@
         <v>0</v>
       </c>
       <c r="V45" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W45" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="X45" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
+    <row r="46" spans="1:24">
       <c r="A46" s="4">
         <v>20040012</v>
       </c>
@@ -4995,19 +5097,19 @@
         <v>200400</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D46" s="3">
         <v>200400009</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F46" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H46" s="3">
         <v>3</v>
@@ -5016,16 +5118,16 @@
         <v>1980000</v>
       </c>
       <c r="J46" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K46" s="38">
         <v>0</v>
       </c>
       <c r="L46" s="38" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M46" s="38" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N46" s="38">
         <v>9700</v>
@@ -5052,13 +5154,16 @@
         <v>0</v>
       </c>
       <c r="V46" s="45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W46" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X46" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:24">
       <c r="A47" s="4">
         <v>20050010</v>
       </c>
@@ -5066,19 +5171,19 @@
         <v>200500</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D47" s="3">
         <v>200500025</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F47" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
@@ -5087,16 +5192,16 @@
         <v>1980000</v>
       </c>
       <c r="J47" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K47" s="38">
         <v>1</v>
       </c>
       <c r="L47" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M47" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N47" s="38">
         <v>9700</v>
@@ -5123,13 +5228,16 @@
         <v>0</v>
       </c>
       <c r="V47" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W47" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="X47" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:24">
       <c r="A48" s="4">
         <v>20050011</v>
       </c>
@@ -5137,19 +5245,19 @@
         <v>200500</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D48" s="3">
         <v>200500025</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F48" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
@@ -5158,16 +5266,16 @@
         <v>1980000</v>
       </c>
       <c r="J48" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K48" s="38">
         <v>1</v>
       </c>
       <c r="L48" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M48" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N48" s="38">
         <v>9700</v>
@@ -5194,13 +5302,16 @@
         <v>0</v>
       </c>
       <c r="V48" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W48" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="X48" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:24">
       <c r="A49" s="4">
         <v>20050012</v>
       </c>
@@ -5208,19 +5319,19 @@
         <v>200500</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D49" s="3">
         <v>200500025</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F49" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H49" s="3">
         <v>3</v>
@@ -5229,16 +5340,16 @@
         <v>1980000</v>
       </c>
       <c r="J49" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K49" s="38">
         <v>1</v>
       </c>
       <c r="L49" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M49" s="38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N49" s="38">
         <v>9700</v>
@@ -5265,13 +5376,16 @@
         <v>0</v>
       </c>
       <c r="V49" s="45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W49" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X49" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:24">
       <c r="A50" s="4">
         <v>20060010</v>
       </c>
@@ -5279,19 +5393,19 @@
         <v>200600</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D50" s="3">
         <v>200600001</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F50" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
@@ -5300,16 +5414,16 @@
         <v>1980000</v>
       </c>
       <c r="J50" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K50" s="38">
         <v>0</v>
       </c>
       <c r="L50" s="38" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M50" s="38" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N50" s="38">
         <v>9700</v>
@@ -5330,19 +5444,22 @@
         <v>16008</v>
       </c>
       <c r="T50" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U50" s="5">
         <v>0</v>
       </c>
       <c r="V50" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W50" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="X50" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:24">
       <c r="A51" s="4">
         <v>20060011</v>
       </c>
@@ -5350,19 +5467,19 @@
         <v>200600</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D51" s="3">
         <v>200600001</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F51" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
@@ -5371,16 +5488,16 @@
         <v>1980000</v>
       </c>
       <c r="J51" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K51" s="38">
         <v>0</v>
       </c>
       <c r="L51" s="38" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M51" s="38" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N51" s="38">
         <v>9700</v>
@@ -5401,19 +5518,22 @@
         <v>16008</v>
       </c>
       <c r="T51" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U51" s="5">
         <v>0</v>
       </c>
       <c r="V51" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W51" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="X51" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:24">
       <c r="A52" s="4">
         <v>20060012</v>
       </c>
@@ -5421,19 +5541,19 @@
         <v>200600</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D52" s="3">
         <v>200600001</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F52" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H52" s="3">
         <v>3</v>
@@ -5442,16 +5562,16 @@
         <v>1980000</v>
       </c>
       <c r="J52" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N52" s="3">
         <v>9700</v>
@@ -5472,19 +5592,22 @@
         <v>16008</v>
       </c>
       <c r="T52" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U52" s="5">
         <v>0</v>
       </c>
       <c r="V52" s="45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W52" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X52" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:24">
       <c r="A53" s="4">
         <v>20070010</v>
       </c>
@@ -5492,19 +5615,19 @@
         <v>200700</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D53" s="3">
         <v>200700001</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F53" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
@@ -5513,16 +5636,16 @@
         <v>1980000</v>
       </c>
       <c r="J53" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K53" s="3">
         <v>1</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N53" s="3">
         <v>9700</v>
@@ -5549,13 +5672,16 @@
         <v>1</v>
       </c>
       <c r="V53" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W53" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="X53" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:24">
       <c r="A54" s="4">
         <v>20070011</v>
       </c>
@@ -5563,19 +5689,19 @@
         <v>200700</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D54" s="3">
         <v>200700001</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F54" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
@@ -5584,16 +5710,16 @@
         <v>1980000</v>
       </c>
       <c r="J54" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K54" s="3">
         <v>1</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N54" s="3">
         <v>9700</v>
@@ -5620,13 +5746,16 @@
         <v>1</v>
       </c>
       <c r="V54" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W54" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="X54" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:24">
       <c r="A55" s="4">
         <v>20070012</v>
       </c>
@@ -5634,19 +5763,19 @@
         <v>200700</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D55" s="3">
         <v>200700001</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F55" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H55" s="3">
         <v>3</v>
@@ -5655,16 +5784,16 @@
         <v>1980000</v>
       </c>
       <c r="J55" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K55" s="3">
         <v>1</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N55" s="3">
         <v>9700</v>
@@ -5691,13 +5820,16 @@
         <v>1</v>
       </c>
       <c r="V55" s="45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W55" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X55" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:24">
       <c r="A56" s="4">
         <v>20080010</v>
       </c>
@@ -5705,19 +5837,19 @@
         <v>200800</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D56" s="3">
         <v>200800001</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F56" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
@@ -5726,16 +5858,16 @@
         <v>1980000</v>
       </c>
       <c r="J56" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K56" s="3">
         <v>0</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N56" s="3">
         <v>9700</v>
@@ -5756,19 +5888,22 @@
         <v>16008</v>
       </c>
       <c r="T56" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U56" s="5">
         <v>0</v>
       </c>
       <c r="V56" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W56" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="X56" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:24">
       <c r="A57" s="4">
         <v>20080011</v>
       </c>
@@ -5776,19 +5911,19 @@
         <v>200800</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D57" s="3">
         <v>200800001</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F57" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
@@ -5797,16 +5932,16 @@
         <v>1980000</v>
       </c>
       <c r="J57" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N57" s="3">
         <v>9700</v>
@@ -5827,19 +5962,22 @@
         <v>16008</v>
       </c>
       <c r="T57" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U57" s="5">
         <v>0</v>
       </c>
       <c r="V57" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W57" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="X57" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:24">
       <c r="A58" s="4">
         <v>20080012</v>
       </c>
@@ -5847,19 +5985,19 @@
         <v>200800</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D58" s="3">
         <v>200800001</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F58" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H58" s="3">
         <v>3</v>
@@ -5868,16 +6006,16 @@
         <v>1980000</v>
       </c>
       <c r="J58" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N58" s="3">
         <v>9700</v>
@@ -5898,19 +6036,22 @@
         <v>16008</v>
       </c>
       <c r="T58" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U58" s="5">
         <v>0</v>
       </c>
       <c r="V58" s="45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W58" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X58" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:24">
       <c r="A59" s="4">
         <v>20090010</v>
       </c>
@@ -5918,19 +6059,19 @@
         <v>200900</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D59" s="3">
         <v>200900001</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F59" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H59" s="3">
         <v>1</v>
@@ -5939,16 +6080,16 @@
         <v>1980000</v>
       </c>
       <c r="J59" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N59" s="3">
         <v>9700</v>
@@ -5969,19 +6110,22 @@
         <v>16008</v>
       </c>
       <c r="T59" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U59" s="5">
         <v>0</v>
       </c>
       <c r="V59" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W59" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="X59" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:24">
       <c r="A60" s="4">
         <v>20090011</v>
       </c>
@@ -5989,19 +6133,19 @@
         <v>200900</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D60" s="3">
         <v>200900001</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F60" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H60" s="3">
         <v>2</v>
@@ -6010,16 +6154,16 @@
         <v>1980000</v>
       </c>
       <c r="J60" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N60" s="3">
         <v>9700</v>
@@ -6040,19 +6184,22 @@
         <v>16008</v>
       </c>
       <c r="T60" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U60" s="5">
         <v>0</v>
       </c>
       <c r="V60" s="45" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W60" s="46" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="X60" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:24">
       <c r="A61" s="4">
         <v>20090012</v>
       </c>
@@ -6060,19 +6207,19 @@
         <v>200900</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D61" s="3">
         <v>200900001</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F61" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H61" s="3">
         <v>3</v>
@@ -6081,16 +6228,16 @@
         <v>1980000</v>
       </c>
       <c r="J61" s="33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N61" s="3">
         <v>9700</v>
@@ -6111,16 +6258,19 @@
         <v>16008</v>
       </c>
       <c r="T61" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="U61" s="5">
         <v>0</v>
       </c>
       <c r="V61" s="45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="W61" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="X61" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="89">
   <si>
     <t>游戏ID</t>
   </si>
@@ -473,7 +473,7 @@
     <t>0:6:28|6:12:36|12:18:45|18:24:43</t>
   </si>
   <si>
-    <t>100_200_500_1000_2000_5000_10000</t>
+    <t>50_100_200_500_1000_2000_5000</t>
   </si>
   <si>
     <t>组合</t>
@@ -491,7 +491,7 @@
     <t>中级场</t>
   </si>
   <si>
-    <t>10000_20000_50000_100000_200000_500000_1000000</t>
+    <t>5000_10000_20000_50000_100000_200000_500000</t>
   </si>
   <si>
     <t>50000000_17001</t>
@@ -503,7 +503,7 @@
     <t>高级场</t>
   </si>
   <si>
-    <t>1000000_2000000_5000000_10000000_20000000_50000000_100000000</t>
+    <t>500000_1000000_2000000_5000000_10000000_20000000_50000000</t>
   </si>
   <si>
     <t>5000000000_17001</t>
@@ -566,7 +566,7 @@
     <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
   </si>
   <si>
-    <t>1_2_5_10_20_50_100</t>
+    <t>100_200_300_400_500_800_1000</t>
   </si>
   <si>
     <t>5000_17001</t>
@@ -575,7 +575,13 @@
     <t>1980000_1000</t>
   </si>
   <si>
+    <t>1000_2000_3000_4000_5000_8000_10000</t>
+  </si>
+  <si>
     <t>1980000_100000</t>
+  </si>
+  <si>
+    <t>10000_20000_30000_40000_50000_80000_100000</t>
   </si>
   <si>
     <t>1980000_10000000</t>
@@ -784,12 +790,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4316,10 +4322,10 @@
         <v>53</v>
       </c>
       <c r="N35" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P35" s="3">
         <v>180000</v>
@@ -4378,7 +4384,7 @@
         <v>1980000</v>
       </c>
       <c r="J36" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K36" s="3">
         <v>1</v>
@@ -4390,10 +4396,10 @@
         <v>53</v>
       </c>
       <c r="N36" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O36" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P36" s="3">
         <v>180000</v>
@@ -4417,7 +4423,7 @@
         <v>54</v>
       </c>
       <c r="W36" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X36" s="2">
         <v>0</v>
@@ -4452,7 +4458,7 @@
         <v>1980000</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K37" s="3">
         <v>1</v>
@@ -4464,10 +4470,10 @@
         <v>53</v>
       </c>
       <c r="N37" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O37" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P37" s="3">
         <v>180000</v>
@@ -4491,7 +4497,7 @@
         <v>58</v>
       </c>
       <c r="W37" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X37" s="2">
         <v>0</v>
@@ -4538,10 +4544,10 @@
         <v>66</v>
       </c>
       <c r="N38" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O38" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P38" s="3">
         <v>180000</v>
@@ -4600,7 +4606,7 @@
         <v>1980000</v>
       </c>
       <c r="J39" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -4612,10 +4618,10 @@
         <v>66</v>
       </c>
       <c r="N39" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O39" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P39" s="3">
         <v>180000</v>
@@ -4639,7 +4645,7 @@
         <v>54</v>
       </c>
       <c r="W39" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X39" s="2">
         <v>0</v>
@@ -4674,7 +4680,7 @@
         <v>1980000</v>
       </c>
       <c r="J40" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K40" s="3">
         <v>0</v>
@@ -4686,10 +4692,10 @@
         <v>66</v>
       </c>
       <c r="N40" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O40" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P40" s="3">
         <v>180000</v>
@@ -4713,7 +4719,7 @@
         <v>58</v>
       </c>
       <c r="W40" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X40" s="2">
         <v>0</v>
@@ -4760,10 +4766,10 @@
         <v>68</v>
       </c>
       <c r="N41" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O41" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P41" s="3">
         <v>180000</v>
@@ -4822,7 +4828,7 @@
         <v>1980000</v>
       </c>
       <c r="J42" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -4834,10 +4840,10 @@
         <v>68</v>
       </c>
       <c r="N42" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P42" s="3">
         <v>180000</v>
@@ -4861,7 +4867,7 @@
         <v>54</v>
       </c>
       <c r="W42" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X42" s="2">
         <v>0</v>
@@ -4896,7 +4902,7 @@
         <v>1980000</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K43" s="38">
         <v>0</v>
@@ -4907,11 +4913,11 @@
       <c r="M43" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="N43" s="38">
-        <v>9700</v>
-      </c>
-      <c r="O43" s="38">
-        <v>300</v>
+      <c r="N43" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O43" s="3">
+        <v>100</v>
       </c>
       <c r="P43" s="38">
         <v>180000</v>
@@ -4935,7 +4941,7 @@
         <v>58</v>
       </c>
       <c r="W43" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X43" s="2">
         <v>0</v>
@@ -4981,11 +4987,11 @@
       <c r="M44" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="N44" s="38">
-        <v>9700</v>
-      </c>
-      <c r="O44" s="38">
-        <v>300</v>
+      <c r="N44" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O44" s="3">
+        <v>100</v>
       </c>
       <c r="P44" s="38">
         <v>180000</v>
@@ -5044,7 +5050,7 @@
         <v>1980000</v>
       </c>
       <c r="J45" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K45" s="38">
         <v>0</v>
@@ -5055,11 +5061,11 @@
       <c r="M45" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="N45" s="38">
-        <v>9700</v>
-      </c>
-      <c r="O45" s="38">
-        <v>300</v>
+      <c r="N45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O45" s="3">
+        <v>100</v>
       </c>
       <c r="P45" s="38">
         <v>180000</v>
@@ -5083,7 +5089,7 @@
         <v>54</v>
       </c>
       <c r="W45" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X45" s="2">
         <v>0</v>
@@ -5118,7 +5124,7 @@
         <v>1980000</v>
       </c>
       <c r="J46" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K46" s="38">
         <v>0</v>
@@ -5129,11 +5135,11 @@
       <c r="M46" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="N46" s="38">
-        <v>9700</v>
-      </c>
-      <c r="O46" s="38">
-        <v>300</v>
+      <c r="N46" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O46" s="3">
+        <v>100</v>
       </c>
       <c r="P46" s="38">
         <v>180000</v>
@@ -5157,7 +5163,7 @@
         <v>58</v>
       </c>
       <c r="W46" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X46" s="2">
         <v>0</v>
@@ -5203,11 +5209,11 @@
       <c r="M47" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="N47" s="38">
-        <v>9700</v>
-      </c>
-      <c r="O47" s="38">
-        <v>300</v>
+      <c r="N47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O47" s="3">
+        <v>100</v>
       </c>
       <c r="P47" s="38">
         <v>180000</v>
@@ -5266,7 +5272,7 @@
         <v>1980000</v>
       </c>
       <c r="J48" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K48" s="38">
         <v>1</v>
@@ -5277,11 +5283,11 @@
       <c r="M48" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="N48" s="38">
-        <v>9700</v>
-      </c>
-      <c r="O48" s="38">
-        <v>300</v>
+      <c r="N48" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O48" s="3">
+        <v>100</v>
       </c>
       <c r="P48" s="38">
         <v>180000</v>
@@ -5305,7 +5311,7 @@
         <v>54</v>
       </c>
       <c r="W48" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X48" s="2">
         <v>0</v>
@@ -5340,7 +5346,7 @@
         <v>1980000</v>
       </c>
       <c r="J49" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K49" s="38">
         <v>1</v>
@@ -5351,11 +5357,11 @@
       <c r="M49" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="N49" s="38">
-        <v>9700</v>
-      </c>
-      <c r="O49" s="38">
-        <v>300</v>
+      <c r="N49" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O49" s="3">
+        <v>100</v>
       </c>
       <c r="P49" s="38">
         <v>180000</v>
@@ -5379,7 +5385,7 @@
         <v>58</v>
       </c>
       <c r="W49" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X49" s="2">
         <v>0</v>
@@ -5425,11 +5431,11 @@
       <c r="M50" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="N50" s="38">
-        <v>9700</v>
-      </c>
-      <c r="O50" s="38">
-        <v>300</v>
+      <c r="N50" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O50" s="3">
+        <v>100</v>
       </c>
       <c r="P50" s="38">
         <v>180000</v>
@@ -5488,7 +5494,7 @@
         <v>1980000</v>
       </c>
       <c r="J51" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K51" s="38">
         <v>0</v>
@@ -5499,11 +5505,11 @@
       <c r="M51" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="N51" s="38">
-        <v>9700</v>
-      </c>
-      <c r="O51" s="38">
-        <v>300</v>
+      <c r="N51" s="3">
+        <v>10000</v>
+      </c>
+      <c r="O51" s="3">
+        <v>100</v>
       </c>
       <c r="P51" s="38">
         <v>180000</v>
@@ -5527,7 +5533,7 @@
         <v>54</v>
       </c>
       <c r="W51" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X51" s="2">
         <v>0</v>
@@ -5562,7 +5568,7 @@
         <v>1980000</v>
       </c>
       <c r="J52" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -5574,10 +5580,10 @@
         <v>74</v>
       </c>
       <c r="N52" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O52" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P52" s="3">
         <v>180000</v>
@@ -5601,7 +5607,7 @@
         <v>58</v>
       </c>
       <c r="W52" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X52" s="2">
         <v>0</v>
@@ -5648,7 +5654,7 @@
         <v>74</v>
       </c>
       <c r="N53" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O53" s="3">
         <v>0</v>
@@ -5710,7 +5716,7 @@
         <v>1980000</v>
       </c>
       <c r="J54" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K54" s="3">
         <v>1</v>
@@ -5722,7 +5728,7 @@
         <v>74</v>
       </c>
       <c r="N54" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O54" s="3">
         <v>0</v>
@@ -5749,7 +5755,7 @@
         <v>54</v>
       </c>
       <c r="W54" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X54" s="2">
         <v>0</v>
@@ -5784,7 +5790,7 @@
         <v>1980000</v>
       </c>
       <c r="J55" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K55" s="3">
         <v>1</v>
@@ -5796,7 +5802,7 @@
         <v>74</v>
       </c>
       <c r="N55" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O55" s="3">
         <v>0</v>
@@ -5823,7 +5829,7 @@
         <v>58</v>
       </c>
       <c r="W55" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X55" s="2">
         <v>0</v>
@@ -5870,10 +5876,10 @@
         <v>74</v>
       </c>
       <c r="N56" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O56" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P56" s="3">
         <v>180000</v>
@@ -5932,7 +5938,7 @@
         <v>1980000</v>
       </c>
       <c r="J57" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5944,10 +5950,10 @@
         <v>74</v>
       </c>
       <c r="N57" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O57" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>180000</v>
@@ -5971,7 +5977,7 @@
         <v>54</v>
       </c>
       <c r="W57" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X57" s="2">
         <v>0</v>
@@ -6006,7 +6012,7 @@
         <v>1980000</v>
       </c>
       <c r="J58" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -6018,10 +6024,10 @@
         <v>74</v>
       </c>
       <c r="N58" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O58" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P58" s="3">
         <v>180000</v>
@@ -6045,7 +6051,7 @@
         <v>58</v>
       </c>
       <c r="W58" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X58" s="2">
         <v>0</v>
@@ -6092,10 +6098,10 @@
         <v>74</v>
       </c>
       <c r="N59" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P59" s="3">
         <v>180000</v>
@@ -6154,7 +6160,7 @@
         <v>1980000</v>
       </c>
       <c r="J60" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -6166,10 +6172,10 @@
         <v>74</v>
       </c>
       <c r="N60" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O60" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P60" s="3">
         <v>180000</v>
@@ -6193,7 +6199,7 @@
         <v>54</v>
       </c>
       <c r="W60" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X60" s="2">
         <v>0</v>
@@ -6228,7 +6234,7 @@
         <v>1980000</v>
       </c>
       <c r="J61" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -6240,10 +6246,10 @@
         <v>74</v>
       </c>
       <c r="N61" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="O61" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P61" s="3">
         <v>180000</v>
@@ -6267,7 +6273,7 @@
         <v>58</v>
       </c>
       <c r="W61" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X61" s="2">
         <v>0</v>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="89">
   <si>
     <t>游戏ID</t>
   </si>
@@ -473,7 +473,7 @@
     <t>0:6:28|6:12:36|12:18:45|18:24:43</t>
   </si>
   <si>
-    <t>100_200_500_1000_2000_5000_10000</t>
+    <t>50_100_200_500_1000_2000_5000</t>
   </si>
   <si>
     <t>组合</t>
@@ -491,7 +491,7 @@
     <t>中级场</t>
   </si>
   <si>
-    <t>10000_20000_50000_100000_200000_500000_1000000</t>
+    <t>5000_10000_20000_50000_100000_200000_500000</t>
   </si>
   <si>
     <t>50000000_17001</t>
@@ -503,7 +503,7 @@
     <t>高级场</t>
   </si>
   <si>
-    <t>1000000_2000000_5000000_10000000_20000000_50000000_100000000</t>
+    <t>500000_1000000_2000000_5000000_10000000_20000000_50000000</t>
   </si>
   <si>
     <t>5000000000_17001</t>
@@ -566,7 +566,7 @@
     <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
   </si>
   <si>
-    <t>1_2_5_10_20_50_100</t>
+    <t>50_100_200_500_1000</t>
   </si>
   <si>
     <t>5000_17001</t>
@@ -575,7 +575,13 @@
     <t>1980000_1000</t>
   </si>
   <si>
+    <t>1000_2000_5000_10000_20000</t>
+  </si>
+  <si>
     <t>1980000_100000</t>
+  </si>
+  <si>
+    <t>20000_50000_100000_200000_500000</t>
   </si>
   <si>
     <t>1980000_10000000</t>
@@ -4378,7 +4384,7 @@
         <v>1980000</v>
       </c>
       <c r="J36" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K36" s="3">
         <v>1</v>
@@ -4417,7 +4423,7 @@
         <v>54</v>
       </c>
       <c r="W36" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X36" s="2">
         <v>0</v>
@@ -4452,7 +4458,7 @@
         <v>1980000</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K37" s="3">
         <v>1</v>
@@ -4491,7 +4497,7 @@
         <v>58</v>
       </c>
       <c r="W37" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X37" s="2">
         <v>0</v>
@@ -4600,7 +4606,7 @@
         <v>1980000</v>
       </c>
       <c r="J39" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -4639,7 +4645,7 @@
         <v>54</v>
       </c>
       <c r="W39" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X39" s="2">
         <v>0</v>
@@ -4674,7 +4680,7 @@
         <v>1980000</v>
       </c>
       <c r="J40" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K40" s="3">
         <v>0</v>
@@ -4713,7 +4719,7 @@
         <v>58</v>
       </c>
       <c r="W40" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X40" s="2">
         <v>0</v>
@@ -4822,7 +4828,7 @@
         <v>1980000</v>
       </c>
       <c r="J42" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -4861,7 +4867,7 @@
         <v>54</v>
       </c>
       <c r="W42" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X42" s="2">
         <v>0</v>
@@ -4896,7 +4902,7 @@
         <v>1980000</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K43" s="38">
         <v>0</v>
@@ -4907,10 +4913,10 @@
       <c r="M43" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="N43" s="38">
+      <c r="N43" s="3">
         <v>9700</v>
       </c>
-      <c r="O43" s="38">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
       <c r="P43" s="38">
@@ -4935,7 +4941,7 @@
         <v>58</v>
       </c>
       <c r="W43" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X43" s="2">
         <v>0</v>
@@ -4981,10 +4987,10 @@
       <c r="M44" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="N44" s="38">
+      <c r="N44" s="3">
         <v>9700</v>
       </c>
-      <c r="O44" s="38">
+      <c r="O44" s="3">
         <v>300</v>
       </c>
       <c r="P44" s="38">
@@ -5044,7 +5050,7 @@
         <v>1980000</v>
       </c>
       <c r="J45" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K45" s="38">
         <v>0</v>
@@ -5055,10 +5061,10 @@
       <c r="M45" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="N45" s="38">
+      <c r="N45" s="3">
         <v>9700</v>
       </c>
-      <c r="O45" s="38">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
       <c r="P45" s="38">
@@ -5083,7 +5089,7 @@
         <v>54</v>
       </c>
       <c r="W45" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X45" s="2">
         <v>0</v>
@@ -5118,7 +5124,7 @@
         <v>1980000</v>
       </c>
       <c r="J46" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K46" s="38">
         <v>0</v>
@@ -5129,10 +5135,10 @@
       <c r="M46" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="N46" s="38">
+      <c r="N46" s="3">
         <v>9700</v>
       </c>
-      <c r="O46" s="38">
+      <c r="O46" s="3">
         <v>300</v>
       </c>
       <c r="P46" s="38">
@@ -5157,7 +5163,7 @@
         <v>58</v>
       </c>
       <c r="W46" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X46" s="2">
         <v>0</v>
@@ -5203,10 +5209,10 @@
       <c r="M47" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="N47" s="38">
+      <c r="N47" s="3">
         <v>9700</v>
       </c>
-      <c r="O47" s="38">
+      <c r="O47" s="3">
         <v>300</v>
       </c>
       <c r="P47" s="38">
@@ -5266,7 +5272,7 @@
         <v>1980000</v>
       </c>
       <c r="J48" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K48" s="38">
         <v>1</v>
@@ -5277,10 +5283,10 @@
       <c r="M48" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="N48" s="38">
+      <c r="N48" s="3">
         <v>9700</v>
       </c>
-      <c r="O48" s="38">
+      <c r="O48" s="3">
         <v>300</v>
       </c>
       <c r="P48" s="38">
@@ -5305,7 +5311,7 @@
         <v>54</v>
       </c>
       <c r="W48" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X48" s="2">
         <v>0</v>
@@ -5340,7 +5346,7 @@
         <v>1980000</v>
       </c>
       <c r="J49" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K49" s="38">
         <v>1</v>
@@ -5351,10 +5357,10 @@
       <c r="M49" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="N49" s="38">
+      <c r="N49" s="3">
         <v>9700</v>
       </c>
-      <c r="O49" s="38">
+      <c r="O49" s="3">
         <v>300</v>
       </c>
       <c r="P49" s="38">
@@ -5379,7 +5385,7 @@
         <v>58</v>
       </c>
       <c r="W49" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X49" s="2">
         <v>0</v>
@@ -5425,10 +5431,10 @@
       <c r="M50" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="N50" s="38">
+      <c r="N50" s="3">
         <v>9700</v>
       </c>
-      <c r="O50" s="38">
+      <c r="O50" s="3">
         <v>300</v>
       </c>
       <c r="P50" s="38">
@@ -5488,7 +5494,7 @@
         <v>1980000</v>
       </c>
       <c r="J51" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K51" s="38">
         <v>0</v>
@@ -5499,10 +5505,10 @@
       <c r="M51" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="N51" s="38">
+      <c r="N51" s="3">
         <v>9700</v>
       </c>
-      <c r="O51" s="38">
+      <c r="O51" s="3">
         <v>300</v>
       </c>
       <c r="P51" s="38">
@@ -5527,7 +5533,7 @@
         <v>54</v>
       </c>
       <c r="W51" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X51" s="2">
         <v>0</v>
@@ -5562,7 +5568,7 @@
         <v>1980000</v>
       </c>
       <c r="J52" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -5601,7 +5607,7 @@
         <v>58</v>
       </c>
       <c r="W52" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X52" s="2">
         <v>0</v>
@@ -5710,7 +5716,7 @@
         <v>1980000</v>
       </c>
       <c r="J54" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K54" s="3">
         <v>1</v>
@@ -5749,7 +5755,7 @@
         <v>54</v>
       </c>
       <c r="W54" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X54" s="2">
         <v>0</v>
@@ -5784,7 +5790,7 @@
         <v>1980000</v>
       </c>
       <c r="J55" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K55" s="3">
         <v>1</v>
@@ -5823,7 +5829,7 @@
         <v>58</v>
       </c>
       <c r="W55" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X55" s="2">
         <v>0</v>
@@ -5932,7 +5938,7 @@
         <v>1980000</v>
       </c>
       <c r="J57" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5971,7 +5977,7 @@
         <v>54</v>
       </c>
       <c r="W57" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X57" s="2">
         <v>0</v>
@@ -6006,7 +6012,7 @@
         <v>1980000</v>
       </c>
       <c r="J58" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -6045,7 +6051,7 @@
         <v>58</v>
       </c>
       <c r="W58" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X58" s="2">
         <v>0</v>
@@ -6154,7 +6160,7 @@
         <v>1980000</v>
       </c>
       <c r="J60" s="35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -6193,7 +6199,7 @@
         <v>54</v>
       </c>
       <c r="W60" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X60" s="2">
         <v>0</v>
@@ -6228,7 +6234,7 @@
         <v>1980000</v>
       </c>
       <c r="J61" s="33" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -6267,7 +6273,7 @@
         <v>58</v>
       </c>
       <c r="W61" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X61" s="2">
         <v>0</v>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="91">
   <si>
     <t>游戏ID</t>
   </si>
@@ -548,7 +548,13 @@
     <t>色碟</t>
   </si>
   <si>
+    <t>2000,16000,8000,0</t>
+  </si>
+  <si>
     <t>大小骰子</t>
+  </si>
+  <si>
+    <t>4000,16000,8000,0</t>
   </si>
   <si>
     <t>鱼虾蟹</t>
@@ -1316,7 +1322,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1456,9 +1462,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1892,13 +1895,13 @@
       <c r="P1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="42" t="s">
+      <c r="Q1" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="43" t="s">
+      <c r="R1" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="44" t="s">
+      <c r="S1" s="43" t="s">
         <v>15</v>
       </c>
       <c r="T1" s="5" t="s">
@@ -1975,7 +1978,7 @@
       <c r="U2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="45" t="s">
+      <c r="V2" s="44" t="s">
         <v>25</v>
       </c>
       <c r="W2" s="5" t="s">
@@ -2093,7 +2096,7 @@
       <c r="E5" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G5" s="17" t="s">
@@ -2132,13 +2135,13 @@
       <c r="R5" s="3">
         <v>15000</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="45">
         <v>16008</v>
       </c>
       <c r="T5" s="5">
         <v>48</v>
       </c>
-      <c r="U5" s="47">
+      <c r="U5" s="46">
         <v>0</v>
       </c>
       <c r="V5" t="s">
@@ -2165,7 +2168,7 @@
       <c r="E6" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G6" s="17" t="s">
@@ -2204,13 +2207,13 @@
       <c r="R6" s="3">
         <v>15000</v>
       </c>
-      <c r="S6" s="46">
+      <c r="S6" s="45">
         <v>16008</v>
       </c>
       <c r="T6" s="5">
         <v>48</v>
       </c>
-      <c r="U6" s="47">
+      <c r="U6" s="46">
         <v>0</v>
       </c>
       <c r="V6" t="s">
@@ -2237,7 +2240,7 @@
       <c r="E7" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G7" s="17" t="s">
@@ -2276,13 +2279,13 @@
       <c r="R7" s="3">
         <v>15000</v>
       </c>
-      <c r="S7" s="46">
+      <c r="S7" s="45">
         <v>16008</v>
       </c>
       <c r="T7" s="5">
         <v>48</v>
       </c>
-      <c r="U7" s="47">
+      <c r="U7" s="46">
         <v>0</v>
       </c>
       <c r="V7" t="s">
@@ -2309,7 +2312,7 @@
       <c r="E8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G8" s="17" t="s">
@@ -2348,13 +2351,13 @@
       <c r="R8" s="3">
         <v>15000</v>
       </c>
-      <c r="S8" s="46">
+      <c r="S8" s="45">
         <v>16008</v>
       </c>
       <c r="T8" s="5">
         <v>48</v>
       </c>
-      <c r="U8" s="47">
+      <c r="U8" s="46">
         <v>0</v>
       </c>
       <c r="V8" t="s">
@@ -2381,7 +2384,7 @@
       <c r="E9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G9" s="17" t="s">
@@ -2420,13 +2423,13 @@
       <c r="R9" s="3">
         <v>15000</v>
       </c>
-      <c r="S9" s="46">
+      <c r="S9" s="45">
         <v>16008</v>
       </c>
       <c r="T9" s="5">
         <v>48</v>
       </c>
-      <c r="U9" s="47">
+      <c r="U9" s="46">
         <v>0</v>
       </c>
       <c r="V9" t="s">
@@ -2453,7 +2456,7 @@
       <c r="E10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G10" s="17" t="s">
@@ -2492,13 +2495,13 @@
       <c r="R10" s="3">
         <v>15000</v>
       </c>
-      <c r="S10" s="46">
+      <c r="S10" s="45">
         <v>16008</v>
       </c>
       <c r="T10" s="5">
         <v>48</v>
       </c>
-      <c r="U10" s="47">
+      <c r="U10" s="46">
         <v>0</v>
       </c>
       <c r="V10" t="s">
@@ -2525,7 +2528,7 @@
       <c r="E11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G11" s="17" t="s">
@@ -2564,13 +2567,13 @@
       <c r="R11" s="3">
         <v>15000</v>
       </c>
-      <c r="S11" s="46">
+      <c r="S11" s="45">
         <v>16008</v>
       </c>
       <c r="T11" s="5">
         <v>50</v>
       </c>
-      <c r="U11" s="47">
+      <c r="U11" s="46">
         <v>0</v>
       </c>
       <c r="V11" t="s">
@@ -2597,7 +2600,7 @@
       <c r="E12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="17" t="s">
@@ -2636,13 +2639,13 @@
       <c r="R12" s="3">
         <v>15000</v>
       </c>
-      <c r="S12" s="46">
+      <c r="S12" s="45">
         <v>16008</v>
       </c>
       <c r="T12" s="5">
         <v>50</v>
       </c>
-      <c r="U12" s="47">
+      <c r="U12" s="46">
         <v>0</v>
       </c>
       <c r="V12" t="s">
@@ -2669,7 +2672,7 @@
       <c r="E13" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G13" s="17" t="s">
@@ -2708,13 +2711,13 @@
       <c r="R13" s="3">
         <v>15000</v>
       </c>
-      <c r="S13" s="46">
+      <c r="S13" s="45">
         <v>16008</v>
       </c>
       <c r="T13" s="5">
         <v>50</v>
       </c>
-      <c r="U13" s="47">
+      <c r="U13" s="46">
         <v>0</v>
       </c>
       <c r="V13" t="s">
@@ -2741,7 +2744,7 @@
       <c r="E14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G14" s="17" t="s">
@@ -2780,13 +2783,13 @@
       <c r="R14" s="3">
         <v>15000</v>
       </c>
-      <c r="S14" s="46">
+      <c r="S14" s="45">
         <v>16008</v>
       </c>
       <c r="T14" s="5">
         <v>50</v>
       </c>
-      <c r="U14" s="47">
+      <c r="U14" s="46">
         <v>0</v>
       </c>
       <c r="V14" t="s">
@@ -2813,7 +2816,7 @@
       <c r="E15" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G15" s="17" t="s">
@@ -2852,13 +2855,13 @@
       <c r="R15" s="3">
         <v>15000</v>
       </c>
-      <c r="S15" s="46">
+      <c r="S15" s="45">
         <v>16008</v>
       </c>
       <c r="T15" s="5">
         <v>50</v>
       </c>
-      <c r="U15" s="47">
+      <c r="U15" s="46">
         <v>0</v>
       </c>
       <c r="V15" t="s">
@@ -2885,7 +2888,7 @@
       <c r="E16" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G16" s="17" t="s">
@@ -2924,13 +2927,13 @@
       <c r="R16" s="3">
         <v>15000</v>
       </c>
-      <c r="S16" s="46">
+      <c r="S16" s="45">
         <v>16008</v>
       </c>
       <c r="T16" s="5">
         <v>50</v>
       </c>
-      <c r="U16" s="47">
+      <c r="U16" s="46">
         <v>0</v>
       </c>
       <c r="V16" t="s">
@@ -2957,7 +2960,7 @@
       <c r="E17" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G17" s="17" t="s">
@@ -2996,13 +2999,13 @@
       <c r="R17" s="3">
         <v>15000</v>
       </c>
-      <c r="S17" s="46">
+      <c r="S17" s="45">
         <v>16008</v>
       </c>
       <c r="T17" s="5">
         <v>48</v>
       </c>
-      <c r="U17" s="47">
+      <c r="U17" s="46">
         <v>0</v>
       </c>
       <c r="V17" t="s">
@@ -3032,7 +3035,7 @@
       <c r="E18" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G18" s="17" t="s">
@@ -3071,13 +3074,13 @@
       <c r="R18" s="3">
         <v>15000</v>
       </c>
-      <c r="S18" s="46">
+      <c r="S18" s="45">
         <v>16008</v>
       </c>
       <c r="T18" s="5">
         <v>48</v>
       </c>
-      <c r="U18" s="47">
+      <c r="U18" s="46">
         <v>0</v>
       </c>
       <c r="V18" t="s">
@@ -3107,7 +3110,7 @@
       <c r="E19" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G19" s="17" t="s">
@@ -3146,13 +3149,13 @@
       <c r="R19" s="3">
         <v>15000</v>
       </c>
-      <c r="S19" s="46">
+      <c r="S19" s="45">
         <v>16008</v>
       </c>
       <c r="T19" s="5">
         <v>48</v>
       </c>
-      <c r="U19" s="47">
+      <c r="U19" s="46">
         <v>0</v>
       </c>
       <c r="V19" t="s">
@@ -3182,7 +3185,7 @@
       <c r="E20" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G20" s="17" t="s">
@@ -3221,13 +3224,13 @@
       <c r="R20" s="3">
         <v>15000</v>
       </c>
-      <c r="S20" s="46">
+      <c r="S20" s="45">
         <v>16008</v>
       </c>
       <c r="T20" s="5">
         <v>20</v>
       </c>
-      <c r="U20" s="47">
+      <c r="U20" s="46">
         <v>0</v>
       </c>
       <c r="V20" t="s">
@@ -3257,7 +3260,7 @@
       <c r="E21" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="50" t="s">
+      <c r="F21" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G21" s="17" t="s">
@@ -3296,13 +3299,13 @@
       <c r="R21" s="3">
         <v>15000</v>
       </c>
-      <c r="S21" s="46">
+      <c r="S21" s="45">
         <v>16008</v>
       </c>
       <c r="T21" s="5">
         <v>20</v>
       </c>
-      <c r="U21" s="47">
+      <c r="U21" s="46">
         <v>0</v>
       </c>
       <c r="V21" t="s">
@@ -3332,7 +3335,7 @@
       <c r="E22" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G22" s="17" t="s">
@@ -3371,13 +3374,13 @@
       <c r="R22" s="3">
         <v>15000</v>
       </c>
-      <c r="S22" s="46">
+      <c r="S22" s="45">
         <v>16008</v>
       </c>
       <c r="T22" s="5">
         <v>20</v>
       </c>
-      <c r="U22" s="47">
+      <c r="U22" s="46">
         <v>0</v>
       </c>
       <c r="V22" t="s">
@@ -3407,7 +3410,7 @@
       <c r="E23" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G23" s="17" t="s">
@@ -3429,7 +3432,7 @@
         <v>65</v>
       </c>
       <c r="M23" s="36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N23" s="3">
         <v>9700</v>
@@ -3446,13 +3449,13 @@
       <c r="R23" s="3">
         <v>15000</v>
       </c>
-      <c r="S23" s="46">
+      <c r="S23" s="45">
         <v>16008</v>
       </c>
       <c r="T23" s="5">
         <v>30</v>
       </c>
-      <c r="U23" s="47">
+      <c r="U23" s="46">
         <v>1</v>
       </c>
       <c r="V23" t="s">
@@ -3482,7 +3485,7 @@
       <c r="E24" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G24" s="17" t="s">
@@ -3504,7 +3507,7 @@
         <v>65</v>
       </c>
       <c r="M24" s="36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N24" s="3">
         <v>9700</v>
@@ -3521,13 +3524,13 @@
       <c r="R24" s="3">
         <v>15000</v>
       </c>
-      <c r="S24" s="46">
+      <c r="S24" s="45">
         <v>16008</v>
       </c>
       <c r="T24" s="5">
         <v>30</v>
       </c>
-      <c r="U24" s="47">
+      <c r="U24" s="46">
         <v>1</v>
       </c>
       <c r="V24" t="s">
@@ -3557,7 +3560,7 @@
       <c r="E25" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G25" s="17" t="s">
@@ -3579,7 +3582,7 @@
         <v>65</v>
       </c>
       <c r="M25" s="36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N25" s="3">
         <v>9700</v>
@@ -3596,13 +3599,13 @@
       <c r="R25" s="3">
         <v>15000</v>
       </c>
-      <c r="S25" s="46">
+      <c r="S25" s="45">
         <v>16008</v>
       </c>
       <c r="T25" s="5">
         <v>30</v>
       </c>
-      <c r="U25" s="47">
+      <c r="U25" s="46">
         <v>1</v>
       </c>
       <c r="V25" t="s">
@@ -3624,7 +3627,7 @@
         <v>200800</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D26" s="15">
         <v>200800001</v>
@@ -3632,7 +3635,7 @@
       <c r="E26" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G26" s="17" t="s">
@@ -3654,7 +3657,7 @@
         <v>65</v>
       </c>
       <c r="M26" s="36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N26" s="3">
         <v>9700</v>
@@ -3671,13 +3674,13 @@
       <c r="R26" s="3">
         <v>15000</v>
       </c>
-      <c r="S26" s="46">
+      <c r="S26" s="45">
         <v>16008</v>
       </c>
       <c r="T26" s="5">
         <v>20</v>
       </c>
-      <c r="U26" s="47">
+      <c r="U26" s="46">
         <v>0</v>
       </c>
       <c r="V26" t="s">
@@ -3699,7 +3702,7 @@
         <v>200800</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D27" s="15">
         <v>200800001</v>
@@ -3707,7 +3710,7 @@
       <c r="E27" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G27" s="17" t="s">
@@ -3729,7 +3732,7 @@
         <v>65</v>
       </c>
       <c r="M27" s="36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N27" s="3">
         <v>9700</v>
@@ -3746,13 +3749,13 @@
       <c r="R27" s="3">
         <v>15000</v>
       </c>
-      <c r="S27" s="46">
+      <c r="S27" s="45">
         <v>16008</v>
       </c>
       <c r="T27" s="5">
         <v>20</v>
       </c>
-      <c r="U27" s="47">
+      <c r="U27" s="46">
         <v>0</v>
       </c>
       <c r="V27" t="s">
@@ -3774,7 +3777,7 @@
         <v>200800</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D28" s="15">
         <v>200800001</v>
@@ -3782,7 +3785,7 @@
       <c r="E28" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G28" s="17" t="s">
@@ -3804,7 +3807,7 @@
         <v>65</v>
       </c>
       <c r="M28" s="36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N28" s="3">
         <v>9700</v>
@@ -3821,13 +3824,13 @@
       <c r="R28" s="3">
         <v>15000</v>
       </c>
-      <c r="S28" s="46">
+      <c r="S28" s="45">
         <v>16008</v>
       </c>
       <c r="T28" s="5">
         <v>20</v>
       </c>
-      <c r="U28" s="47">
+      <c r="U28" s="46">
         <v>0</v>
       </c>
       <c r="V28" t="s">
@@ -3849,7 +3852,7 @@
         <v>200900</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D29" s="15">
         <v>200900001</v>
@@ -3857,7 +3860,7 @@
       <c r="E29" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F29" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G29" s="17" t="s">
@@ -3879,7 +3882,7 @@
         <v>65</v>
       </c>
       <c r="M29" s="36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N29" s="3">
         <v>9700</v>
@@ -3896,13 +3899,13 @@
       <c r="R29" s="3">
         <v>15000</v>
       </c>
-      <c r="S29" s="46">
+      <c r="S29" s="45">
         <v>16008</v>
       </c>
       <c r="T29" s="5">
         <v>20</v>
       </c>
-      <c r="U29" s="47">
+      <c r="U29" s="46">
         <v>0</v>
       </c>
       <c r="V29" t="s">
@@ -3924,7 +3927,7 @@
         <v>200900</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D30" s="18">
         <v>200900001</v>
@@ -3932,7 +3935,7 @@
       <c r="E30" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G30" s="17" t="s">
@@ -3954,7 +3957,7 @@
         <v>65</v>
       </c>
       <c r="M30" s="36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N30" s="3">
         <v>9700</v>
@@ -3971,13 +3974,13 @@
       <c r="R30" s="3">
         <v>15000</v>
       </c>
-      <c r="S30" s="46">
+      <c r="S30" s="45">
         <v>16008</v>
       </c>
       <c r="T30" s="5">
         <v>20</v>
       </c>
-      <c r="U30" s="47">
+      <c r="U30" s="46">
         <v>0</v>
       </c>
       <c r="V30" t="s">
@@ -3999,7 +4002,7 @@
         <v>200900</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D31" s="24">
         <v>200900001</v>
@@ -4007,7 +4010,7 @@
       <c r="E31" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G31" s="17" t="s">
@@ -4029,7 +4032,7 @@
         <v>65</v>
       </c>
       <c r="M31" s="36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N31" s="3">
         <v>9700</v>
@@ -4046,13 +4049,13 @@
       <c r="R31" s="3">
         <v>15000</v>
       </c>
-      <c r="S31" s="46">
+      <c r="S31" s="45">
         <v>16008</v>
       </c>
       <c r="T31" s="5">
         <v>20</v>
       </c>
-      <c r="U31" s="47">
+      <c r="U31" s="46">
         <v>0</v>
       </c>
       <c r="V31" t="s">
@@ -4074,7 +4077,7 @@
         <v>201000</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D32" s="3">
         <v>101000006</v>
@@ -4082,11 +4085,11 @@
       <c r="E32" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F32" s="50" t="s">
+      <c r="F32" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="51" t="s">
-        <v>79</v>
+      <c r="G32" s="50" t="s">
+        <v>81</v>
       </c>
       <c r="H32" s="15">
         <v>1</v>
@@ -4104,7 +4107,7 @@
         <v>65</v>
       </c>
       <c r="M32" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N32" s="3">
         <v>9700</v>
@@ -4121,13 +4124,13 @@
       <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="46">
+      <c r="S32" s="45">
         <v>16008</v>
       </c>
       <c r="T32" s="5">
         <v>50</v>
       </c>
-      <c r="U32" s="47">
+      <c r="U32" s="46">
         <v>0</v>
       </c>
       <c r="V32" t="s">
@@ -4149,7 +4152,7 @@
         <v>201000</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D33" s="3">
         <v>101000006</v>
@@ -4157,11 +4160,11 @@
       <c r="E33" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="50" t="s">
+      <c r="F33" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="G33" s="51" t="s">
-        <v>79</v>
+      <c r="G33" s="50" t="s">
+        <v>81</v>
       </c>
       <c r="H33" s="18">
         <v>2</v>
@@ -4179,7 +4182,7 @@
         <v>65</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N33" s="3">
         <v>9700</v>
@@ -4196,13 +4199,13 @@
       <c r="R33" s="3">
         <v>15000</v>
       </c>
-      <c r="S33" s="46">
+      <c r="S33" s="45">
         <v>16008</v>
       </c>
       <c r="T33" s="5">
         <v>50</v>
       </c>
-      <c r="U33" s="47">
+      <c r="U33" s="46">
         <v>0</v>
       </c>
       <c r="V33" t="s">
@@ -4224,7 +4227,7 @@
         <v>201000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D34" s="3">
         <v>101000006</v>
@@ -4232,11 +4235,11 @@
       <c r="E34" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="50" t="s">
+      <c r="F34" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="G34" s="51" t="s">
-        <v>79</v>
+      <c r="G34" s="50" t="s">
+        <v>81</v>
       </c>
       <c r="H34" s="15">
         <v>3</v>
@@ -4254,7 +4257,7 @@
         <v>65</v>
       </c>
       <c r="M34" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N34" s="3">
         <v>9700</v>
@@ -4271,13 +4274,13 @@
       <c r="R34" s="3">
         <v>15000</v>
       </c>
-      <c r="S34" s="46">
+      <c r="S34" s="45">
         <v>16008</v>
       </c>
       <c r="T34" s="5">
         <v>50</v>
       </c>
-      <c r="U34" s="47">
+      <c r="U34" s="46">
         <v>0</v>
       </c>
       <c r="V34" t="s">
@@ -4306,11 +4309,11 @@
       <c r="E35" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="50" t="s">
+      <c r="F35" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H35" s="15">
         <v>1</v>
@@ -4319,7 +4322,7 @@
         <v>1980000</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K35" s="3">
         <v>1</v>
@@ -4345,20 +4348,20 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="46">
+      <c r="S35" s="45">
         <v>16008</v>
       </c>
       <c r="T35" s="5">
         <v>48</v>
       </c>
-      <c r="U35" s="47">
-        <v>0</v>
-      </c>
-      <c r="V35" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="W35" s="49" t="s">
-        <v>84</v>
+      <c r="U35" s="46">
+        <v>0</v>
+      </c>
+      <c r="V35" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="W35" s="48" t="s">
+        <v>86</v>
       </c>
       <c r="X35" s="2">
         <v>0</v>
@@ -4380,11 +4383,11 @@
       <c r="E36" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="50" t="s">
+      <c r="F36" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H36" s="18">
         <v>2</v>
@@ -4393,7 +4396,7 @@
         <v>1980000</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K36" s="3">
         <v>1</v>
@@ -4419,20 +4422,20 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="46">
+      <c r="S36" s="45">
         <v>16008</v>
       </c>
       <c r="T36" s="5">
         <v>48</v>
       </c>
-      <c r="U36" s="47">
-        <v>0</v>
-      </c>
-      <c r="V36" s="48" t="s">
+      <c r="U36" s="46">
+        <v>0</v>
+      </c>
+      <c r="V36" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="W36" s="49" t="s">
-        <v>86</v>
+      <c r="W36" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="X36" s="2">
         <v>0</v>
@@ -4454,11 +4457,11 @@
       <c r="E37" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="50" t="s">
+      <c r="F37" s="49" t="s">
         <v>49</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H37" s="15">
         <v>3</v>
@@ -4467,7 +4470,7 @@
         <v>1980000</v>
       </c>
       <c r="J37" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K37" s="3">
         <v>1</v>
@@ -4493,20 +4496,20 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="46">
+      <c r="S37" s="45">
         <v>16008</v>
       </c>
       <c r="T37" s="5">
         <v>48</v>
       </c>
-      <c r="U37" s="47">
-        <v>0</v>
-      </c>
-      <c r="V37" s="48" t="s">
+      <c r="U37" s="46">
+        <v>0</v>
+      </c>
+      <c r="V37" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="W37" s="49" t="s">
-        <v>88</v>
+      <c r="W37" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="X37" s="2">
         <v>0</v>
@@ -4528,7 +4531,7 @@
       <c r="E38" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F38" s="52" t="s">
+      <c r="F38" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G38" s="3" t="s">
@@ -4541,7 +4544,7 @@
         <v>1980000</v>
       </c>
       <c r="J38" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K38" s="3">
         <v>0</v>
@@ -4573,14 +4576,14 @@
       <c r="T38" s="6">
         <v>48</v>
       </c>
-      <c r="U38" s="47">
-        <v>0</v>
-      </c>
-      <c r="V38" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="W38" s="49" t="s">
-        <v>84</v>
+      <c r="U38" s="46">
+        <v>0</v>
+      </c>
+      <c r="V38" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="W38" s="48" t="s">
+        <v>86</v>
       </c>
       <c r="X38" s="2">
         <v>0</v>
@@ -4602,7 +4605,7 @@
       <c r="E39" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F39" s="52" t="s">
+      <c r="F39" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G39" s="3" t="s">
@@ -4615,7 +4618,7 @@
         <v>1980000</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -4647,14 +4650,14 @@
       <c r="T39" s="6">
         <v>48</v>
       </c>
-      <c r="U39" s="47">
-        <v>0</v>
-      </c>
-      <c r="V39" s="48" t="s">
+      <c r="U39" s="46">
+        <v>0</v>
+      </c>
+      <c r="V39" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="W39" s="49" t="s">
-        <v>86</v>
+      <c r="W39" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="X39" s="2">
         <v>0</v>
@@ -4676,7 +4679,7 @@
       <c r="E40" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F40" s="52" t="s">
+      <c r="F40" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G40" s="3" t="s">
@@ -4689,7 +4692,7 @@
         <v>1980000</v>
       </c>
       <c r="J40" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K40" s="3">
         <v>0</v>
@@ -4721,14 +4724,14 @@
       <c r="T40" s="6">
         <v>48</v>
       </c>
-      <c r="U40" s="47">
-        <v>0</v>
-      </c>
-      <c r="V40" s="48" t="s">
+      <c r="U40" s="46">
+        <v>0</v>
+      </c>
+      <c r="V40" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="W40" s="49" t="s">
-        <v>88</v>
+      <c r="W40" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="X40" s="2">
         <v>0</v>
@@ -4750,7 +4753,7 @@
       <c r="E41" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F41" s="52" t="s">
+      <c r="F41" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -4763,7 +4766,7 @@
         <v>1980000</v>
       </c>
       <c r="J41" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
@@ -4795,14 +4798,14 @@
       <c r="T41" s="6">
         <v>50</v>
       </c>
-      <c r="U41" s="47">
-        <v>0</v>
-      </c>
-      <c r="V41" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="W41" s="49" t="s">
-        <v>84</v>
+      <c r="U41" s="46">
+        <v>0</v>
+      </c>
+      <c r="V41" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="W41" s="48" t="s">
+        <v>86</v>
       </c>
       <c r="X41" s="2">
         <v>0</v>
@@ -4824,7 +4827,7 @@
       <c r="E42" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F42" s="52" t="s">
+      <c r="F42" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G42" s="3" t="s">
@@ -4837,7 +4840,7 @@
         <v>1980000</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -4869,14 +4872,14 @@
       <c r="T42" s="6">
         <v>50</v>
       </c>
-      <c r="U42" s="47">
-        <v>0</v>
-      </c>
-      <c r="V42" s="48" t="s">
+      <c r="U42" s="46">
+        <v>0</v>
+      </c>
+      <c r="V42" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="W42" s="49" t="s">
-        <v>86</v>
+      <c r="W42" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="X42" s="2">
         <v>0</v>
@@ -4898,7 +4901,7 @@
       <c r="E43" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="52" t="s">
+      <c r="F43" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G43" s="3" t="s">
@@ -4911,7 +4914,7 @@
         <v>1980000</v>
       </c>
       <c r="J43" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K43" s="40">
         <v>0</v>
@@ -4943,14 +4946,14 @@
       <c r="T43" s="6">
         <v>50</v>
       </c>
-      <c r="U43" s="47">
-        <v>0</v>
-      </c>
-      <c r="V43" s="48" t="s">
+      <c r="U43" s="46">
+        <v>0</v>
+      </c>
+      <c r="V43" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="W43" s="49" t="s">
-        <v>88</v>
+      <c r="W43" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="X43" s="2">
         <v>0</v>
@@ -4972,7 +4975,7 @@
       <c r="E44" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="52" t="s">
+      <c r="F44" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G44" s="3" t="s">
@@ -4985,7 +4988,7 @@
         <v>1980000</v>
       </c>
       <c r="J44" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K44" s="40">
         <v>0</v>
@@ -5017,14 +5020,14 @@
       <c r="T44" s="6">
         <v>50</v>
       </c>
-      <c r="U44" s="47">
-        <v>0</v>
-      </c>
-      <c r="V44" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="W44" s="49" t="s">
-        <v>84</v>
+      <c r="U44" s="46">
+        <v>0</v>
+      </c>
+      <c r="V44" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="W44" s="48" t="s">
+        <v>86</v>
       </c>
       <c r="X44" s="2">
         <v>0</v>
@@ -5046,7 +5049,7 @@
       <c r="E45" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="52" t="s">
+      <c r="F45" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G45" s="3" t="s">
@@ -5059,7 +5062,7 @@
         <v>1980000</v>
       </c>
       <c r="J45" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K45" s="40">
         <v>0</v>
@@ -5091,14 +5094,14 @@
       <c r="T45" s="6">
         <v>50</v>
       </c>
-      <c r="U45" s="47">
-        <v>0</v>
-      </c>
-      <c r="V45" s="48" t="s">
+      <c r="U45" s="46">
+        <v>0</v>
+      </c>
+      <c r="V45" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="W45" s="49" t="s">
-        <v>86</v>
+      <c r="W45" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="X45" s="2">
         <v>0</v>
@@ -5120,7 +5123,7 @@
       <c r="E46" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F46" s="52" t="s">
+      <c r="F46" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G46" s="3" t="s">
@@ -5133,7 +5136,7 @@
         <v>1980000</v>
       </c>
       <c r="J46" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K46" s="40">
         <v>0</v>
@@ -5165,14 +5168,14 @@
       <c r="T46" s="6">
         <v>50</v>
       </c>
-      <c r="U46" s="47">
-        <v>0</v>
-      </c>
-      <c r="V46" s="48" t="s">
+      <c r="U46" s="46">
+        <v>0</v>
+      </c>
+      <c r="V46" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="W46" s="49" t="s">
-        <v>88</v>
+      <c r="W46" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="X46" s="2">
         <v>0</v>
@@ -5194,7 +5197,7 @@
       <c r="E47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F47" s="52" t="s">
+      <c r="F47" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G47" s="3" t="s">
@@ -5207,7 +5210,7 @@
         <v>1980000</v>
       </c>
       <c r="J47" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K47" s="40">
         <v>1</v>
@@ -5242,11 +5245,11 @@
       <c r="U47" s="6">
         <v>0</v>
       </c>
-      <c r="V47" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="W47" s="49" t="s">
-        <v>84</v>
+      <c r="V47" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="W47" s="48" t="s">
+        <v>86</v>
       </c>
       <c r="X47" s="2">
         <v>0</v>
@@ -5268,7 +5271,7 @@
       <c r="E48" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F48" s="52" t="s">
+      <c r="F48" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G48" s="3" t="s">
@@ -5281,7 +5284,7 @@
         <v>1980000</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K48" s="40">
         <v>1</v>
@@ -5316,11 +5319,11 @@
       <c r="U48" s="6">
         <v>0</v>
       </c>
-      <c r="V48" s="48" t="s">
+      <c r="V48" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="W48" s="49" t="s">
-        <v>86</v>
+      <c r="W48" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="X48" s="2">
         <v>0</v>
@@ -5342,7 +5345,7 @@
       <c r="E49" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F49" s="52" t="s">
+      <c r="F49" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G49" s="3" t="s">
@@ -5355,7 +5358,7 @@
         <v>1980000</v>
       </c>
       <c r="J49" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K49" s="40">
         <v>1</v>
@@ -5390,11 +5393,11 @@
       <c r="U49" s="6">
         <v>0</v>
       </c>
-      <c r="V49" s="48" t="s">
+      <c r="V49" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="W49" s="49" t="s">
-        <v>88</v>
+      <c r="W49" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="X49" s="2">
         <v>0</v>
@@ -5416,7 +5419,7 @@
       <c r="E50" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F50" s="52" t="s">
+      <c r="F50" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G50" s="3" t="s">
@@ -5429,7 +5432,7 @@
         <v>1980000</v>
       </c>
       <c r="J50" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K50" s="40">
         <v>0</v>
@@ -5437,7 +5440,7 @@
       <c r="L50" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="M50" s="41" t="s">
+      <c r="M50" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N50" s="3">
@@ -5464,11 +5467,11 @@
       <c r="U50" s="6">
         <v>0</v>
       </c>
-      <c r="V50" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="W50" s="49" t="s">
-        <v>84</v>
+      <c r="V50" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="W50" s="48" t="s">
+        <v>86</v>
       </c>
       <c r="X50" s="2">
         <v>0</v>
@@ -5490,7 +5493,7 @@
       <c r="E51" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F51" s="52" t="s">
+      <c r="F51" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G51" s="3" t="s">
@@ -5503,7 +5506,7 @@
         <v>1980000</v>
       </c>
       <c r="J51" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K51" s="40">
         <v>0</v>
@@ -5511,7 +5514,7 @@
       <c r="L51" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="M51" s="41" t="s">
+      <c r="M51" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N51" s="3">
@@ -5538,11 +5541,11 @@
       <c r="U51" s="6">
         <v>0</v>
       </c>
-      <c r="V51" s="48" t="s">
+      <c r="V51" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="W51" s="49" t="s">
-        <v>86</v>
+      <c r="W51" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="X51" s="2">
         <v>0</v>
@@ -5564,7 +5567,7 @@
       <c r="E52" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F52" s="52" t="s">
+      <c r="F52" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G52" s="3" t="s">
@@ -5577,7 +5580,7 @@
         <v>1980000</v>
       </c>
       <c r="J52" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -5585,7 +5588,7 @@
       <c r="L52" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M52" s="4" t="s">
+      <c r="M52" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N52" s="3">
@@ -5612,11 +5615,11 @@
       <c r="U52" s="6">
         <v>0</v>
       </c>
-      <c r="V52" s="48" t="s">
+      <c r="V52" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="W52" s="49" t="s">
-        <v>88</v>
+      <c r="W52" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="X52" s="2">
         <v>0</v>
@@ -5638,7 +5641,7 @@
       <c r="E53" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F53" s="52" t="s">
+      <c r="F53" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G53" s="3" t="s">
@@ -5651,7 +5654,7 @@
         <v>1980000</v>
       </c>
       <c r="J53" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K53" s="3">
         <v>1</v>
@@ -5659,8 +5662,8 @@
       <c r="L53" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M53" s="4" t="s">
-        <v>74</v>
+      <c r="M53" s="36" t="s">
+        <v>76</v>
       </c>
       <c r="N53" s="3">
         <v>9700</v>
@@ -5686,11 +5689,11 @@
       <c r="U53" s="6">
         <v>1</v>
       </c>
-      <c r="V53" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="W53" s="49" t="s">
-        <v>84</v>
+      <c r="V53" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="W53" s="48" t="s">
+        <v>86</v>
       </c>
       <c r="X53" s="2">
         <v>0</v>
@@ -5712,7 +5715,7 @@
       <c r="E54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F54" s="52" t="s">
+      <c r="F54" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G54" s="3" t="s">
@@ -5725,7 +5728,7 @@
         <v>1980000</v>
       </c>
       <c r="J54" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K54" s="3">
         <v>1</v>
@@ -5733,8 +5736,8 @@
       <c r="L54" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M54" s="4" t="s">
-        <v>74</v>
+      <c r="M54" s="36" t="s">
+        <v>76</v>
       </c>
       <c r="N54" s="3">
         <v>9700</v>
@@ -5760,11 +5763,11 @@
       <c r="U54" s="6">
         <v>1</v>
       </c>
-      <c r="V54" s="48" t="s">
+      <c r="V54" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="W54" s="49" t="s">
-        <v>86</v>
+      <c r="W54" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="X54" s="2">
         <v>0</v>
@@ -5786,7 +5789,7 @@
       <c r="E55" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="52" t="s">
+      <c r="F55" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G55" s="3" t="s">
@@ -5799,7 +5802,7 @@
         <v>1980000</v>
       </c>
       <c r="J55" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K55" s="3">
         <v>1</v>
@@ -5807,8 +5810,8 @@
       <c r="L55" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M55" s="4" t="s">
-        <v>74</v>
+      <c r="M55" s="36" t="s">
+        <v>76</v>
       </c>
       <c r="N55" s="3">
         <v>9700</v>
@@ -5834,11 +5837,11 @@
       <c r="U55" s="6">
         <v>1</v>
       </c>
-      <c r="V55" s="48" t="s">
+      <c r="V55" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="W55" s="49" t="s">
-        <v>88</v>
+      <c r="W55" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="X55" s="2">
         <v>0</v>
@@ -5852,7 +5855,7 @@
         <v>200800</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D56" s="3">
         <v>200800001</v>
@@ -5860,7 +5863,7 @@
       <c r="E56" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F56" s="52" t="s">
+      <c r="F56" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G56" s="3" t="s">
@@ -5873,7 +5876,7 @@
         <v>1980000</v>
       </c>
       <c r="J56" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K56" s="3">
         <v>0</v>
@@ -5881,8 +5884,8 @@
       <c r="L56" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M56" s="4" t="s">
-        <v>74</v>
+      <c r="M56" s="36" t="s">
+        <v>78</v>
       </c>
       <c r="N56" s="3">
         <v>9700</v>
@@ -5908,11 +5911,11 @@
       <c r="U56" s="6">
         <v>0</v>
       </c>
-      <c r="V56" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="W56" s="49" t="s">
-        <v>84</v>
+      <c r="V56" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="W56" s="48" t="s">
+        <v>86</v>
       </c>
       <c r="X56" s="2">
         <v>0</v>
@@ -5926,7 +5929,7 @@
         <v>200800</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D57" s="3">
         <v>200800001</v>
@@ -5934,7 +5937,7 @@
       <c r="E57" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F57" s="52" t="s">
+      <c r="F57" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G57" s="3" t="s">
@@ -5947,7 +5950,7 @@
         <v>1980000</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5955,8 +5958,8 @@
       <c r="L57" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M57" s="4" t="s">
-        <v>74</v>
+      <c r="M57" s="36" t="s">
+        <v>78</v>
       </c>
       <c r="N57" s="3">
         <v>9700</v>
@@ -5982,11 +5985,11 @@
       <c r="U57" s="6">
         <v>0</v>
       </c>
-      <c r="V57" s="48" t="s">
+      <c r="V57" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="W57" s="49" t="s">
-        <v>86</v>
+      <c r="W57" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="X57" s="2">
         <v>0</v>
@@ -6000,7 +6003,7 @@
         <v>200800</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D58" s="3">
         <v>200800001</v>
@@ -6008,7 +6011,7 @@
       <c r="E58" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F58" s="52" t="s">
+      <c r="F58" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G58" s="3" t="s">
@@ -6021,7 +6024,7 @@
         <v>1980000</v>
       </c>
       <c r="J58" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -6029,8 +6032,8 @@
       <c r="L58" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M58" s="4" t="s">
-        <v>74</v>
+      <c r="M58" s="36" t="s">
+        <v>78</v>
       </c>
       <c r="N58" s="3">
         <v>9700</v>
@@ -6056,11 +6059,11 @@
       <c r="U58" s="6">
         <v>0</v>
       </c>
-      <c r="V58" s="48" t="s">
+      <c r="V58" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="W58" s="49" t="s">
-        <v>88</v>
+      <c r="W58" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="X58" s="2">
         <v>0</v>
@@ -6074,7 +6077,7 @@
         <v>200900</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D59" s="3">
         <v>200900001</v>
@@ -6082,7 +6085,7 @@
       <c r="E59" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F59" s="52" t="s">
+      <c r="F59" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G59" s="3" t="s">
@@ -6095,7 +6098,7 @@
         <v>1980000</v>
       </c>
       <c r="J59" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -6103,8 +6106,8 @@
       <c r="L59" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M59" s="4" t="s">
-        <v>74</v>
+      <c r="M59" s="36" t="s">
+        <v>78</v>
       </c>
       <c r="N59" s="3">
         <v>9700</v>
@@ -6130,11 +6133,11 @@
       <c r="U59" s="6">
         <v>0</v>
       </c>
-      <c r="V59" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="W59" s="49" t="s">
-        <v>84</v>
+      <c r="V59" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="W59" s="48" t="s">
+        <v>86</v>
       </c>
       <c r="X59" s="2">
         <v>0</v>
@@ -6148,7 +6151,7 @@
         <v>200900</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D60" s="3">
         <v>200900001</v>
@@ -6156,7 +6159,7 @@
       <c r="E60" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F60" s="52" t="s">
+      <c r="F60" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G60" s="3" t="s">
@@ -6169,7 +6172,7 @@
         <v>1980000</v>
       </c>
       <c r="J60" s="37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -6177,8 +6180,8 @@
       <c r="L60" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M60" s="4" t="s">
-        <v>74</v>
+      <c r="M60" s="36" t="s">
+        <v>78</v>
       </c>
       <c r="N60" s="3">
         <v>9700</v>
@@ -6204,11 +6207,11 @@
       <c r="U60" s="6">
         <v>0</v>
       </c>
-      <c r="V60" s="48" t="s">
+      <c r="V60" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="W60" s="49" t="s">
-        <v>86</v>
+      <c r="W60" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="X60" s="2">
         <v>0</v>
@@ -6222,7 +6225,7 @@
         <v>200900</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D61" s="3">
         <v>200900001</v>
@@ -6230,7 +6233,7 @@
       <c r="E61" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="51" t="s">
         <v>49</v>
       </c>
       <c r="G61" s="3" t="s">
@@ -6243,7 +6246,7 @@
         <v>1980000</v>
       </c>
       <c r="J61" s="35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -6251,8 +6254,8 @@
       <c r="L61" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M61" s="4" t="s">
-        <v>74</v>
+      <c r="M61" s="36" t="s">
+        <v>78</v>
       </c>
       <c r="N61" s="3">
         <v>9700</v>
@@ -6278,11 +6281,11 @@
       <c r="U61" s="6">
         <v>0</v>
       </c>
-      <c r="V61" s="48" t="s">
+      <c r="V61" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="W61" s="49" t="s">
-        <v>88</v>
+      <c r="W61" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="X61" s="2">
         <v>0</v>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -518,25 +518,25 @@
     <t>直接</t>
   </si>
   <si>
+    <t>1000,16000,10000,0</t>
+  </si>
+  <si>
+    <t>飞禽走兽</t>
+  </si>
+  <si>
+    <t>0,16000,13000,0</t>
+  </si>
+  <si>
+    <t>豪车俱乐部</t>
+  </si>
+  <si>
+    <t>1000,16000,12000,0</t>
+  </si>
+  <si>
+    <t>百家乐</t>
+  </si>
+  <si>
     <t>2000,16000,10000,0</t>
-  </si>
-  <si>
-    <t>飞禽走兽</t>
-  </si>
-  <si>
-    <t>2000,16000,13000,0</t>
-  </si>
-  <si>
-    <t>豪车俱乐部</t>
-  </si>
-  <si>
-    <t>2000,16000,12000,0</t>
-  </si>
-  <si>
-    <t>百家乐</t>
-  </si>
-  <si>
-    <t>2000,16000,11000,0</t>
   </si>
   <si>
     <t>三个骰子</t>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -479,7 +479,7 @@
     <t>组合</t>
   </si>
   <si>
-    <t>3000,14000,11000,0</t>
+    <t>1000,16000,8000,0</t>
   </si>
   <si>
     <t>500000_17001</t>
@@ -518,13 +518,13 @@
     <t>直接</t>
   </si>
   <si>
-    <t>3000,14000,13000,0</t>
+    <t>2000,16000,10000,0</t>
   </si>
   <si>
     <t>飞禽走兽</t>
   </si>
   <si>
-    <t>2000,16000,17000,0</t>
+    <t>2000,16000,13000,0</t>
   </si>
   <si>
     <t>豪车俱乐部</t>
@@ -536,13 +536,13 @@
     <t>百家乐</t>
   </si>
   <si>
-    <t>2000,16000,14000,0</t>
+    <t>2000,16000,11000,0</t>
   </si>
   <si>
     <t>三个骰子</t>
   </si>
   <si>
-    <t>4000,14000,11000,0</t>
+    <t>4000,16000,11000,0</t>
   </si>
   <si>
     <t>色碟</t>
@@ -560,7 +560,7 @@
     <t>0:24:0</t>
   </si>
   <si>
-    <t>0,15000,10000,4000</t>
+    <t>0,16000,10000,4000</t>
   </si>
   <si>
     <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
@@ -1316,7 +1316,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1327,6 +1327,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1412,13 +1415,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1450,6 +1456,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1829,11 +1838,11 @@
     <col min="10" max="10" width="65" style="3" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="3" customWidth="1"/>
     <col min="12" max="12" width="5.125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="24.75" style="3" customWidth="1"/>
+    <col min="13" max="13" width="24.75" style="4" customWidth="1"/>
     <col min="14" max="15" width="16.3166666666667" style="3" customWidth="1"/>
     <col min="16" max="19" width="9.81666666666667" style="3" customWidth="1"/>
-    <col min="20" max="20" width="17.2166666666667" style="4" customWidth="1"/>
-    <col min="21" max="22" width="19.5" style="5" customWidth="1"/>
+    <col min="20" max="20" width="17.2166666666667" style="5" customWidth="1"/>
+    <col min="21" max="22" width="19.5" style="6" customWidth="1"/>
     <col min="23" max="23" width="19.125" style="2" customWidth="1"/>
     <col min="24" max="24" width="12.875" style="2" customWidth="1"/>
     <col min="25" max="25" width="20.125" style="2" customWidth="1"/>
@@ -1841,61 +1850,61 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:24">
-      <c r="A1" s="6"/>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="7"/>
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="26"/>
-      <c r="M1" s="27" t="s">
+      <c r="L1" s="27"/>
+      <c r="M1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="O1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="P1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="39" t="s">
+      <c r="Q1" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="40" t="s">
+      <c r="R1" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="V1" t="s">
@@ -1916,14 +1925,14 @@
         <v>21</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -1939,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="3"/>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="N2" s="3" t="s">
@@ -1960,19 +1969,19 @@
       <c r="S2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="42" t="s">
+      <c r="V2" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1984,14 +1993,14 @@
         <v>27</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
@@ -2007,7 +2016,7 @@
         <v>34</v>
       </c>
       <c r="L3" s="3"/>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>35</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -2028,10 +2037,10 @@
       <c r="S3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="5" t="s">
         <v>43</v>
       </c>
       <c r="V3" t="s">
@@ -2045,58 +2054,58 @@
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:22">
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="3">
         <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <v>200100</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="15">
         <v>200100038</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="14">
+      <c r="G5" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="15">
         <v>1</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="34">
         <v>1990000</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="35" t="s">
         <v>51</v>
       </c>
       <c r="K5" s="3">
@@ -2105,7 +2114,7 @@
       <c r="L5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="M5" s="36" t="s">
         <v>53</v>
       </c>
       <c r="N5" s="3">
@@ -2123,13 +2132,13 @@
       <c r="R5" s="3">
         <v>15000</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="46">
         <v>16008</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="5">
         <v>48</v>
       </c>
-      <c r="U5" s="44">
+      <c r="U5" s="47">
         <v>0</v>
       </c>
       <c r="V5" t="s">
@@ -2144,31 +2153,31 @@
         <f t="shared" si="0"/>
         <v>2001002</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="18">
         <v>200100</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <v>200100038</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="17">
+      <c r="G6" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="18">
         <v>2</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="34">
         <v>1990000</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="J6" s="37" t="s">
         <v>57</v>
       </c>
       <c r="K6" s="3">
@@ -2177,7 +2186,7 @@
       <c r="L6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="M6" s="36" t="s">
         <v>53</v>
       </c>
       <c r="N6" s="3">
@@ -2195,13 +2204,13 @@
       <c r="R6" s="3">
         <v>15000</v>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="46">
         <v>16008</v>
       </c>
-      <c r="T6" s="4">
+      <c r="T6" s="5">
         <v>48</v>
       </c>
-      <c r="U6" s="44">
+      <c r="U6" s="47">
         <v>0</v>
       </c>
       <c r="V6" t="s">
@@ -2216,31 +2225,31 @@
         <f t="shared" si="0"/>
         <v>2001003</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="15">
         <v>200100</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="15">
         <v>200100038</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="14">
+      <c r="G7" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="15">
         <v>3</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="34">
         <v>1990000</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="35" t="s">
         <v>61</v>
       </c>
       <c r="K7" s="3">
@@ -2249,7 +2258,7 @@
       <c r="L7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="34" t="s">
+      <c r="M7" s="36" t="s">
         <v>53</v>
       </c>
       <c r="N7" s="3">
@@ -2267,13 +2276,13 @@
       <c r="R7" s="3">
         <v>15000</v>
       </c>
-      <c r="S7" s="43">
+      <c r="S7" s="46">
         <v>16008</v>
       </c>
-      <c r="T7" s="4">
+      <c r="T7" s="5">
         <v>48</v>
       </c>
-      <c r="U7" s="44">
+      <c r="U7" s="47">
         <v>0</v>
       </c>
       <c r="V7" t="s">
@@ -2288,31 +2297,31 @@
         <f t="shared" si="0"/>
         <v>2001011</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="15">
         <v>200101</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <v>200101001</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="14">
+      <c r="G8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="15">
         <v>1</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="34">
         <v>1990000</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="35" t="s">
         <v>51</v>
       </c>
       <c r="K8" s="3">
@@ -2321,7 +2330,7 @@
       <c r="L8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="M8" s="36" t="s">
         <v>66</v>
       </c>
       <c r="N8" s="3">
@@ -2339,13 +2348,13 @@
       <c r="R8" s="3">
         <v>15000</v>
       </c>
-      <c r="S8" s="43">
+      <c r="S8" s="46">
         <v>16008</v>
       </c>
-      <c r="T8" s="4">
+      <c r="T8" s="5">
         <v>48</v>
       </c>
-      <c r="U8" s="44">
+      <c r="U8" s="47">
         <v>0</v>
       </c>
       <c r="V8" t="s">
@@ -2360,31 +2369,31 @@
         <f t="shared" si="0"/>
         <v>2001012</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="18">
         <v>200101</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <v>200101001</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="17">
+      <c r="G9" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="18">
         <v>2</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="34">
         <v>1990000</v>
       </c>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="37" t="s">
         <v>57</v>
       </c>
       <c r="K9" s="3">
@@ -2393,7 +2402,7 @@
       <c r="L9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="34" t="s">
+      <c r="M9" s="36" t="s">
         <v>66</v>
       </c>
       <c r="N9" s="3">
@@ -2411,13 +2420,13 @@
       <c r="R9" s="3">
         <v>15000</v>
       </c>
-      <c r="S9" s="43">
+      <c r="S9" s="46">
         <v>16008</v>
       </c>
-      <c r="T9" s="4">
+      <c r="T9" s="5">
         <v>48</v>
       </c>
-      <c r="U9" s="44">
+      <c r="U9" s="47">
         <v>0</v>
       </c>
       <c r="V9" t="s">
@@ -2432,31 +2441,31 @@
         <f t="shared" si="0"/>
         <v>2001013</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="15">
         <v>200101</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <v>200101001</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="47" t="s">
+      <c r="F10" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="14">
+      <c r="G10" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="15">
         <v>3</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="34">
         <v>1990000</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="J10" s="35" t="s">
         <v>61</v>
       </c>
       <c r="K10" s="3">
@@ -2465,7 +2474,7 @@
       <c r="L10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="34" t="s">
+      <c r="M10" s="36" t="s">
         <v>66</v>
       </c>
       <c r="N10" s="3">
@@ -2483,13 +2492,13 @@
       <c r="R10" s="3">
         <v>15000</v>
       </c>
-      <c r="S10" s="43">
+      <c r="S10" s="46">
         <v>16008</v>
       </c>
-      <c r="T10" s="4">
+      <c r="T10" s="5">
         <v>48</v>
       </c>
-      <c r="U10" s="44">
+      <c r="U10" s="47">
         <v>0</v>
       </c>
       <c r="V10" t="s">
@@ -2504,31 +2513,31 @@
         <f t="shared" si="0"/>
         <v>2003001</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="15">
         <v>200300</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="15">
         <v>200300001</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="14">
+      <c r="G11" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="15">
         <v>1</v>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="34">
         <v>1990000</v>
       </c>
-      <c r="J11" s="33" t="s">
+      <c r="J11" s="35" t="s">
         <v>51</v>
       </c>
       <c r="K11" s="3">
@@ -2537,7 +2546,7 @@
       <c r="L11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M11" s="34" t="s">
+      <c r="M11" s="36" t="s">
         <v>68</v>
       </c>
       <c r="N11" s="3">
@@ -2555,13 +2564,13 @@
       <c r="R11" s="3">
         <v>15000</v>
       </c>
-      <c r="S11" s="43">
+      <c r="S11" s="46">
         <v>16008</v>
       </c>
-      <c r="T11" s="4">
-        <v>50</v>
-      </c>
-      <c r="U11" s="44">
+      <c r="T11" s="5">
+        <v>50</v>
+      </c>
+      <c r="U11" s="47">
         <v>0</v>
       </c>
       <c r="V11" t="s">
@@ -2576,31 +2585,31 @@
         <f t="shared" si="0"/>
         <v>2003002</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="18">
         <v>200300</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <v>200300001</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="17">
+      <c r="G12" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="18">
         <v>2</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="34">
         <v>1990000</v>
       </c>
-      <c r="J12" s="35" t="s">
+      <c r="J12" s="37" t="s">
         <v>57</v>
       </c>
       <c r="K12" s="3">
@@ -2609,7 +2618,7 @@
       <c r="L12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M12" s="34" t="s">
+      <c r="M12" s="36" t="s">
         <v>68</v>
       </c>
       <c r="N12" s="3">
@@ -2627,13 +2636,13 @@
       <c r="R12" s="3">
         <v>15000</v>
       </c>
-      <c r="S12" s="43">
+      <c r="S12" s="46">
         <v>16008</v>
       </c>
-      <c r="T12" s="4">
-        <v>50</v>
-      </c>
-      <c r="U12" s="44">
+      <c r="T12" s="5">
+        <v>50</v>
+      </c>
+      <c r="U12" s="47">
         <v>0</v>
       </c>
       <c r="V12" t="s">
@@ -2648,31 +2657,31 @@
         <f t="shared" si="0"/>
         <v>2003003</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="15">
         <v>200300</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="15">
         <v>200300001</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="47" t="s">
+      <c r="F13" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="14">
+      <c r="G13" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="15">
         <v>3</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="34">
         <v>1990000</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="J13" s="35" t="s">
         <v>61</v>
       </c>
       <c r="K13" s="3">
@@ -2681,7 +2690,7 @@
       <c r="L13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M13" s="34" t="s">
+      <c r="M13" s="36" t="s">
         <v>68</v>
       </c>
       <c r="N13" s="3">
@@ -2699,13 +2708,13 @@
       <c r="R13" s="3">
         <v>15000</v>
       </c>
-      <c r="S13" s="43">
+      <c r="S13" s="46">
         <v>16008</v>
       </c>
-      <c r="T13" s="4">
-        <v>50</v>
-      </c>
-      <c r="U13" s="44">
+      <c r="T13" s="5">
+        <v>50</v>
+      </c>
+      <c r="U13" s="47">
         <v>0</v>
       </c>
       <c r="V13" t="s">
@@ -2720,31 +2729,31 @@
         <f t="shared" si="0"/>
         <v>2004001</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="15">
         <v>200400</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="15">
         <v>200400009</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="14">
+      <c r="G14" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="15">
         <v>1</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="34">
         <v>1990000</v>
       </c>
-      <c r="J14" s="33" t="s">
+      <c r="J14" s="35" t="s">
         <v>51</v>
       </c>
       <c r="K14" s="3">
@@ -2753,7 +2762,7 @@
       <c r="L14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="34" t="s">
+      <c r="M14" s="36" t="s">
         <v>70</v>
       </c>
       <c r="N14" s="3">
@@ -2771,13 +2780,13 @@
       <c r="R14" s="3">
         <v>15000</v>
       </c>
-      <c r="S14" s="43">
+      <c r="S14" s="46">
         <v>16008</v>
       </c>
-      <c r="T14" s="4">
-        <v>50</v>
-      </c>
-      <c r="U14" s="44">
+      <c r="T14" s="5">
+        <v>50</v>
+      </c>
+      <c r="U14" s="47">
         <v>0</v>
       </c>
       <c r="V14" t="s">
@@ -2792,31 +2801,31 @@
         <f t="shared" si="0"/>
         <v>2004002</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="18">
         <v>200400</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="18">
         <v>200400009</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="47" t="s">
+      <c r="F15" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="17">
+      <c r="G15" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="18">
         <v>2</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="34">
         <v>1990000</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J15" s="37" t="s">
         <v>57</v>
       </c>
       <c r="K15" s="3">
@@ -2825,7 +2834,7 @@
       <c r="L15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M15" s="34" t="s">
+      <c r="M15" s="36" t="s">
         <v>70</v>
       </c>
       <c r="N15" s="3">
@@ -2843,13 +2852,13 @@
       <c r="R15" s="3">
         <v>15000</v>
       </c>
-      <c r="S15" s="43">
+      <c r="S15" s="46">
         <v>16008</v>
       </c>
-      <c r="T15" s="4">
-        <v>50</v>
-      </c>
-      <c r="U15" s="44">
+      <c r="T15" s="5">
+        <v>50</v>
+      </c>
+      <c r="U15" s="47">
         <v>0</v>
       </c>
       <c r="V15" t="s">
@@ -2864,31 +2873,31 @@
         <f t="shared" si="0"/>
         <v>2004003</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <v>200400</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="15">
         <v>200400009</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="14">
+      <c r="G16" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="15">
         <v>3</v>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="34">
         <v>1990000</v>
       </c>
-      <c r="J16" s="33" t="s">
+      <c r="J16" s="35" t="s">
         <v>61</v>
       </c>
       <c r="K16" s="3">
@@ -2897,7 +2906,7 @@
       <c r="L16" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M16" s="34" t="s">
+      <c r="M16" s="36" t="s">
         <v>70</v>
       </c>
       <c r="N16" s="3">
@@ -2915,13 +2924,13 @@
       <c r="R16" s="3">
         <v>15000</v>
       </c>
-      <c r="S16" s="43">
+      <c r="S16" s="46">
         <v>16008</v>
       </c>
-      <c r="T16" s="4">
-        <v>50</v>
-      </c>
-      <c r="U16" s="44">
+      <c r="T16" s="5">
+        <v>50</v>
+      </c>
+      <c r="U16" s="47">
         <v>0</v>
       </c>
       <c r="V16" t="s">
@@ -2936,31 +2945,31 @@
         <f t="shared" si="0"/>
         <v>2005001</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="15">
         <v>200500</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="15">
         <v>200500025</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="47" t="s">
+      <c r="F17" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="14">
+      <c r="G17" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="15">
         <v>1</v>
       </c>
-      <c r="I17" s="32">
+      <c r="I17" s="34">
         <v>1990000</v>
       </c>
-      <c r="J17" s="33" t="s">
+      <c r="J17" s="35" t="s">
         <v>51</v>
       </c>
       <c r="K17" s="3">
@@ -2969,7 +2978,7 @@
       <c r="L17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M17" s="34" t="s">
+      <c r="M17" s="36" t="s">
         <v>72</v>
       </c>
       <c r="N17" s="3">
@@ -2987,13 +2996,13 @@
       <c r="R17" s="3">
         <v>15000</v>
       </c>
-      <c r="S17" s="43">
+      <c r="S17" s="46">
         <v>16008</v>
       </c>
-      <c r="T17" s="4">
+      <c r="T17" s="5">
         <v>48</v>
       </c>
-      <c r="U17" s="44">
+      <c r="U17" s="47">
         <v>0</v>
       </c>
       <c r="V17" t="s">
@@ -3011,31 +3020,31 @@
         <f t="shared" si="0"/>
         <v>2005002</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="18">
         <v>200500</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="18">
         <v>200500025</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="17">
+      <c r="G18" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="18">
         <v>2</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="34">
         <v>1990000</v>
       </c>
-      <c r="J18" s="35" t="s">
+      <c r="J18" s="37" t="s">
         <v>57</v>
       </c>
       <c r="K18" s="3">
@@ -3044,7 +3053,7 @@
       <c r="L18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M18" s="34" t="s">
+      <c r="M18" s="36" t="s">
         <v>72</v>
       </c>
       <c r="N18" s="3">
@@ -3062,13 +3071,13 @@
       <c r="R18" s="3">
         <v>15000</v>
       </c>
-      <c r="S18" s="43">
+      <c r="S18" s="46">
         <v>16008</v>
       </c>
-      <c r="T18" s="4">
+      <c r="T18" s="5">
         <v>48</v>
       </c>
-      <c r="U18" s="44">
+      <c r="U18" s="47">
         <v>0</v>
       </c>
       <c r="V18" t="s">
@@ -3086,31 +3095,31 @@
         <f t="shared" si="0"/>
         <v>2005003</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="15">
         <v>200500</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="15">
         <v>200500025</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="47" t="s">
+      <c r="F19" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="14">
+      <c r="G19" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="15">
         <v>3</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="34">
         <v>1990000</v>
       </c>
-      <c r="J19" s="33" t="s">
+      <c r="J19" s="35" t="s">
         <v>61</v>
       </c>
       <c r="K19" s="3">
@@ -3119,7 +3128,7 @@
       <c r="L19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M19" s="34" t="s">
+      <c r="M19" s="36" t="s">
         <v>72</v>
       </c>
       <c r="N19" s="3">
@@ -3137,13 +3146,13 @@
       <c r="R19" s="3">
         <v>15000</v>
       </c>
-      <c r="S19" s="43">
+      <c r="S19" s="46">
         <v>16008</v>
       </c>
-      <c r="T19" s="4">
+      <c r="T19" s="5">
         <v>48</v>
       </c>
-      <c r="U19" s="44">
+      <c r="U19" s="47">
         <v>0</v>
       </c>
       <c r="V19" t="s">
@@ -3161,31 +3170,31 @@
         <f t="shared" si="0"/>
         <v>2006001</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="15">
         <v>200600</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="15">
         <v>200600001</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G20" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="14">
+      <c r="G20" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" s="15">
         <v>1</v>
       </c>
-      <c r="I20" s="32">
+      <c r="I20" s="34">
         <v>1990000</v>
       </c>
-      <c r="J20" s="33" t="s">
+      <c r="J20" s="35" t="s">
         <v>51</v>
       </c>
       <c r="K20" s="3">
@@ -3194,7 +3203,7 @@
       <c r="L20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M20" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N20" s="3">
@@ -3212,13 +3221,13 @@
       <c r="R20" s="3">
         <v>15000</v>
       </c>
-      <c r="S20" s="43">
+      <c r="S20" s="46">
         <v>16008</v>
       </c>
-      <c r="T20" s="4">
+      <c r="T20" s="5">
         <v>20</v>
       </c>
-      <c r="U20" s="44">
+      <c r="U20" s="47">
         <v>0</v>
       </c>
       <c r="V20" t="s">
@@ -3236,31 +3245,31 @@
         <f t="shared" si="0"/>
         <v>2006002</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="18">
         <v>200600</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <v>200600001</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G21" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="17">
+      <c r="G21" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="18">
         <v>2</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="34">
         <v>1990000</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="37" t="s">
         <v>57</v>
       </c>
       <c r="K21" s="3">
@@ -3269,7 +3278,7 @@
       <c r="L21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M21" s="34" t="s">
+      <c r="M21" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N21" s="3">
@@ -3287,13 +3296,13 @@
       <c r="R21" s="3">
         <v>15000</v>
       </c>
-      <c r="S21" s="43">
+      <c r="S21" s="46">
         <v>16008</v>
       </c>
-      <c r="T21" s="4">
+      <c r="T21" s="5">
         <v>20</v>
       </c>
-      <c r="U21" s="44">
+      <c r="U21" s="47">
         <v>0</v>
       </c>
       <c r="V21" t="s">
@@ -3311,31 +3320,31 @@
         <f t="shared" si="0"/>
         <v>2006003</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="15">
         <v>200600</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="15">
         <v>200600001</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F22" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G22" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H22" s="14">
+      <c r="G22" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="15">
         <v>3</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="34">
         <v>1990000</v>
       </c>
-      <c r="J22" s="33" t="s">
+      <c r="J22" s="35" t="s">
         <v>61</v>
       </c>
       <c r="K22" s="3">
@@ -3344,7 +3353,7 @@
       <c r="L22" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M22" s="34" t="s">
+      <c r="M22" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N22" s="3">
@@ -3362,13 +3371,13 @@
       <c r="R22" s="3">
         <v>15000</v>
       </c>
-      <c r="S22" s="43">
+      <c r="S22" s="46">
         <v>16008</v>
       </c>
-      <c r="T22" s="4">
+      <c r="T22" s="5">
         <v>20</v>
       </c>
-      <c r="U22" s="44">
+      <c r="U22" s="47">
         <v>0</v>
       </c>
       <c r="V22" t="s">
@@ -3386,31 +3395,31 @@
         <f t="shared" si="0"/>
         <v>2007001</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="15">
         <v>200700</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="15">
         <v>200700001</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="47" t="s">
+      <c r="F23" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G23" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H23" s="14">
+      <c r="G23" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" s="15">
         <v>1</v>
       </c>
-      <c r="I23" s="32">
+      <c r="I23" s="34">
         <v>1990000</v>
       </c>
-      <c r="J23" s="33" t="s">
+      <c r="J23" s="35" t="s">
         <v>51</v>
       </c>
       <c r="K23" s="3">
@@ -3419,7 +3428,7 @@
       <c r="L23" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M23" s="34" t="s">
+      <c r="M23" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N23" s="3">
@@ -3437,13 +3446,13 @@
       <c r="R23" s="3">
         <v>15000</v>
       </c>
-      <c r="S23" s="43">
+      <c r="S23" s="46">
         <v>16008</v>
       </c>
-      <c r="T23" s="4">
+      <c r="T23" s="5">
         <v>30</v>
       </c>
-      <c r="U23" s="44">
+      <c r="U23" s="47">
         <v>1</v>
       </c>
       <c r="V23" t="s">
@@ -3461,31 +3470,31 @@
         <f t="shared" si="0"/>
         <v>2007002</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="18">
         <v>200700</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="18">
         <v>200700001</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H24" s="17">
+      <c r="G24" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="18">
         <v>2</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="34">
         <v>1990000</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="37" t="s">
         <v>57</v>
       </c>
       <c r="K24" s="3">
@@ -3494,7 +3503,7 @@
       <c r="L24" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M24" s="34" t="s">
+      <c r="M24" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N24" s="3">
@@ -3512,13 +3521,13 @@
       <c r="R24" s="3">
         <v>15000</v>
       </c>
-      <c r="S24" s="43">
+      <c r="S24" s="46">
         <v>16008</v>
       </c>
-      <c r="T24" s="4">
+      <c r="T24" s="5">
         <v>30</v>
       </c>
-      <c r="U24" s="44">
+      <c r="U24" s="47">
         <v>1</v>
       </c>
       <c r="V24" t="s">
@@ -3536,31 +3545,31 @@
         <f t="shared" si="0"/>
         <v>2007003</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="15">
         <v>200700</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="15">
         <v>200700001</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G25" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="14">
+      <c r="G25" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="15">
         <v>3</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="34">
         <v>1990000</v>
       </c>
-      <c r="J25" s="33" t="s">
+      <c r="J25" s="35" t="s">
         <v>61</v>
       </c>
       <c r="K25" s="3">
@@ -3569,7 +3578,7 @@
       <c r="L25" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M25" s="34" t="s">
+      <c r="M25" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N25" s="3">
@@ -3587,13 +3596,13 @@
       <c r="R25" s="3">
         <v>15000</v>
       </c>
-      <c r="S25" s="43">
+      <c r="S25" s="46">
         <v>16008</v>
       </c>
-      <c r="T25" s="4">
+      <c r="T25" s="5">
         <v>30</v>
       </c>
-      <c r="U25" s="44">
+      <c r="U25" s="47">
         <v>1</v>
       </c>
       <c r="V25" t="s">
@@ -3611,31 +3620,31 @@
         <f t="shared" si="0"/>
         <v>2008001</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="15">
         <v>200800</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="15">
         <v>200800001</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="14">
+      <c r="G26" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="15">
         <v>1</v>
       </c>
-      <c r="I26" s="32">
+      <c r="I26" s="34">
         <v>1990000</v>
       </c>
-      <c r="J26" s="33" t="s">
+      <c r="J26" s="35" t="s">
         <v>51</v>
       </c>
       <c r="K26" s="3">
@@ -3644,7 +3653,7 @@
       <c r="L26" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M26" s="34" t="s">
+      <c r="M26" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N26" s="3">
@@ -3662,13 +3671,13 @@
       <c r="R26" s="3">
         <v>15000</v>
       </c>
-      <c r="S26" s="43">
+      <c r="S26" s="46">
         <v>16008</v>
       </c>
-      <c r="T26" s="4">
+      <c r="T26" s="5">
         <v>20</v>
       </c>
-      <c r="U26" s="44">
+      <c r="U26" s="47">
         <v>0</v>
       </c>
       <c r="V26" t="s">
@@ -3686,31 +3695,31 @@
         <f t="shared" si="0"/>
         <v>2008002</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="15">
         <v>200800</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="15">
         <v>200800001</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H27" s="17">
+      <c r="G27" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" s="18">
         <v>2</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="34">
         <v>1990000</v>
       </c>
-      <c r="J27" s="35" t="s">
+      <c r="J27" s="37" t="s">
         <v>57</v>
       </c>
       <c r="K27" s="3">
@@ -3719,7 +3728,7 @@
       <c r="L27" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M27" s="34" t="s">
+      <c r="M27" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N27" s="3">
@@ -3737,13 +3746,13 @@
       <c r="R27" s="3">
         <v>15000</v>
       </c>
-      <c r="S27" s="43">
+      <c r="S27" s="46">
         <v>16008</v>
       </c>
-      <c r="T27" s="4">
+      <c r="T27" s="5">
         <v>20</v>
       </c>
-      <c r="U27" s="44">
+      <c r="U27" s="47">
         <v>0</v>
       </c>
       <c r="V27" t="s">
@@ -3761,31 +3770,31 @@
         <f t="shared" si="0"/>
         <v>2008003</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="15">
         <v>200800</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="15">
         <v>200800001</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G28" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H28" s="14">
+      <c r="G28" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="15">
         <v>3</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="34">
         <v>1990000</v>
       </c>
-      <c r="J28" s="33" t="s">
+      <c r="J28" s="35" t="s">
         <v>61</v>
       </c>
       <c r="K28" s="3">
@@ -3794,7 +3803,7 @@
       <c r="L28" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N28" s="3">
@@ -3812,13 +3821,13 @@
       <c r="R28" s="3">
         <v>15000</v>
       </c>
-      <c r="S28" s="43">
+      <c r="S28" s="46">
         <v>16008</v>
       </c>
-      <c r="T28" s="4">
+      <c r="T28" s="5">
         <v>20</v>
       </c>
-      <c r="U28" s="44">
+      <c r="U28" s="47">
         <v>0</v>
       </c>
       <c r="V28" t="s">
@@ -3836,40 +3845,40 @@
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="21">
         <v>200900</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="15">
         <v>200900001</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="47" t="s">
+      <c r="F29" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G29" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H29" s="14">
+      <c r="G29" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" s="15">
         <v>1</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="34">
         <v>1990000</v>
       </c>
-      <c r="J29" s="33" t="s">
+      <c r="J29" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="K29" s="36">
+      <c r="K29" s="38">
         <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M29" s="34" t="s">
+      <c r="M29" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N29" s="3">
@@ -3887,13 +3896,13 @@
       <c r="R29" s="3">
         <v>15000</v>
       </c>
-      <c r="S29" s="43">
+      <c r="S29" s="46">
         <v>16008</v>
       </c>
-      <c r="T29" s="4">
+      <c r="T29" s="5">
         <v>20</v>
       </c>
-      <c r="U29" s="44">
+      <c r="U29" s="47">
         <v>0</v>
       </c>
       <c r="V29" t="s">
@@ -3911,40 +3920,40 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="22">
         <v>200900</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="18">
         <v>200900001</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="47" t="s">
+      <c r="F30" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G30" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H30" s="17">
+      <c r="G30" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" s="18">
         <v>2</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="34">
         <v>1990000</v>
       </c>
-      <c r="J30" s="35" t="s">
+      <c r="J30" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="38">
         <v>0</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M30" s="34" t="s">
+      <c r="M30" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N30" s="3">
@@ -3962,13 +3971,13 @@
       <c r="R30" s="3">
         <v>15000</v>
       </c>
-      <c r="S30" s="43">
+      <c r="S30" s="46">
         <v>16008</v>
       </c>
-      <c r="T30" s="4">
+      <c r="T30" s="5">
         <v>20</v>
       </c>
-      <c r="U30" s="44">
+      <c r="U30" s="47">
         <v>0</v>
       </c>
       <c r="V30" t="s">
@@ -3986,40 +3995,40 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="23">
         <v>200900</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="24">
         <v>200900001</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="47" t="s">
+      <c r="F31" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G31" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H31" s="14">
+      <c r="G31" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" s="15">
         <v>3</v>
       </c>
-      <c r="I31" s="32">
+      <c r="I31" s="34">
         <v>1990000</v>
       </c>
-      <c r="J31" s="33" t="s">
+      <c r="J31" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="38">
         <v>0</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M31" s="34" t="s">
+      <c r="M31" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N31" s="3">
@@ -4037,13 +4046,13 @@
       <c r="R31" s="3">
         <v>15000</v>
       </c>
-      <c r="S31" s="43">
+      <c r="S31" s="46">
         <v>16008</v>
       </c>
-      <c r="T31" s="4">
+      <c r="T31" s="5">
         <v>20</v>
       </c>
-      <c r="U31" s="44">
+      <c r="U31" s="47">
         <v>0</v>
       </c>
       <c r="V31" t="s">
@@ -4061,7 +4070,7 @@
         <f t="shared" si="0"/>
         <v>2010001</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="25">
         <v>201000</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -4070,31 +4079,31 @@
       <c r="D32" s="3">
         <v>101000006</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F32" s="47" t="s">
+      <c r="F32" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="48" t="s">
+      <c r="G32" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="15">
         <v>1</v>
       </c>
-      <c r="I32" s="32">
+      <c r="I32" s="34">
         <v>1990000</v>
       </c>
-      <c r="J32" s="33" t="s">
+      <c r="J32" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="K32" s="36">
+      <c r="K32" s="38">
         <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M32" s="34" t="s">
+      <c r="M32" s="36" t="s">
         <v>80</v>
       </c>
       <c r="N32" s="3">
@@ -4112,13 +4121,13 @@
       <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="43">
+      <c r="S32" s="46">
         <v>16008</v>
       </c>
-      <c r="T32" s="4">
-        <v>50</v>
-      </c>
-      <c r="U32" s="44">
+      <c r="T32" s="5">
+        <v>50</v>
+      </c>
+      <c r="U32" s="47">
         <v>0</v>
       </c>
       <c r="V32" t="s">
@@ -4136,7 +4145,7 @@
         <f t="shared" si="0"/>
         <v>2010002</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="25">
         <v>201000</v>
       </c>
       <c r="C33" s="3" t="s">
@@ -4145,31 +4154,31 @@
       <c r="D33" s="3">
         <v>101000006</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="47" t="s">
+      <c r="F33" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G33" s="48" t="s">
+      <c r="G33" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="18">
         <v>2</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="34">
         <v>1990000</v>
       </c>
-      <c r="J33" s="35" t="s">
+      <c r="J33" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="38">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M33" s="34" t="s">
+      <c r="M33" s="36" t="s">
         <v>80</v>
       </c>
       <c r="N33" s="3">
@@ -4187,13 +4196,13 @@
       <c r="R33" s="3">
         <v>15000</v>
       </c>
-      <c r="S33" s="43">
+      <c r="S33" s="46">
         <v>16008</v>
       </c>
-      <c r="T33" s="4">
-        <v>50</v>
-      </c>
-      <c r="U33" s="44">
+      <c r="T33" s="5">
+        <v>50</v>
+      </c>
+      <c r="U33" s="47">
         <v>0</v>
       </c>
       <c r="V33" t="s">
@@ -4211,7 +4220,7 @@
         <f t="shared" si="0"/>
         <v>2010003</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="25">
         <v>201000</v>
       </c>
       <c r="C34" s="3" t="s">
@@ -4220,31 +4229,31 @@
       <c r="D34" s="3">
         <v>101000006</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="47" t="s">
+      <c r="F34" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G34" s="48" t="s">
+      <c r="G34" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="15">
         <v>3</v>
       </c>
-      <c r="I34" s="32">
+      <c r="I34" s="34">
         <v>1990000</v>
       </c>
-      <c r="J34" s="33" t="s">
+      <c r="J34" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="K34" s="36">
+      <c r="K34" s="38">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M34" s="34" t="s">
+      <c r="M34" s="36" t="s">
         <v>80</v>
       </c>
       <c r="N34" s="3">
@@ -4262,13 +4271,13 @@
       <c r="R34" s="3">
         <v>15000</v>
       </c>
-      <c r="S34" s="43">
+      <c r="S34" s="46">
         <v>16008</v>
       </c>
-      <c r="T34" s="4">
-        <v>50</v>
-      </c>
-      <c r="U34" s="44">
+      <c r="T34" s="5">
+        <v>50</v>
+      </c>
+      <c r="U34" s="47">
         <v>0</v>
       </c>
       <c r="V34" t="s">
@@ -4282,34 +4291,34 @@
       </c>
     </row>
     <row r="35" spans="1:24">
-      <c r="A35" s="4">
+      <c r="A35" s="5">
         <v>20010010</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="26">
         <v>200100</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="15">
         <v>200100038</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="47" t="s">
+      <c r="F35" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G35" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="15">
         <v>1</v>
       </c>
-      <c r="I35" s="37">
+      <c r="I35" s="39">
         <v>1980000</v>
       </c>
-      <c r="J35" s="33" t="s">
+      <c r="J35" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K35" s="3">
@@ -4318,7 +4327,7 @@
       <c r="L35" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M35" s="34" t="s">
+      <c r="M35" s="36" t="s">
         <v>53</v>
       </c>
       <c r="N35" s="3">
@@ -4336,19 +4345,19 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="43">
+      <c r="S35" s="46">
         <v>16008</v>
       </c>
-      <c r="T35" s="4">
+      <c r="T35" s="5">
         <v>48</v>
       </c>
-      <c r="U35" s="44">
-        <v>0</v>
-      </c>
-      <c r="V35" s="45" t="s">
+      <c r="U35" s="47">
+        <v>0</v>
+      </c>
+      <c r="V35" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="W35" s="46" t="s">
+      <c r="W35" s="49" t="s">
         <v>84</v>
       </c>
       <c r="X35" s="2">
@@ -4356,34 +4365,34 @@
       </c>
     </row>
     <row r="36" spans="1:24">
-      <c r="A36" s="4">
+      <c r="A36" s="5">
         <v>20010011</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="26">
         <v>200100</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="18">
         <v>200100038</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="47" t="s">
+      <c r="F36" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="18">
         <v>2</v>
       </c>
-      <c r="I36" s="37">
+      <c r="I36" s="39">
         <v>1980000</v>
       </c>
-      <c r="J36" s="35" t="s">
+      <c r="J36" s="37" t="s">
         <v>85</v>
       </c>
       <c r="K36" s="3">
@@ -4392,7 +4401,7 @@
       <c r="L36" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M36" s="34" t="s">
+      <c r="M36" s="36" t="s">
         <v>53</v>
       </c>
       <c r="N36" s="3">
@@ -4410,19 +4419,19 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="43">
+      <c r="S36" s="46">
         <v>16008</v>
       </c>
-      <c r="T36" s="4">
+      <c r="T36" s="5">
         <v>48</v>
       </c>
-      <c r="U36" s="44">
-        <v>0</v>
-      </c>
-      <c r="V36" s="45" t="s">
+      <c r="U36" s="47">
+        <v>0</v>
+      </c>
+      <c r="V36" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="W36" s="46" t="s">
+      <c r="W36" s="49" t="s">
         <v>86</v>
       </c>
       <c r="X36" s="2">
@@ -4430,34 +4439,34 @@
       </c>
     </row>
     <row r="37" spans="1:24">
-      <c r="A37" s="4">
+      <c r="A37" s="5">
         <v>20010012</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="26">
         <v>200100</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="15">
         <v>200100038</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="47" t="s">
+      <c r="F37" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="G37" s="16" t="s">
+      <c r="G37" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H37" s="15">
         <v>3</v>
       </c>
-      <c r="I37" s="37">
+      <c r="I37" s="39">
         <v>1980000</v>
       </c>
-      <c r="J37" s="33" t="s">
+      <c r="J37" s="35" t="s">
         <v>87</v>
       </c>
       <c r="K37" s="3">
@@ -4466,7 +4475,7 @@
       <c r="L37" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M37" s="34" t="s">
+      <c r="M37" s="36" t="s">
         <v>53</v>
       </c>
       <c r="N37" s="3">
@@ -4484,19 +4493,19 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="43">
+      <c r="S37" s="46">
         <v>16008</v>
       </c>
-      <c r="T37" s="4">
+      <c r="T37" s="5">
         <v>48</v>
       </c>
-      <c r="U37" s="44">
-        <v>0</v>
-      </c>
-      <c r="V37" s="45" t="s">
+      <c r="U37" s="47">
+        <v>0</v>
+      </c>
+      <c r="V37" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="W37" s="46" t="s">
+      <c r="W37" s="49" t="s">
         <v>88</v>
       </c>
       <c r="X37" s="2">
@@ -4504,10 +4513,10 @@
       </c>
     </row>
     <row r="38" spans="1:24">
-      <c r="A38" s="4">
+      <c r="A38" s="5">
         <v>20010110</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B38" s="26">
         <v>200101</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -4519,7 +4528,7 @@
       <c r="E38" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F38" s="49" t="s">
+      <c r="F38" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G38" s="3" t="s">
@@ -4528,10 +4537,10 @@
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="37">
+      <c r="I38" s="39">
         <v>1980000</v>
       </c>
-      <c r="J38" s="33" t="s">
+      <c r="J38" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K38" s="3">
@@ -4540,7 +4549,7 @@
       <c r="L38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="M38" s="36" t="s">
         <v>66</v>
       </c>
       <c r="N38" s="3">
@@ -4561,16 +4570,16 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="5">
+      <c r="T38" s="6">
         <v>48</v>
       </c>
-      <c r="U38" s="44">
-        <v>0</v>
-      </c>
-      <c r="V38" s="45" t="s">
+      <c r="U38" s="47">
+        <v>0</v>
+      </c>
+      <c r="V38" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="W38" s="46" t="s">
+      <c r="W38" s="49" t="s">
         <v>84</v>
       </c>
       <c r="X38" s="2">
@@ -4578,10 +4587,10 @@
       </c>
     </row>
     <row r="39" spans="1:24">
-      <c r="A39" s="4">
+      <c r="A39" s="5">
         <v>20010111</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="26">
         <v>200101</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -4593,7 +4602,7 @@
       <c r="E39" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F39" s="49" t="s">
+      <c r="F39" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G39" s="3" t="s">
@@ -4602,10 +4611,10 @@
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="37">
+      <c r="I39" s="39">
         <v>1980000</v>
       </c>
-      <c r="J39" s="35" t="s">
+      <c r="J39" s="37" t="s">
         <v>85</v>
       </c>
       <c r="K39" s="3">
@@ -4614,7 +4623,7 @@
       <c r="L39" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M39" s="3" t="s">
+      <c r="M39" s="36" t="s">
         <v>66</v>
       </c>
       <c r="N39" s="3">
@@ -4635,16 +4644,16 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="5">
+      <c r="T39" s="6">
         <v>48</v>
       </c>
-      <c r="U39" s="44">
-        <v>0</v>
-      </c>
-      <c r="V39" s="45" t="s">
+      <c r="U39" s="47">
+        <v>0</v>
+      </c>
+      <c r="V39" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="W39" s="46" t="s">
+      <c r="W39" s="49" t="s">
         <v>86</v>
       </c>
       <c r="X39" s="2">
@@ -4652,10 +4661,10 @@
       </c>
     </row>
     <row r="40" spans="1:24">
-      <c r="A40" s="4">
+      <c r="A40" s="5">
         <v>20010112</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="26">
         <v>200101</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -4667,7 +4676,7 @@
       <c r="E40" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F40" s="49" t="s">
+      <c r="F40" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G40" s="3" t="s">
@@ -4676,10 +4685,10 @@
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="37">
+      <c r="I40" s="39">
         <v>1980000</v>
       </c>
-      <c r="J40" s="33" t="s">
+      <c r="J40" s="35" t="s">
         <v>87</v>
       </c>
       <c r="K40" s="3">
@@ -4688,7 +4697,7 @@
       <c r="L40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M40" s="3" t="s">
+      <c r="M40" s="36" t="s">
         <v>66</v>
       </c>
       <c r="N40" s="3">
@@ -4709,16 +4718,16 @@
       <c r="S40" s="3">
         <v>16008</v>
       </c>
-      <c r="T40" s="5">
+      <c r="T40" s="6">
         <v>48</v>
       </c>
-      <c r="U40" s="44">
-        <v>0</v>
-      </c>
-      <c r="V40" s="45" t="s">
+      <c r="U40" s="47">
+        <v>0</v>
+      </c>
+      <c r="V40" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="W40" s="46" t="s">
+      <c r="W40" s="49" t="s">
         <v>88</v>
       </c>
       <c r="X40" s="2">
@@ -4726,10 +4735,10 @@
       </c>
     </row>
     <row r="41" spans="1:24">
-      <c r="A41" s="4">
+      <c r="A41" s="5">
         <v>20030010</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="26">
         <v>200300</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -4741,7 +4750,7 @@
       <c r="E41" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F41" s="49" t="s">
+      <c r="F41" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -4750,10 +4759,10 @@
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="37">
+      <c r="I41" s="39">
         <v>1980000</v>
       </c>
-      <c r="J41" s="33" t="s">
+      <c r="J41" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K41" s="3">
@@ -4762,7 +4771,7 @@
       <c r="L41" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M41" s="3" t="s">
+      <c r="M41" s="36" t="s">
         <v>68</v>
       </c>
       <c r="N41" s="3">
@@ -4783,16 +4792,16 @@
       <c r="S41" s="3">
         <v>16008</v>
       </c>
-      <c r="T41" s="5">
-        <v>50</v>
-      </c>
-      <c r="U41" s="44">
-        <v>0</v>
-      </c>
-      <c r="V41" s="45" t="s">
+      <c r="T41" s="6">
+        <v>50</v>
+      </c>
+      <c r="U41" s="47">
+        <v>0</v>
+      </c>
+      <c r="V41" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="W41" s="46" t="s">
+      <c r="W41" s="49" t="s">
         <v>84</v>
       </c>
       <c r="X41" s="2">
@@ -4800,10 +4809,10 @@
       </c>
     </row>
     <row r="42" spans="1:24">
-      <c r="A42" s="4">
+      <c r="A42" s="5">
         <v>20030011</v>
       </c>
-      <c r="B42" s="25">
+      <c r="B42" s="26">
         <v>200300</v>
       </c>
       <c r="C42" s="3" t="s">
@@ -4815,7 +4824,7 @@
       <c r="E42" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F42" s="49" t="s">
+      <c r="F42" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G42" s="3" t="s">
@@ -4824,10 +4833,10 @@
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="37">
+      <c r="I42" s="39">
         <v>1980000</v>
       </c>
-      <c r="J42" s="35" t="s">
+      <c r="J42" s="37" t="s">
         <v>85</v>
       </c>
       <c r="K42" s="3">
@@ -4836,7 +4845,7 @@
       <c r="L42" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M42" s="3" t="s">
+      <c r="M42" s="36" t="s">
         <v>68</v>
       </c>
       <c r="N42" s="3">
@@ -4857,16 +4866,16 @@
       <c r="S42" s="3">
         <v>16008</v>
       </c>
-      <c r="T42" s="5">
-        <v>50</v>
-      </c>
-      <c r="U42" s="44">
-        <v>0</v>
-      </c>
-      <c r="V42" s="45" t="s">
+      <c r="T42" s="6">
+        <v>50</v>
+      </c>
+      <c r="U42" s="47">
+        <v>0</v>
+      </c>
+      <c r="V42" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="W42" s="46" t="s">
+      <c r="W42" s="49" t="s">
         <v>86</v>
       </c>
       <c r="X42" s="2">
@@ -4874,10 +4883,10 @@
       </c>
     </row>
     <row r="43" spans="1:24">
-      <c r="A43" s="4">
+      <c r="A43" s="5">
         <v>20030012</v>
       </c>
-      <c r="B43" s="25">
+      <c r="B43" s="26">
         <v>200300</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -4889,7 +4898,7 @@
       <c r="E43" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="49" t="s">
+      <c r="F43" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G43" s="3" t="s">
@@ -4898,19 +4907,19 @@
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="37">
+      <c r="I43" s="39">
         <v>1980000</v>
       </c>
-      <c r="J43" s="33" t="s">
+      <c r="J43" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="K43" s="38">
-        <v>0</v>
-      </c>
-      <c r="L43" s="38" t="s">
+      <c r="K43" s="40">
+        <v>0</v>
+      </c>
+      <c r="L43" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="M43" s="38" t="s">
+      <c r="M43" s="36" t="s">
         <v>68</v>
       </c>
       <c r="N43" s="3">
@@ -4919,28 +4928,28 @@
       <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="38">
+      <c r="P43" s="40">
         <v>180000</v>
       </c>
-      <c r="Q43" s="38">
+      <c r="Q43" s="40">
         <v>16000</v>
       </c>
-      <c r="R43" s="38">
+      <c r="R43" s="40">
         <v>15000</v>
       </c>
-      <c r="S43" s="38">
+      <c r="S43" s="40">
         <v>16008</v>
       </c>
-      <c r="T43" s="5">
-        <v>50</v>
-      </c>
-      <c r="U43" s="44">
-        <v>0</v>
-      </c>
-      <c r="V43" s="45" t="s">
+      <c r="T43" s="6">
+        <v>50</v>
+      </c>
+      <c r="U43" s="47">
+        <v>0</v>
+      </c>
+      <c r="V43" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="W43" s="46" t="s">
+      <c r="W43" s="49" t="s">
         <v>88</v>
       </c>
       <c r="X43" s="2">
@@ -4948,10 +4957,10 @@
       </c>
     </row>
     <row r="44" spans="1:24">
-      <c r="A44" s="4">
+      <c r="A44" s="5">
         <v>20040010</v>
       </c>
-      <c r="B44" s="25">
+      <c r="B44" s="26">
         <v>200400</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -4963,7 +4972,7 @@
       <c r="E44" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="49" t="s">
+      <c r="F44" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G44" s="3" t="s">
@@ -4972,19 +4981,19 @@
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="37">
+      <c r="I44" s="39">
         <v>1980000</v>
       </c>
-      <c r="J44" s="33" t="s">
+      <c r="J44" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K44" s="38">
-        <v>0</v>
-      </c>
-      <c r="L44" s="38" t="s">
+      <c r="K44" s="40">
+        <v>0</v>
+      </c>
+      <c r="L44" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="M44" s="38" t="s">
+      <c r="M44" s="36" t="s">
         <v>70</v>
       </c>
       <c r="N44" s="3">
@@ -4993,28 +5002,28 @@
       <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="38">
+      <c r="P44" s="40">
         <v>180000</v>
       </c>
-      <c r="Q44" s="38">
+      <c r="Q44" s="40">
         <v>16000</v>
       </c>
-      <c r="R44" s="38">
+      <c r="R44" s="40">
         <v>15000</v>
       </c>
-      <c r="S44" s="38">
+      <c r="S44" s="40">
         <v>16008</v>
       </c>
-      <c r="T44" s="5">
-        <v>50</v>
-      </c>
-      <c r="U44" s="44">
-        <v>0</v>
-      </c>
-      <c r="V44" s="45" t="s">
+      <c r="T44" s="6">
+        <v>50</v>
+      </c>
+      <c r="U44" s="47">
+        <v>0</v>
+      </c>
+      <c r="V44" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="W44" s="46" t="s">
+      <c r="W44" s="49" t="s">
         <v>84</v>
       </c>
       <c r="X44" s="2">
@@ -5022,10 +5031,10 @@
       </c>
     </row>
     <row r="45" spans="1:24">
-      <c r="A45" s="4">
+      <c r="A45" s="5">
         <v>20040011</v>
       </c>
-      <c r="B45" s="25">
+      <c r="B45" s="26">
         <v>200400</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -5037,7 +5046,7 @@
       <c r="E45" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="49" t="s">
+      <c r="F45" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G45" s="3" t="s">
@@ -5046,19 +5055,19 @@
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="37">
+      <c r="I45" s="39">
         <v>1980000</v>
       </c>
-      <c r="J45" s="35" t="s">
+      <c r="J45" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="K45" s="38">
-        <v>0</v>
-      </c>
-      <c r="L45" s="38" t="s">
+      <c r="K45" s="40">
+        <v>0</v>
+      </c>
+      <c r="L45" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="M45" s="38" t="s">
+      <c r="M45" s="36" t="s">
         <v>70</v>
       </c>
       <c r="N45" s="3">
@@ -5067,28 +5076,28 @@
       <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="38">
+      <c r="P45" s="40">
         <v>180000</v>
       </c>
-      <c r="Q45" s="38">
+      <c r="Q45" s="40">
         <v>16000</v>
       </c>
-      <c r="R45" s="38">
+      <c r="R45" s="40">
         <v>15000</v>
       </c>
-      <c r="S45" s="38">
+      <c r="S45" s="40">
         <v>16008</v>
       </c>
-      <c r="T45" s="5">
-        <v>50</v>
-      </c>
-      <c r="U45" s="44">
-        <v>0</v>
-      </c>
-      <c r="V45" s="45" t="s">
+      <c r="T45" s="6">
+        <v>50</v>
+      </c>
+      <c r="U45" s="47">
+        <v>0</v>
+      </c>
+      <c r="V45" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="W45" s="46" t="s">
+      <c r="W45" s="49" t="s">
         <v>86</v>
       </c>
       <c r="X45" s="2">
@@ -5096,10 +5105,10 @@
       </c>
     </row>
     <row r="46" spans="1:24">
-      <c r="A46" s="4">
+      <c r="A46" s="5">
         <v>20040012</v>
       </c>
-      <c r="B46" s="25">
+      <c r="B46" s="26">
         <v>200400</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -5111,7 +5120,7 @@
       <c r="E46" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F46" s="49" t="s">
+      <c r="F46" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G46" s="3" t="s">
@@ -5120,19 +5129,19 @@
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="37">
+      <c r="I46" s="39">
         <v>1980000</v>
       </c>
-      <c r="J46" s="33" t="s">
+      <c r="J46" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="K46" s="38">
-        <v>0</v>
-      </c>
-      <c r="L46" s="38" t="s">
+      <c r="K46" s="40">
+        <v>0</v>
+      </c>
+      <c r="L46" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="M46" s="38" t="s">
+      <c r="M46" s="36" t="s">
         <v>70</v>
       </c>
       <c r="N46" s="3">
@@ -5141,28 +5150,28 @@
       <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="38">
+      <c r="P46" s="40">
         <v>180000</v>
       </c>
-      <c r="Q46" s="38">
+      <c r="Q46" s="40">
         <v>16000</v>
       </c>
-      <c r="R46" s="38">
+      <c r="R46" s="40">
         <v>15000</v>
       </c>
-      <c r="S46" s="38">
+      <c r="S46" s="40">
         <v>16008</v>
       </c>
-      <c r="T46" s="5">
-        <v>50</v>
-      </c>
-      <c r="U46" s="44">
-        <v>0</v>
-      </c>
-      <c r="V46" s="45" t="s">
+      <c r="T46" s="6">
+        <v>50</v>
+      </c>
+      <c r="U46" s="47">
+        <v>0</v>
+      </c>
+      <c r="V46" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="W46" s="46" t="s">
+      <c r="W46" s="49" t="s">
         <v>88</v>
       </c>
       <c r="X46" s="2">
@@ -5170,10 +5179,10 @@
       </c>
     </row>
     <row r="47" spans="1:24">
-      <c r="A47" s="4">
+      <c r="A47" s="5">
         <v>20050010</v>
       </c>
-      <c r="B47" s="25">
+      <c r="B47" s="26">
         <v>200500</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -5185,7 +5194,7 @@
       <c r="E47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F47" s="49" t="s">
+      <c r="F47" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G47" s="3" t="s">
@@ -5194,19 +5203,19 @@
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="37">
+      <c r="I47" s="39">
         <v>1980000</v>
       </c>
-      <c r="J47" s="33" t="s">
+      <c r="J47" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K47" s="38">
+      <c r="K47" s="40">
         <v>1</v>
       </c>
-      <c r="L47" s="38" t="s">
+      <c r="L47" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="M47" s="38" t="s">
+      <c r="M47" s="36" t="s">
         <v>72</v>
       </c>
       <c r="N47" s="3">
@@ -5215,28 +5224,28 @@
       <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="38">
+      <c r="P47" s="40">
         <v>180000</v>
       </c>
-      <c r="Q47" s="38">
+      <c r="Q47" s="40">
         <v>16000</v>
       </c>
-      <c r="R47" s="38">
+      <c r="R47" s="40">
         <v>15000</v>
       </c>
-      <c r="S47" s="38">
+      <c r="S47" s="40">
         <v>16008</v>
       </c>
-      <c r="T47" s="4">
+      <c r="T47" s="5">
         <v>48</v>
       </c>
-      <c r="U47" s="5">
-        <v>0</v>
-      </c>
-      <c r="V47" s="45" t="s">
+      <c r="U47" s="6">
+        <v>0</v>
+      </c>
+      <c r="V47" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="W47" s="46" t="s">
+      <c r="W47" s="49" t="s">
         <v>84</v>
       </c>
       <c r="X47" s="2">
@@ -5244,10 +5253,10 @@
       </c>
     </row>
     <row r="48" spans="1:24">
-      <c r="A48" s="4">
+      <c r="A48" s="5">
         <v>20050011</v>
       </c>
-      <c r="B48" s="25">
+      <c r="B48" s="26">
         <v>200500</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -5259,7 +5268,7 @@
       <c r="E48" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F48" s="49" t="s">
+      <c r="F48" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G48" s="3" t="s">
@@ -5268,19 +5277,19 @@
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="37">
+      <c r="I48" s="39">
         <v>1980000</v>
       </c>
-      <c r="J48" s="35" t="s">
+      <c r="J48" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="K48" s="38">
+      <c r="K48" s="40">
         <v>1</v>
       </c>
-      <c r="L48" s="38" t="s">
+      <c r="L48" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="M48" s="38" t="s">
+      <c r="M48" s="36" t="s">
         <v>72</v>
       </c>
       <c r="N48" s="3">
@@ -5289,28 +5298,28 @@
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="38">
+      <c r="P48" s="40">
         <v>180000</v>
       </c>
-      <c r="Q48" s="38">
+      <c r="Q48" s="40">
         <v>16000</v>
       </c>
-      <c r="R48" s="38">
+      <c r="R48" s="40">
         <v>15000</v>
       </c>
-      <c r="S48" s="38">
+      <c r="S48" s="40">
         <v>16008</v>
       </c>
-      <c r="T48" s="4">
+      <c r="T48" s="5">
         <v>48</v>
       </c>
-      <c r="U48" s="5">
-        <v>0</v>
-      </c>
-      <c r="V48" s="45" t="s">
+      <c r="U48" s="6">
+        <v>0</v>
+      </c>
+      <c r="V48" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="W48" s="46" t="s">
+      <c r="W48" s="49" t="s">
         <v>86</v>
       </c>
       <c r="X48" s="2">
@@ -5318,10 +5327,10 @@
       </c>
     </row>
     <row r="49" spans="1:24">
-      <c r="A49" s="4">
+      <c r="A49" s="5">
         <v>20050012</v>
       </c>
-      <c r="B49" s="25">
+      <c r="B49" s="26">
         <v>200500</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -5333,7 +5342,7 @@
       <c r="E49" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F49" s="49" t="s">
+      <c r="F49" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G49" s="3" t="s">
@@ -5342,19 +5351,19 @@
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="37">
+      <c r="I49" s="39">
         <v>1980000</v>
       </c>
-      <c r="J49" s="33" t="s">
+      <c r="J49" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="K49" s="38">
+      <c r="K49" s="40">
         <v>1</v>
       </c>
-      <c r="L49" s="38" t="s">
+      <c r="L49" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="M49" s="38" t="s">
+      <c r="M49" s="36" t="s">
         <v>72</v>
       </c>
       <c r="N49" s="3">
@@ -5363,28 +5372,28 @@
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="38">
+      <c r="P49" s="40">
         <v>180000</v>
       </c>
-      <c r="Q49" s="38">
+      <c r="Q49" s="40">
         <v>16000</v>
       </c>
-      <c r="R49" s="38">
+      <c r="R49" s="40">
         <v>15000</v>
       </c>
-      <c r="S49" s="38">
+      <c r="S49" s="40">
         <v>16008</v>
       </c>
-      <c r="T49" s="4">
+      <c r="T49" s="5">
         <v>48</v>
       </c>
-      <c r="U49" s="5">
-        <v>0</v>
-      </c>
-      <c r="V49" s="45" t="s">
+      <c r="U49" s="6">
+        <v>0</v>
+      </c>
+      <c r="V49" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="W49" s="46" t="s">
+      <c r="W49" s="49" t="s">
         <v>88</v>
       </c>
       <c r="X49" s="2">
@@ -5392,10 +5401,10 @@
       </c>
     </row>
     <row r="50" spans="1:24">
-      <c r="A50" s="4">
+      <c r="A50" s="5">
         <v>20060010</v>
       </c>
-      <c r="B50" s="25">
+      <c r="B50" s="26">
         <v>200600</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -5407,7 +5416,7 @@
       <c r="E50" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F50" s="49" t="s">
+      <c r="F50" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G50" s="3" t="s">
@@ -5416,19 +5425,19 @@
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="37">
+      <c r="I50" s="39">
         <v>1980000</v>
       </c>
-      <c r="J50" s="33" t="s">
+      <c r="J50" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K50" s="38">
-        <v>0</v>
-      </c>
-      <c r="L50" s="38" t="s">
+      <c r="K50" s="40">
+        <v>0</v>
+      </c>
+      <c r="L50" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="M50" s="38" t="s">
+      <c r="M50" s="41" t="s">
         <v>74</v>
       </c>
       <c r="N50" s="3">
@@ -5437,28 +5446,28 @@
       <c r="O50" s="3">
         <v>300</v>
       </c>
-      <c r="P50" s="38">
+      <c r="P50" s="40">
         <v>180000</v>
       </c>
-      <c r="Q50" s="38">
+      <c r="Q50" s="40">
         <v>16000</v>
       </c>
-      <c r="R50" s="38">
+      <c r="R50" s="40">
         <v>15000</v>
       </c>
-      <c r="S50" s="38">
+      <c r="S50" s="40">
         <v>16008</v>
       </c>
-      <c r="T50" s="4">
+      <c r="T50" s="5">
         <v>20</v>
       </c>
-      <c r="U50" s="5">
-        <v>0</v>
-      </c>
-      <c r="V50" s="45" t="s">
+      <c r="U50" s="6">
+        <v>0</v>
+      </c>
+      <c r="V50" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="W50" s="46" t="s">
+      <c r="W50" s="49" t="s">
         <v>84</v>
       </c>
       <c r="X50" s="2">
@@ -5466,10 +5475,10 @@
       </c>
     </row>
     <row r="51" spans="1:24">
-      <c r="A51" s="4">
+      <c r="A51" s="5">
         <v>20060011</v>
       </c>
-      <c r="B51" s="25">
+      <c r="B51" s="26">
         <v>200600</v>
       </c>
       <c r="C51" s="3" t="s">
@@ -5481,7 +5490,7 @@
       <c r="E51" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F51" s="49" t="s">
+      <c r="F51" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G51" s="3" t="s">
@@ -5490,19 +5499,19 @@
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="37">
+      <c r="I51" s="39">
         <v>1980000</v>
       </c>
-      <c r="J51" s="35" t="s">
+      <c r="J51" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="K51" s="38">
-        <v>0</v>
-      </c>
-      <c r="L51" s="38" t="s">
+      <c r="K51" s="40">
+        <v>0</v>
+      </c>
+      <c r="L51" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="M51" s="38" t="s">
+      <c r="M51" s="41" t="s">
         <v>74</v>
       </c>
       <c r="N51" s="3">
@@ -5511,28 +5520,28 @@
       <c r="O51" s="3">
         <v>300</v>
       </c>
-      <c r="P51" s="38">
+      <c r="P51" s="40">
         <v>180000</v>
       </c>
-      <c r="Q51" s="38">
+      <c r="Q51" s="40">
         <v>16000</v>
       </c>
-      <c r="R51" s="38">
+      <c r="R51" s="40">
         <v>15000</v>
       </c>
-      <c r="S51" s="38">
+      <c r="S51" s="40">
         <v>16008</v>
       </c>
-      <c r="T51" s="4">
+      <c r="T51" s="5">
         <v>20</v>
       </c>
-      <c r="U51" s="5">
-        <v>0</v>
-      </c>
-      <c r="V51" s="45" t="s">
+      <c r="U51" s="6">
+        <v>0</v>
+      </c>
+      <c r="V51" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="W51" s="46" t="s">
+      <c r="W51" s="49" t="s">
         <v>86</v>
       </c>
       <c r="X51" s="2">
@@ -5540,10 +5549,10 @@
       </c>
     </row>
     <row r="52" spans="1:24">
-      <c r="A52" s="4">
+      <c r="A52" s="5">
         <v>20060012</v>
       </c>
-      <c r="B52" s="25">
+      <c r="B52" s="26">
         <v>200600</v>
       </c>
       <c r="C52" s="3" t="s">
@@ -5555,7 +5564,7 @@
       <c r="E52" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F52" s="49" t="s">
+      <c r="F52" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G52" s="3" t="s">
@@ -5564,10 +5573,10 @@
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="37">
+      <c r="I52" s="39">
         <v>1980000</v>
       </c>
-      <c r="J52" s="33" t="s">
+      <c r="J52" s="35" t="s">
         <v>87</v>
       </c>
       <c r="K52" s="3">
@@ -5576,7 +5585,7 @@
       <c r="L52" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="M52" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N52" s="3">
@@ -5597,16 +5606,16 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="4">
+      <c r="T52" s="5">
         <v>20</v>
       </c>
-      <c r="U52" s="5">
-        <v>0</v>
-      </c>
-      <c r="V52" s="45" t="s">
+      <c r="U52" s="6">
+        <v>0</v>
+      </c>
+      <c r="V52" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="W52" s="46" t="s">
+      <c r="W52" s="49" t="s">
         <v>88</v>
       </c>
       <c r="X52" s="2">
@@ -5614,10 +5623,10 @@
       </c>
     </row>
     <row r="53" spans="1:24">
-      <c r="A53" s="4">
+      <c r="A53" s="5">
         <v>20070010</v>
       </c>
-      <c r="B53" s="25">
+      <c r="B53" s="26">
         <v>200700</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -5629,7 +5638,7 @@
       <c r="E53" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F53" s="49" t="s">
+      <c r="F53" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G53" s="3" t="s">
@@ -5638,10 +5647,10 @@
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="37">
+      <c r="I53" s="39">
         <v>1980000</v>
       </c>
-      <c r="J53" s="33" t="s">
+      <c r="J53" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K53" s="3">
@@ -5650,7 +5659,7 @@
       <c r="L53" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M53" s="3" t="s">
+      <c r="M53" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N53" s="3">
@@ -5671,16 +5680,16 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="4">
+      <c r="T53" s="5">
         <v>30</v>
       </c>
-      <c r="U53" s="5">
+      <c r="U53" s="6">
         <v>1</v>
       </c>
-      <c r="V53" s="45" t="s">
+      <c r="V53" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="W53" s="46" t="s">
+      <c r="W53" s="49" t="s">
         <v>84</v>
       </c>
       <c r="X53" s="2">
@@ -5688,10 +5697,10 @@
       </c>
     </row>
     <row r="54" spans="1:24">
-      <c r="A54" s="4">
+      <c r="A54" s="5">
         <v>20070011</v>
       </c>
-      <c r="B54" s="25">
+      <c r="B54" s="26">
         <v>200700</v>
       </c>
       <c r="C54" s="3" t="s">
@@ -5703,7 +5712,7 @@
       <c r="E54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F54" s="49" t="s">
+      <c r="F54" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G54" s="3" t="s">
@@ -5712,10 +5721,10 @@
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="37">
+      <c r="I54" s="39">
         <v>1980000</v>
       </c>
-      <c r="J54" s="35" t="s">
+      <c r="J54" s="37" t="s">
         <v>85</v>
       </c>
       <c r="K54" s="3">
@@ -5724,7 +5733,7 @@
       <c r="L54" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M54" s="3" t="s">
+      <c r="M54" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N54" s="3">
@@ -5745,16 +5754,16 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="4">
+      <c r="T54" s="5">
         <v>30</v>
       </c>
-      <c r="U54" s="5">
+      <c r="U54" s="6">
         <v>1</v>
       </c>
-      <c r="V54" s="45" t="s">
+      <c r="V54" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="W54" s="46" t="s">
+      <c r="W54" s="49" t="s">
         <v>86</v>
       </c>
       <c r="X54" s="2">
@@ -5762,10 +5771,10 @@
       </c>
     </row>
     <row r="55" spans="1:24">
-      <c r="A55" s="4">
+      <c r="A55" s="5">
         <v>20070012</v>
       </c>
-      <c r="B55" s="25">
+      <c r="B55" s="26">
         <v>200700</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -5777,7 +5786,7 @@
       <c r="E55" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="49" t="s">
+      <c r="F55" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G55" s="3" t="s">
@@ -5786,10 +5795,10 @@
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="37">
+      <c r="I55" s="39">
         <v>1980000</v>
       </c>
-      <c r="J55" s="33" t="s">
+      <c r="J55" s="35" t="s">
         <v>87</v>
       </c>
       <c r="K55" s="3">
@@ -5798,7 +5807,7 @@
       <c r="L55" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M55" s="3" t="s">
+      <c r="M55" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N55" s="3">
@@ -5819,16 +5828,16 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="4">
+      <c r="T55" s="5">
         <v>30</v>
       </c>
-      <c r="U55" s="5">
+      <c r="U55" s="6">
         <v>1</v>
       </c>
-      <c r="V55" s="45" t="s">
+      <c r="V55" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="W55" s="46" t="s">
+      <c r="W55" s="49" t="s">
         <v>88</v>
       </c>
       <c r="X55" s="2">
@@ -5836,10 +5845,10 @@
       </c>
     </row>
     <row r="56" spans="1:24">
-      <c r="A56" s="4">
+      <c r="A56" s="5">
         <v>20080010</v>
       </c>
-      <c r="B56" s="25">
+      <c r="B56" s="26">
         <v>200800</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -5851,7 +5860,7 @@
       <c r="E56" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F56" s="49" t="s">
+      <c r="F56" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G56" s="3" t="s">
@@ -5860,10 +5869,10 @@
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="37">
+      <c r="I56" s="39">
         <v>1980000</v>
       </c>
-      <c r="J56" s="33" t="s">
+      <c r="J56" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K56" s="3">
@@ -5872,7 +5881,7 @@
       <c r="L56" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M56" s="3" t="s">
+      <c r="M56" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N56" s="3">
@@ -5893,16 +5902,16 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="4">
+      <c r="T56" s="5">
         <v>20</v>
       </c>
-      <c r="U56" s="5">
-        <v>0</v>
-      </c>
-      <c r="V56" s="45" t="s">
+      <c r="U56" s="6">
+        <v>0</v>
+      </c>
+      <c r="V56" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="W56" s="46" t="s">
+      <c r="W56" s="49" t="s">
         <v>84</v>
       </c>
       <c r="X56" s="2">
@@ -5910,10 +5919,10 @@
       </c>
     </row>
     <row r="57" spans="1:24">
-      <c r="A57" s="4">
+      <c r="A57" s="5">
         <v>20080011</v>
       </c>
-      <c r="B57" s="25">
+      <c r="B57" s="26">
         <v>200800</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -5925,7 +5934,7 @@
       <c r="E57" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F57" s="49" t="s">
+      <c r="F57" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G57" s="3" t="s">
@@ -5934,10 +5943,10 @@
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="37">
+      <c r="I57" s="39">
         <v>1980000</v>
       </c>
-      <c r="J57" s="35" t="s">
+      <c r="J57" s="37" t="s">
         <v>85</v>
       </c>
       <c r="K57" s="3">
@@ -5946,7 +5955,7 @@
       <c r="L57" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M57" s="3" t="s">
+      <c r="M57" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N57" s="3">
@@ -5967,16 +5976,16 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="4">
+      <c r="T57" s="5">
         <v>20</v>
       </c>
-      <c r="U57" s="5">
-        <v>0</v>
-      </c>
-      <c r="V57" s="45" t="s">
+      <c r="U57" s="6">
+        <v>0</v>
+      </c>
+      <c r="V57" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="W57" s="46" t="s">
+      <c r="W57" s="49" t="s">
         <v>86</v>
       </c>
       <c r="X57" s="2">
@@ -5984,10 +5993,10 @@
       </c>
     </row>
     <row r="58" spans="1:24">
-      <c r="A58" s="4">
+      <c r="A58" s="5">
         <v>20080012</v>
       </c>
-      <c r="B58" s="25">
+      <c r="B58" s="26">
         <v>200800</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -5999,7 +6008,7 @@
       <c r="E58" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F58" s="49" t="s">
+      <c r="F58" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G58" s="3" t="s">
@@ -6008,10 +6017,10 @@
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="37">
+      <c r="I58" s="39">
         <v>1980000</v>
       </c>
-      <c r="J58" s="33" t="s">
+      <c r="J58" s="35" t="s">
         <v>87</v>
       </c>
       <c r="K58" s="3">
@@ -6020,7 +6029,7 @@
       <c r="L58" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="M58" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N58" s="3">
@@ -6041,16 +6050,16 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="4">
+      <c r="T58" s="5">
         <v>20</v>
       </c>
-      <c r="U58" s="5">
-        <v>0</v>
-      </c>
-      <c r="V58" s="45" t="s">
+      <c r="U58" s="6">
+        <v>0</v>
+      </c>
+      <c r="V58" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="W58" s="46" t="s">
+      <c r="W58" s="49" t="s">
         <v>88</v>
       </c>
       <c r="X58" s="2">
@@ -6058,10 +6067,10 @@
       </c>
     </row>
     <row r="59" spans="1:24">
-      <c r="A59" s="4">
+      <c r="A59" s="5">
         <v>20090010</v>
       </c>
-      <c r="B59" s="25">
+      <c r="B59" s="26">
         <v>200900</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -6073,7 +6082,7 @@
       <c r="E59" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F59" s="49" t="s">
+      <c r="F59" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G59" s="3" t="s">
@@ -6082,10 +6091,10 @@
       <c r="H59" s="3">
         <v>1</v>
       </c>
-      <c r="I59" s="37">
+      <c r="I59" s="39">
         <v>1980000</v>
       </c>
-      <c r="J59" s="33" t="s">
+      <c r="J59" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K59" s="3">
@@ -6094,7 +6103,7 @@
       <c r="L59" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M59" s="3" t="s">
+      <c r="M59" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N59" s="3">
@@ -6115,16 +6124,16 @@
       <c r="S59" s="3">
         <v>16008</v>
       </c>
-      <c r="T59" s="4">
+      <c r="T59" s="5">
         <v>20</v>
       </c>
-      <c r="U59" s="5">
-        <v>0</v>
-      </c>
-      <c r="V59" s="45" t="s">
+      <c r="U59" s="6">
+        <v>0</v>
+      </c>
+      <c r="V59" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="W59" s="46" t="s">
+      <c r="W59" s="49" t="s">
         <v>84</v>
       </c>
       <c r="X59" s="2">
@@ -6132,10 +6141,10 @@
       </c>
     </row>
     <row r="60" spans="1:24">
-      <c r="A60" s="4">
+      <c r="A60" s="5">
         <v>20090011</v>
       </c>
-      <c r="B60" s="25">
+      <c r="B60" s="26">
         <v>200900</v>
       </c>
       <c r="C60" s="3" t="s">
@@ -6147,7 +6156,7 @@
       <c r="E60" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F60" s="49" t="s">
+      <c r="F60" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G60" s="3" t="s">
@@ -6156,10 +6165,10 @@
       <c r="H60" s="3">
         <v>2</v>
       </c>
-      <c r="I60" s="37">
+      <c r="I60" s="39">
         <v>1980000</v>
       </c>
-      <c r="J60" s="35" t="s">
+      <c r="J60" s="37" t="s">
         <v>85</v>
       </c>
       <c r="K60" s="3">
@@ -6168,7 +6177,7 @@
       <c r="L60" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M60" s="3" t="s">
+      <c r="M60" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N60" s="3">
@@ -6189,16 +6198,16 @@
       <c r="S60" s="3">
         <v>16008</v>
       </c>
-      <c r="T60" s="4">
+      <c r="T60" s="5">
         <v>20</v>
       </c>
-      <c r="U60" s="5">
-        <v>0</v>
-      </c>
-      <c r="V60" s="45" t="s">
+      <c r="U60" s="6">
+        <v>0</v>
+      </c>
+      <c r="V60" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="W60" s="46" t="s">
+      <c r="W60" s="49" t="s">
         <v>86</v>
       </c>
       <c r="X60" s="2">
@@ -6206,10 +6215,10 @@
       </c>
     </row>
     <row r="61" spans="1:24">
-      <c r="A61" s="4">
+      <c r="A61" s="5">
         <v>20090012</v>
       </c>
-      <c r="B61" s="25">
+      <c r="B61" s="26">
         <v>200900</v>
       </c>
       <c r="C61" s="3" t="s">
@@ -6221,7 +6230,7 @@
       <c r="E61" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F61" s="49" t="s">
+      <c r="F61" s="52" t="s">
         <v>49</v>
       </c>
       <c r="G61" s="3" t="s">
@@ -6230,10 +6239,10 @@
       <c r="H61" s="3">
         <v>3</v>
       </c>
-      <c r="I61" s="37">
+      <c r="I61" s="39">
         <v>1980000</v>
       </c>
-      <c r="J61" s="33" t="s">
+      <c r="J61" s="35" t="s">
         <v>87</v>
       </c>
       <c r="K61" s="3">
@@ -6242,7 +6251,7 @@
       <c r="L61" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M61" s="3" t="s">
+      <c r="M61" s="4" t="s">
         <v>74</v>
       </c>
       <c r="N61" s="3">
@@ -6263,16 +6272,16 @@
       <c r="S61" s="3">
         <v>16008</v>
       </c>
-      <c r="T61" s="4">
+      <c r="T61" s="5">
         <v>20</v>
       </c>
-      <c r="U61" s="5">
-        <v>0</v>
-      </c>
-      <c r="V61" s="45" t="s">
+      <c r="U61" s="6">
+        <v>0</v>
+      </c>
+      <c r="V61" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="W61" s="46" t="s">
+      <c r="W61" s="49" t="s">
         <v>88</v>
       </c>
       <c r="X61" s="2">

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -2079,7 +2079,7 @@
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" s="3">
         <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
@@ -2150,8 +2150,11 @@
       <c r="W5" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="X5" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>2001002</v>
@@ -2222,8 +2225,11 @@
       <c r="W6" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="X6" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:23">
+    <row r="7" s="2" customFormat="1" spans="1:24">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -2294,8 +2300,11 @@
       <c r="W7" s="2" t="s">
         <v>63</v>
       </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:23">
+    <row r="8" s="2" customFormat="1" spans="1:24">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -2366,8 +2375,11 @@
       <c r="W8" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>2001012</v>
@@ -2438,8 +2450,11 @@
       <c r="W9" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>2001013</v>
@@ -2510,8 +2525,11 @@
       <c r="W10" s="2" t="s">
         <v>63</v>
       </c>
+      <c r="X10" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>2003001</v>
@@ -2582,8 +2600,11 @@
       <c r="W11" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:23">
+    <row r="12" s="2" customFormat="1" spans="1:24">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>2003002</v>
@@ -2654,8 +2675,11 @@
       <c r="W12" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>2003003</v>
@@ -2726,8 +2750,11 @@
       <c r="W13" s="2" t="s">
         <v>63</v>
       </c>
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>2004001</v>
@@ -2798,8 +2825,11 @@
       <c r="W14" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="X14" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>2004002</v>
@@ -2870,8 +2900,11 @@
       <c r="W15" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:23">
+    <row r="16" s="2" customFormat="1" spans="1:24">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -2941,6 +2974,9 @@
       </c>
       <c r="W16" s="2" t="s">
         <v>63</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:24">
@@ -4364,7 +4400,7 @@
         <v>86</v>
       </c>
       <c r="X35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:24">
@@ -4438,7 +4474,7 @@
         <v>88</v>
       </c>
       <c r="X36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:24">
@@ -4512,7 +4548,7 @@
         <v>90</v>
       </c>
       <c r="X37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:24">
@@ -4586,7 +4622,7 @@
         <v>86</v>
       </c>
       <c r="X38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:24">
@@ -4660,7 +4696,7 @@
         <v>88</v>
       </c>
       <c r="X39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:24">
@@ -4734,7 +4770,7 @@
         <v>90</v>
       </c>
       <c r="X40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:24">
@@ -4808,7 +4844,7 @@
         <v>86</v>
       </c>
       <c r="X41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:24">
@@ -4882,7 +4918,7 @@
         <v>88</v>
       </c>
       <c r="X42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:24">
@@ -4956,7 +4992,7 @@
         <v>90</v>
       </c>
       <c r="X43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:24">
@@ -5030,7 +5066,7 @@
         <v>86</v>
       </c>
       <c r="X44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:24">
@@ -5104,7 +5140,7 @@
         <v>88</v>
       </c>
       <c r="X45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:24">
@@ -5178,7 +5214,7 @@
         <v>90</v>
       </c>
       <c r="X46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:24">
@@ -5252,7 +5288,7 @@
         <v>86</v>
       </c>
       <c r="X47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -5326,7 +5362,7 @@
         <v>88</v>
       </c>
       <c r="X48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -5400,7 +5436,7 @@
         <v>90</v>
       </c>
       <c r="X49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -5474,7 +5510,7 @@
         <v>86</v>
       </c>
       <c r="X50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:24">
@@ -5548,7 +5584,7 @@
         <v>88</v>
       </c>
       <c r="X51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:24">
@@ -5622,7 +5658,7 @@
         <v>90</v>
       </c>
       <c r="X52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:24">
@@ -5696,7 +5732,7 @@
         <v>86</v>
       </c>
       <c r="X53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:24">
@@ -5770,7 +5806,7 @@
         <v>88</v>
       </c>
       <c r="X54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:24">
@@ -5844,7 +5880,7 @@
         <v>90</v>
       </c>
       <c r="X55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:24">
@@ -5918,7 +5954,7 @@
         <v>86</v>
       </c>
       <c r="X56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:24">
@@ -5992,7 +6028,7 @@
         <v>88</v>
       </c>
       <c r="X57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:24">
@@ -6066,7 +6102,7 @@
         <v>90</v>
       </c>
       <c r="X58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:24">
@@ -6140,7 +6176,7 @@
         <v>86</v>
       </c>
       <c r="X59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:24">
@@ -6214,7 +6250,7 @@
         <v>88</v>
       </c>
       <c r="X60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -6288,7 +6324,7 @@
         <v>90</v>
       </c>
       <c r="X61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -313,12 +313,24 @@
         </r>
       </text>
     </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>最大押分值*10000</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="94">
   <si>
     <t>游戏ID</t>
   </si>
@@ -383,6 +395,9 @@
     <t>是否允许庄家参与游戏</t>
   </si>
   <si>
+    <t>初始化标准池</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -398,6 +413,9 @@
     <t>List&lt;long&gt;{_}</t>
   </si>
   <si>
+    <t>long</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -459,6 +477,9 @@
   </si>
   <si>
     <t>bankerBets</t>
+  </si>
+  <si>
+    <t>initBasePool</t>
   </si>
   <si>
     <t>红黑大战</t>
@@ -597,13 +618,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -630,7 +652,18 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -816,6 +849,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -840,12 +879,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -858,7 +891,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1173,156 +1206,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1330,6 +1363,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1339,26 +1375,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1372,6 +1438,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1383,9 +1458,36 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1395,15 +1497,18 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1414,75 +1519,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
@@ -1492,7 +1560,11 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1827,87 +1899,88 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:Z61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="3"/>
-    <col min="2" max="2" width="12" style="3" customWidth="1"/>
-    <col min="3" max="4" width="20.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.1416666666667" style="3" customWidth="1"/>
-    <col min="7" max="7" width="28.2333333333333" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.025" style="3" customWidth="1"/>
-    <col min="10" max="10" width="65" style="3" customWidth="1"/>
-    <col min="11" max="11" width="8.875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="24.75" style="4" customWidth="1"/>
-    <col min="14" max="15" width="16.3166666666667" style="3" customWidth="1"/>
-    <col min="16" max="19" width="9.81666666666667" style="3" customWidth="1"/>
-    <col min="20" max="20" width="17.2166666666667" style="5" customWidth="1"/>
-    <col min="21" max="22" width="19.5" style="6" customWidth="1"/>
+    <col min="1" max="1" width="9.25" style="4"/>
+    <col min="2" max="2" width="12" style="4" customWidth="1"/>
+    <col min="3" max="4" width="20.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.1416666666667" style="4" customWidth="1"/>
+    <col min="7" max="7" width="28.2333333333333" style="4" customWidth="1"/>
+    <col min="8" max="8" width="8.625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="21.025" style="4" customWidth="1"/>
+    <col min="10" max="10" width="65" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="24.75" style="5" customWidth="1"/>
+    <col min="14" max="15" width="16.3166666666667" style="4" customWidth="1"/>
+    <col min="16" max="19" width="9.81666666666667" style="4" customWidth="1"/>
+    <col min="20" max="20" width="17.2166666666667" style="6" customWidth="1"/>
+    <col min="21" max="22" width="19.5" style="7" customWidth="1"/>
     <col min="23" max="23" width="19.125" style="2" customWidth="1"/>
     <col min="24" max="24" width="12.875" style="2" customWidth="1"/>
     <col min="25" max="25" width="20.125" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="2"/>
+    <col min="26" max="26" width="14.375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:24">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
+    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:26">
+      <c r="A1" s="8"/>
+      <c r="B1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="8"/>
+      <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="27"/>
-      <c r="M1" s="28" t="s">
+      <c r="L1" s="12"/>
+      <c r="M1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="29" t="s">
+      <c r="O1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="P1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="41" t="s">
+      <c r="Q1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="42" t="s">
+      <c r="R1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="S1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="V1" t="s">
@@ -1919,2455 +1992,2587 @@
       <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="Y1" s="19" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:24">
+    <row r="2" s="1" customFormat="1" spans="1:26">
       <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="G2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="V2" s="44" t="s">
+      <c r="I2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>21</v>
+      <c r="K2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y2" s="22" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:24">
+    <row r="3" s="1" customFormat="1" spans="1:26">
       <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="G3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="L3" s="4"/>
+      <c r="M3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="P3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="Q3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="R3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="S3" s="4" t="s">
         <v>43</v>
       </c>
+      <c r="T3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="Y3" s="22" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="2:22">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
+    <row r="4" s="1" customFormat="1" spans="1:26">
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
     </row>
-    <row r="5" spans="1:24">
-      <c r="A5" s="3">
+    <row r="5" spans="1:26">
+      <c r="A5" s="4">
         <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="29">
         <v>200100</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="29">
         <v>200100038</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="29">
+        <v>1</v>
+      </c>
+      <c r="I5" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" s="4">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O5" s="4">
+        <v>300</v>
+      </c>
+      <c r="P5" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R5" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S5" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T5" s="6">
         <v>48</v>
       </c>
-      <c r="F5" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="15">
-        <v>1</v>
-      </c>
-      <c r="I5" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J5" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O5" s="3">
-        <v>300</v>
-      </c>
-      <c r="P5" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R5" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S5" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T5" s="5">
-        <v>48</v>
-      </c>
-      <c r="U5" s="46">
+      <c r="U5" s="36">
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X5" s="2">
         <v>0</v>
       </c>
+      <c r="Y5" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
+      <c r="Z5" s="22"/>
     </row>
-    <row r="6" spans="1:24">
-      <c r="A6" s="3">
+    <row r="6" spans="1:26">
+      <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>2001002</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="37">
         <v>200100</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="18">
+      <c r="C6" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="37">
         <v>200100038</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="37">
+        <v>2</v>
+      </c>
+      <c r="I6" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J6" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="4">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="18">
-        <v>2</v>
-      </c>
-      <c r="I6" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J6" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="N6" s="3">
+      <c r="N6" s="4">
         <v>9700</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="4">
         <v>300</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="4">
         <v>180000</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="4">
         <v>16000</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="4">
         <v>15000</v>
       </c>
-      <c r="S6" s="45">
+      <c r="S6" s="35">
         <v>16008</v>
       </c>
-      <c r="T6" s="5">
+      <c r="T6" s="6">
         <v>48</v>
       </c>
-      <c r="U6" s="46">
+      <c r="U6" s="36">
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X6" s="2">
         <v>0</v>
       </c>
+      <c r="Y6" s="2">
+        <f t="shared" ref="Y6:Y10" si="1">Y5*100</f>
+        <v>5000000000</v>
+      </c>
+      <c r="Z6" s="22"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:24">
-      <c r="A7" s="3">
+    <row r="7" s="2" customFormat="1" spans="1:26">
+      <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>2001003</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="29">
         <v>200100</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="29">
         <v>200100038</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="15">
+      <c r="E7" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="29">
         <v>3</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="32">
         <v>1990000</v>
       </c>
-      <c r="J7" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M7" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="N7" s="3">
+      <c r="J7" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" s="4">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="4">
         <v>9700</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="4">
         <v>300</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="4">
         <v>180000</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="4">
         <v>16000</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="4">
         <v>15000</v>
       </c>
-      <c r="S7" s="45">
+      <c r="S7" s="35">
         <v>16008</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7" s="6">
         <v>48</v>
       </c>
-      <c r="U7" s="46">
+      <c r="U7" s="36">
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X7" s="2">
         <v>0</v>
       </c>
+      <c r="Y7" s="39">
+        <f t="shared" si="1"/>
+        <v>500000000000</v>
+      </c>
+      <c r="Z7" s="40"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:24">
-      <c r="A8" s="3">
+    <row r="8" s="2" customFormat="1" spans="1:26">
+      <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>2001011</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="29">
         <v>200101</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="29">
         <v>200101001</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="29">
+        <v>1</v>
+      </c>
+      <c r="I8" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="N8" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O8" s="4">
+        <v>300</v>
+      </c>
+      <c r="P8" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R8" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S8" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T8" s="6">
         <v>48</v>
       </c>
-      <c r="F8" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="15">
-        <v>1</v>
-      </c>
-      <c r="I8" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O8" s="3">
-        <v>300</v>
-      </c>
-      <c r="P8" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R8" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S8" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T8" s="5">
-        <v>48</v>
-      </c>
-      <c r="U8" s="46">
+      <c r="U8" s="36">
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X8" s="2">
         <v>0</v>
       </c>
+      <c r="Y8" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
-      <c r="A9" s="3">
+    <row r="9" spans="1:26">
+      <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>2001012</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="37">
         <v>200101</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="18">
+      <c r="C9" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="37">
         <v>200101001</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="18">
+      <c r="E9" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="37">
         <v>2</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="32">
         <v>1990000</v>
       </c>
-      <c r="J9" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M9" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="J9" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" s="4">
         <v>9700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="4">
         <v>300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="4">
         <v>180000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="4">
         <v>16000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="4">
         <v>15000</v>
       </c>
-      <c r="S9" s="45">
+      <c r="S9" s="35">
         <v>16008</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="6">
         <v>48</v>
       </c>
-      <c r="U9" s="46">
+      <c r="U9" s="36">
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X9" s="2">
         <v>0</v>
       </c>
+      <c r="Y9" s="2">
+        <f t="shared" si="1"/>
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
-      <c r="A10" s="3">
+    <row r="10" spans="1:26">
+      <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>2001013</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="29">
         <v>200101</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="29">
+        <v>200101001</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="29">
+        <v>3</v>
+      </c>
+      <c r="I10" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J10" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="15">
-        <v>200101001</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="15">
-        <v>3</v>
-      </c>
-      <c r="I10" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J10" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="s">
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="N10" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O10" s="4">
+        <v>300</v>
+      </c>
+      <c r="P10" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R10" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S10" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T10" s="6">
+        <v>48</v>
+      </c>
+      <c r="U10" s="36">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="36" t="s">
+      <c r="W10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="N10" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O10" s="3">
-        <v>300</v>
-      </c>
-      <c r="P10" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R10" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S10" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T10" s="5">
-        <v>48</v>
-      </c>
-      <c r="U10" s="46">
-        <v>0</v>
-      </c>
-      <c r="V10" t="s">
-        <v>62</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="X10" s="2">
         <v>0</v>
       </c>
+      <c r="Y10" s="39">
+        <f t="shared" si="1"/>
+        <v>500000000000</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
-      <c r="A11" s="3">
+    <row r="11" spans="1:26">
+      <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>2003001</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="29">
         <v>200300</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="29">
         <v>200300001</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="17" t="s">
+      <c r="E11" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="29">
+        <v>1</v>
+      </c>
+      <c r="I11" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M11" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="N11" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O11" s="4">
+        <v>300</v>
+      </c>
+      <c r="P11" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R11" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S11" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T11" s="6">
         <v>50</v>
       </c>
-      <c r="H11" s="15">
-        <v>1</v>
-      </c>
-      <c r="I11" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J11" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O11" s="3">
-        <v>300</v>
-      </c>
-      <c r="P11" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R11" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S11" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T11" s="5">
-        <v>50</v>
-      </c>
-      <c r="U11" s="46">
+      <c r="U11" s="36">
         <v>0</v>
       </c>
       <c r="V11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X11" s="2">
         <v>0</v>
       </c>
+      <c r="Y11" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:24">
-      <c r="A12" s="3">
+    <row r="12" s="2" customFormat="1" spans="1:26">
+      <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>2003002</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="37">
         <v>200300</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="18">
+      <c r="C12" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="37">
         <v>200300001</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="17" t="s">
+      <c r="E12" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="37">
+        <v>2</v>
+      </c>
+      <c r="I12" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J12" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="N12" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O12" s="4">
+        <v>300</v>
+      </c>
+      <c r="P12" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R12" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S12" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T12" s="6">
         <v>50</v>
       </c>
-      <c r="H12" s="18">
-        <v>2</v>
-      </c>
-      <c r="I12" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="N12" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O12" s="3">
-        <v>300</v>
-      </c>
-      <c r="P12" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S12" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T12" s="5">
-        <v>50</v>
-      </c>
-      <c r="U12" s="46">
+      <c r="U12" s="36">
         <v>0</v>
       </c>
       <c r="V12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X12" s="2">
         <v>0</v>
       </c>
+      <c r="Y12" s="2">
+        <f t="shared" ref="Y12:Y16" si="2">Y11*100</f>
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
-      <c r="A13" s="3">
+    <row r="13" spans="1:26">
+      <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>2003003</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="29">
         <v>200300</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="C13" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="29">
         <v>200300001</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="17" t="s">
+      <c r="E13" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="29">
+        <v>3</v>
+      </c>
+      <c r="I13" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="N13" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O13" s="4">
+        <v>300</v>
+      </c>
+      <c r="P13" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R13" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S13" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T13" s="6">
         <v>50</v>
       </c>
-      <c r="H13" s="15">
-        <v>3</v>
-      </c>
-      <c r="I13" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J13" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K13" s="3">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="s">
+      <c r="U13" s="36">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
         <v>65</v>
       </c>
-      <c r="M13" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="N13" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O13" s="3">
-        <v>300</v>
-      </c>
-      <c r="P13" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R13" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S13" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T13" s="5">
-        <v>50</v>
-      </c>
-      <c r="U13" s="46">
-        <v>0</v>
-      </c>
-      <c r="V13" t="s">
-        <v>62</v>
-      </c>
       <c r="W13" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X13" s="2">
         <v>0</v>
       </c>
+      <c r="Y13" s="39">
+        <f t="shared" si="2"/>
+        <v>500000000000</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
-      <c r="A14" s="3">
+    <row r="14" spans="1:26">
+      <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>2004001</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="29">
         <v>200400</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="15">
+      <c r="C14" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="29">
         <v>200400009</v>
       </c>
-      <c r="E14" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="17" t="s">
+      <c r="E14" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="29">
+        <v>1</v>
+      </c>
+      <c r="I14" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="N14" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O14" s="4">
+        <v>300</v>
+      </c>
+      <c r="P14" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R14" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S14" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T14" s="6">
         <v>50</v>
       </c>
-      <c r="H14" s="15">
-        <v>1</v>
-      </c>
-      <c r="I14" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J14" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M14" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="N14" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O14" s="3">
-        <v>300</v>
-      </c>
-      <c r="P14" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R14" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S14" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T14" s="5">
-        <v>50</v>
-      </c>
-      <c r="U14" s="46">
+      <c r="U14" s="36">
         <v>0</v>
       </c>
       <c r="V14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X14" s="2">
         <v>0</v>
       </c>
+      <c r="Y14" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
-      <c r="A15" s="3">
+    <row r="15" spans="1:26">
+      <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>2004002</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="37">
         <v>200400</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="18">
+      <c r="C15" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="37">
         <v>200400009</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="17" t="s">
+      <c r="E15" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="37">
+        <v>2</v>
+      </c>
+      <c r="I15" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J15" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="N15" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O15" s="4">
+        <v>300</v>
+      </c>
+      <c r="P15" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R15" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S15" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T15" s="6">
         <v>50</v>
       </c>
-      <c r="H15" s="18">
-        <v>2</v>
-      </c>
-      <c r="I15" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M15" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="N15" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O15" s="3">
-        <v>300</v>
-      </c>
-      <c r="P15" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S15" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T15" s="5">
-        <v>50</v>
-      </c>
-      <c r="U15" s="46">
+      <c r="U15" s="36">
         <v>0</v>
       </c>
       <c r="V15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X15" s="2">
         <v>0</v>
       </c>
+      <c r="Y15" s="2">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:24">
-      <c r="A16" s="3">
+    <row r="16" s="2" customFormat="1" spans="1:26">
+      <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>2004003</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="29">
         <v>200400</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="29">
         <v>200400009</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="17" t="s">
+      <c r="E16" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="29">
+        <v>3</v>
+      </c>
+      <c r="I16" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J16" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="N16" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O16" s="4">
+        <v>300</v>
+      </c>
+      <c r="P16" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R16" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S16" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T16" s="6">
         <v>50</v>
       </c>
-      <c r="H16" s="15">
-        <v>3</v>
-      </c>
-      <c r="I16" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J16" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K16" s="3">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3" t="s">
+      <c r="U16" s="36">
+        <v>0</v>
+      </c>
+      <c r="V16" t="s">
         <v>65</v>
       </c>
-      <c r="M16" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="N16" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O16" s="3">
-        <v>300</v>
-      </c>
-      <c r="P16" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R16" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S16" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T16" s="5">
-        <v>50</v>
-      </c>
-      <c r="U16" s="46">
-        <v>0</v>
-      </c>
-      <c r="V16" t="s">
-        <v>62</v>
-      </c>
       <c r="W16" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X16" s="2">
         <v>0</v>
       </c>
+      <c r="Y16" s="39">
+        <f t="shared" si="2"/>
+        <v>500000000000</v>
+      </c>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:24">
-      <c r="A17" s="3">
+    <row r="17" s="2" customFormat="1" spans="1:25">
+      <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>2005001</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="29">
         <v>200500</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="C17" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="29">
         <v>200500025</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="29">
+        <v>1</v>
+      </c>
+      <c r="I17" s="32">
+        <v>1990000</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="N17" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O17" s="4">
+        <v>300</v>
+      </c>
+      <c r="P17" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R17" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S17" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T17" s="6">
         <v>48</v>
       </c>
-      <c r="F17" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="15">
-        <v>1</v>
-      </c>
-      <c r="I17" s="34">
-        <v>1990000</v>
-      </c>
-      <c r="J17" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M17" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="N17" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>300</v>
-      </c>
-      <c r="P17" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R17" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S17" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T17" s="5">
-        <v>48</v>
-      </c>
-      <c r="U17" s="46">
+      <c r="U17" s="36">
         <v>0</v>
       </c>
       <c r="V17" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
       </c>
+      <c r="Y17" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
     </row>
-    <row r="18" spans="1:24">
-      <c r="A18" s="3">
+    <row r="18" spans="1:25">
+      <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>2005002</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="37">
         <v>200500</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="18">
+      <c r="C18" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="37">
         <v>200500025</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="18">
+      <c r="E18" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="37">
         <v>2</v>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="32">
         <v>1990000</v>
       </c>
-      <c r="J18" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M18" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="J18" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K18" s="4">
+        <v>1</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="N18" s="4">
         <v>9700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="4">
         <v>300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="4">
         <v>180000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="4">
         <v>16000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="4">
         <v>15000</v>
       </c>
-      <c r="S18" s="45">
+      <c r="S18" s="35">
         <v>16008</v>
       </c>
-      <c r="T18" s="5">
+      <c r="T18" s="6">
         <v>48</v>
       </c>
-      <c r="U18" s="46">
+      <c r="U18" s="36">
         <v>0</v>
       </c>
       <c r="V18" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X18" s="2">
         <v>0</v>
       </c>
+      <c r="Y18" s="2">
+        <f t="shared" ref="Y18:Y22" si="3">Y17*100</f>
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="19" spans="1:24">
-      <c r="A19" s="3">
+    <row r="19" spans="1:25">
+      <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>2005003</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="29">
         <v>200500</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="29">
         <v>200500025</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="15">
+      <c r="E19" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="29">
         <v>3</v>
       </c>
-      <c r="I19" s="34">
+      <c r="I19" s="32">
         <v>1990000</v>
       </c>
-      <c r="J19" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K19" s="3">
-        <v>1</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M19" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="N19" s="3">
+      <c r="J19" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="N19" s="4">
         <v>9700</v>
       </c>
-      <c r="O19" s="3">
+      <c r="O19" s="4">
         <v>300</v>
       </c>
-      <c r="P19" s="3">
+      <c r="P19" s="4">
         <v>180000</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="Q19" s="4">
         <v>16000</v>
       </c>
-      <c r="R19" s="3">
+      <c r="R19" s="4">
         <v>15000</v>
       </c>
-      <c r="S19" s="45">
+      <c r="S19" s="35">
         <v>16008</v>
       </c>
-      <c r="T19" s="5">
+      <c r="T19" s="6">
         <v>48</v>
       </c>
-      <c r="U19" s="46">
+      <c r="U19" s="36">
         <v>0</v>
       </c>
       <c r="V19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X19" s="2">
         <v>0</v>
       </c>
+      <c r="Y19" s="39">
+        <f t="shared" si="3"/>
+        <v>500000000000</v>
+      </c>
     </row>
-    <row r="20" spans="1:24">
-      <c r="A20" s="3">
+    <row r="20" spans="1:25">
+      <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>2006001</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="29">
         <v>200600</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="29">
         <v>200600001</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="15">
-        <v>1</v>
-      </c>
-      <c r="I20" s="34">
+      <c r="E20" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="29">
+        <v>1</v>
+      </c>
+      <c r="I20" s="32">
         <v>1990000</v>
       </c>
-      <c r="J20" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M20" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="J20" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="N20" s="4">
         <v>9700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="4">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="4">
         <v>180000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="4">
         <v>16000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="4">
         <v>15000</v>
       </c>
-      <c r="S20" s="45">
+      <c r="S20" s="35">
         <v>16008</v>
       </c>
-      <c r="T20" s="5">
+      <c r="T20" s="6">
         <v>20</v>
       </c>
-      <c r="U20" s="46">
+      <c r="U20" s="36">
         <v>0</v>
       </c>
       <c r="V20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X20" s="2">
         <v>0</v>
       </c>
+      <c r="Y20" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:24">
-      <c r="A21" s="3">
+    <row r="21" s="2" customFormat="1" spans="1:25">
+      <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>2006002</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="37">
         <v>200600</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="18">
+      <c r="C21" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="37">
         <v>200600001</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="18">
+      <c r="E21" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="37">
         <v>2</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="32">
         <v>1990000</v>
       </c>
-      <c r="J21" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M21" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="J21" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="N21" s="4">
         <v>9700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="4">
         <v>300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="4">
         <v>180000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="4">
         <v>16000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="4">
         <v>15000</v>
       </c>
-      <c r="S21" s="45">
+      <c r="S21" s="35">
         <v>16008</v>
       </c>
-      <c r="T21" s="5">
+      <c r="T21" s="6">
         <v>20</v>
       </c>
-      <c r="U21" s="46">
+      <c r="U21" s="36">
         <v>0</v>
       </c>
       <c r="V21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X21" s="2">
         <v>0</v>
       </c>
+      <c r="Y21" s="2">
+        <f t="shared" si="3"/>
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="22" spans="1:24">
-      <c r="A22" s="3">
+    <row r="22" spans="1:25">
+      <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>2006003</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="29">
         <v>200600</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="29">
         <v>200600001</v>
       </c>
-      <c r="E22" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H22" s="15">
+      <c r="E22" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="29">
         <v>3</v>
       </c>
-      <c r="I22" s="34">
+      <c r="I22" s="32">
         <v>1990000</v>
       </c>
-      <c r="J22" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
+      <c r="J22" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="N22" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O22" s="4">
+        <v>300</v>
+      </c>
+      <c r="P22" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R22" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S22" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T22" s="6">
+        <v>20</v>
+      </c>
+      <c r="U22" s="36">
+        <v>0</v>
+      </c>
+      <c r="V22" t="s">
         <v>65</v>
       </c>
-      <c r="M22" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="N22" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>300</v>
-      </c>
-      <c r="P22" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S22" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T22" s="5">
-        <v>20</v>
-      </c>
-      <c r="U22" s="46">
-        <v>0</v>
-      </c>
-      <c r="V22" t="s">
-        <v>62</v>
-      </c>
       <c r="W22" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X22" s="2">
         <v>0</v>
       </c>
+      <c r="Y22" s="39">
+        <f t="shared" si="3"/>
+        <v>500000000000</v>
+      </c>
     </row>
-    <row r="23" spans="1:24">
-      <c r="A23" s="3">
+    <row r="23" spans="1:25">
+      <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>2007001</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="29">
         <v>200700</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="29">
         <v>200700001</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H23" s="15">
-        <v>1</v>
-      </c>
-      <c r="I23" s="34">
+      <c r="E23" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="29">
+        <v>1</v>
+      </c>
+      <c r="I23" s="32">
         <v>1990000</v>
       </c>
-      <c r="J23" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M23" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="J23" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K23" s="4">
+        <v>1</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M23" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="N23" s="4">
         <v>9700</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="O23" s="4">
+        <v>0</v>
+      </c>
+      <c r="P23" s="4">
         <v>180000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="4">
         <v>16000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="4">
         <v>15000</v>
       </c>
-      <c r="S23" s="45">
+      <c r="S23" s="35">
         <v>16008</v>
       </c>
-      <c r="T23" s="5">
+      <c r="T23" s="6">
         <v>30</v>
       </c>
-      <c r="U23" s="46">
+      <c r="U23" s="36">
         <v>1</v>
       </c>
       <c r="V23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X23" s="2">
         <v>0</v>
       </c>
+      <c r="Y23" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
     </row>
-    <row r="24" spans="1:24">
-      <c r="A24" s="3">
+    <row r="24" spans="1:25">
+      <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>2007002</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="37">
         <v>200700</v>
       </c>
-      <c r="C24" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="18">
+      <c r="C24" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="37">
         <v>200700001</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H24" s="18">
+      <c r="E24" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="37">
         <v>2</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="32">
         <v>1990000</v>
       </c>
-      <c r="J24" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M24" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="J24" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K24" s="4">
+        <v>1</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M24" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="N24" s="4">
         <v>9700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="O24" s="4">
+        <v>0</v>
+      </c>
+      <c r="P24" s="4">
         <v>180000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="4">
         <v>16000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="4">
         <v>15000</v>
       </c>
-      <c r="S24" s="45">
+      <c r="S24" s="35">
         <v>16008</v>
       </c>
-      <c r="T24" s="5">
+      <c r="T24" s="6">
         <v>30</v>
       </c>
-      <c r="U24" s="46">
+      <c r="U24" s="36">
         <v>1</v>
       </c>
       <c r="V24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X24" s="2">
         <v>0</v>
       </c>
+      <c r="Y24" s="2">
+        <f t="shared" ref="Y24:Y28" si="4">Y23*100</f>
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="1:24">
-      <c r="A25" s="3">
+    <row r="25" s="2" customFormat="1" spans="1:25">
+      <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>2007003</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="29">
         <v>200700</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="29">
         <v>200700001</v>
       </c>
-      <c r="E25" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="15">
+      <c r="E25" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="29">
         <v>3</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="32">
         <v>1990000</v>
       </c>
-      <c r="J25" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K25" s="3">
-        <v>1</v>
-      </c>
-      <c r="L25" s="3" t="s">
+      <c r="J25" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K25" s="4">
+        <v>1</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M25" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="N25" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O25" s="4">
+        <v>0</v>
+      </c>
+      <c r="P25" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R25" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S25" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T25" s="6">
+        <v>30</v>
+      </c>
+      <c r="U25" s="36">
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
         <v>65</v>
       </c>
-      <c r="M25" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="N25" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O25" s="3">
-        <v>0</v>
-      </c>
-      <c r="P25" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R25" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S25" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T25" s="5">
-        <v>30</v>
-      </c>
-      <c r="U25" s="46">
-        <v>1</v>
-      </c>
-      <c r="V25" t="s">
-        <v>62</v>
-      </c>
       <c r="W25" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X25" s="2">
         <v>0</v>
       </c>
+      <c r="Y25" s="39">
+        <f t="shared" si="4"/>
+        <v>500000000000</v>
+      </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="1:24">
-      <c r="A26" s="3">
+    <row r="26" s="2" customFormat="1" spans="1:25">
+      <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>2008001</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="29">
         <v>200800</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="29">
         <v>200800001</v>
       </c>
-      <c r="E26" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="15">
-        <v>1</v>
-      </c>
-      <c r="I26" s="34">
+      <c r="E26" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="29">
+        <v>1</v>
+      </c>
+      <c r="I26" s="32">
         <v>1990000</v>
       </c>
-      <c r="J26" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="J26" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" s="4">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="N26" s="4">
         <v>9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="4">
         <v>300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="4">
         <v>180000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="4">
         <v>16000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="4">
         <v>15000</v>
       </c>
-      <c r="S26" s="45">
+      <c r="S26" s="35">
         <v>16008</v>
       </c>
-      <c r="T26" s="5">
+      <c r="T26" s="6">
         <v>20</v>
       </c>
-      <c r="U26" s="46">
+      <c r="U26" s="36">
         <v>0</v>
       </c>
       <c r="V26" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X26" s="2">
         <v>0</v>
       </c>
+      <c r="Y26" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="1:24">
-      <c r="A27" s="3">
+    <row r="27" s="2" customFormat="1" spans="1:25">
+      <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>2008002</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="29">
         <v>200800</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="29">
         <v>200800001</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H27" s="18">
+      <c r="E27" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="37">
         <v>2</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="32">
         <v>1990000</v>
       </c>
-      <c r="J27" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M27" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="J27" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M27" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="N27" s="4">
         <v>9700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="4">
         <v>300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="4">
         <v>180000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="4">
         <v>16000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="4">
         <v>15000</v>
       </c>
-      <c r="S27" s="45">
+      <c r="S27" s="35">
         <v>16008</v>
       </c>
-      <c r="T27" s="5">
+      <c r="T27" s="6">
         <v>20</v>
       </c>
-      <c r="U27" s="46">
+      <c r="U27" s="36">
         <v>0</v>
       </c>
       <c r="V27" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X27" s="2">
         <v>0</v>
       </c>
+      <c r="Y27" s="2">
+        <f t="shared" si="4"/>
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="1:24">
-      <c r="A28" s="3">
+    <row r="28" s="2" customFormat="1" spans="1:25">
+      <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>2008003</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="29">
         <v>200800</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="29">
         <v>200800001</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F28" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H28" s="15">
+      <c r="E28" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="29">
         <v>3</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="32">
         <v>1990000</v>
       </c>
-      <c r="J28" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3" t="s">
+      <c r="J28" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M28" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="N28" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O28" s="4">
+        <v>300</v>
+      </c>
+      <c r="P28" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R28" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S28" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T28" s="6">
+        <v>20</v>
+      </c>
+      <c r="U28" s="36">
+        <v>0</v>
+      </c>
+      <c r="V28" t="s">
         <v>65</v>
       </c>
-      <c r="M28" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="N28" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O28" s="3">
-        <v>300</v>
-      </c>
-      <c r="P28" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q28" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R28" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S28" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T28" s="5">
-        <v>20</v>
-      </c>
-      <c r="U28" s="46">
-        <v>0</v>
-      </c>
-      <c r="V28" t="s">
-        <v>62</v>
-      </c>
       <c r="W28" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X28" s="2">
         <v>0</v>
       </c>
+      <c r="Y28" s="39">
+        <f t="shared" si="4"/>
+        <v>500000000000</v>
+      </c>
     </row>
-    <row r="29" s="2" customFormat="1" spans="1:24">
-      <c r="A29" s="3">
+    <row r="29" s="2" customFormat="1" spans="1:25">
+      <c r="A29" s="4">
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="43">
         <v>200900</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="15">
+      <c r="C29" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="29">
         <v>200900001</v>
       </c>
-      <c r="E29" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H29" s="15">
-        <v>1</v>
-      </c>
-      <c r="I29" s="34">
+      <c r="E29" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="29">
+        <v>1</v>
+      </c>
+      <c r="I29" s="32">
         <v>1990000</v>
       </c>
-      <c r="J29" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K29" s="38">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M29" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="J29" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K29" s="44">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M29" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="N29" s="4">
         <v>9700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="4">
         <v>300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="4">
         <v>180000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="4">
         <v>16000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="4">
         <v>15000</v>
       </c>
-      <c r="S29" s="45">
+      <c r="S29" s="35">
         <v>16008</v>
       </c>
-      <c r="T29" s="5">
+      <c r="T29" s="6">
         <v>20</v>
       </c>
-      <c r="U29" s="46">
+      <c r="U29" s="36">
         <v>0</v>
       </c>
       <c r="V29" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X29" s="2">
         <v>0</v>
       </c>
+      <c r="Y29" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
     </row>
-    <row r="30" spans="1:24">
-      <c r="A30" s="3">
+    <row r="30" spans="1:25">
+      <c r="A30" s="4">
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="45">
         <v>200900</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" s="18">
+      <c r="C30" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="37">
         <v>200900001</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H30" s="18">
+      <c r="E30" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="37">
         <v>2</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="32">
         <v>1990000</v>
       </c>
-      <c r="J30" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K30" s="38">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M30" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="N30" s="3">
+      <c r="J30" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K30" s="44">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="N30" s="4">
         <v>9700</v>
       </c>
-      <c r="O30" s="3">
+      <c r="O30" s="4">
         <v>300</v>
       </c>
-      <c r="P30" s="3">
+      <c r="P30" s="4">
         <v>180000</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="Q30" s="4">
         <v>16000</v>
       </c>
-      <c r="R30" s="3">
+      <c r="R30" s="4">
         <v>15000</v>
       </c>
-      <c r="S30" s="45">
+      <c r="S30" s="35">
         <v>16008</v>
       </c>
-      <c r="T30" s="5">
+      <c r="T30" s="6">
         <v>20</v>
       </c>
-      <c r="U30" s="46">
+      <c r="U30" s="36">
         <v>0</v>
       </c>
       <c r="V30" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X30" s="2">
         <v>0</v>
       </c>
+      <c r="Y30" s="2">
+        <f t="shared" ref="Y30:Y34" si="5">Y29*100</f>
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="31" spans="1:24">
-      <c r="A31" s="3">
+    <row r="31" spans="1:25">
+      <c r="A31" s="4">
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="46">
         <v>200900</v>
       </c>
-      <c r="C31" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="24">
+      <c r="C31" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="47">
         <v>200900001</v>
       </c>
-      <c r="E31" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F31" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H31" s="15">
+      <c r="E31" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="29">
         <v>3</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="32">
         <v>1990000</v>
       </c>
-      <c r="J31" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K31" s="38">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3" t="s">
+      <c r="J31" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K31" s="44">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M31" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="N31" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O31" s="4">
+        <v>300</v>
+      </c>
+      <c r="P31" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R31" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S31" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T31" s="6">
+        <v>20</v>
+      </c>
+      <c r="U31" s="36">
+        <v>0</v>
+      </c>
+      <c r="V31" t="s">
         <v>65</v>
       </c>
-      <c r="M31" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="N31" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O31" s="3">
-        <v>300</v>
-      </c>
-      <c r="P31" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q31" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R31" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S31" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T31" s="5">
-        <v>20</v>
-      </c>
-      <c r="U31" s="46">
-        <v>0</v>
-      </c>
-      <c r="V31" t="s">
-        <v>62</v>
-      </c>
       <c r="W31" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X31" s="2">
         <v>0</v>
       </c>
+      <c r="Y31" s="39">
+        <f t="shared" si="5"/>
+        <v>500000000000</v>
+      </c>
     </row>
-    <row r="32" spans="1:24">
-      <c r="A32" s="3">
+    <row r="32" spans="1:25">
+      <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>2010001</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="48">
         <v>201000</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" s="3">
+      <c r="C32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="4">
         <v>101000006</v>
       </c>
-      <c r="E32" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G32" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="H32" s="15">
-        <v>1</v>
-      </c>
-      <c r="I32" s="34">
+      <c r="E32" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" s="29">
+        <v>1</v>
+      </c>
+      <c r="I32" s="32">
         <v>1990000</v>
       </c>
-      <c r="J32" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="K32" s="38">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M32" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="J32" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K32" s="44">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M32" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="N32" s="4">
         <v>9700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="4">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="4">
         <v>180000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="4">
         <v>16000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="4">
         <v>15000</v>
       </c>
-      <c r="S32" s="45">
+      <c r="S32" s="35">
         <v>16008</v>
       </c>
-      <c r="T32" s="5">
+      <c r="T32" s="6">
         <v>50</v>
       </c>
-      <c r="U32" s="46">
+      <c r="U32" s="36">
         <v>0</v>
       </c>
       <c r="V32" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X32" s="2">
         <v>0</v>
       </c>
+      <c r="Y32" s="2">
+        <f>5000*10000</f>
+        <v>50000000</v>
+      </c>
     </row>
-    <row r="33" spans="1:24">
-      <c r="A33" s="3">
+    <row r="33" spans="1:25">
+      <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>2010002</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="48">
         <v>201000</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="3">
+      <c r="C33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="4">
         <v>101000006</v>
       </c>
-      <c r="E33" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F33" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G33" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="H33" s="18">
+      <c r="E33" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="37">
         <v>2</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="32">
         <v>1990000</v>
       </c>
-      <c r="J33" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K33" s="38">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M33" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="J33" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="K33" s="44">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M33" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="N33" s="4">
         <v>9700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="4">
         <v>300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="4">
         <v>180000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="4">
         <v>16000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="4">
         <v>15000</v>
       </c>
-      <c r="S33" s="45">
+      <c r="S33" s="35">
         <v>16008</v>
       </c>
-      <c r="T33" s="5">
+      <c r="T33" s="6">
         <v>50</v>
       </c>
-      <c r="U33" s="46">
+      <c r="U33" s="36">
         <v>0</v>
       </c>
       <c r="V33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X33" s="2">
         <v>0</v>
       </c>
+      <c r="Y33" s="2">
+        <f t="shared" si="5"/>
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="34" spans="1:24">
-      <c r="A34" s="3">
+    <row r="34" spans="1:25">
+      <c r="A34" s="4">
         <f t="shared" si="0"/>
         <v>2010003</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="48">
         <v>201000</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="3">
+      <c r="C34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="4">
         <v>101000006</v>
       </c>
-      <c r="E34" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F34" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G34" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="H34" s="15">
+      <c r="E34" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="29">
         <v>3</v>
       </c>
-      <c r="I34" s="34">
+      <c r="I34" s="32">
         <v>1990000</v>
       </c>
-      <c r="J34" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K34" s="38">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3" t="s">
+      <c r="J34" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K34" s="44">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M34" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="N34" s="4">
+        <v>9700</v>
+      </c>
+      <c r="O34" s="4">
+        <v>300</v>
+      </c>
+      <c r="P34" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>16000</v>
+      </c>
+      <c r="R34" s="4">
+        <v>15000</v>
+      </c>
+      <c r="S34" s="35">
+        <v>16008</v>
+      </c>
+      <c r="T34" s="6">
+        <v>50</v>
+      </c>
+      <c r="U34" s="36">
+        <v>0</v>
+      </c>
+      <c r="V34" t="s">
         <v>65</v>
       </c>
-      <c r="M34" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="N34" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O34" s="3">
-        <v>300</v>
-      </c>
-      <c r="P34" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R34" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S34" s="45">
-        <v>16008</v>
-      </c>
-      <c r="T34" s="5">
+      <c r="W34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X34" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="39">
+        <f t="shared" si="5"/>
+        <v>500000000000</v>
+      </c>
+    </row>
+    <row r="35" s="3" customFormat="1" spans="1:25">
+      <c r="A35" s="49">
+        <v>20010010</v>
+      </c>
+      <c r="B35" s="3">
+        <v>200100</v>
+      </c>
+      <c r="C35" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="U34" s="46">
-        <v>0</v>
-      </c>
-      <c r="V34" t="s">
-        <v>62</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="X34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24">
-      <c r="A35" s="5">
-        <v>20010010</v>
-      </c>
-      <c r="B35" s="26">
-        <v>200100</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="15">
+      <c r="D35" s="50">
         <v>200100038</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="15">
-        <v>1</v>
-      </c>
-      <c r="I35" s="39">
+      <c r="E35" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="H35" s="50">
+        <v>1</v>
+      </c>
+      <c r="I35" s="50">
         <v>1980000</v>
       </c>
-      <c r="J35" s="35" t="s">
-        <v>84</v>
+      <c r="J35" s="53" t="s">
+        <v>87</v>
       </c>
       <c r="K35" s="3">
         <v>1</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M35" s="36" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="M35" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N35" s="3">
         <v>9700</v>
@@ -4384,64 +4589,67 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="45">
+      <c r="S35" s="55">
         <v>16008</v>
       </c>
-      <c r="T35" s="5">
+      <c r="T35" s="49">
         <v>48</v>
       </c>
-      <c r="U35" s="46">
-        <v>0</v>
-      </c>
-      <c r="V35" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="W35" s="48" t="s">
+      <c r="U35" s="56">
+        <v>0</v>
+      </c>
+      <c r="V35" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X35" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="3" customFormat="1" spans="1:25">
+      <c r="A36" s="49">
+        <v>20010011</v>
+      </c>
+      <c r="B36" s="3">
+        <v>200100</v>
+      </c>
+      <c r="C36" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="50">
+        <v>200100038</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="X35" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24">
-      <c r="A36" s="5">
-        <v>20010011</v>
-      </c>
-      <c r="B36" s="26">
-        <v>200100</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="18">
-        <v>200100038</v>
-      </c>
-      <c r="E36" s="18" t="s">
+      <c r="H36" s="50">
+        <v>2</v>
+      </c>
+      <c r="I36" s="50">
+        <v>1980000</v>
+      </c>
+      <c r="J36" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="K36" s="3">
+        <v>1</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M36" s="54" t="s">
         <v>56</v>
-      </c>
-      <c r="F36" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="18">
-        <v>2</v>
-      </c>
-      <c r="I36" s="39">
-        <v>1980000</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="K36" s="3">
-        <v>1</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M36" s="36" t="s">
-        <v>53</v>
       </c>
       <c r="N36" s="3">
         <v>9700</v>
@@ -4458,64 +4666,67 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="45">
+      <c r="S36" s="55">
         <v>16008</v>
       </c>
-      <c r="T36" s="5">
+      <c r="T36" s="49">
         <v>48</v>
       </c>
-      <c r="U36" s="46">
-        <v>0</v>
-      </c>
-      <c r="V36" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="W36" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="X36" s="2">
-        <v>1</v>
+      <c r="U36" s="56">
+        <v>0</v>
+      </c>
+      <c r="V36" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W36" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X36" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
-      <c r="A37" s="5">
+    <row r="37" s="3" customFormat="1" spans="1:25">
+      <c r="A37" s="49">
         <v>20010012</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="3">
         <v>200100</v>
       </c>
-      <c r="C37" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="15">
+      <c r="C37" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="50">
         <v>200100038</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F37" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="15">
+      <c r="E37" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="H37" s="50">
         <v>3</v>
       </c>
-      <c r="I37" s="39">
+      <c r="I37" s="50">
         <v>1980000</v>
       </c>
-      <c r="J37" s="35" t="s">
-        <v>89</v>
+      <c r="J37" s="53" t="s">
+        <v>92</v>
       </c>
       <c r="K37" s="3">
         <v>1</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M37" s="36" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="M37" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N37" s="3">
         <v>9700</v>
@@ -4532,64 +4743,67 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="45">
+      <c r="S37" s="55">
         <v>16008</v>
       </c>
-      <c r="T37" s="5">
+      <c r="T37" s="49">
         <v>48</v>
       </c>
-      <c r="U37" s="46">
-        <v>0</v>
-      </c>
-      <c r="V37" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="W37" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="X37" s="2">
-        <v>1</v>
+      <c r="U37" s="56">
+        <v>0</v>
+      </c>
+      <c r="V37" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W37" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X37" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
-      <c r="A38" s="5">
+    <row r="38" s="3" customFormat="1" spans="1:25">
+      <c r="A38" s="49">
         <v>20010110</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="3">
         <v>200101</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D38" s="3">
         <v>200101001</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" s="51" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F38" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="39">
+      <c r="I38" s="50">
         <v>1980000</v>
       </c>
-      <c r="J38" s="35" t="s">
-        <v>84</v>
+      <c r="J38" s="53" t="s">
+        <v>87</v>
       </c>
       <c r="K38" s="3">
         <v>0</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M38" s="36" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="M38" s="54" t="s">
+        <v>69</v>
       </c>
       <c r="N38" s="3">
         <v>9700</v>
@@ -4609,61 +4823,64 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="6">
+      <c r="T38" s="49">
         <v>48</v>
       </c>
-      <c r="U38" s="46">
-        <v>0</v>
-      </c>
-      <c r="V38" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="W38" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="X38" s="2">
-        <v>1</v>
+      <c r="U38" s="56">
+        <v>0</v>
+      </c>
+      <c r="V38" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W38" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X38" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
-      <c r="A39" s="5">
+    <row r="39" s="3" customFormat="1" spans="1:25">
+      <c r="A39" s="49">
         <v>20010111</v>
       </c>
-      <c r="B39" s="26">
+      <c r="B39" s="3">
         <v>200101</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D39" s="3">
         <v>200101001</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F39" s="51" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="F39" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="39">
+      <c r="I39" s="50">
         <v>1980000</v>
       </c>
-      <c r="J39" s="37" t="s">
-        <v>87</v>
+      <c r="J39" s="53" t="s">
+        <v>90</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M39" s="36" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="M39" s="54" t="s">
+        <v>69</v>
       </c>
       <c r="N39" s="3">
         <v>9700</v>
@@ -4683,61 +4900,64 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="6">
+      <c r="T39" s="49">
         <v>48</v>
       </c>
-      <c r="U39" s="46">
-        <v>0</v>
-      </c>
-      <c r="V39" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="W39" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="X39" s="2">
-        <v>1</v>
+      <c r="U39" s="56">
+        <v>0</v>
+      </c>
+      <c r="V39" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W39" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X39" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y39" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
-      <c r="A40" s="5">
+    <row r="40" s="3" customFormat="1" spans="1:25">
+      <c r="A40" s="49">
         <v>20010112</v>
       </c>
-      <c r="B40" s="26">
+      <c r="B40" s="3">
         <v>200101</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D40" s="3">
         <v>200101001</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F40" s="51" t="s">
-        <v>49</v>
+        <v>63</v>
+      </c>
+      <c r="F40" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="39">
+      <c r="I40" s="50">
         <v>1980000</v>
       </c>
-      <c r="J40" s="35" t="s">
-        <v>89</v>
+      <c r="J40" s="53" t="s">
+        <v>92</v>
       </c>
       <c r="K40" s="3">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M40" s="36" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="M40" s="54" t="s">
+        <v>69</v>
       </c>
       <c r="N40" s="3">
         <v>9700</v>
@@ -4757,61 +4977,64 @@
       <c r="S40" s="3">
         <v>16008</v>
       </c>
-      <c r="T40" s="6">
+      <c r="T40" s="49">
         <v>48</v>
       </c>
-      <c r="U40" s="46">
-        <v>0</v>
-      </c>
-      <c r="V40" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="W40" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="X40" s="2">
-        <v>1</v>
+      <c r="U40" s="56">
+        <v>0</v>
+      </c>
+      <c r="V40" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W40" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X40" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
-      <c r="A41" s="5">
+    <row r="41" s="3" customFormat="1" spans="1:25">
+      <c r="A41" s="49">
         <v>20030010</v>
       </c>
-      <c r="B41" s="26">
+      <c r="B41" s="3">
         <v>200300</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D41" s="3">
         <v>200300001</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" s="51" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F41" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="39">
+      <c r="I41" s="50">
         <v>1980000</v>
       </c>
-      <c r="J41" s="35" t="s">
-        <v>84</v>
+      <c r="J41" s="53" t="s">
+        <v>87</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M41" s="36" t="s">
         <v>68</v>
+      </c>
+      <c r="M41" s="54" t="s">
+        <v>71</v>
       </c>
       <c r="N41" s="3">
         <v>9700</v>
@@ -4831,61 +5054,64 @@
       <c r="S41" s="3">
         <v>16008</v>
       </c>
-      <c r="T41" s="6">
+      <c r="T41" s="49">
         <v>50</v>
       </c>
-      <c r="U41" s="46">
-        <v>0</v>
-      </c>
-      <c r="V41" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="W41" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="X41" s="2">
-        <v>1</v>
+      <c r="U41" s="56">
+        <v>0</v>
+      </c>
+      <c r="V41" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X41" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
-      <c r="A42" s="5">
+    <row r="42" s="3" customFormat="1" spans="1:25">
+      <c r="A42" s="49">
         <v>20030011</v>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="3">
         <v>200300</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D42" s="3">
         <v>200300001</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F42" s="51" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="F42" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="39">
+      <c r="I42" s="50">
         <v>1980000</v>
       </c>
-      <c r="J42" s="37" t="s">
-        <v>87</v>
+      <c r="J42" s="53" t="s">
+        <v>90</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M42" s="36" t="s">
         <v>68</v>
+      </c>
+      <c r="M42" s="54" t="s">
+        <v>71</v>
       </c>
       <c r="N42" s="3">
         <v>9700</v>
@@ -4905,61 +5131,64 @@
       <c r="S42" s="3">
         <v>16008</v>
       </c>
-      <c r="T42" s="6">
+      <c r="T42" s="49">
         <v>50</v>
       </c>
-      <c r="U42" s="46">
-        <v>0</v>
-      </c>
-      <c r="V42" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="W42" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="X42" s="2">
-        <v>1</v>
+      <c r="U42" s="56">
+        <v>0</v>
+      </c>
+      <c r="V42" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X42" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
-      <c r="A43" s="5">
+    <row r="43" s="3" customFormat="1" spans="1:25">
+      <c r="A43" s="49">
         <v>20030012</v>
       </c>
-      <c r="B43" s="26">
+      <c r="B43" s="3">
         <v>200300</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D43" s="3">
         <v>200300001</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F43" s="51" t="s">
-        <v>49</v>
+        <v>63</v>
+      </c>
+      <c r="F43" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="39">
+      <c r="I43" s="50">
         <v>1980000</v>
       </c>
-      <c r="J43" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="K43" s="40">
-        <v>0</v>
-      </c>
-      <c r="L43" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="M43" s="36" t="s">
+      <c r="J43" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="K43" s="59">
+        <v>0</v>
+      </c>
+      <c r="L43" s="59" t="s">
         <v>68</v>
+      </c>
+      <c r="M43" s="54" t="s">
+        <v>71</v>
       </c>
       <c r="N43" s="3">
         <v>9700</v>
@@ -4967,73 +5196,76 @@
       <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="40">
+      <c r="P43" s="59">
         <v>180000</v>
       </c>
-      <c r="Q43" s="40">
+      <c r="Q43" s="59">
         <v>16000</v>
       </c>
-      <c r="R43" s="40">
+      <c r="R43" s="59">
         <v>15000</v>
       </c>
-      <c r="S43" s="40">
+      <c r="S43" s="59">
         <v>16008</v>
       </c>
-      <c r="T43" s="6">
+      <c r="T43" s="49">
         <v>50</v>
       </c>
-      <c r="U43" s="46">
-        <v>0</v>
-      </c>
-      <c r="V43" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="W43" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="X43" s="2">
-        <v>1</v>
+      <c r="U43" s="56">
+        <v>0</v>
+      </c>
+      <c r="V43" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X43" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
-      <c r="A44" s="5">
+    <row r="44" s="3" customFormat="1" spans="1:25">
+      <c r="A44" s="49">
         <v>20040010</v>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="3">
         <v>200400</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D44" s="3">
         <v>200400009</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="51" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F44" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="39">
+      <c r="I44" s="50">
         <v>1980000</v>
       </c>
-      <c r="J44" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="K44" s="40">
-        <v>0</v>
-      </c>
-      <c r="L44" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="M44" s="36" t="s">
-        <v>70</v>
+      <c r="J44" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="K44" s="59">
+        <v>0</v>
+      </c>
+      <c r="L44" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="M44" s="54" t="s">
+        <v>73</v>
       </c>
       <c r="N44" s="3">
         <v>9700</v>
@@ -5041,73 +5273,76 @@
       <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="40">
+      <c r="P44" s="59">
         <v>180000</v>
       </c>
-      <c r="Q44" s="40">
+      <c r="Q44" s="59">
         <v>16000</v>
       </c>
-      <c r="R44" s="40">
+      <c r="R44" s="59">
         <v>15000</v>
       </c>
-      <c r="S44" s="40">
+      <c r="S44" s="59">
         <v>16008</v>
       </c>
-      <c r="T44" s="6">
+      <c r="T44" s="49">
         <v>50</v>
       </c>
-      <c r="U44" s="46">
-        <v>0</v>
-      </c>
-      <c r="V44" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="W44" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="X44" s="2">
-        <v>1</v>
+      <c r="U44" s="56">
+        <v>0</v>
+      </c>
+      <c r="V44" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X44" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y44" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
-      <c r="A45" s="5">
+    <row r="45" s="3" customFormat="1" spans="1:25">
+      <c r="A45" s="49">
         <v>20040011</v>
       </c>
-      <c r="B45" s="26">
+      <c r="B45" s="3">
         <v>200400</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D45" s="3">
         <v>200400009</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F45" s="51" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="F45" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="39">
+      <c r="I45" s="50">
         <v>1980000</v>
       </c>
-      <c r="J45" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="K45" s="40">
-        <v>0</v>
-      </c>
-      <c r="L45" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="M45" s="36" t="s">
-        <v>70</v>
+      <c r="J45" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="K45" s="59">
+        <v>0</v>
+      </c>
+      <c r="L45" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="M45" s="54" t="s">
+        <v>73</v>
       </c>
       <c r="N45" s="3">
         <v>9700</v>
@@ -5115,73 +5350,76 @@
       <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="40">
+      <c r="P45" s="59">
         <v>180000</v>
       </c>
-      <c r="Q45" s="40">
+      <c r="Q45" s="59">
         <v>16000</v>
       </c>
-      <c r="R45" s="40">
+      <c r="R45" s="59">
         <v>15000</v>
       </c>
-      <c r="S45" s="40">
+      <c r="S45" s="59">
         <v>16008</v>
       </c>
-      <c r="T45" s="6">
+      <c r="T45" s="49">
         <v>50</v>
       </c>
-      <c r="U45" s="46">
-        <v>0</v>
-      </c>
-      <c r="V45" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="W45" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="X45" s="2">
-        <v>1</v>
+      <c r="U45" s="56">
+        <v>0</v>
+      </c>
+      <c r="V45" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X45" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
-      <c r="A46" s="5">
+    <row r="46" s="3" customFormat="1" spans="1:25">
+      <c r="A46" s="49">
         <v>20040012</v>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="3">
         <v>200400</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D46" s="3">
         <v>200400009</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F46" s="51" t="s">
-        <v>49</v>
+        <v>63</v>
+      </c>
+      <c r="F46" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="39">
+      <c r="I46" s="50">
         <v>1980000</v>
       </c>
-      <c r="J46" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="K46" s="40">
-        <v>0</v>
-      </c>
-      <c r="L46" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="M46" s="36" t="s">
-        <v>70</v>
+      <c r="J46" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="K46" s="59">
+        <v>0</v>
+      </c>
+      <c r="L46" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="M46" s="54" t="s">
+        <v>73</v>
       </c>
       <c r="N46" s="3">
         <v>9700</v>
@@ -5189,73 +5427,76 @@
       <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="40">
+      <c r="P46" s="59">
         <v>180000</v>
       </c>
-      <c r="Q46" s="40">
+      <c r="Q46" s="59">
         <v>16000</v>
       </c>
-      <c r="R46" s="40">
+      <c r="R46" s="59">
         <v>15000</v>
       </c>
-      <c r="S46" s="40">
+      <c r="S46" s="59">
         <v>16008</v>
       </c>
-      <c r="T46" s="6">
+      <c r="T46" s="49">
         <v>50</v>
       </c>
-      <c r="U46" s="46">
-        <v>0</v>
-      </c>
-      <c r="V46" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="W46" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="X46" s="2">
-        <v>1</v>
+      <c r="U46" s="56">
+        <v>0</v>
+      </c>
+      <c r="V46" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X46" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
-      <c r="A47" s="5">
+    <row r="47" s="3" customFormat="1" spans="1:25">
+      <c r="A47" s="49">
         <v>20050010</v>
       </c>
-      <c r="B47" s="26">
+      <c r="B47" s="3">
         <v>200500</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D47" s="3">
         <v>200500025</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F47" s="51" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F47" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="39">
+      <c r="I47" s="50">
         <v>1980000</v>
       </c>
-      <c r="J47" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="K47" s="40">
-        <v>1</v>
-      </c>
-      <c r="L47" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="M47" s="36" t="s">
-        <v>72</v>
+      <c r="J47" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="K47" s="59">
+        <v>1</v>
+      </c>
+      <c r="L47" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="M47" s="54" t="s">
+        <v>75</v>
       </c>
       <c r="N47" s="3">
         <v>9700</v>
@@ -5263,73 +5504,76 @@
       <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="40">
+      <c r="P47" s="59">
         <v>180000</v>
       </c>
-      <c r="Q47" s="40">
+      <c r="Q47" s="59">
         <v>16000</v>
       </c>
-      <c r="R47" s="40">
+      <c r="R47" s="59">
         <v>15000</v>
       </c>
-      <c r="S47" s="40">
+      <c r="S47" s="59">
         <v>16008</v>
       </c>
-      <c r="T47" s="5">
+      <c r="T47" s="49">
         <v>48</v>
       </c>
-      <c r="U47" s="6">
-        <v>0</v>
-      </c>
-      <c r="V47" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="W47" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="X47" s="2">
-        <v>1</v>
+      <c r="U47" s="49">
+        <v>0</v>
+      </c>
+      <c r="V47" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X47" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
-      <c r="A48" s="5">
+    <row r="48" s="3" customFormat="1" spans="1:25">
+      <c r="A48" s="49">
         <v>20050011</v>
       </c>
-      <c r="B48" s="26">
+      <c r="B48" s="3">
         <v>200500</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D48" s="3">
         <v>200500025</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F48" s="51" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="F48" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="39">
+      <c r="I48" s="50">
         <v>1980000</v>
       </c>
-      <c r="J48" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="K48" s="40">
-        <v>1</v>
-      </c>
-      <c r="L48" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="M48" s="36" t="s">
-        <v>72</v>
+      <c r="J48" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="K48" s="59">
+        <v>1</v>
+      </c>
+      <c r="L48" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="M48" s="54" t="s">
+        <v>75</v>
       </c>
       <c r="N48" s="3">
         <v>9700</v>
@@ -5337,73 +5581,76 @@
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="40">
+      <c r="P48" s="59">
         <v>180000</v>
       </c>
-      <c r="Q48" s="40">
+      <c r="Q48" s="59">
         <v>16000</v>
       </c>
-      <c r="R48" s="40">
+      <c r="R48" s="59">
         <v>15000</v>
       </c>
-      <c r="S48" s="40">
+      <c r="S48" s="59">
         <v>16008</v>
       </c>
-      <c r="T48" s="5">
+      <c r="T48" s="49">
         <v>48</v>
       </c>
-      <c r="U48" s="6">
-        <v>0</v>
-      </c>
-      <c r="V48" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="W48" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="X48" s="2">
-        <v>1</v>
+      <c r="U48" s="49">
+        <v>0</v>
+      </c>
+      <c r="V48" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X48" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y48" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
-      <c r="A49" s="5">
+    <row r="49" s="3" customFormat="1" spans="1:25">
+      <c r="A49" s="49">
         <v>20050012</v>
       </c>
-      <c r="B49" s="26">
+      <c r="B49" s="3">
         <v>200500</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D49" s="3">
         <v>200500025</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F49" s="51" t="s">
-        <v>49</v>
+        <v>63</v>
+      </c>
+      <c r="F49" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="39">
+      <c r="I49" s="50">
         <v>1980000</v>
       </c>
-      <c r="J49" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="K49" s="40">
-        <v>1</v>
-      </c>
-      <c r="L49" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="M49" s="36" t="s">
-        <v>72</v>
+      <c r="J49" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="K49" s="59">
+        <v>1</v>
+      </c>
+      <c r="L49" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="M49" s="54" t="s">
+        <v>75</v>
       </c>
       <c r="N49" s="3">
         <v>9700</v>
@@ -5411,73 +5658,76 @@
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="40">
+      <c r="P49" s="59">
         <v>180000</v>
       </c>
-      <c r="Q49" s="40">
+      <c r="Q49" s="59">
         <v>16000</v>
       </c>
-      <c r="R49" s="40">
+      <c r="R49" s="59">
         <v>15000</v>
       </c>
-      <c r="S49" s="40">
+      <c r="S49" s="59">
         <v>16008</v>
       </c>
-      <c r="T49" s="5">
+      <c r="T49" s="49">
         <v>48</v>
       </c>
-      <c r="U49" s="6">
-        <v>0</v>
-      </c>
-      <c r="V49" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="W49" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="X49" s="2">
-        <v>1</v>
+      <c r="U49" s="49">
+        <v>0</v>
+      </c>
+      <c r="V49" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X49" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
-      <c r="A50" s="5">
+    <row r="50" s="3" customFormat="1" spans="1:25">
+      <c r="A50" s="49">
         <v>20060010</v>
       </c>
-      <c r="B50" s="26">
+      <c r="B50" s="3">
         <v>200600</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D50" s="3">
         <v>200600001</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F50" s="51" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F50" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="39">
+      <c r="I50" s="50">
         <v>1980000</v>
       </c>
-      <c r="J50" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="K50" s="40">
-        <v>0</v>
-      </c>
-      <c r="L50" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="M50" s="36" t="s">
-        <v>74</v>
+      <c r="J50" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="K50" s="59">
+        <v>0</v>
+      </c>
+      <c r="L50" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="M50" s="54" t="s">
+        <v>77</v>
       </c>
       <c r="N50" s="3">
         <v>9700</v>
@@ -5485,73 +5735,76 @@
       <c r="O50" s="3">
         <v>300</v>
       </c>
-      <c r="P50" s="40">
+      <c r="P50" s="59">
         <v>180000</v>
       </c>
-      <c r="Q50" s="40">
+      <c r="Q50" s="59">
         <v>16000</v>
       </c>
-      <c r="R50" s="40">
+      <c r="R50" s="59">
         <v>15000</v>
       </c>
-      <c r="S50" s="40">
+      <c r="S50" s="59">
         <v>16008</v>
       </c>
-      <c r="T50" s="5">
+      <c r="T50" s="49">
         <v>20</v>
       </c>
-      <c r="U50" s="6">
-        <v>0</v>
-      </c>
-      <c r="V50" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="W50" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="X50" s="2">
-        <v>1</v>
+      <c r="U50" s="49">
+        <v>0</v>
+      </c>
+      <c r="V50" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W50" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X50" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
-      <c r="A51" s="5">
+    <row r="51" s="3" customFormat="1" spans="1:25">
+      <c r="A51" s="49">
         <v>20060011</v>
       </c>
-      <c r="B51" s="26">
+      <c r="B51" s="3">
         <v>200600</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D51" s="3">
         <v>200600001</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F51" s="51" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="F51" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="39">
+      <c r="I51" s="50">
         <v>1980000</v>
       </c>
-      <c r="J51" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="K51" s="40">
-        <v>0</v>
-      </c>
-      <c r="L51" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="M51" s="36" t="s">
-        <v>74</v>
+      <c r="J51" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="K51" s="59">
+        <v>0</v>
+      </c>
+      <c r="L51" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="M51" s="54" t="s">
+        <v>77</v>
       </c>
       <c r="N51" s="3">
         <v>9700</v>
@@ -5559,73 +5812,76 @@
       <c r="O51" s="3">
         <v>300</v>
       </c>
-      <c r="P51" s="40">
+      <c r="P51" s="59">
         <v>180000</v>
       </c>
-      <c r="Q51" s="40">
+      <c r="Q51" s="59">
         <v>16000</v>
       </c>
-      <c r="R51" s="40">
+      <c r="R51" s="59">
         <v>15000</v>
       </c>
-      <c r="S51" s="40">
+      <c r="S51" s="59">
         <v>16008</v>
       </c>
-      <c r="T51" s="5">
+      <c r="T51" s="49">
         <v>20</v>
       </c>
-      <c r="U51" s="6">
-        <v>0</v>
-      </c>
-      <c r="V51" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="W51" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="X51" s="2">
-        <v>1</v>
+      <c r="U51" s="49">
+        <v>0</v>
+      </c>
+      <c r="V51" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W51" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X51" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
-      <c r="A52" s="5">
+    <row r="52" s="3" customFormat="1" spans="1:25">
+      <c r="A52" s="49">
         <v>20060012</v>
       </c>
-      <c r="B52" s="26">
+      <c r="B52" s="3">
         <v>200600</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D52" s="3">
         <v>200600001</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F52" s="51" t="s">
-        <v>49</v>
+        <v>63</v>
+      </c>
+      <c r="F52" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="39">
+      <c r="I52" s="50">
         <v>1980000</v>
       </c>
-      <c r="J52" s="35" t="s">
-        <v>89</v>
+      <c r="J52" s="53" t="s">
+        <v>92</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M52" s="36" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="M52" s="54" t="s">
+        <v>77</v>
       </c>
       <c r="N52" s="3">
         <v>9700</v>
@@ -5645,61 +5901,64 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="5">
+      <c r="T52" s="49">
         <v>20</v>
       </c>
-      <c r="U52" s="6">
-        <v>0</v>
-      </c>
-      <c r="V52" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="W52" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="X52" s="2">
-        <v>1</v>
+      <c r="U52" s="49">
+        <v>0</v>
+      </c>
+      <c r="V52" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X52" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
-      <c r="A53" s="5">
+    <row r="53" s="3" customFormat="1" spans="1:25">
+      <c r="A53" s="49">
         <v>20070010</v>
       </c>
-      <c r="B53" s="26">
+      <c r="B53" s="3">
         <v>200700</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D53" s="3">
         <v>200700001</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F53" s="51" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F53" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="39">
+      <c r="I53" s="50">
         <v>1980000</v>
       </c>
-      <c r="J53" s="35" t="s">
-        <v>84</v>
+      <c r="J53" s="53" t="s">
+        <v>87</v>
       </c>
       <c r="K53" s="3">
         <v>1</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M53" s="36" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="M53" s="54" t="s">
+        <v>79</v>
       </c>
       <c r="N53" s="3">
         <v>9700</v>
@@ -5719,61 +5978,64 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="5">
+      <c r="T53" s="49">
         <v>30</v>
       </c>
-      <c r="U53" s="6">
-        <v>1</v>
-      </c>
-      <c r="V53" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="W53" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="X53" s="2">
-        <v>1</v>
+      <c r="U53" s="49">
+        <v>1</v>
+      </c>
+      <c r="V53" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W53" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X53" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y53" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
-      <c r="A54" s="5">
+    <row r="54" s="3" customFormat="1" spans="1:25">
+      <c r="A54" s="49">
         <v>20070011</v>
       </c>
-      <c r="B54" s="26">
+      <c r="B54" s="3">
         <v>200700</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D54" s="3">
         <v>200700001</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F54" s="51" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="F54" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="39">
+      <c r="I54" s="50">
         <v>1980000</v>
       </c>
-      <c r="J54" s="37" t="s">
-        <v>87</v>
+      <c r="J54" s="53" t="s">
+        <v>90</v>
       </c>
       <c r="K54" s="3">
         <v>1</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M54" s="36" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="M54" s="54" t="s">
+        <v>79</v>
       </c>
       <c r="N54" s="3">
         <v>9700</v>
@@ -5793,61 +6055,64 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="5">
+      <c r="T54" s="49">
         <v>30</v>
       </c>
-      <c r="U54" s="6">
-        <v>1</v>
-      </c>
-      <c r="V54" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="W54" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="X54" s="2">
-        <v>1</v>
+      <c r="U54" s="49">
+        <v>1</v>
+      </c>
+      <c r="V54" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X54" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y54" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
-      <c r="A55" s="5">
+    <row r="55" s="3" customFormat="1" spans="1:25">
+      <c r="A55" s="49">
         <v>20070012</v>
       </c>
-      <c r="B55" s="26">
+      <c r="B55" s="3">
         <v>200700</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D55" s="3">
         <v>200700001</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F55" s="51" t="s">
-        <v>49</v>
+        <v>63</v>
+      </c>
+      <c r="F55" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="39">
+      <c r="I55" s="50">
         <v>1980000</v>
       </c>
-      <c r="J55" s="35" t="s">
-        <v>89</v>
+      <c r="J55" s="53" t="s">
+        <v>92</v>
       </c>
       <c r="K55" s="3">
         <v>1</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M55" s="36" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="M55" s="54" t="s">
+        <v>79</v>
       </c>
       <c r="N55" s="3">
         <v>9700</v>
@@ -5867,61 +6132,64 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="5">
+      <c r="T55" s="49">
         <v>30</v>
       </c>
-      <c r="U55" s="6">
-        <v>1</v>
-      </c>
-      <c r="V55" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="W55" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="X55" s="2">
-        <v>1</v>
+      <c r="U55" s="49">
+        <v>1</v>
+      </c>
+      <c r="V55" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W55" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X55" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y55" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
-      <c r="A56" s="5">
+    <row r="56" s="3" customFormat="1" spans="1:25">
+      <c r="A56" s="49">
         <v>20080010</v>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="3">
         <v>200800</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D56" s="3">
         <v>200800001</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F56" s="51" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F56" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="39">
+      <c r="I56" s="50">
         <v>1980000</v>
       </c>
-      <c r="J56" s="35" t="s">
-        <v>84</v>
+      <c r="J56" s="53" t="s">
+        <v>87</v>
       </c>
       <c r="K56" s="3">
         <v>0</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M56" s="36" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="M56" s="54" t="s">
+        <v>81</v>
       </c>
       <c r="N56" s="3">
         <v>9700</v>
@@ -5941,61 +6209,64 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="5">
+      <c r="T56" s="49">
         <v>20</v>
       </c>
-      <c r="U56" s="6">
-        <v>0</v>
-      </c>
-      <c r="V56" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="W56" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="X56" s="2">
-        <v>1</v>
+      <c r="U56" s="49">
+        <v>0</v>
+      </c>
+      <c r="V56" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W56" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X56" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
-      <c r="A57" s="5">
+    <row r="57" s="3" customFormat="1" spans="1:25">
+      <c r="A57" s="49">
         <v>20080011</v>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="3">
         <v>200800</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D57" s="3">
         <v>200800001</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F57" s="51" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="F57" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="39">
+      <c r="I57" s="50">
         <v>1980000</v>
       </c>
-      <c r="J57" s="37" t="s">
-        <v>87</v>
+      <c r="J57" s="53" t="s">
+        <v>90</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M57" s="36" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="M57" s="54" t="s">
+        <v>81</v>
       </c>
       <c r="N57" s="3">
         <v>9700</v>
@@ -6015,61 +6286,64 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="5">
+      <c r="T57" s="49">
         <v>20</v>
       </c>
-      <c r="U57" s="6">
-        <v>0</v>
-      </c>
-      <c r="V57" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="W57" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="X57" s="2">
-        <v>1</v>
+      <c r="U57" s="49">
+        <v>0</v>
+      </c>
+      <c r="V57" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X57" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y57" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
-      <c r="A58" s="5">
+    <row r="58" s="3" customFormat="1" spans="1:25">
+      <c r="A58" s="49">
         <v>20080012</v>
       </c>
-      <c r="B58" s="26">
+      <c r="B58" s="3">
         <v>200800</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D58" s="3">
         <v>200800001</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F58" s="51" t="s">
-        <v>49</v>
+        <v>63</v>
+      </c>
+      <c r="F58" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="39">
+      <c r="I58" s="50">
         <v>1980000</v>
       </c>
-      <c r="J58" s="35" t="s">
-        <v>89</v>
+      <c r="J58" s="53" t="s">
+        <v>92</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M58" s="36" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="M58" s="54" t="s">
+        <v>81</v>
       </c>
       <c r="N58" s="3">
         <v>9700</v>
@@ -6089,61 +6363,64 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="5">
+      <c r="T58" s="49">
         <v>20</v>
       </c>
-      <c r="U58" s="6">
-        <v>0</v>
-      </c>
-      <c r="V58" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="W58" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="X58" s="2">
-        <v>1</v>
+      <c r="U58" s="49">
+        <v>0</v>
+      </c>
+      <c r="V58" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X58" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
-      <c r="A59" s="5">
+    <row r="59" s="3" customFormat="1" spans="1:25">
+      <c r="A59" s="49">
         <v>20090010</v>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="3">
         <v>200900</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D59" s="3">
         <v>200900001</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F59" s="51" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="F59" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H59" s="3">
         <v>1</v>
       </c>
-      <c r="I59" s="39">
+      <c r="I59" s="50">
         <v>1980000</v>
       </c>
-      <c r="J59" s="35" t="s">
-        <v>84</v>
+      <c r="J59" s="53" t="s">
+        <v>87</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M59" s="36" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="M59" s="54" t="s">
+        <v>81</v>
       </c>
       <c r="N59" s="3">
         <v>9700</v>
@@ -6163,61 +6440,64 @@
       <c r="S59" s="3">
         <v>16008</v>
       </c>
-      <c r="T59" s="5">
+      <c r="T59" s="49">
         <v>20</v>
       </c>
-      <c r="U59" s="6">
-        <v>0</v>
-      </c>
-      <c r="V59" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="W59" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="X59" s="2">
-        <v>1</v>
+      <c r="U59" s="49">
+        <v>0</v>
+      </c>
+      <c r="V59" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X59" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y59" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
-      <c r="A60" s="5">
+    <row r="60" s="3" customFormat="1" spans="1:25">
+      <c r="A60" s="49">
         <v>20090011</v>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="3">
         <v>200900</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D60" s="3">
         <v>200900001</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F60" s="51" t="s">
-        <v>49</v>
+        <v>59</v>
+      </c>
+      <c r="F60" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H60" s="3">
         <v>2</v>
       </c>
-      <c r="I60" s="39">
+      <c r="I60" s="50">
         <v>1980000</v>
       </c>
-      <c r="J60" s="37" t="s">
-        <v>87</v>
+      <c r="J60" s="53" t="s">
+        <v>90</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M60" s="36" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="M60" s="54" t="s">
+        <v>81</v>
       </c>
       <c r="N60" s="3">
         <v>9700</v>
@@ -6237,61 +6517,64 @@
       <c r="S60" s="3">
         <v>16008</v>
       </c>
-      <c r="T60" s="5">
+      <c r="T60" s="49">
         <v>20</v>
       </c>
-      <c r="U60" s="6">
-        <v>0</v>
-      </c>
-      <c r="V60" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="W60" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="X60" s="2">
-        <v>1</v>
+      <c r="U60" s="49">
+        <v>0</v>
+      </c>
+      <c r="V60" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X60" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="58">
+        <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
-      <c r="A61" s="5">
+    <row r="61" s="3" customFormat="1" spans="1:25">
+      <c r="A61" s="49">
         <v>20090012</v>
       </c>
-      <c r="B61" s="26">
+      <c r="B61" s="3">
         <v>200900</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D61" s="3">
         <v>200900001</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F61" s="51" t="s">
-        <v>49</v>
+        <v>63</v>
+      </c>
+      <c r="F61" s="63" t="s">
+        <v>52</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H61" s="3">
         <v>3</v>
       </c>
-      <c r="I61" s="39">
+      <c r="I61" s="50">
         <v>1980000</v>
       </c>
-      <c r="J61" s="35" t="s">
-        <v>89</v>
+      <c r="J61" s="53" t="s">
+        <v>92</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M61" s="36" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="M61" s="54" t="s">
+        <v>81</v>
       </c>
       <c r="N61" s="3">
         <v>9700</v>
@@ -6311,20 +6594,23 @@
       <c r="S61" s="3">
         <v>16008</v>
       </c>
-      <c r="T61" s="5">
+      <c r="T61" s="49">
         <v>20</v>
       </c>
-      <c r="U61" s="6">
-        <v>0</v>
-      </c>
-      <c r="V61" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="W61" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="X61" s="2">
-        <v>1</v>
+      <c r="U61" s="49">
+        <v>0</v>
+      </c>
+      <c r="V61" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W61" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X61" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="58">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -1355,7 +1355,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1485,9 +1485,6 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1899,7 +1896,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Z61"/>
+  <dimension ref="A1:Y61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.25" style="4"/>
@@ -1914,18 +1911,17 @@
     <col min="11" max="11" width="8.875" style="4" customWidth="1"/>
     <col min="12" max="12" width="5.125" style="4" customWidth="1"/>
     <col min="13" max="13" width="24.75" style="5" customWidth="1"/>
-    <col min="14" max="15" width="16.3166666666667" style="4" customWidth="1"/>
+    <col min="14" max="14" width="19.2833333333333" style="4" customWidth="1"/>
+    <col min="15" max="15" width="18.75" style="4" customWidth="1"/>
     <col min="16" max="19" width="9.81666666666667" style="4" customWidth="1"/>
     <col min="20" max="20" width="17.2166666666667" style="6" customWidth="1"/>
     <col min="21" max="22" width="19.5" style="7" customWidth="1"/>
     <col min="23" max="23" width="19.125" style="2" customWidth="1"/>
     <col min="24" max="24" width="12.875" style="2" customWidth="1"/>
     <col min="25" max="25" width="20.125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="14.375" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:26">
+    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:25">
       <c r="A1" s="8"/>
       <c r="B1" s="9" t="s">
         <v>0</v>
@@ -1996,7 +1992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:26">
+    <row r="2" s="1" customFormat="1" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -2067,7 +2063,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:26">
+    <row r="3" s="1" customFormat="1" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -2138,7 +2134,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:26">
+    <row r="4" s="1" customFormat="1" spans="1:25">
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
@@ -2161,7 +2157,7 @@
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:25">
       <c r="A5" s="4">
         <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
@@ -2178,7 +2174,7 @@
       <c r="E5" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="60" t="s">
+      <c r="F5" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G5" s="31" t="s">
@@ -2239,9 +2235,8 @@
         <f>5000*10000</f>
         <v>50000000</v>
       </c>
-      <c r="Z5" s="22"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:25">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>2001002</v>
@@ -2258,7 +2253,7 @@
       <c r="E6" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="60" t="s">
+      <c r="F6" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G6" s="31" t="s">
@@ -2319,9 +2314,8 @@
         <f t="shared" ref="Y6:Y10" si="1">Y5*100</f>
         <v>5000000000</v>
       </c>
-      <c r="Z6" s="22"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:26">
+    <row r="7" s="2" customFormat="1" spans="1:25">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -2338,7 +2332,7 @@
       <c r="E7" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="60" t="s">
+      <c r="F7" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G7" s="31" t="s">
@@ -2399,9 +2393,8 @@
         <f t="shared" si="1"/>
         <v>500000000000</v>
       </c>
-      <c r="Z7" s="40"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:26">
+    <row r="8" s="2" customFormat="1" spans="1:25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -2415,10 +2408,10 @@
       <c r="D8" s="29">
         <v>200101001</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="31" t="s">
@@ -2480,7 +2473,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>2001012</v>
@@ -2497,7 +2490,7 @@
       <c r="E9" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="60" t="s">
+      <c r="F9" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G9" s="31" t="s">
@@ -2559,7 +2552,7 @@
         <v>5000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>2001013</v>
@@ -2576,7 +2569,7 @@
       <c r="E10" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="60" t="s">
+      <c r="F10" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G10" s="31" t="s">
@@ -2638,7 +2631,7 @@
         <v>500000000000</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>2003001</v>
@@ -2652,10 +2645,10 @@
       <c r="D11" s="29">
         <v>200300001</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="60" t="s">
+      <c r="F11" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G11" s="31" t="s">
@@ -2717,7 +2710,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:26">
+    <row r="12" s="2" customFormat="1" spans="1:25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>2003002</v>
@@ -2734,7 +2727,7 @@
       <c r="E12" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="60" t="s">
+      <c r="F12" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G12" s="31" t="s">
@@ -2796,7 +2789,7 @@
         <v>5000000000</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>2003003</v>
@@ -2813,7 +2806,7 @@
       <c r="E13" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="60" t="s">
+      <c r="F13" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G13" s="31" t="s">
@@ -2875,7 +2868,7 @@
         <v>500000000000</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>2004001</v>
@@ -2889,10 +2882,10 @@
       <c r="D14" s="29">
         <v>200400009</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="60" t="s">
+      <c r="F14" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G14" s="31" t="s">
@@ -2954,7 +2947,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>2004002</v>
@@ -2971,7 +2964,7 @@
       <c r="E15" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="60" t="s">
+      <c r="F15" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="31" t="s">
@@ -3033,7 +3026,7 @@
         <v>5000000000</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:26">
+    <row r="16" s="2" customFormat="1" spans="1:25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -3050,7 +3043,7 @@
       <c r="E16" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="60" t="s">
+      <c r="F16" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G16" s="31" t="s">
@@ -3129,7 +3122,7 @@
       <c r="E17" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="60" t="s">
+      <c r="F17" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G17" s="31" t="s">
@@ -3208,7 +3201,7 @@
       <c r="E18" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="60" t="s">
+      <c r="F18" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G18" s="31" t="s">
@@ -3287,7 +3280,7 @@
       <c r="E19" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="60" t="s">
+      <c r="F19" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G19" s="31" t="s">
@@ -3363,10 +3356,10 @@
       <c r="D20" s="29">
         <v>200600001</v>
       </c>
-      <c r="E20" s="42" t="s">
+      <c r="E20" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="60" t="s">
+      <c r="F20" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G20" s="31" t="s">
@@ -3445,7 +3438,7 @@
       <c r="E21" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="60" t="s">
+      <c r="F21" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G21" s="31" t="s">
@@ -3524,7 +3517,7 @@
       <c r="E22" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="60" t="s">
+      <c r="F22" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G22" s="31" t="s">
@@ -3603,7 +3596,7 @@
       <c r="E23" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="60" t="s">
+      <c r="F23" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="31" t="s">
@@ -3682,7 +3675,7 @@
       <c r="E24" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="60" t="s">
+      <c r="F24" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G24" s="31" t="s">
@@ -3761,7 +3754,7 @@
       <c r="E25" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="60" t="s">
+      <c r="F25" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G25" s="31" t="s">
@@ -3837,10 +3830,10 @@
       <c r="D26" s="29">
         <v>200800001</v>
       </c>
-      <c r="E26" s="42" t="s">
+      <c r="E26" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="60" t="s">
+      <c r="F26" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G26" s="31" t="s">
@@ -3919,7 +3912,7 @@
       <c r="E27" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="60" t="s">
+      <c r="F27" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G27" s="31" t="s">
@@ -3998,7 +3991,7 @@
       <c r="E28" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="60" t="s">
+      <c r="F28" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G28" s="31" t="s">
@@ -4065,7 +4058,7 @@
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="43">
+      <c r="B29" s="42">
         <v>200900</v>
       </c>
       <c r="C29" s="29" t="s">
@@ -4074,10 +4067,10 @@
       <c r="D29" s="29">
         <v>200900001</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="60" t="s">
+      <c r="F29" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="31" t="s">
@@ -4092,7 +4085,7 @@
       <c r="J29" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="44">
+      <c r="K29" s="43">
         <v>0</v>
       </c>
       <c r="L29" s="4" t="s">
@@ -4144,7 +4137,7 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="45">
+      <c r="B30" s="44">
         <v>200900</v>
       </c>
       <c r="C30" s="37" t="s">
@@ -4156,7 +4149,7 @@
       <c r="E30" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="60" t="s">
+      <c r="F30" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="31" t="s">
@@ -4171,7 +4164,7 @@
       <c r="J30" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="44">
+      <c r="K30" s="43">
         <v>0</v>
       </c>
       <c r="L30" s="4" t="s">
@@ -4223,19 +4216,19 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="46">
+      <c r="B31" s="45">
         <v>200900</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="47">
+      <c r="D31" s="46">
         <v>200900001</v>
       </c>
-      <c r="E31" s="47" t="s">
+      <c r="E31" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="60" t="s">
+      <c r="F31" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="31" t="s">
@@ -4250,7 +4243,7 @@
       <c r="J31" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="44">
+      <c r="K31" s="43">
         <v>0</v>
       </c>
       <c r="L31" s="4" t="s">
@@ -4302,7 +4295,7 @@
         <f t="shared" si="0"/>
         <v>2010001</v>
       </c>
-      <c r="B32" s="48">
+      <c r="B32" s="47">
         <v>201000</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -4311,13 +4304,13 @@
       <c r="D32" s="4">
         <v>101000006</v>
       </c>
-      <c r="E32" s="41" t="s">
+      <c r="E32" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="60" t="s">
+      <c r="F32" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="61" t="s">
+      <c r="G32" s="60" t="s">
         <v>84</v>
       </c>
       <c r="H32" s="29">
@@ -4329,7 +4322,7 @@
       <c r="J32" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="44">
+      <c r="K32" s="43">
         <v>0</v>
       </c>
       <c r="L32" s="4" t="s">
@@ -4381,7 +4374,7 @@
         <f t="shared" si="0"/>
         <v>2010002</v>
       </c>
-      <c r="B33" s="48">
+      <c r="B33" s="47">
         <v>201000</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -4393,10 +4386,10 @@
       <c r="E33" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="60" t="s">
+      <c r="F33" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="61" t="s">
+      <c r="G33" s="60" t="s">
         <v>84</v>
       </c>
       <c r="H33" s="37">
@@ -4408,7 +4401,7 @@
       <c r="J33" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="44">
+      <c r="K33" s="43">
         <v>0</v>
       </c>
       <c r="L33" s="4" t="s">
@@ -4460,7 +4453,7 @@
         <f t="shared" si="0"/>
         <v>2010003</v>
       </c>
-      <c r="B34" s="48">
+      <c r="B34" s="47">
         <v>201000</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -4469,13 +4462,13 @@
       <c r="D34" s="4">
         <v>101000006</v>
       </c>
-      <c r="E34" s="47" t="s">
+      <c r="E34" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="60" t="s">
+      <c r="F34" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="61" t="s">
+      <c r="G34" s="60" t="s">
         <v>84</v>
       </c>
       <c r="H34" s="29">
@@ -4487,7 +4480,7 @@
       <c r="J34" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="44">
+      <c r="K34" s="43">
         <v>0</v>
       </c>
       <c r="L34" s="4" t="s">
@@ -4535,34 +4528,34 @@
       </c>
     </row>
     <row r="35" s="3" customFormat="1" spans="1:25">
-      <c r="A35" s="49">
+      <c r="A35" s="48">
         <v>20010010</v>
       </c>
       <c r="B35" s="3">
         <v>200100</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="50">
+      <c r="D35" s="49">
         <v>200100038</v>
       </c>
-      <c r="E35" s="50" t="s">
+      <c r="E35" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="62" t="s">
+      <c r="F35" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="52" t="s">
+      <c r="G35" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="50">
-        <v>1</v>
-      </c>
-      <c r="I35" s="50">
+      <c r="H35" s="49">
+        <v>1</v>
+      </c>
+      <c r="I35" s="49">
         <v>1980000</v>
       </c>
-      <c r="J35" s="53" t="s">
+      <c r="J35" s="52" t="s">
         <v>87</v>
       </c>
       <c r="K35" s="3">
@@ -4571,7 +4564,7 @@
       <c r="L35" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M35" s="54" t="s">
+      <c r="M35" s="53" t="s">
         <v>56</v>
       </c>
       <c r="N35" s="3">
@@ -4589,16 +4582,16 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="55">
+      <c r="S35" s="54">
         <v>16008</v>
       </c>
-      <c r="T35" s="49">
+      <c r="T35" s="48">
         <v>48</v>
       </c>
-      <c r="U35" s="56">
-        <v>0</v>
-      </c>
-      <c r="V35" s="57" t="s">
+      <c r="U35" s="55">
+        <v>0</v>
+      </c>
+      <c r="V35" s="56" t="s">
         <v>88</v>
       </c>
       <c r="W35" s="3" t="s">
@@ -4607,39 +4600,39 @@
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="58">
+      <c r="Y35" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:25">
-      <c r="A36" s="49">
+      <c r="A36" s="48">
         <v>20010011</v>
       </c>
       <c r="B36" s="3">
         <v>200100</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="50">
+      <c r="D36" s="49">
         <v>200100038</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="62" t="s">
+      <c r="F36" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="52" t="s">
+      <c r="G36" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H36" s="50">
+      <c r="H36" s="49">
         <v>2</v>
       </c>
-      <c r="I36" s="50">
+      <c r="I36" s="49">
         <v>1980000</v>
       </c>
-      <c r="J36" s="53" t="s">
+      <c r="J36" s="52" t="s">
         <v>90</v>
       </c>
       <c r="K36" s="3">
@@ -4648,7 +4641,7 @@
       <c r="L36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M36" s="54" t="s">
+      <c r="M36" s="53" t="s">
         <v>56</v>
       </c>
       <c r="N36" s="3">
@@ -4666,16 +4659,16 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="55">
+      <c r="S36" s="54">
         <v>16008</v>
       </c>
-      <c r="T36" s="49">
+      <c r="T36" s="48">
         <v>48</v>
       </c>
-      <c r="U36" s="56">
-        <v>0</v>
-      </c>
-      <c r="V36" s="57" t="s">
+      <c r="U36" s="55">
+        <v>0</v>
+      </c>
+      <c r="V36" s="56" t="s">
         <v>57</v>
       </c>
       <c r="W36" s="3" t="s">
@@ -4684,39 +4677,39 @@
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="58">
+      <c r="Y36" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:25">
-      <c r="A37" s="49">
+      <c r="A37" s="48">
         <v>20010012</v>
       </c>
       <c r="B37" s="3">
         <v>200100</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="50">
+      <c r="D37" s="49">
         <v>200100038</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="E37" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="62" t="s">
+      <c r="F37" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="52" t="s">
+      <c r="G37" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="H37" s="50">
+      <c r="H37" s="49">
         <v>3</v>
       </c>
-      <c r="I37" s="50">
+      <c r="I37" s="49">
         <v>1980000</v>
       </c>
-      <c r="J37" s="53" t="s">
+      <c r="J37" s="52" t="s">
         <v>92</v>
       </c>
       <c r="K37" s="3">
@@ -4725,7 +4718,7 @@
       <c r="L37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M37" s="54" t="s">
+      <c r="M37" s="53" t="s">
         <v>56</v>
       </c>
       <c r="N37" s="3">
@@ -4743,16 +4736,16 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="55">
+      <c r="S37" s="54">
         <v>16008</v>
       </c>
-      <c r="T37" s="49">
+      <c r="T37" s="48">
         <v>48</v>
       </c>
-      <c r="U37" s="56">
-        <v>0</v>
-      </c>
-      <c r="V37" s="57" t="s">
+      <c r="U37" s="55">
+        <v>0</v>
+      </c>
+      <c r="V37" s="56" t="s">
         <v>61</v>
       </c>
       <c r="W37" s="3" t="s">
@@ -4761,12 +4754,12 @@
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="58">
+      <c r="Y37" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:25">
-      <c r="A38" s="49">
+      <c r="A38" s="48">
         <v>20010110</v>
       </c>
       <c r="B38" s="3">
@@ -4781,7 +4774,7 @@
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="63" t="s">
+      <c r="F38" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G38" s="3" t="s">
@@ -4790,10 +4783,10 @@
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="50">
+      <c r="I38" s="49">
         <v>1980000</v>
       </c>
-      <c r="J38" s="53" t="s">
+      <c r="J38" s="52" t="s">
         <v>87</v>
       </c>
       <c r="K38" s="3">
@@ -4802,7 +4795,7 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="54" t="s">
+      <c r="M38" s="53" t="s">
         <v>69</v>
       </c>
       <c r="N38" s="3">
@@ -4823,13 +4816,13 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="49">
+      <c r="T38" s="48">
         <v>48</v>
       </c>
-      <c r="U38" s="56">
-        <v>0</v>
-      </c>
-      <c r="V38" s="57" t="s">
+      <c r="U38" s="55">
+        <v>0</v>
+      </c>
+      <c r="V38" s="56" t="s">
         <v>88</v>
       </c>
       <c r="W38" s="3" t="s">
@@ -4838,12 +4831,12 @@
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="58">
+      <c r="Y38" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:25">
-      <c r="A39" s="49">
+      <c r="A39" s="48">
         <v>20010111</v>
       </c>
       <c r="B39" s="3">
@@ -4858,7 +4851,7 @@
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="63" t="s">
+      <c r="F39" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G39" s="3" t="s">
@@ -4867,10 +4860,10 @@
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="50">
+      <c r="I39" s="49">
         <v>1980000</v>
       </c>
-      <c r="J39" s="53" t="s">
+      <c r="J39" s="52" t="s">
         <v>90</v>
       </c>
       <c r="K39" s="3">
@@ -4879,7 +4872,7 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="54" t="s">
+      <c r="M39" s="53" t="s">
         <v>69</v>
       </c>
       <c r="N39" s="3">
@@ -4900,13 +4893,13 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="49">
+      <c r="T39" s="48">
         <v>48</v>
       </c>
-      <c r="U39" s="56">
-        <v>0</v>
-      </c>
-      <c r="V39" s="57" t="s">
+      <c r="U39" s="55">
+        <v>0</v>
+      </c>
+      <c r="V39" s="56" t="s">
         <v>57</v>
       </c>
       <c r="W39" s="3" t="s">
@@ -4915,12 +4908,12 @@
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="58">
+      <c r="Y39" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:25">
-      <c r="A40" s="49">
+      <c r="A40" s="48">
         <v>20010112</v>
       </c>
       <c r="B40" s="3">
@@ -4935,7 +4928,7 @@
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="63" t="s">
+      <c r="F40" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G40" s="3" t="s">
@@ -4944,10 +4937,10 @@
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="50">
+      <c r="I40" s="49">
         <v>1980000</v>
       </c>
-      <c r="J40" s="53" t="s">
+      <c r="J40" s="52" t="s">
         <v>92</v>
       </c>
       <c r="K40" s="3">
@@ -4956,7 +4949,7 @@
       <c r="L40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="54" t="s">
+      <c r="M40" s="53" t="s">
         <v>69</v>
       </c>
       <c r="N40" s="3">
@@ -4977,13 +4970,13 @@
       <c r="S40" s="3">
         <v>16008</v>
       </c>
-      <c r="T40" s="49">
+      <c r="T40" s="48">
         <v>48</v>
       </c>
-      <c r="U40" s="56">
-        <v>0</v>
-      </c>
-      <c r="V40" s="57" t="s">
+      <c r="U40" s="55">
+        <v>0</v>
+      </c>
+      <c r="V40" s="56" t="s">
         <v>61</v>
       </c>
       <c r="W40" s="3" t="s">
@@ -4992,12 +4985,12 @@
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="58">
+      <c r="Y40" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:25">
-      <c r="A41" s="49">
+      <c r="A41" s="48">
         <v>20030010</v>
       </c>
       <c r="B41" s="3">
@@ -5012,7 +5005,7 @@
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="63" t="s">
+      <c r="F41" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -5021,10 +5014,10 @@
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="50">
+      <c r="I41" s="49">
         <v>1980000</v>
       </c>
-      <c r="J41" s="53" t="s">
+      <c r="J41" s="52" t="s">
         <v>87</v>
       </c>
       <c r="K41" s="3">
@@ -5033,7 +5026,7 @@
       <c r="L41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="54" t="s">
+      <c r="M41" s="53" t="s">
         <v>71</v>
       </c>
       <c r="N41" s="3">
@@ -5054,13 +5047,13 @@
       <c r="S41" s="3">
         <v>16008</v>
       </c>
-      <c r="T41" s="49">
+      <c r="T41" s="48">
         <v>50</v>
       </c>
-      <c r="U41" s="56">
-        <v>0</v>
-      </c>
-      <c r="V41" s="57" t="s">
+      <c r="U41" s="55">
+        <v>0</v>
+      </c>
+      <c r="V41" s="56" t="s">
         <v>88</v>
       </c>
       <c r="W41" s="3" t="s">
@@ -5069,12 +5062,12 @@
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="58">
+      <c r="Y41" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:25">
-      <c r="A42" s="49">
+      <c r="A42" s="48">
         <v>20030011</v>
       </c>
       <c r="B42" s="3">
@@ -5089,7 +5082,7 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="63" t="s">
+      <c r="F42" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G42" s="3" t="s">
@@ -5098,10 +5091,10 @@
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="50">
+      <c r="I42" s="49">
         <v>1980000</v>
       </c>
-      <c r="J42" s="53" t="s">
+      <c r="J42" s="52" t="s">
         <v>90</v>
       </c>
       <c r="K42" s="3">
@@ -5110,7 +5103,7 @@
       <c r="L42" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="54" t="s">
+      <c r="M42" s="53" t="s">
         <v>71</v>
       </c>
       <c r="N42" s="3">
@@ -5131,13 +5124,13 @@
       <c r="S42" s="3">
         <v>16008</v>
       </c>
-      <c r="T42" s="49">
+      <c r="T42" s="48">
         <v>50</v>
       </c>
-      <c r="U42" s="56">
-        <v>0</v>
-      </c>
-      <c r="V42" s="57" t="s">
+      <c r="U42" s="55">
+        <v>0</v>
+      </c>
+      <c r="V42" s="56" t="s">
         <v>57</v>
       </c>
       <c r="W42" s="3" t="s">
@@ -5146,12 +5139,12 @@
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="58">
+      <c r="Y42" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:25">
-      <c r="A43" s="49">
+      <c r="A43" s="48">
         <v>20030012</v>
       </c>
       <c r="B43" s="3">
@@ -5166,7 +5159,7 @@
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="63" t="s">
+      <c r="F43" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G43" s="3" t="s">
@@ -5175,19 +5168,19 @@
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="50">
+      <c r="I43" s="49">
         <v>1980000</v>
       </c>
-      <c r="J43" s="53" t="s">
+      <c r="J43" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="K43" s="59">
-        <v>0</v>
-      </c>
-      <c r="L43" s="59" t="s">
+      <c r="K43" s="58">
+        <v>0</v>
+      </c>
+      <c r="L43" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="54" t="s">
+      <c r="M43" s="53" t="s">
         <v>71</v>
       </c>
       <c r="N43" s="3">
@@ -5196,25 +5189,25 @@
       <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="59">
+      <c r="P43" s="58">
         <v>180000</v>
       </c>
-      <c r="Q43" s="59">
+      <c r="Q43" s="58">
         <v>16000</v>
       </c>
-      <c r="R43" s="59">
+      <c r="R43" s="58">
         <v>15000</v>
       </c>
-      <c r="S43" s="59">
+      <c r="S43" s="58">
         <v>16008</v>
       </c>
-      <c r="T43" s="49">
+      <c r="T43" s="48">
         <v>50</v>
       </c>
-      <c r="U43" s="56">
-        <v>0</v>
-      </c>
-      <c r="V43" s="57" t="s">
+      <c r="U43" s="55">
+        <v>0</v>
+      </c>
+      <c r="V43" s="56" t="s">
         <v>61</v>
       </c>
       <c r="W43" s="3" t="s">
@@ -5223,12 +5216,12 @@
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="58">
+      <c r="Y43" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:25">
-      <c r="A44" s="49">
+      <c r="A44" s="48">
         <v>20040010</v>
       </c>
       <c r="B44" s="3">
@@ -5243,7 +5236,7 @@
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="63" t="s">
+      <c r="F44" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G44" s="3" t="s">
@@ -5252,19 +5245,19 @@
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="50">
+      <c r="I44" s="49">
         <v>1980000</v>
       </c>
-      <c r="J44" s="53" t="s">
+      <c r="J44" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="K44" s="59">
-        <v>0</v>
-      </c>
-      <c r="L44" s="59" t="s">
+      <c r="K44" s="58">
+        <v>0</v>
+      </c>
+      <c r="L44" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M44" s="54" t="s">
+      <c r="M44" s="53" t="s">
         <v>73</v>
       </c>
       <c r="N44" s="3">
@@ -5273,25 +5266,25 @@
       <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="59">
+      <c r="P44" s="58">
         <v>180000</v>
       </c>
-      <c r="Q44" s="59">
+      <c r="Q44" s="58">
         <v>16000</v>
       </c>
-      <c r="R44" s="59">
+      <c r="R44" s="58">
         <v>15000</v>
       </c>
-      <c r="S44" s="59">
+      <c r="S44" s="58">
         <v>16008</v>
       </c>
-      <c r="T44" s="49">
+      <c r="T44" s="48">
         <v>50</v>
       </c>
-      <c r="U44" s="56">
-        <v>0</v>
-      </c>
-      <c r="V44" s="57" t="s">
+      <c r="U44" s="55">
+        <v>0</v>
+      </c>
+      <c r="V44" s="56" t="s">
         <v>88</v>
       </c>
       <c r="W44" s="3" t="s">
@@ -5300,12 +5293,12 @@
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="58">
+      <c r="Y44" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:25">
-      <c r="A45" s="49">
+      <c r="A45" s="48">
         <v>20040011</v>
       </c>
       <c r="B45" s="3">
@@ -5320,7 +5313,7 @@
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="63" t="s">
+      <c r="F45" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G45" s="3" t="s">
@@ -5329,19 +5322,19 @@
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="50">
+      <c r="I45" s="49">
         <v>1980000</v>
       </c>
-      <c r="J45" s="53" t="s">
+      <c r="J45" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="K45" s="59">
-        <v>0</v>
-      </c>
-      <c r="L45" s="59" t="s">
+      <c r="K45" s="58">
+        <v>0</v>
+      </c>
+      <c r="L45" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M45" s="54" t="s">
+      <c r="M45" s="53" t="s">
         <v>73</v>
       </c>
       <c r="N45" s="3">
@@ -5350,25 +5343,25 @@
       <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="59">
+      <c r="P45" s="58">
         <v>180000</v>
       </c>
-      <c r="Q45" s="59">
+      <c r="Q45" s="58">
         <v>16000</v>
       </c>
-      <c r="R45" s="59">
+      <c r="R45" s="58">
         <v>15000</v>
       </c>
-      <c r="S45" s="59">
+      <c r="S45" s="58">
         <v>16008</v>
       </c>
-      <c r="T45" s="49">
+      <c r="T45" s="48">
         <v>50</v>
       </c>
-      <c r="U45" s="56">
-        <v>0</v>
-      </c>
-      <c r="V45" s="57" t="s">
+      <c r="U45" s="55">
+        <v>0</v>
+      </c>
+      <c r="V45" s="56" t="s">
         <v>57</v>
       </c>
       <c r="W45" s="3" t="s">
@@ -5377,12 +5370,12 @@
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="58">
+      <c r="Y45" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:25">
-      <c r="A46" s="49">
+      <c r="A46" s="48">
         <v>20040012</v>
       </c>
       <c r="B46" s="3">
@@ -5397,7 +5390,7 @@
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="63" t="s">
+      <c r="F46" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G46" s="3" t="s">
@@ -5406,19 +5399,19 @@
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="50">
+      <c r="I46" s="49">
         <v>1980000</v>
       </c>
-      <c r="J46" s="53" t="s">
+      <c r="J46" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="K46" s="59">
-        <v>0</v>
-      </c>
-      <c r="L46" s="59" t="s">
+      <c r="K46" s="58">
+        <v>0</v>
+      </c>
+      <c r="L46" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M46" s="54" t="s">
+      <c r="M46" s="53" t="s">
         <v>73</v>
       </c>
       <c r="N46" s="3">
@@ -5427,25 +5420,25 @@
       <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="59">
+      <c r="P46" s="58">
         <v>180000</v>
       </c>
-      <c r="Q46" s="59">
+      <c r="Q46" s="58">
         <v>16000</v>
       </c>
-      <c r="R46" s="59">
+      <c r="R46" s="58">
         <v>15000</v>
       </c>
-      <c r="S46" s="59">
+      <c r="S46" s="58">
         <v>16008</v>
       </c>
-      <c r="T46" s="49">
+      <c r="T46" s="48">
         <v>50</v>
       </c>
-      <c r="U46" s="56">
-        <v>0</v>
-      </c>
-      <c r="V46" s="57" t="s">
+      <c r="U46" s="55">
+        <v>0</v>
+      </c>
+      <c r="V46" s="56" t="s">
         <v>61</v>
       </c>
       <c r="W46" s="3" t="s">
@@ -5454,12 +5447,12 @@
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="58">
+      <c r="Y46" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:25">
-      <c r="A47" s="49">
+      <c r="A47" s="48">
         <v>20050010</v>
       </c>
       <c r="B47" s="3">
@@ -5474,7 +5467,7 @@
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="63" t="s">
+      <c r="F47" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G47" s="3" t="s">
@@ -5483,19 +5476,19 @@
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="50">
+      <c r="I47" s="49">
         <v>1980000</v>
       </c>
-      <c r="J47" s="53" t="s">
+      <c r="J47" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="K47" s="59">
-        <v>1</v>
-      </c>
-      <c r="L47" s="59" t="s">
+      <c r="K47" s="58">
+        <v>1</v>
+      </c>
+      <c r="L47" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M47" s="54" t="s">
+      <c r="M47" s="53" t="s">
         <v>75</v>
       </c>
       <c r="N47" s="3">
@@ -5504,25 +5497,25 @@
       <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="59">
+      <c r="P47" s="58">
         <v>180000</v>
       </c>
-      <c r="Q47" s="59">
+      <c r="Q47" s="58">
         <v>16000</v>
       </c>
-      <c r="R47" s="59">
+      <c r="R47" s="58">
         <v>15000</v>
       </c>
-      <c r="S47" s="59">
+      <c r="S47" s="58">
         <v>16008</v>
       </c>
-      <c r="T47" s="49">
+      <c r="T47" s="48">
         <v>48</v>
       </c>
-      <c r="U47" s="49">
-        <v>0</v>
-      </c>
-      <c r="V47" s="57" t="s">
+      <c r="U47" s="48">
+        <v>0</v>
+      </c>
+      <c r="V47" s="56" t="s">
         <v>88</v>
       </c>
       <c r="W47" s="3" t="s">
@@ -5531,12 +5524,12 @@
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="58">
+      <c r="Y47" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:25">
-      <c r="A48" s="49">
+      <c r="A48" s="48">
         <v>20050011</v>
       </c>
       <c r="B48" s="3">
@@ -5551,7 +5544,7 @@
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="63" t="s">
+      <c r="F48" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G48" s="3" t="s">
@@ -5560,19 +5553,19 @@
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="50">
+      <c r="I48" s="49">
         <v>1980000</v>
       </c>
-      <c r="J48" s="53" t="s">
+      <c r="J48" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="K48" s="59">
-        <v>1</v>
-      </c>
-      <c r="L48" s="59" t="s">
+      <c r="K48" s="58">
+        <v>1</v>
+      </c>
+      <c r="L48" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M48" s="54" t="s">
+      <c r="M48" s="53" t="s">
         <v>75</v>
       </c>
       <c r="N48" s="3">
@@ -5581,25 +5574,25 @@
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="59">
+      <c r="P48" s="58">
         <v>180000</v>
       </c>
-      <c r="Q48" s="59">
+      <c r="Q48" s="58">
         <v>16000</v>
       </c>
-      <c r="R48" s="59">
+      <c r="R48" s="58">
         <v>15000</v>
       </c>
-      <c r="S48" s="59">
+      <c r="S48" s="58">
         <v>16008</v>
       </c>
-      <c r="T48" s="49">
+      <c r="T48" s="48">
         <v>48</v>
       </c>
-      <c r="U48" s="49">
-        <v>0</v>
-      </c>
-      <c r="V48" s="57" t="s">
+      <c r="U48" s="48">
+        <v>0</v>
+      </c>
+      <c r="V48" s="56" t="s">
         <v>57</v>
       </c>
       <c r="W48" s="3" t="s">
@@ -5608,12 +5601,12 @@
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="58">
+      <c r="Y48" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:25">
-      <c r="A49" s="49">
+      <c r="A49" s="48">
         <v>20050012</v>
       </c>
       <c r="B49" s="3">
@@ -5628,7 +5621,7 @@
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="63" t="s">
+      <c r="F49" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G49" s="3" t="s">
@@ -5637,19 +5630,19 @@
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="50">
+      <c r="I49" s="49">
         <v>1980000</v>
       </c>
-      <c r="J49" s="53" t="s">
+      <c r="J49" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="K49" s="59">
-        <v>1</v>
-      </c>
-      <c r="L49" s="59" t="s">
+      <c r="K49" s="58">
+        <v>1</v>
+      </c>
+      <c r="L49" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M49" s="54" t="s">
+      <c r="M49" s="53" t="s">
         <v>75</v>
       </c>
       <c r="N49" s="3">
@@ -5658,25 +5651,25 @@
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="59">
+      <c r="P49" s="58">
         <v>180000</v>
       </c>
-      <c r="Q49" s="59">
+      <c r="Q49" s="58">
         <v>16000</v>
       </c>
-      <c r="R49" s="59">
+      <c r="R49" s="58">
         <v>15000</v>
       </c>
-      <c r="S49" s="59">
+      <c r="S49" s="58">
         <v>16008</v>
       </c>
-      <c r="T49" s="49">
+      <c r="T49" s="48">
         <v>48</v>
       </c>
-      <c r="U49" s="49">
-        <v>0</v>
-      </c>
-      <c r="V49" s="57" t="s">
+      <c r="U49" s="48">
+        <v>0</v>
+      </c>
+      <c r="V49" s="56" t="s">
         <v>61</v>
       </c>
       <c r="W49" s="3" t="s">
@@ -5685,12 +5678,12 @@
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="58">
+      <c r="Y49" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:25">
-      <c r="A50" s="49">
+      <c r="A50" s="48">
         <v>20060010</v>
       </c>
       <c r="B50" s="3">
@@ -5705,7 +5698,7 @@
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="63" t="s">
+      <c r="F50" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G50" s="3" t="s">
@@ -5714,19 +5707,19 @@
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="50">
+      <c r="I50" s="49">
         <v>1980000</v>
       </c>
-      <c r="J50" s="53" t="s">
+      <c r="J50" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="K50" s="59">
-        <v>0</v>
-      </c>
-      <c r="L50" s="59" t="s">
+      <c r="K50" s="58">
+        <v>0</v>
+      </c>
+      <c r="L50" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="54" t="s">
+      <c r="M50" s="53" t="s">
         <v>77</v>
       </c>
       <c r="N50" s="3">
@@ -5735,25 +5728,25 @@
       <c r="O50" s="3">
         <v>300</v>
       </c>
-      <c r="P50" s="59">
+      <c r="P50" s="58">
         <v>180000</v>
       </c>
-      <c r="Q50" s="59">
+      <c r="Q50" s="58">
         <v>16000</v>
       </c>
-      <c r="R50" s="59">
+      <c r="R50" s="58">
         <v>15000</v>
       </c>
-      <c r="S50" s="59">
+      <c r="S50" s="58">
         <v>16008</v>
       </c>
-      <c r="T50" s="49">
+      <c r="T50" s="48">
         <v>20</v>
       </c>
-      <c r="U50" s="49">
-        <v>0</v>
-      </c>
-      <c r="V50" s="57" t="s">
+      <c r="U50" s="48">
+        <v>0</v>
+      </c>
+      <c r="V50" s="56" t="s">
         <v>88</v>
       </c>
       <c r="W50" s="3" t="s">
@@ -5762,12 +5755,12 @@
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="58">
+      <c r="Y50" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:25">
-      <c r="A51" s="49">
+      <c r="A51" s="48">
         <v>20060011</v>
       </c>
       <c r="B51" s="3">
@@ -5782,7 +5775,7 @@
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="63" t="s">
+      <c r="F51" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G51" s="3" t="s">
@@ -5791,19 +5784,19 @@
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="50">
+      <c r="I51" s="49">
         <v>1980000</v>
       </c>
-      <c r="J51" s="53" t="s">
+      <c r="J51" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="K51" s="59">
-        <v>0</v>
-      </c>
-      <c r="L51" s="59" t="s">
+      <c r="K51" s="58">
+        <v>0</v>
+      </c>
+      <c r="L51" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="54" t="s">
+      <c r="M51" s="53" t="s">
         <v>77</v>
       </c>
       <c r="N51" s="3">
@@ -5812,25 +5805,25 @@
       <c r="O51" s="3">
         <v>300</v>
       </c>
-      <c r="P51" s="59">
+      <c r="P51" s="58">
         <v>180000</v>
       </c>
-      <c r="Q51" s="59">
+      <c r="Q51" s="58">
         <v>16000</v>
       </c>
-      <c r="R51" s="59">
+      <c r="R51" s="58">
         <v>15000</v>
       </c>
-      <c r="S51" s="59">
+      <c r="S51" s="58">
         <v>16008</v>
       </c>
-      <c r="T51" s="49">
+      <c r="T51" s="48">
         <v>20</v>
       </c>
-      <c r="U51" s="49">
-        <v>0</v>
-      </c>
-      <c r="V51" s="57" t="s">
+      <c r="U51" s="48">
+        <v>0</v>
+      </c>
+      <c r="V51" s="56" t="s">
         <v>57</v>
       </c>
       <c r="W51" s="3" t="s">
@@ -5839,12 +5832,12 @@
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="58">
+      <c r="Y51" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:25">
-      <c r="A52" s="49">
+      <c r="A52" s="48">
         <v>20060012</v>
       </c>
       <c r="B52" s="3">
@@ -5859,7 +5852,7 @@
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="63" t="s">
+      <c r="F52" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G52" s="3" t="s">
@@ -5868,10 +5861,10 @@
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="50">
+      <c r="I52" s="49">
         <v>1980000</v>
       </c>
-      <c r="J52" s="53" t="s">
+      <c r="J52" s="52" t="s">
         <v>92</v>
       </c>
       <c r="K52" s="3">
@@ -5880,7 +5873,7 @@
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="54" t="s">
+      <c r="M52" s="53" t="s">
         <v>77</v>
       </c>
       <c r="N52" s="3">
@@ -5901,13 +5894,13 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="49">
+      <c r="T52" s="48">
         <v>20</v>
       </c>
-      <c r="U52" s="49">
-        <v>0</v>
-      </c>
-      <c r="V52" s="57" t="s">
+      <c r="U52" s="48">
+        <v>0</v>
+      </c>
+      <c r="V52" s="56" t="s">
         <v>61</v>
       </c>
       <c r="W52" s="3" t="s">
@@ -5916,12 +5909,12 @@
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="58">
+      <c r="Y52" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:25">
-      <c r="A53" s="49">
+      <c r="A53" s="48">
         <v>20070010</v>
       </c>
       <c r="B53" s="3">
@@ -5936,7 +5929,7 @@
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="63" t="s">
+      <c r="F53" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G53" s="3" t="s">
@@ -5945,10 +5938,10 @@
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="50">
+      <c r="I53" s="49">
         <v>1980000</v>
       </c>
-      <c r="J53" s="53" t="s">
+      <c r="J53" s="52" t="s">
         <v>87</v>
       </c>
       <c r="K53" s="3">
@@ -5957,7 +5950,7 @@
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="54" t="s">
+      <c r="M53" s="53" t="s">
         <v>79</v>
       </c>
       <c r="N53" s="3">
@@ -5978,13 +5971,13 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="49">
+      <c r="T53" s="48">
         <v>30</v>
       </c>
-      <c r="U53" s="49">
-        <v>1</v>
-      </c>
-      <c r="V53" s="57" t="s">
+      <c r="U53" s="48">
+        <v>1</v>
+      </c>
+      <c r="V53" s="56" t="s">
         <v>88</v>
       </c>
       <c r="W53" s="3" t="s">
@@ -5993,12 +5986,12 @@
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="58">
+      <c r="Y53" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:25">
-      <c r="A54" s="49">
+      <c r="A54" s="48">
         <v>20070011</v>
       </c>
       <c r="B54" s="3">
@@ -6013,7 +6006,7 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="63" t="s">
+      <c r="F54" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G54" s="3" t="s">
@@ -6022,10 +6015,10 @@
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="50">
+      <c r="I54" s="49">
         <v>1980000</v>
       </c>
-      <c r="J54" s="53" t="s">
+      <c r="J54" s="52" t="s">
         <v>90</v>
       </c>
       <c r="K54" s="3">
@@ -6034,7 +6027,7 @@
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="54" t="s">
+      <c r="M54" s="53" t="s">
         <v>79</v>
       </c>
       <c r="N54" s="3">
@@ -6055,13 +6048,13 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="49">
+      <c r="T54" s="48">
         <v>30</v>
       </c>
-      <c r="U54" s="49">
-        <v>1</v>
-      </c>
-      <c r="V54" s="57" t="s">
+      <c r="U54" s="48">
+        <v>1</v>
+      </c>
+      <c r="V54" s="56" t="s">
         <v>57</v>
       </c>
       <c r="W54" s="3" t="s">
@@ -6070,12 +6063,12 @@
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="58">
+      <c r="Y54" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" spans="1:25">
-      <c r="A55" s="49">
+      <c r="A55" s="48">
         <v>20070012</v>
       </c>
       <c r="B55" s="3">
@@ -6090,7 +6083,7 @@
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="63" t="s">
+      <c r="F55" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G55" s="3" t="s">
@@ -6099,10 +6092,10 @@
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="50">
+      <c r="I55" s="49">
         <v>1980000</v>
       </c>
-      <c r="J55" s="53" t="s">
+      <c r="J55" s="52" t="s">
         <v>92</v>
       </c>
       <c r="K55" s="3">
@@ -6111,7 +6104,7 @@
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="54" t="s">
+      <c r="M55" s="53" t="s">
         <v>79</v>
       </c>
       <c r="N55" s="3">
@@ -6132,13 +6125,13 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="49">
+      <c r="T55" s="48">
         <v>30</v>
       </c>
-      <c r="U55" s="49">
-        <v>1</v>
-      </c>
-      <c r="V55" s="57" t="s">
+      <c r="U55" s="48">
+        <v>1</v>
+      </c>
+      <c r="V55" s="56" t="s">
         <v>61</v>
       </c>
       <c r="W55" s="3" t="s">
@@ -6147,12 +6140,12 @@
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="58">
+      <c r="Y55" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" spans="1:25">
-      <c r="A56" s="49">
+      <c r="A56" s="48">
         <v>20080010</v>
       </c>
       <c r="B56" s="3">
@@ -6167,7 +6160,7 @@
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="63" t="s">
+      <c r="F56" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G56" s="3" t="s">
@@ -6176,10 +6169,10 @@
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="50">
+      <c r="I56" s="49">
         <v>1980000</v>
       </c>
-      <c r="J56" s="53" t="s">
+      <c r="J56" s="52" t="s">
         <v>87</v>
       </c>
       <c r="K56" s="3">
@@ -6188,7 +6181,7 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="54" t="s">
+      <c r="M56" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N56" s="3">
@@ -6209,13 +6202,13 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="49">
+      <c r="T56" s="48">
         <v>20</v>
       </c>
-      <c r="U56" s="49">
-        <v>0</v>
-      </c>
-      <c r="V56" s="57" t="s">
+      <c r="U56" s="48">
+        <v>0</v>
+      </c>
+      <c r="V56" s="56" t="s">
         <v>88</v>
       </c>
       <c r="W56" s="3" t="s">
@@ -6224,12 +6217,12 @@
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="58">
+      <c r="Y56" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:25">
-      <c r="A57" s="49">
+      <c r="A57" s="48">
         <v>20080011</v>
       </c>
       <c r="B57" s="3">
@@ -6244,7 +6237,7 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="63" t="s">
+      <c r="F57" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G57" s="3" t="s">
@@ -6253,10 +6246,10 @@
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="50">
+      <c r="I57" s="49">
         <v>1980000</v>
       </c>
-      <c r="J57" s="53" t="s">
+      <c r="J57" s="52" t="s">
         <v>90</v>
       </c>
       <c r="K57" s="3">
@@ -6265,7 +6258,7 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="54" t="s">
+      <c r="M57" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N57" s="3">
@@ -6286,13 +6279,13 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="49">
+      <c r="T57" s="48">
         <v>20</v>
       </c>
-      <c r="U57" s="49">
-        <v>0</v>
-      </c>
-      <c r="V57" s="57" t="s">
+      <c r="U57" s="48">
+        <v>0</v>
+      </c>
+      <c r="V57" s="56" t="s">
         <v>57</v>
       </c>
       <c r="W57" s="3" t="s">
@@ -6301,12 +6294,12 @@
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="58">
+      <c r="Y57" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:25">
-      <c r="A58" s="49">
+      <c r="A58" s="48">
         <v>20080012</v>
       </c>
       <c r="B58" s="3">
@@ -6321,7 +6314,7 @@
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="63" t="s">
+      <c r="F58" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G58" s="3" t="s">
@@ -6330,10 +6323,10 @@
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="50">
+      <c r="I58" s="49">
         <v>1980000</v>
       </c>
-      <c r="J58" s="53" t="s">
+      <c r="J58" s="52" t="s">
         <v>92</v>
       </c>
       <c r="K58" s="3">
@@ -6342,7 +6335,7 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="54" t="s">
+      <c r="M58" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N58" s="3">
@@ -6363,13 +6356,13 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="49">
+      <c r="T58" s="48">
         <v>20</v>
       </c>
-      <c r="U58" s="49">
-        <v>0</v>
-      </c>
-      <c r="V58" s="57" t="s">
+      <c r="U58" s="48">
+        <v>0</v>
+      </c>
+      <c r="V58" s="56" t="s">
         <v>61</v>
       </c>
       <c r="W58" s="3" t="s">
@@ -6378,12 +6371,12 @@
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="58">
+      <c r="Y58" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:25">
-      <c r="A59" s="49">
+      <c r="A59" s="48">
         <v>20090010</v>
       </c>
       <c r="B59" s="3">
@@ -6398,7 +6391,7 @@
       <c r="E59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="63" t="s">
+      <c r="F59" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G59" s="3" t="s">
@@ -6407,10 +6400,10 @@
       <c r="H59" s="3">
         <v>1</v>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="49">
         <v>1980000</v>
       </c>
-      <c r="J59" s="53" t="s">
+      <c r="J59" s="52" t="s">
         <v>87</v>
       </c>
       <c r="K59" s="3">
@@ -6419,7 +6412,7 @@
       <c r="L59" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M59" s="54" t="s">
+      <c r="M59" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N59" s="3">
@@ -6440,13 +6433,13 @@
       <c r="S59" s="3">
         <v>16008</v>
       </c>
-      <c r="T59" s="49">
+      <c r="T59" s="48">
         <v>20</v>
       </c>
-      <c r="U59" s="49">
-        <v>0</v>
-      </c>
-      <c r="V59" s="57" t="s">
+      <c r="U59" s="48">
+        <v>0</v>
+      </c>
+      <c r="V59" s="56" t="s">
         <v>88</v>
       </c>
       <c r="W59" s="3" t="s">
@@ -6455,12 +6448,12 @@
       <c r="X59" s="3">
         <v>1</v>
       </c>
-      <c r="Y59" s="58">
+      <c r="Y59" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:25">
-      <c r="A60" s="49">
+      <c r="A60" s="48">
         <v>20090011</v>
       </c>
       <c r="B60" s="3">
@@ -6475,7 +6468,7 @@
       <c r="E60" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F60" s="63" t="s">
+      <c r="F60" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G60" s="3" t="s">
@@ -6484,10 +6477,10 @@
       <c r="H60" s="3">
         <v>2</v>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="49">
         <v>1980000</v>
       </c>
-      <c r="J60" s="53" t="s">
+      <c r="J60" s="52" t="s">
         <v>90</v>
       </c>
       <c r="K60" s="3">
@@ -6496,7 +6489,7 @@
       <c r="L60" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M60" s="54" t="s">
+      <c r="M60" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N60" s="3">
@@ -6517,13 +6510,13 @@
       <c r="S60" s="3">
         <v>16008</v>
       </c>
-      <c r="T60" s="49">
+      <c r="T60" s="48">
         <v>20</v>
       </c>
-      <c r="U60" s="49">
-        <v>0</v>
-      </c>
-      <c r="V60" s="57" t="s">
+      <c r="U60" s="48">
+        <v>0</v>
+      </c>
+      <c r="V60" s="56" t="s">
         <v>57</v>
       </c>
       <c r="W60" s="3" t="s">
@@ -6532,12 +6525,12 @@
       <c r="X60" s="3">
         <v>1</v>
       </c>
-      <c r="Y60" s="58">
+      <c r="Y60" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:25">
-      <c r="A61" s="49">
+      <c r="A61" s="48">
         <v>20090012</v>
       </c>
       <c r="B61" s="3">
@@ -6552,7 +6545,7 @@
       <c r="E61" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F61" s="63" t="s">
+      <c r="F61" s="62" t="s">
         <v>52</v>
       </c>
       <c r="G61" s="3" t="s">
@@ -6561,10 +6554,10 @@
       <c r="H61" s="3">
         <v>3</v>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="49">
         <v>1980000</v>
       </c>
-      <c r="J61" s="53" t="s">
+      <c r="J61" s="52" t="s">
         <v>92</v>
       </c>
       <c r="K61" s="3">
@@ -6573,7 +6566,7 @@
       <c r="L61" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M61" s="54" t="s">
+      <c r="M61" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N61" s="3">
@@ -6594,13 +6587,13 @@
       <c r="S61" s="3">
         <v>16008</v>
       </c>
-      <c r="T61" s="49">
+      <c r="T61" s="48">
         <v>20</v>
       </c>
-      <c r="U61" s="49">
-        <v>0</v>
-      </c>
-      <c r="V61" s="57" t="s">
+      <c r="U61" s="48">
+        <v>0</v>
+      </c>
+      <c r="V61" s="56" t="s">
         <v>61</v>
       </c>
       <c r="W61" s="3" t="s">
@@ -6609,7 +6602,7 @@
       <c r="X61" s="3">
         <v>1</v>
       </c>
-      <c r="Y61" s="58">
+      <c r="Y61" s="57">
         <v>0</v>
       </c>
     </row>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -2199,7 +2199,7 @@
         <v>56</v>
       </c>
       <c r="N5" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O5" s="4">
         <v>300</v>
@@ -2278,7 +2278,7 @@
         <v>56</v>
       </c>
       <c r="N6" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O6" s="4">
         <v>300</v>
@@ -2357,7 +2357,7 @@
         <v>56</v>
       </c>
       <c r="N7" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O7" s="4">
         <v>300</v>
@@ -2436,7 +2436,7 @@
         <v>69</v>
       </c>
       <c r="N8" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O8" s="4">
         <v>300</v>
@@ -2515,7 +2515,7 @@
         <v>69</v>
       </c>
       <c r="N9" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O9" s="4">
         <v>300</v>
@@ -2594,7 +2594,7 @@
         <v>69</v>
       </c>
       <c r="N10" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O10" s="4">
         <v>300</v>
@@ -2673,7 +2673,7 @@
         <v>71</v>
       </c>
       <c r="N11" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O11" s="4">
         <v>300</v>
@@ -2752,7 +2752,7 @@
         <v>71</v>
       </c>
       <c r="N12" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O12" s="4">
         <v>300</v>
@@ -2831,7 +2831,7 @@
         <v>71</v>
       </c>
       <c r="N13" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O13" s="4">
         <v>300</v>
@@ -2910,7 +2910,7 @@
         <v>73</v>
       </c>
       <c r="N14" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O14" s="4">
         <v>300</v>
@@ -2989,7 +2989,7 @@
         <v>73</v>
       </c>
       <c r="N15" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O15" s="4">
         <v>300</v>
@@ -3068,7 +3068,7 @@
         <v>73</v>
       </c>
       <c r="N16" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O16" s="4">
         <v>300</v>
@@ -3147,7 +3147,7 @@
         <v>75</v>
       </c>
       <c r="N17" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O17" s="4">
         <v>300</v>
@@ -3226,7 +3226,7 @@
         <v>75</v>
       </c>
       <c r="N18" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O18" s="4">
         <v>300</v>
@@ -3305,7 +3305,7 @@
         <v>75</v>
       </c>
       <c r="N19" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O19" s="4">
         <v>300</v>
@@ -3384,7 +3384,7 @@
         <v>77</v>
       </c>
       <c r="N20" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O20" s="4">
         <v>300</v>
@@ -3463,7 +3463,7 @@
         <v>77</v>
       </c>
       <c r="N21" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O21" s="4">
         <v>300</v>
@@ -3542,7 +3542,7 @@
         <v>77</v>
       </c>
       <c r="N22" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O22" s="4">
         <v>300</v>
@@ -3621,7 +3621,7 @@
         <v>79</v>
       </c>
       <c r="N23" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O23" s="4">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>79</v>
       </c>
       <c r="N24" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O24" s="4">
         <v>0</v>
@@ -3779,7 +3779,7 @@
         <v>79</v>
       </c>
       <c r="N25" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O25" s="4">
         <v>0</v>
@@ -3858,7 +3858,7 @@
         <v>81</v>
       </c>
       <c r="N26" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O26" s="4">
         <v>300</v>
@@ -3937,7 +3937,7 @@
         <v>81</v>
       </c>
       <c r="N27" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O27" s="4">
         <v>300</v>
@@ -4016,7 +4016,7 @@
         <v>81</v>
       </c>
       <c r="N28" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O28" s="4">
         <v>300</v>
@@ -4095,7 +4095,7 @@
         <v>81</v>
       </c>
       <c r="N29" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O29" s="4">
         <v>300</v>
@@ -4174,7 +4174,7 @@
         <v>81</v>
       </c>
       <c r="N30" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O30" s="4">
         <v>300</v>
@@ -4253,7 +4253,7 @@
         <v>81</v>
       </c>
       <c r="N31" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O31" s="4">
         <v>300</v>
@@ -4332,7 +4332,7 @@
         <v>85</v>
       </c>
       <c r="N32" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O32" s="4">
         <v>300</v>
@@ -4411,7 +4411,7 @@
         <v>85</v>
       </c>
       <c r="N33" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O33" s="4">
         <v>300</v>
@@ -4490,7 +4490,7 @@
         <v>85</v>
       </c>
       <c r="N34" s="4">
-        <v>9700</v>
+        <v>9000</v>
       </c>
       <c r="O34" s="4">
         <v>300</v>
@@ -4568,7 +4568,7 @@
         <v>56</v>
       </c>
       <c r="N35" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O35" s="3">
         <v>300</v>
@@ -4645,7 +4645,7 @@
         <v>56</v>
       </c>
       <c r="N36" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O36" s="3">
         <v>300</v>
@@ -4722,7 +4722,7 @@
         <v>56</v>
       </c>
       <c r="N37" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O37" s="3">
         <v>300</v>
@@ -4799,7 +4799,7 @@
         <v>69</v>
       </c>
       <c r="N38" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O38" s="3">
         <v>300</v>
@@ -4876,7 +4876,7 @@
         <v>69</v>
       </c>
       <c r="N39" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O39" s="3">
         <v>300</v>
@@ -4953,7 +4953,7 @@
         <v>69</v>
       </c>
       <c r="N40" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O40" s="3">
         <v>300</v>
@@ -5030,7 +5030,7 @@
         <v>71</v>
       </c>
       <c r="N41" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O41" s="3">
         <v>300</v>
@@ -5107,7 +5107,7 @@
         <v>71</v>
       </c>
       <c r="N42" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O42" s="3">
         <v>300</v>
@@ -5184,7 +5184,7 @@
         <v>71</v>
       </c>
       <c r="N43" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O43" s="3">
         <v>300</v>
@@ -5261,7 +5261,7 @@
         <v>73</v>
       </c>
       <c r="N44" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
@@ -5338,7 +5338,7 @@
         <v>73</v>
       </c>
       <c r="N45" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O45" s="3">
         <v>300</v>
@@ -5415,7 +5415,7 @@
         <v>73</v>
       </c>
       <c r="N46" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O46" s="3">
         <v>300</v>
@@ -5492,7 +5492,7 @@
         <v>75</v>
       </c>
       <c r="N47" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
@@ -5569,7 +5569,7 @@
         <v>75</v>
       </c>
       <c r="N48" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -5646,7 +5646,7 @@
         <v>75</v>
       </c>
       <c r="N49" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
@@ -5723,7 +5723,7 @@
         <v>77</v>
       </c>
       <c r="N50" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O50" s="3">
         <v>300</v>
@@ -5800,7 +5800,7 @@
         <v>77</v>
       </c>
       <c r="N51" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O51" s="3">
         <v>300</v>
@@ -5877,7 +5877,7 @@
         <v>77</v>
       </c>
       <c r="N52" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
@@ -5954,7 +5954,7 @@
         <v>79</v>
       </c>
       <c r="N53" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O53" s="3">
         <v>0</v>
@@ -6031,7 +6031,7 @@
         <v>79</v>
       </c>
       <c r="N54" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O54" s="3">
         <v>0</v>
@@ -6108,7 +6108,7 @@
         <v>79</v>
       </c>
       <c r="N55" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O55" s="3">
         <v>0</v>
@@ -6185,7 +6185,7 @@
         <v>81</v>
       </c>
       <c r="N56" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O56" s="3">
         <v>300</v>
@@ -6262,7 +6262,7 @@
         <v>81</v>
       </c>
       <c r="N57" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O57" s="3">
         <v>300</v>
@@ -6339,7 +6339,7 @@
         <v>81</v>
       </c>
       <c r="N58" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
@@ -6416,7 +6416,7 @@
         <v>81</v>
       </c>
       <c r="N59" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
@@ -6493,7 +6493,7 @@
         <v>81</v>
       </c>
       <c r="N60" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O60" s="3">
         <v>300</v>
@@ -6570,7 +6570,7 @@
         <v>81</v>
       </c>
       <c r="N61" s="3">
-        <v>9700</v>
+        <v>9200</v>
       </c>
       <c r="O61" s="3">
         <v>300</v>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -330,7 +330,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="87">
   <si>
     <t>游戏ID</t>
   </si>
@@ -494,7 +494,7 @@
     <t>0:6:28|6:12:36|12:18:45|18:24:43</t>
   </si>
   <si>
-    <t>50_100_200_500_1000_2000_5000</t>
+    <t>1000_2000_5000_10000_20000_50000_100000</t>
   </si>
   <si>
     <t>组合</t>
@@ -503,34 +503,34 @@
     <t>1000,16000,8000,0</t>
   </si>
   <si>
-    <t>500000_17001</t>
-  </si>
-  <si>
-    <t>1990000_100000</t>
+    <t>5000000_17001</t>
+  </si>
+  <si>
+    <t>1990000_500000</t>
   </si>
   <si>
     <t>中级场</t>
   </si>
   <si>
-    <t>5000_10000_20000_50000_100000_200000_500000</t>
+    <t>10000_20000_50000_100000_200000_500000_1000000</t>
   </si>
   <si>
     <t>50000000_17001</t>
   </si>
   <si>
-    <t>1990000_10000000</t>
+    <t>1990000_5000000</t>
   </si>
   <si>
     <t>高级场</t>
   </si>
   <si>
-    <t>500000_1000000_2000000_5000000_10000000_20000000_50000000</t>
-  </si>
-  <si>
-    <t>5000000000_17001</t>
-  </si>
-  <si>
-    <t>1990000_100000000</t>
+    <t>100000_200000_500000_1000000_2000000_5000000_10000000</t>
+  </si>
+  <si>
+    <t>500000000_17001</t>
+  </si>
+  <si>
+    <t>1990000_50000000</t>
   </si>
   <si>
     <t>龙虎斗</t>
@@ -581,37 +581,16 @@
     <t>鱼虾蟹</t>
   </si>
   <si>
-    <t>水果机</t>
-  </si>
-  <si>
-    <t>0:24:0</t>
-  </si>
-  <si>
-    <t>0,16000,10000,4000</t>
-  </si>
-  <si>
     <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
   </si>
   <si>
-    <t>50_100_200_500_1000</t>
-  </si>
-  <si>
-    <t>5000_17001</t>
-  </si>
-  <si>
-    <t>1980000_1000</t>
-  </si>
-  <si>
-    <t>1000_2000_5000_10000_20000</t>
-  </si>
-  <si>
-    <t>1980000_100000</t>
-  </si>
-  <si>
-    <t>20000_50000_100000_200000_500000</t>
-  </si>
-  <si>
-    <t>1980000_10000000</t>
+    <t>1980000_500000</t>
+  </si>
+  <si>
+    <t>1980000_5000000</t>
+  </si>
+  <si>
+    <t>1980000_50000000</t>
   </si>
 </sst>
 </file>
@@ -1378,6 +1357,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1414,14 +1396,20 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1484,7 +1472,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1513,9 +1501,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1530,10 +1515,6 @@
     <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1543,7 +1524,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1553,9 +1533,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
@@ -1896,10 +1873,10 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:Y58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="4"/>
+    <col min="1" max="1" width="9.375" style="4"/>
     <col min="2" max="2" width="12" style="4" customWidth="1"/>
     <col min="3" max="4" width="20.625" style="4" customWidth="1"/>
     <col min="5" max="5" width="8.625" style="4" customWidth="1"/>
@@ -1916,61 +1893,61 @@
     <col min="16" max="19" width="9.81666666666667" style="4" customWidth="1"/>
     <col min="20" max="20" width="17.2166666666667" style="6" customWidth="1"/>
     <col min="21" max="22" width="19.5" style="7" customWidth="1"/>
-    <col min="23" max="23" width="19.125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="19.125" style="8" customWidth="1"/>
     <col min="24" max="24" width="12.875" style="2" customWidth="1"/>
-    <col min="25" max="25" width="20.125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="20.125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:25">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="9"/>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="13" t="s">
+      <c r="L1" s="13"/>
+      <c r="M1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="19" t="s">
         <v>15</v>
       </c>
       <c r="T1" s="6" t="s">
@@ -1982,13 +1959,13 @@
       <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="20" t="s">
         <v>19</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="19" t="s">
+      <c r="Y1" s="21" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2000,7 +1977,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="22" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="4"/>
@@ -2050,16 +2027,16 @@
       <c r="U2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="21" t="s">
+      <c r="V2" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="24" t="s">
         <v>25</v>
       </c>
       <c r="X2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="Y2" s="25" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2124,69 +2101,71 @@
       <c r="V3" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W3" s="20" t="s">
         <v>47</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Y3" s="22" t="s">
+      <c r="Y3" s="25" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:25">
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
       <c r="T4" s="6"/>
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
+      <c r="W4" s="20"/>
+      <c r="Y4" s="20"/>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="4">
         <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="32">
         <v>200100</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="32">
         <v>200100038</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="32" t="s">
         <v>51</v>
       </c>
       <c r="F5" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="29">
-        <v>1</v>
-      </c>
-      <c r="I5" s="32">
+      <c r="H5" s="32">
+        <v>1</v>
+      </c>
+      <c r="I5" s="35">
         <v>1990000</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K5" s="4">
@@ -2195,11 +2174,11 @@
       <c r="L5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="M5" s="37" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O5" s="4">
         <v>300</v>
@@ -2213,27 +2192,27 @@
       <c r="R5" s="4">
         <v>15000</v>
       </c>
-      <c r="S5" s="35">
+      <c r="S5" s="38">
         <v>16008</v>
       </c>
       <c r="T5" s="6">
         <v>48</v>
       </c>
-      <c r="U5" s="36">
+      <c r="U5" s="39">
         <v>0</v>
       </c>
       <c r="V5" t="s">
         <v>57</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="W5" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X5" s="2">
         <v>0</v>
       </c>
-      <c r="Y5" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y5" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -2241,31 +2220,31 @@
         <f t="shared" si="0"/>
         <v>2001002</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="40">
         <v>200100</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="40">
         <v>200100038</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="40">
         <v>2</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="35">
         <v>1990000</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="J6" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="4">
@@ -2274,11 +2253,11 @@
       <c r="L6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="M6" s="37" t="s">
         <v>56</v>
       </c>
       <c r="N6" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O6" s="4">
         <v>300</v>
@@ -2292,27 +2271,27 @@
       <c r="R6" s="4">
         <v>15000</v>
       </c>
-      <c r="S6" s="35">
+      <c r="S6" s="38">
         <v>16008</v>
       </c>
       <c r="T6" s="6">
         <v>48</v>
       </c>
-      <c r="U6" s="36">
+      <c r="U6" s="39">
         <v>0</v>
       </c>
       <c r="V6" t="s">
         <v>61</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="W6" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X6" s="2">
         <v>0</v>
       </c>
-      <c r="Y6" s="2">
-        <f t="shared" ref="Y6:Y10" si="1">Y5*100</f>
-        <v>5000000000</v>
+      <c r="Y6" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:25">
@@ -2320,31 +2299,31 @@
         <f t="shared" si="0"/>
         <v>2001003</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="32">
         <v>200100</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="32">
         <v>200100038</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F7" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="32">
         <v>3</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="35">
         <v>1990000</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K7" s="4">
@@ -2353,11 +2332,11 @@
       <c r="L7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="34" t="s">
+      <c r="M7" s="37" t="s">
         <v>56</v>
       </c>
       <c r="N7" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O7" s="4">
         <v>300</v>
@@ -2371,27 +2350,27 @@
       <c r="R7" s="4">
         <v>15000</v>
       </c>
-      <c r="S7" s="35">
+      <c r="S7" s="38">
         <v>16008</v>
       </c>
       <c r="T7" s="6">
         <v>48</v>
       </c>
-      <c r="U7" s="36">
+      <c r="U7" s="39">
         <v>0</v>
       </c>
       <c r="V7" t="s">
         <v>65</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W7" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X7" s="2">
         <v>0</v>
       </c>
-      <c r="Y7" s="39">
-        <f t="shared" si="1"/>
-        <v>500000000000</v>
+      <c r="Y7" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:25">
@@ -2399,31 +2378,31 @@
         <f t="shared" si="0"/>
         <v>2001011</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="32">
         <v>200101</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="32">
         <v>200101001</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="43" t="s">
         <v>51</v>
       </c>
       <c r="F8" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="29">
-        <v>1</v>
-      </c>
-      <c r="I8" s="32">
+      <c r="H8" s="32">
+        <v>1</v>
+      </c>
+      <c r="I8" s="35">
         <v>1990000</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K8" s="4">
@@ -2432,11 +2411,11 @@
       <c r="L8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="M8" s="37" t="s">
         <v>69</v>
       </c>
       <c r="N8" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O8" s="4">
         <v>300</v>
@@ -2450,27 +2429,27 @@
       <c r="R8" s="4">
         <v>15000</v>
       </c>
-      <c r="S8" s="35">
+      <c r="S8" s="38">
         <v>16008</v>
       </c>
       <c r="T8" s="6">
         <v>48</v>
       </c>
-      <c r="U8" s="36">
+      <c r="U8" s="39">
         <v>0</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="W8" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X8" s="2">
         <v>0</v>
       </c>
-      <c r="Y8" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y8" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -2478,31 +2457,31 @@
         <f t="shared" si="0"/>
         <v>2001012</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="40">
         <v>200101</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="40">
         <v>200101001</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F9" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="40">
         <v>2</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="35">
         <v>1990000</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K9" s="4">
@@ -2511,11 +2490,11 @@
       <c r="L9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M9" s="34" t="s">
+      <c r="M9" s="37" t="s">
         <v>69</v>
       </c>
       <c r="N9" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O9" s="4">
         <v>300</v>
@@ -2529,27 +2508,27 @@
       <c r="R9" s="4">
         <v>15000</v>
       </c>
-      <c r="S9" s="35">
+      <c r="S9" s="38">
         <v>16008</v>
       </c>
       <c r="T9" s="6">
         <v>48</v>
       </c>
-      <c r="U9" s="36">
+      <c r="U9" s="39">
         <v>0</v>
       </c>
       <c r="V9" t="s">
         <v>61</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="W9" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X9" s="2">
         <v>0</v>
       </c>
-      <c r="Y9" s="2">
-        <f t="shared" si="1"/>
-        <v>5000000000</v>
+      <c r="Y9" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -2557,31 +2536,31 @@
         <f t="shared" si="0"/>
         <v>2001013</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="32">
         <v>200101</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="32">
         <v>200101001</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F10" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="32">
         <v>3</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="35">
         <v>1990000</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="J10" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K10" s="4">
@@ -2590,11 +2569,11 @@
       <c r="L10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="34" t="s">
+      <c r="M10" s="37" t="s">
         <v>69</v>
       </c>
       <c r="N10" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O10" s="4">
         <v>300</v>
@@ -2608,27 +2587,27 @@
       <c r="R10" s="4">
         <v>15000</v>
       </c>
-      <c r="S10" s="35">
+      <c r="S10" s="38">
         <v>16008</v>
       </c>
       <c r="T10" s="6">
         <v>48</v>
       </c>
-      <c r="U10" s="36">
+      <c r="U10" s="39">
         <v>0</v>
       </c>
       <c r="V10" t="s">
         <v>65</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="W10" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X10" s="2">
         <v>0</v>
       </c>
-      <c r="Y10" s="39">
-        <f t="shared" si="1"/>
-        <v>500000000000</v>
+      <c r="Y10" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -2636,31 +2615,31 @@
         <f t="shared" si="0"/>
         <v>2003001</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="32">
         <v>200300</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="32">
         <v>200300001</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="44" t="s">
         <v>51</v>
       </c>
       <c r="F11" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="29">
-        <v>1</v>
-      </c>
-      <c r="I11" s="32">
+      <c r="H11" s="32">
+        <v>1</v>
+      </c>
+      <c r="I11" s="35">
         <v>1990000</v>
       </c>
-      <c r="J11" s="33" t="s">
+      <c r="J11" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K11" s="4">
@@ -2669,11 +2648,11 @@
       <c r="L11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="34" t="s">
+      <c r="M11" s="37" t="s">
         <v>71</v>
       </c>
       <c r="N11" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O11" s="4">
         <v>300</v>
@@ -2687,27 +2666,27 @@
       <c r="R11" s="4">
         <v>15000</v>
       </c>
-      <c r="S11" s="35">
+      <c r="S11" s="38">
         <v>16008</v>
       </c>
       <c r="T11" s="6">
         <v>50</v>
       </c>
-      <c r="U11" s="36">
+      <c r="U11" s="39">
         <v>0</v>
       </c>
       <c r="V11" t="s">
         <v>57</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="W11" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X11" s="2">
         <v>0</v>
       </c>
-      <c r="Y11" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y11" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:25">
@@ -2715,31 +2694,31 @@
         <f t="shared" si="0"/>
         <v>2003002</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="40">
         <v>200300</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="40">
         <v>200300001</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F12" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="40">
         <v>2</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="35">
         <v>1990000</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K12" s="4">
@@ -2748,11 +2727,11 @@
       <c r="L12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="34" t="s">
+      <c r="M12" s="37" t="s">
         <v>71</v>
       </c>
       <c r="N12" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O12" s="4">
         <v>300</v>
@@ -2766,27 +2745,27 @@
       <c r="R12" s="4">
         <v>15000</v>
       </c>
-      <c r="S12" s="35">
+      <c r="S12" s="38">
         <v>16008</v>
       </c>
       <c r="T12" s="6">
         <v>50</v>
       </c>
-      <c r="U12" s="36">
+      <c r="U12" s="39">
         <v>0</v>
       </c>
       <c r="V12" t="s">
         <v>61</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="W12" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X12" s="2">
         <v>0</v>
       </c>
-      <c r="Y12" s="2">
-        <f t="shared" ref="Y12:Y16" si="2">Y11*100</f>
-        <v>5000000000</v>
+      <c r="Y12" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2794,31 +2773,31 @@
         <f t="shared" si="0"/>
         <v>2003003</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="32">
         <v>200300</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="32">
         <v>200300001</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F13" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="32">
         <v>3</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="35">
         <v>1990000</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="J13" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K13" s="4">
@@ -2827,11 +2806,11 @@
       <c r="L13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="34" t="s">
+      <c r="M13" s="37" t="s">
         <v>71</v>
       </c>
       <c r="N13" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O13" s="4">
         <v>300</v>
@@ -2845,27 +2824,27 @@
       <c r="R13" s="4">
         <v>15000</v>
       </c>
-      <c r="S13" s="35">
+      <c r="S13" s="38">
         <v>16008</v>
       </c>
       <c r="T13" s="6">
         <v>50</v>
       </c>
-      <c r="U13" s="36">
+      <c r="U13" s="39">
         <v>0</v>
       </c>
       <c r="V13" t="s">
         <v>65</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="W13" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X13" s="2">
         <v>0</v>
       </c>
-      <c r="Y13" s="39">
-        <f t="shared" si="2"/>
-        <v>500000000000</v>
+      <c r="Y13" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2873,31 +2852,31 @@
         <f t="shared" si="0"/>
         <v>2004001</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="32">
         <v>200400</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="32">
         <v>200400009</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="43" t="s">
         <v>51</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="29">
-        <v>1</v>
-      </c>
-      <c r="I14" s="32">
+      <c r="H14" s="32">
+        <v>1</v>
+      </c>
+      <c r="I14" s="35">
         <v>1990000</v>
       </c>
-      <c r="J14" s="33" t="s">
+      <c r="J14" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="4">
@@ -2906,11 +2885,11 @@
       <c r="L14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="34" t="s">
+      <c r="M14" s="37" t="s">
         <v>73</v>
       </c>
       <c r="N14" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O14" s="4">
         <v>300</v>
@@ -2924,27 +2903,27 @@
       <c r="R14" s="4">
         <v>15000</v>
       </c>
-      <c r="S14" s="35">
+      <c r="S14" s="38">
         <v>16008</v>
       </c>
       <c r="T14" s="6">
         <v>50</v>
       </c>
-      <c r="U14" s="36">
+      <c r="U14" s="39">
         <v>0</v>
       </c>
       <c r="V14" t="s">
         <v>57</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="W14" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X14" s="2">
         <v>0</v>
       </c>
-      <c r="Y14" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y14" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2952,31 +2931,31 @@
         <f t="shared" si="0"/>
         <v>2004002</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="40">
         <v>200400</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="40">
         <v>200400009</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F15" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="40">
         <v>2</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="35">
         <v>1990000</v>
       </c>
-      <c r="J15" s="38" t="s">
+      <c r="J15" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K15" s="4">
@@ -2985,11 +2964,11 @@
       <c r="L15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="34" t="s">
+      <c r="M15" s="37" t="s">
         <v>73</v>
       </c>
       <c r="N15" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O15" s="4">
         <v>300</v>
@@ -3003,27 +2982,27 @@
       <c r="R15" s="4">
         <v>15000</v>
       </c>
-      <c r="S15" s="35">
+      <c r="S15" s="38">
         <v>16008</v>
       </c>
       <c r="T15" s="6">
         <v>50</v>
       </c>
-      <c r="U15" s="36">
+      <c r="U15" s="39">
         <v>0</v>
       </c>
       <c r="V15" t="s">
         <v>61</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="W15" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X15" s="2">
         <v>0</v>
       </c>
-      <c r="Y15" s="2">
-        <f t="shared" si="2"/>
-        <v>5000000000</v>
+      <c r="Y15" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:25">
@@ -3031,31 +3010,31 @@
         <f t="shared" si="0"/>
         <v>2004003</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="32">
         <v>200400</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="32">
         <v>200400009</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="32">
         <v>3</v>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="35">
         <v>1990000</v>
       </c>
-      <c r="J16" s="33" t="s">
+      <c r="J16" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K16" s="4">
@@ -3064,11 +3043,11 @@
       <c r="L16" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M16" s="34" t="s">
+      <c r="M16" s="37" t="s">
         <v>73</v>
       </c>
       <c r="N16" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O16" s="4">
         <v>300</v>
@@ -3082,27 +3061,27 @@
       <c r="R16" s="4">
         <v>15000</v>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="38">
         <v>16008</v>
       </c>
       <c r="T16" s="6">
         <v>50</v>
       </c>
-      <c r="U16" s="36">
+      <c r="U16" s="39">
         <v>0</v>
       </c>
       <c r="V16" t="s">
         <v>65</v>
       </c>
-      <c r="W16" s="2" t="s">
+      <c r="W16" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X16" s="2">
         <v>0</v>
       </c>
-      <c r="Y16" s="39">
-        <f t="shared" si="2"/>
-        <v>500000000000</v>
+      <c r="Y16" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:25">
@@ -3110,31 +3089,31 @@
         <f t="shared" si="0"/>
         <v>2005001</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="32">
         <v>200500</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="32">
         <v>200500025</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="32" t="s">
         <v>51</v>
       </c>
       <c r="F17" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H17" s="29">
-        <v>1</v>
-      </c>
-      <c r="I17" s="32">
+      <c r="H17" s="32">
+        <v>1</v>
+      </c>
+      <c r="I17" s="35">
         <v>1990000</v>
       </c>
-      <c r="J17" s="33" t="s">
+      <c r="J17" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K17" s="4">
@@ -3143,11 +3122,11 @@
       <c r="L17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="34" t="s">
+      <c r="M17" s="37" t="s">
         <v>75</v>
       </c>
       <c r="N17" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O17" s="4">
         <v>300</v>
@@ -3161,27 +3140,27 @@
       <c r="R17" s="4">
         <v>15000</v>
       </c>
-      <c r="S17" s="35">
+      <c r="S17" s="38">
         <v>16008</v>
       </c>
       <c r="T17" s="6">
         <v>48</v>
       </c>
-      <c r="U17" s="36">
+      <c r="U17" s="39">
         <v>0</v>
       </c>
       <c r="V17" t="s">
         <v>57</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="W17" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
       </c>
-      <c r="Y17" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y17" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -3189,31 +3168,31 @@
         <f t="shared" si="0"/>
         <v>2005002</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="40">
         <v>200500</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="40">
         <v>200500025</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F18" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="40">
         <v>2</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="35">
         <v>1990000</v>
       </c>
-      <c r="J18" s="38" t="s">
+      <c r="J18" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K18" s="4">
@@ -3222,11 +3201,11 @@
       <c r="L18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="34" t="s">
+      <c r="M18" s="37" t="s">
         <v>75</v>
       </c>
       <c r="N18" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O18" s="4">
         <v>300</v>
@@ -3240,27 +3219,27 @@
       <c r="R18" s="4">
         <v>15000</v>
       </c>
-      <c r="S18" s="35">
+      <c r="S18" s="38">
         <v>16008</v>
       </c>
       <c r="T18" s="6">
         <v>48</v>
       </c>
-      <c r="U18" s="36">
+      <c r="U18" s="39">
         <v>0</v>
       </c>
       <c r="V18" t="s">
         <v>61</v>
       </c>
-      <c r="W18" s="2" t="s">
+      <c r="W18" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X18" s="2">
         <v>0</v>
       </c>
-      <c r="Y18" s="2">
-        <f t="shared" ref="Y18:Y22" si="3">Y17*100</f>
-        <v>5000000000</v>
+      <c r="Y18" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -3268,31 +3247,31 @@
         <f t="shared" si="0"/>
         <v>2005003</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="32">
         <v>200500</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="32">
         <v>200500025</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F19" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="32">
         <v>3</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="35">
         <v>1990000</v>
       </c>
-      <c r="J19" s="33" t="s">
+      <c r="J19" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K19" s="4">
@@ -3301,11 +3280,11 @@
       <c r="L19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="34" t="s">
+      <c r="M19" s="37" t="s">
         <v>75</v>
       </c>
       <c r="N19" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O19" s="4">
         <v>300</v>
@@ -3319,27 +3298,27 @@
       <c r="R19" s="4">
         <v>15000</v>
       </c>
-      <c r="S19" s="35">
+      <c r="S19" s="38">
         <v>16008</v>
       </c>
       <c r="T19" s="6">
         <v>48</v>
       </c>
-      <c r="U19" s="36">
+      <c r="U19" s="39">
         <v>0</v>
       </c>
       <c r="V19" t="s">
         <v>65</v>
       </c>
-      <c r="W19" s="2" t="s">
+      <c r="W19" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X19" s="2">
         <v>0</v>
       </c>
-      <c r="Y19" s="39">
-        <f t="shared" si="3"/>
-        <v>500000000000</v>
+      <c r="Y19" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -3347,31 +3326,31 @@
         <f t="shared" si="0"/>
         <v>2006001</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="32">
         <v>200600</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="32">
         <v>200600001</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="44" t="s">
         <v>51</v>
       </c>
       <c r="F20" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="29">
-        <v>1</v>
-      </c>
-      <c r="I20" s="32">
+      <c r="H20" s="32">
+        <v>1</v>
+      </c>
+      <c r="I20" s="35">
         <v>1990000</v>
       </c>
-      <c r="J20" s="33" t="s">
+      <c r="J20" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K20" s="4">
@@ -3380,11 +3359,11 @@
       <c r="L20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M20" s="37" t="s">
         <v>77</v>
       </c>
       <c r="N20" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O20" s="4">
         <v>300</v>
@@ -3398,27 +3377,27 @@
       <c r="R20" s="4">
         <v>15000</v>
       </c>
-      <c r="S20" s="35">
+      <c r="S20" s="38">
         <v>16008</v>
       </c>
       <c r="T20" s="6">
         <v>20</v>
       </c>
-      <c r="U20" s="36">
+      <c r="U20" s="39">
         <v>0</v>
       </c>
       <c r="V20" t="s">
         <v>57</v>
       </c>
-      <c r="W20" s="2" t="s">
+      <c r="W20" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X20" s="2">
         <v>0</v>
       </c>
-      <c r="Y20" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y20" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:25">
@@ -3426,31 +3405,31 @@
         <f t="shared" si="0"/>
         <v>2006002</v>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="40">
         <v>200600</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="40">
         <v>200600001</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="E21" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F21" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="37">
+      <c r="H21" s="40">
         <v>2</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="35">
         <v>1990000</v>
       </c>
-      <c r="J21" s="38" t="s">
+      <c r="J21" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K21" s="4">
@@ -3459,11 +3438,11 @@
       <c r="L21" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="34" t="s">
+      <c r="M21" s="37" t="s">
         <v>77</v>
       </c>
       <c r="N21" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O21" s="4">
         <v>300</v>
@@ -3477,27 +3456,27 @@
       <c r="R21" s="4">
         <v>15000</v>
       </c>
-      <c r="S21" s="35">
+      <c r="S21" s="38">
         <v>16008</v>
       </c>
       <c r="T21" s="6">
         <v>20</v>
       </c>
-      <c r="U21" s="36">
+      <c r="U21" s="39">
         <v>0</v>
       </c>
       <c r="V21" t="s">
         <v>61</v>
       </c>
-      <c r="W21" s="2" t="s">
+      <c r="W21" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X21" s="2">
         <v>0</v>
       </c>
-      <c r="Y21" s="2">
-        <f t="shared" si="3"/>
-        <v>5000000000</v>
+      <c r="Y21" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -3505,31 +3484,31 @@
         <f t="shared" si="0"/>
         <v>2006003</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="32">
         <v>200600</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="32">
         <v>200600001</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F22" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="32">
         <v>3</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="35">
         <v>1990000</v>
       </c>
-      <c r="J22" s="33" t="s">
+      <c r="J22" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K22" s="4">
@@ -3538,11 +3517,11 @@
       <c r="L22" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M22" s="34" t="s">
+      <c r="M22" s="37" t="s">
         <v>77</v>
       </c>
       <c r="N22" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O22" s="4">
         <v>300</v>
@@ -3556,27 +3535,27 @@
       <c r="R22" s="4">
         <v>15000</v>
       </c>
-      <c r="S22" s="35">
+      <c r="S22" s="38">
         <v>16008</v>
       </c>
       <c r="T22" s="6">
         <v>20</v>
       </c>
-      <c r="U22" s="36">
+      <c r="U22" s="39">
         <v>0</v>
       </c>
       <c r="V22" t="s">
         <v>65</v>
       </c>
-      <c r="W22" s="2" t="s">
+      <c r="W22" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X22" s="2">
         <v>0</v>
       </c>
-      <c r="Y22" s="39">
-        <f t="shared" si="3"/>
-        <v>500000000000</v>
+      <c r="Y22" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -3584,31 +3563,31 @@
         <f t="shared" si="0"/>
         <v>2007001</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="32">
         <v>200700</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="32">
         <v>200700001</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="32" t="s">
         <v>51</v>
       </c>
       <c r="F23" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H23" s="29">
-        <v>1</v>
-      </c>
-      <c r="I23" s="32">
+      <c r="H23" s="32">
+        <v>1</v>
+      </c>
+      <c r="I23" s="35">
         <v>1990000</v>
       </c>
-      <c r="J23" s="33" t="s">
+      <c r="J23" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K23" s="4">
@@ -3617,11 +3596,11 @@
       <c r="L23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M23" s="34" t="s">
+      <c r="M23" s="37" t="s">
         <v>79</v>
       </c>
       <c r="N23" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O23" s="4">
         <v>0</v>
@@ -3635,27 +3614,27 @@
       <c r="R23" s="4">
         <v>15000</v>
       </c>
-      <c r="S23" s="35">
+      <c r="S23" s="38">
         <v>16008</v>
       </c>
       <c r="T23" s="6">
         <v>30</v>
       </c>
-      <c r="U23" s="36">
+      <c r="U23" s="39">
         <v>1</v>
       </c>
       <c r="V23" t="s">
         <v>57</v>
       </c>
-      <c r="W23" s="2" t="s">
+      <c r="W23" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X23" s="2">
         <v>0</v>
       </c>
-      <c r="Y23" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y23" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -3663,31 +3642,31 @@
         <f t="shared" si="0"/>
         <v>2007002</v>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="40">
         <v>200700</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="37">
+      <c r="D24" s="40">
         <v>200700001</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="E24" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F24" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H24" s="37">
+      <c r="H24" s="40">
         <v>2</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="35">
         <v>1990000</v>
       </c>
-      <c r="J24" s="38" t="s">
+      <c r="J24" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K24" s="4">
@@ -3696,11 +3675,11 @@
       <c r="L24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M24" s="34" t="s">
+      <c r="M24" s="37" t="s">
         <v>79</v>
       </c>
       <c r="N24" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O24" s="4">
         <v>0</v>
@@ -3714,27 +3693,27 @@
       <c r="R24" s="4">
         <v>15000</v>
       </c>
-      <c r="S24" s="35">
+      <c r="S24" s="38">
         <v>16008</v>
       </c>
       <c r="T24" s="6">
         <v>30</v>
       </c>
-      <c r="U24" s="36">
+      <c r="U24" s="39">
         <v>1</v>
       </c>
       <c r="V24" t="s">
         <v>61</v>
       </c>
-      <c r="W24" s="2" t="s">
+      <c r="W24" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X24" s="2">
         <v>0</v>
       </c>
-      <c r="Y24" s="2">
-        <f t="shared" ref="Y24:Y28" si="4">Y23*100</f>
-        <v>5000000000</v>
+      <c r="Y24" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" spans="1:25">
@@ -3742,31 +3721,31 @@
         <f t="shared" si="0"/>
         <v>2007003</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="32">
         <v>200700</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="32">
         <v>200700001</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F25" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="32">
         <v>3</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="35">
         <v>1990000</v>
       </c>
-      <c r="J25" s="33" t="s">
+      <c r="J25" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K25" s="4">
@@ -3775,11 +3754,11 @@
       <c r="L25" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M25" s="34" t="s">
+      <c r="M25" s="37" t="s">
         <v>79</v>
       </c>
       <c r="N25" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O25" s="4">
         <v>0</v>
@@ -3793,27 +3772,27 @@
       <c r="R25" s="4">
         <v>15000</v>
       </c>
-      <c r="S25" s="35">
+      <c r="S25" s="38">
         <v>16008</v>
       </c>
       <c r="T25" s="6">
         <v>30</v>
       </c>
-      <c r="U25" s="36">
+      <c r="U25" s="39">
         <v>1</v>
       </c>
       <c r="V25" t="s">
         <v>65</v>
       </c>
-      <c r="W25" s="2" t="s">
+      <c r="W25" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X25" s="2">
         <v>0</v>
       </c>
-      <c r="Y25" s="39">
-        <f t="shared" si="4"/>
-        <v>500000000000</v>
+      <c r="Y25" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="1:25">
@@ -3821,31 +3800,31 @@
         <f t="shared" si="0"/>
         <v>2008001</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="32">
         <v>200800</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="32">
         <v>200800001</v>
       </c>
-      <c r="E26" s="41" t="s">
+      <c r="E26" s="44" t="s">
         <v>51</v>
       </c>
       <c r="F26" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="29">
-        <v>1</v>
-      </c>
-      <c r="I26" s="32">
+      <c r="H26" s="32">
+        <v>1</v>
+      </c>
+      <c r="I26" s="35">
         <v>1990000</v>
       </c>
-      <c r="J26" s="33" t="s">
+      <c r="J26" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K26" s="4">
@@ -3854,11 +3833,11 @@
       <c r="L26" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M26" s="34" t="s">
+      <c r="M26" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N26" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O26" s="4">
         <v>300</v>
@@ -3872,27 +3851,27 @@
       <c r="R26" s="4">
         <v>15000</v>
       </c>
-      <c r="S26" s="35">
+      <c r="S26" s="38">
         <v>16008</v>
       </c>
       <c r="T26" s="6">
         <v>20</v>
       </c>
-      <c r="U26" s="36">
+      <c r="U26" s="39">
         <v>0</v>
       </c>
       <c r="V26" t="s">
         <v>57</v>
       </c>
-      <c r="W26" s="2" t="s">
+      <c r="W26" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X26" s="2">
         <v>0</v>
       </c>
-      <c r="Y26" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y26" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:25">
@@ -3900,31 +3879,31 @@
         <f t="shared" si="0"/>
         <v>2008002</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="32">
         <v>200800</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="32">
         <v>200800001</v>
       </c>
-      <c r="E27" s="37" t="s">
+      <c r="E27" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F27" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="37">
+      <c r="H27" s="40">
         <v>2</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="35">
         <v>1990000</v>
       </c>
-      <c r="J27" s="38" t="s">
+      <c r="J27" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K27" s="4">
@@ -3933,11 +3912,11 @@
       <c r="L27" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M27" s="34" t="s">
+      <c r="M27" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N27" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O27" s="4">
         <v>300</v>
@@ -3951,27 +3930,27 @@
       <c r="R27" s="4">
         <v>15000</v>
       </c>
-      <c r="S27" s="35">
+      <c r="S27" s="38">
         <v>16008</v>
       </c>
       <c r="T27" s="6">
         <v>20</v>
       </c>
-      <c r="U27" s="36">
+      <c r="U27" s="39">
         <v>0</v>
       </c>
       <c r="V27" t="s">
         <v>61</v>
       </c>
-      <c r="W27" s="2" t="s">
+      <c r="W27" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X27" s="2">
         <v>0</v>
       </c>
-      <c r="Y27" s="2">
-        <f t="shared" si="4"/>
-        <v>5000000000</v>
+      <c r="Y27" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" spans="1:25">
@@ -3979,31 +3958,31 @@
         <f t="shared" si="0"/>
         <v>2008003</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="32">
         <v>200800</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="32">
         <v>200800001</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F28" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="32">
         <v>3</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="35">
         <v>1990000</v>
       </c>
-      <c r="J28" s="33" t="s">
+      <c r="J28" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K28" s="4">
@@ -4012,11 +3991,11 @@
       <c r="L28" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N28" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O28" s="4">
         <v>300</v>
@@ -4030,27 +4009,27 @@
       <c r="R28" s="4">
         <v>15000</v>
       </c>
-      <c r="S28" s="35">
+      <c r="S28" s="38">
         <v>16008</v>
       </c>
       <c r="T28" s="6">
         <v>20</v>
       </c>
-      <c r="U28" s="36">
+      <c r="U28" s="39">
         <v>0</v>
       </c>
       <c r="V28" t="s">
         <v>65</v>
       </c>
-      <c r="W28" s="2" t="s">
+      <c r="W28" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X28" s="2">
         <v>0</v>
       </c>
-      <c r="Y28" s="39">
-        <f t="shared" si="4"/>
-        <v>500000000000</v>
+      <c r="Y28" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:25">
@@ -4058,44 +4037,44 @@
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="42">
+      <c r="B29" s="45">
         <v>200900</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="32">
         <v>200900001</v>
       </c>
-      <c r="E29" s="40" t="s">
+      <c r="E29" s="43" t="s">
         <v>51</v>
       </c>
       <c r="F29" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H29" s="29">
-        <v>1</v>
-      </c>
-      <c r="I29" s="32">
+      <c r="H29" s="32">
+        <v>1</v>
+      </c>
+      <c r="I29" s="35">
         <v>1990000</v>
       </c>
-      <c r="J29" s="33" t="s">
+      <c r="J29" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="43">
+      <c r="K29" s="46">
         <v>0</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M29" s="34" t="s">
+      <c r="M29" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N29" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O29" s="4">
         <v>300</v>
@@ -4109,27 +4088,27 @@
       <c r="R29" s="4">
         <v>15000</v>
       </c>
-      <c r="S29" s="35">
+      <c r="S29" s="38">
         <v>16008</v>
       </c>
       <c r="T29" s="6">
         <v>20</v>
       </c>
-      <c r="U29" s="36">
+      <c r="U29" s="39">
         <v>0</v>
       </c>
       <c r="V29" t="s">
         <v>57</v>
       </c>
-      <c r="W29" s="2" t="s">
+      <c r="W29" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X29" s="2">
         <v>0</v>
       </c>
-      <c r="Y29" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y29" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -4137,44 +4116,44 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="44">
+      <c r="B30" s="47">
         <v>200900</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="40">
         <v>200900001</v>
       </c>
-      <c r="E30" s="37" t="s">
+      <c r="E30" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F30" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="31" t="s">
+      <c r="G30" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="37">
+      <c r="H30" s="40">
         <v>2</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="35">
         <v>1990000</v>
       </c>
-      <c r="J30" s="38" t="s">
+      <c r="J30" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="43">
+      <c r="K30" s="46">
         <v>0</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M30" s="34" t="s">
+      <c r="M30" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N30" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O30" s="4">
         <v>300</v>
@@ -4188,27 +4167,27 @@
       <c r="R30" s="4">
         <v>15000</v>
       </c>
-      <c r="S30" s="35">
+      <c r="S30" s="38">
         <v>16008</v>
       </c>
       <c r="T30" s="6">
         <v>20</v>
       </c>
-      <c r="U30" s="36">
+      <c r="U30" s="39">
         <v>0</v>
       </c>
       <c r="V30" t="s">
         <v>61</v>
       </c>
-      <c r="W30" s="2" t="s">
+      <c r="W30" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X30" s="2">
         <v>0</v>
       </c>
-      <c r="Y30" s="2">
-        <f t="shared" ref="Y30:Y34" si="5">Y29*100</f>
-        <v>5000000000</v>
+      <c r="Y30" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -4216,44 +4195,44 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="45">
+      <c r="B31" s="48">
         <v>200900</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="46">
+      <c r="D31" s="49">
         <v>200900001</v>
       </c>
-      <c r="E31" s="46" t="s">
+      <c r="E31" s="49" t="s">
         <v>63</v>
       </c>
       <c r="F31" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="32">
         <v>3</v>
       </c>
-      <c r="I31" s="32">
+      <c r="I31" s="35">
         <v>1990000</v>
       </c>
-      <c r="J31" s="33" t="s">
+      <c r="J31" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="43">
+      <c r="K31" s="46">
         <v>0</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M31" s="34" t="s">
+      <c r="M31" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N31" s="4">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="O31" s="4">
         <v>300</v>
@@ -4267,308 +4246,302 @@
       <c r="R31" s="4">
         <v>15000</v>
       </c>
-      <c r="S31" s="35">
+      <c r="S31" s="38">
         <v>16008</v>
       </c>
       <c r="T31" s="6">
         <v>20</v>
       </c>
-      <c r="U31" s="36">
+      <c r="U31" s="39">
         <v>0</v>
       </c>
       <c r="V31" t="s">
         <v>65</v>
       </c>
-      <c r="W31" s="2" t="s">
+      <c r="W31" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X31" s="2">
         <v>0</v>
       </c>
-      <c r="Y31" s="39">
-        <f t="shared" si="5"/>
-        <v>500000000000</v>
+      <c r="Y31" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
-      <c r="A32" s="4">
-        <f t="shared" si="0"/>
-        <v>2010001</v>
-      </c>
-      <c r="B32" s="47">
-        <v>201000</v>
-      </c>
-      <c r="C32" s="4" t="s">
+    <row r="32" s="3" customFormat="1" spans="1:25">
+      <c r="A32" s="50">
+        <v>20010010</v>
+      </c>
+      <c r="B32" s="3">
+        <v>200100</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="51">
+        <v>200100038</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="4">
-        <v>101000006</v>
-      </c>
-      <c r="E32" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="H32" s="29">
-        <v>1</v>
-      </c>
-      <c r="I32" s="32">
-        <v>1990000</v>
-      </c>
-      <c r="J32" s="33" t="s">
+      <c r="H32" s="51">
+        <v>1</v>
+      </c>
+      <c r="I32" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J32" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="43">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="M32" s="34" t="s">
-        <v>85</v>
+      <c r="K32" s="3">
+        <v>1</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M32" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N32" s="4">
-        <v>9000</v>
-      </c>
-      <c r="O32" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="4">
+      <c r="P32" s="3">
         <v>180000</v>
       </c>
-      <c r="Q32" s="4">
+      <c r="Q32" s="3">
         <v>16000</v>
       </c>
-      <c r="R32" s="4">
+      <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="35">
+      <c r="S32" s="55">
         <v>16008</v>
       </c>
-      <c r="T32" s="6">
-        <v>50</v>
-      </c>
-      <c r="U32" s="36">
+      <c r="T32" s="50">
+        <v>48</v>
+      </c>
+      <c r="U32" s="56">
         <v>0</v>
       </c>
       <c r="V32" t="s">
         <v>57</v>
       </c>
-      <c r="W32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="X32" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="W32" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="X32" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="57">
+        <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
-      <c r="A33" s="4">
-        <f t="shared" si="0"/>
-        <v>2010002</v>
-      </c>
-      <c r="B33" s="47">
-        <v>201000</v>
-      </c>
-      <c r="C33" s="4" t="s">
+    <row r="33" s="3" customFormat="1" spans="1:25">
+      <c r="A33" s="50">
+        <v>20010011</v>
+      </c>
+      <c r="B33" s="3">
+        <v>200100</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="51">
+        <v>200100038</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="4">
-        <v>101000006</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="H33" s="37">
+      <c r="H33" s="51">
         <v>2</v>
       </c>
-      <c r="I33" s="32">
-        <v>1990000</v>
-      </c>
-      <c r="J33" s="38" t="s">
+      <c r="I33" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J33" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="43">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="M33" s="34" t="s">
-        <v>85</v>
+      <c r="K33" s="3">
+        <v>1</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M33" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N33" s="4">
-        <v>9000</v>
-      </c>
-      <c r="O33" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="P33" s="4">
+      <c r="P33" s="3">
         <v>180000</v>
       </c>
-      <c r="Q33" s="4">
+      <c r="Q33" s="3">
         <v>16000</v>
       </c>
-      <c r="R33" s="4">
+      <c r="R33" s="3">
         <v>15000</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="55">
         <v>16008</v>
       </c>
-      <c r="T33" s="6">
-        <v>50</v>
-      </c>
-      <c r="U33" s="36">
+      <c r="T33" s="50">
+        <v>48</v>
+      </c>
+      <c r="U33" s="56">
         <v>0</v>
       </c>
       <c r="V33" t="s">
         <v>61</v>
       </c>
-      <c r="W33" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X33" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="2">
-        <f t="shared" si="5"/>
-        <v>5000000000</v>
+      <c r="W33" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="X33" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="57">
+        <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
-      <c r="A34" s="4">
-        <f t="shared" si="0"/>
-        <v>2010003</v>
-      </c>
-      <c r="B34" s="47">
-        <v>201000</v>
-      </c>
-      <c r="C34" s="4" t="s">
+    <row r="34" s="3" customFormat="1" spans="1:25">
+      <c r="A34" s="50">
+        <v>20010012</v>
+      </c>
+      <c r="B34" s="3">
+        <v>200100</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="51">
+        <v>200100038</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="4">
-        <v>101000006</v>
-      </c>
-      <c r="E34" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="F34" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="G34" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="29">
+      <c r="H34" s="51">
         <v>3</v>
       </c>
-      <c r="I34" s="32">
-        <v>1990000</v>
-      </c>
-      <c r="J34" s="33" t="s">
+      <c r="I34" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J34" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="43">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="M34" s="34" t="s">
-        <v>85</v>
+      <c r="K34" s="3">
+        <v>1</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M34" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N34" s="4">
-        <v>9000</v>
-      </c>
-      <c r="O34" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O34" s="3">
         <v>300</v>
       </c>
-      <c r="P34" s="4">
+      <c r="P34" s="3">
         <v>180000</v>
       </c>
-      <c r="Q34" s="4">
+      <c r="Q34" s="3">
         <v>16000</v>
       </c>
-      <c r="R34" s="4">
+      <c r="R34" s="3">
         <v>15000</v>
       </c>
-      <c r="S34" s="35">
+      <c r="S34" s="55">
         <v>16008</v>
       </c>
-      <c r="T34" s="6">
-        <v>50</v>
-      </c>
-      <c r="U34" s="36">
+      <c r="T34" s="50">
+        <v>48</v>
+      </c>
+      <c r="U34" s="56">
         <v>0</v>
       </c>
       <c r="V34" t="s">
         <v>65</v>
       </c>
-      <c r="W34" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="X34" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="39">
-        <f t="shared" si="5"/>
-        <v>500000000000</v>
+      <c r="W34" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="X34" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="57">
+        <v>0</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" spans="1:25">
-      <c r="A35" s="48">
-        <v>20010010</v>
+      <c r="A35" s="50">
+        <v>20010110</v>
       </c>
       <c r="B35" s="3">
-        <v>200100</v>
-      </c>
-      <c r="C35" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="49">
-        <v>200100038</v>
-      </c>
-      <c r="E35" s="49" t="s">
+        <v>200101</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="3">
+        <v>200101001</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F35" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H35" s="49">
-        <v>1</v>
-      </c>
-      <c r="I35" s="49">
+      <c r="G35" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" s="51">
         <v>1980000</v>
       </c>
-      <c r="J35" s="52" t="s">
-        <v>87</v>
+      <c r="J35" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M35" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="N35" s="3">
-        <v>9200</v>
+        <v>68</v>
+      </c>
+      <c r="M35" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="N35" s="4">
+        <v>9500</v>
       </c>
       <c r="O35" s="3">
         <v>300</v>
@@ -4582,20 +4555,20 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="54">
+      <c r="S35" s="3">
         <v>16008</v>
       </c>
-      <c r="T35" s="48">
+      <c r="T35" s="50">
         <v>48</v>
       </c>
-      <c r="U35" s="55">
-        <v>0</v>
-      </c>
-      <c r="V35" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>89</v>
+      <c r="U35" s="56">
+        <v>0</v>
+      </c>
+      <c r="V35" t="s">
+        <v>57</v>
+      </c>
+      <c r="W35" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X35" s="3">
         <v>1</v>
@@ -4605,47 +4578,47 @@
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:25">
-      <c r="A36" s="48">
-        <v>20010011</v>
+      <c r="A36" s="50">
+        <v>20010111</v>
       </c>
       <c r="B36" s="3">
-        <v>200100</v>
-      </c>
-      <c r="C36" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="49">
-        <v>200100038</v>
-      </c>
-      <c r="E36" s="49" t="s">
+        <v>200101</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="3">
+        <v>200101001</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F36" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H36" s="49">
+      <c r="G36" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="3">
         <v>2</v>
       </c>
-      <c r="I36" s="49">
+      <c r="I36" s="51">
         <v>1980000</v>
       </c>
-      <c r="J36" s="52" t="s">
-        <v>90</v>
+      <c r="J36" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M36" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="N36" s="3">
-        <v>9200</v>
+        <v>68</v>
+      </c>
+      <c r="M36" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="N36" s="4">
+        <v>9500</v>
       </c>
       <c r="O36" s="3">
         <v>300</v>
@@ -4659,20 +4632,20 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="54">
+      <c r="S36" s="3">
         <v>16008</v>
       </c>
-      <c r="T36" s="48">
+      <c r="T36" s="50">
         <v>48</v>
       </c>
-      <c r="U36" s="55">
-        <v>0</v>
-      </c>
-      <c r="V36" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W36" s="3" t="s">
-        <v>91</v>
+      <c r="U36" s="56">
+        <v>0</v>
+      </c>
+      <c r="V36" t="s">
+        <v>61</v>
+      </c>
+      <c r="W36" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X36" s="3">
         <v>1</v>
@@ -4682,47 +4655,47 @@
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:25">
-      <c r="A37" s="48">
-        <v>20010012</v>
+      <c r="A37" s="50">
+        <v>20010112</v>
       </c>
       <c r="B37" s="3">
-        <v>200100</v>
-      </c>
-      <c r="C37" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="49">
-        <v>200100038</v>
-      </c>
-      <c r="E37" s="49" t="s">
+        <v>200101</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="3">
+        <v>200101001</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F37" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H37" s="49">
+      <c r="G37" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="3">
         <v>3</v>
       </c>
-      <c r="I37" s="49">
+      <c r="I37" s="51">
         <v>1980000</v>
       </c>
-      <c r="J37" s="52" t="s">
-        <v>92</v>
+      <c r="J37" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M37" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="N37" s="3">
-        <v>9200</v>
+        <v>68</v>
+      </c>
+      <c r="M37" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="N37" s="4">
+        <v>9500</v>
       </c>
       <c r="O37" s="3">
         <v>300</v>
@@ -4736,20 +4709,20 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="54">
+      <c r="S37" s="3">
         <v>16008</v>
       </c>
-      <c r="T37" s="48">
+      <c r="T37" s="50">
         <v>48</v>
       </c>
-      <c r="U37" s="55">
-        <v>0</v>
-      </c>
-      <c r="V37" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W37" s="3" t="s">
-        <v>93</v>
+      <c r="U37" s="56">
+        <v>0</v>
+      </c>
+      <c r="V37" t="s">
+        <v>65</v>
+      </c>
+      <c r="W37" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X37" s="3">
         <v>1</v>
@@ -4759,35 +4732,35 @@
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:25">
-      <c r="A38" s="48">
-        <v>20010110</v>
+      <c r="A38" s="50">
+        <v>20030010</v>
       </c>
       <c r="B38" s="3">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D38" s="3">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="62" t="s">
+      <c r="F38" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>53</v>
+      <c r="G38" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="49">
+      <c r="I38" s="51">
         <v>1980000</v>
       </c>
-      <c r="J38" s="52" t="s">
-        <v>87</v>
+      <c r="J38" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K38" s="3">
         <v>0</v>
@@ -4795,11 +4768,11 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="N38" s="3">
-        <v>9200</v>
+      <c r="M38" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="N38" s="4">
+        <v>9500</v>
       </c>
       <c r="O38" s="3">
         <v>300</v>
@@ -4816,17 +4789,17 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="48">
-        <v>48</v>
-      </c>
-      <c r="U38" s="55">
-        <v>0</v>
-      </c>
-      <c r="V38" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W38" s="3" t="s">
-        <v>89</v>
+      <c r="T38" s="50">
+        <v>50</v>
+      </c>
+      <c r="U38" s="56">
+        <v>0</v>
+      </c>
+      <c r="V38" t="s">
+        <v>57</v>
+      </c>
+      <c r="W38" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X38" s="3">
         <v>1</v>
@@ -4836,35 +4809,35 @@
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:25">
-      <c r="A39" s="48">
-        <v>20010111</v>
+      <c r="A39" s="50">
+        <v>20030011</v>
       </c>
       <c r="B39" s="3">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D39" s="3">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="62" t="s">
+      <c r="F39" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>53</v>
+      <c r="G39" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="49">
+      <c r="I39" s="51">
         <v>1980000</v>
       </c>
-      <c r="J39" s="52" t="s">
-        <v>90</v>
+      <c r="J39" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -4872,11 +4845,11 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="N39" s="3">
-        <v>9200</v>
+      <c r="M39" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="N39" s="4">
+        <v>9500</v>
       </c>
       <c r="O39" s="3">
         <v>300</v>
@@ -4893,17 +4866,17 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="48">
-        <v>48</v>
-      </c>
-      <c r="U39" s="55">
-        <v>0</v>
-      </c>
-      <c r="V39" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W39" s="3" t="s">
-        <v>91</v>
+      <c r="T39" s="50">
+        <v>50</v>
+      </c>
+      <c r="U39" s="56">
+        <v>0</v>
+      </c>
+      <c r="V39" t="s">
+        <v>61</v>
+      </c>
+      <c r="W39" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X39" s="3">
         <v>1</v>
@@ -4913,74 +4886,74 @@
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:25">
-      <c r="A40" s="48">
-        <v>20010112</v>
+      <c r="A40" s="50">
+        <v>20030012</v>
       </c>
       <c r="B40" s="3">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D40" s="3">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="62" t="s">
+      <c r="F40" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>53</v>
+      <c r="G40" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="49">
+      <c r="I40" s="51">
         <v>1980000</v>
       </c>
-      <c r="J40" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="K40" s="3">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3" t="s">
+      <c r="J40" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="K40" s="58">
+        <v>0</v>
+      </c>
+      <c r="L40" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="N40" s="3">
-        <v>9200</v>
+      <c r="M40" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="N40" s="4">
+        <v>9500</v>
       </c>
       <c r="O40" s="3">
         <v>300</v>
       </c>
-      <c r="P40" s="3">
+      <c r="P40" s="58">
         <v>180000</v>
       </c>
-      <c r="Q40" s="3">
+      <c r="Q40" s="58">
         <v>16000</v>
       </c>
-      <c r="R40" s="3">
+      <c r="R40" s="58">
         <v>15000</v>
       </c>
-      <c r="S40" s="3">
+      <c r="S40" s="58">
         <v>16008</v>
       </c>
-      <c r="T40" s="48">
-        <v>48</v>
-      </c>
-      <c r="U40" s="55">
-        <v>0</v>
-      </c>
-      <c r="V40" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W40" s="3" t="s">
-        <v>93</v>
+      <c r="T40" s="50">
+        <v>50</v>
+      </c>
+      <c r="U40" s="56">
+        <v>0</v>
+      </c>
+      <c r="V40" t="s">
+        <v>65</v>
+      </c>
+      <c r="W40" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X40" s="3">
         <v>1</v>
@@ -4990,74 +4963,74 @@
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:25">
-      <c r="A41" s="48">
-        <v>20030010</v>
+      <c r="A41" s="50">
+        <v>20040010</v>
       </c>
       <c r="B41" s="3">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D41" s="3">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="62" t="s">
+      <c r="F41" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>53</v>
+      <c r="G41" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="49">
+      <c r="I41" s="51">
         <v>1980000</v>
       </c>
-      <c r="J41" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="s">
+      <c r="J41" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="K41" s="58">
+        <v>0</v>
+      </c>
+      <c r="L41" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="N41" s="3">
-        <v>9200</v>
+      <c r="M41" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="N41" s="4">
+        <v>9500</v>
       </c>
       <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="58">
         <v>180000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="58">
         <v>16000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="58">
         <v>15000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="58">
         <v>16008</v>
       </c>
-      <c r="T41" s="48">
+      <c r="T41" s="50">
         <v>50</v>
       </c>
-      <c r="U41" s="55">
-        <v>0</v>
-      </c>
-      <c r="V41" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>89</v>
+      <c r="U41" s="56">
+        <v>0</v>
+      </c>
+      <c r="V41" t="s">
+        <v>57</v>
+      </c>
+      <c r="W41" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X41" s="3">
         <v>1</v>
@@ -5067,74 +5040,74 @@
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:25">
-      <c r="A42" s="48">
-        <v>20030011</v>
+      <c r="A42" s="50">
+        <v>20040011</v>
       </c>
       <c r="B42" s="3">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D42" s="3">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="62" t="s">
+      <c r="F42" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>53</v>
+      <c r="G42" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="49">
+      <c r="I42" s="51">
         <v>1980000</v>
       </c>
-      <c r="J42" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
+      <c r="J42" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="K42" s="58">
+        <v>0</v>
+      </c>
+      <c r="L42" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="N42" s="3">
-        <v>9200</v>
+      <c r="M42" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="N42" s="4">
+        <v>9500</v>
       </c>
       <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="P42" s="58">
         <v>180000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="Q42" s="58">
         <v>16000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="R42" s="58">
         <v>15000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="S42" s="58">
         <v>16008</v>
       </c>
-      <c r="T42" s="48">
+      <c r="T42" s="50">
         <v>50</v>
       </c>
-      <c r="U42" s="55">
-        <v>0</v>
-      </c>
-      <c r="V42" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>91</v>
+      <c r="U42" s="56">
+        <v>0</v>
+      </c>
+      <c r="V42" t="s">
+        <v>61</v>
+      </c>
+      <c r="W42" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X42" s="3">
         <v>1</v>
@@ -5144,35 +5117,35 @@
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:25">
-      <c r="A43" s="48">
-        <v>20030012</v>
+      <c r="A43" s="50">
+        <v>20040012</v>
       </c>
       <c r="B43" s="3">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D43" s="3">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="62" t="s">
+      <c r="F43" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>53</v>
+      <c r="G43" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="49">
+      <c r="I43" s="51">
         <v>1980000</v>
       </c>
-      <c r="J43" s="52" t="s">
-        <v>92</v>
+      <c r="J43" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K43" s="58">
         <v>0</v>
@@ -5180,11 +5153,11 @@
       <c r="L43" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="N43" s="3">
-        <v>9200</v>
+      <c r="M43" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="N43" s="4">
+        <v>9500</v>
       </c>
       <c r="O43" s="3">
         <v>300</v>
@@ -5201,17 +5174,17 @@
       <c r="S43" s="58">
         <v>16008</v>
       </c>
-      <c r="T43" s="48">
+      <c r="T43" s="50">
         <v>50</v>
       </c>
-      <c r="U43" s="55">
-        <v>0</v>
-      </c>
-      <c r="V43" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>93</v>
+      <c r="U43" s="56">
+        <v>0</v>
+      </c>
+      <c r="V43" t="s">
+        <v>65</v>
+      </c>
+      <c r="W43" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X43" s="3">
         <v>1</v>
@@ -5221,47 +5194,47 @@
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:25">
-      <c r="A44" s="48">
-        <v>20040010</v>
+      <c r="A44" s="50">
+        <v>20050010</v>
       </c>
       <c r="B44" s="3">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D44" s="3">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="62" t="s">
+      <c r="F44" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>53</v>
+      <c r="G44" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="49">
+      <c r="I44" s="51">
         <v>1980000</v>
       </c>
-      <c r="J44" s="52" t="s">
-        <v>87</v>
+      <c r="J44" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K44" s="58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="M44" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="N44" s="3">
-        <v>9200</v>
+        <v>55</v>
+      </c>
+      <c r="M44" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="N44" s="4">
+        <v>9500</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
@@ -5278,17 +5251,17 @@
       <c r="S44" s="58">
         <v>16008</v>
       </c>
-      <c r="T44" s="48">
-        <v>50</v>
-      </c>
-      <c r="U44" s="55">
-        <v>0</v>
-      </c>
-      <c r="V44" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>89</v>
+      <c r="T44" s="50">
+        <v>48</v>
+      </c>
+      <c r="U44" s="50">
+        <v>0</v>
+      </c>
+      <c r="V44" t="s">
+        <v>57</v>
+      </c>
+      <c r="W44" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X44" s="3">
         <v>1</v>
@@ -5298,47 +5271,47 @@
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:25">
-      <c r="A45" s="48">
-        <v>20040011</v>
+      <c r="A45" s="50">
+        <v>20050011</v>
       </c>
       <c r="B45" s="3">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D45" s="3">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="62" t="s">
+      <c r="F45" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>53</v>
+      <c r="G45" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="49">
+      <c r="I45" s="51">
         <v>1980000</v>
       </c>
-      <c r="J45" s="52" t="s">
-        <v>90</v>
+      <c r="J45" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K45" s="58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="M45" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="N45" s="3">
-        <v>9200</v>
+        <v>55</v>
+      </c>
+      <c r="M45" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="N45" s="4">
+        <v>9500</v>
       </c>
       <c r="O45" s="3">
         <v>300</v>
@@ -5355,17 +5328,17 @@
       <c r="S45" s="58">
         <v>16008</v>
       </c>
-      <c r="T45" s="48">
-        <v>50</v>
-      </c>
-      <c r="U45" s="55">
-        <v>0</v>
-      </c>
-      <c r="V45" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>91</v>
+      <c r="T45" s="50">
+        <v>48</v>
+      </c>
+      <c r="U45" s="50">
+        <v>0</v>
+      </c>
+      <c r="V45" t="s">
+        <v>61</v>
+      </c>
+      <c r="W45" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X45" s="3">
         <v>1</v>
@@ -5375,47 +5348,47 @@
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:25">
-      <c r="A46" s="48">
-        <v>20040012</v>
+      <c r="A46" s="50">
+        <v>20050012</v>
       </c>
       <c r="B46" s="3">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D46" s="3">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="62" t="s">
+      <c r="F46" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>53</v>
+      <c r="G46" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="49">
+      <c r="I46" s="51">
         <v>1980000</v>
       </c>
-      <c r="J46" s="52" t="s">
-        <v>92</v>
+      <c r="J46" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K46" s="58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="M46" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="N46" s="3">
-        <v>9200</v>
+        <v>55</v>
+      </c>
+      <c r="M46" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="N46" s="4">
+        <v>9500</v>
       </c>
       <c r="O46" s="3">
         <v>300</v>
@@ -5432,17 +5405,17 @@
       <c r="S46" s="58">
         <v>16008</v>
       </c>
-      <c r="T46" s="48">
-        <v>50</v>
-      </c>
-      <c r="U46" s="55">
-        <v>0</v>
-      </c>
-      <c r="V46" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>93</v>
+      <c r="T46" s="50">
+        <v>48</v>
+      </c>
+      <c r="U46" s="50">
+        <v>0</v>
+      </c>
+      <c r="V46" t="s">
+        <v>65</v>
+      </c>
+      <c r="W46" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X46" s="3">
         <v>1</v>
@@ -5452,47 +5425,47 @@
       </c>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:25">
-      <c r="A47" s="48">
-        <v>20050010</v>
+      <c r="A47" s="50">
+        <v>20060010</v>
       </c>
       <c r="B47" s="3">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D47" s="3">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="62" t="s">
+      <c r="F47" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>53</v>
+      <c r="G47" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="49">
+      <c r="I47" s="51">
         <v>1980000</v>
       </c>
-      <c r="J47" s="52" t="s">
-        <v>87</v>
+      <c r="J47" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K47" s="58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="M47" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="N47" s="3">
-        <v>9200</v>
+        <v>68</v>
+      </c>
+      <c r="M47" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N47" s="4">
+        <v>9500</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
@@ -5509,17 +5482,17 @@
       <c r="S47" s="58">
         <v>16008</v>
       </c>
-      <c r="T47" s="48">
-        <v>48</v>
-      </c>
-      <c r="U47" s="48">
-        <v>0</v>
-      </c>
-      <c r="V47" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>89</v>
+      <c r="T47" s="50">
+        <v>20</v>
+      </c>
+      <c r="U47" s="50">
+        <v>0</v>
+      </c>
+      <c r="V47" t="s">
+        <v>57</v>
+      </c>
+      <c r="W47" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X47" s="3">
         <v>1</v>
@@ -5529,47 +5502,47 @@
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:25">
-      <c r="A48" s="48">
-        <v>20050011</v>
+      <c r="A48" s="50">
+        <v>20060011</v>
       </c>
       <c r="B48" s="3">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D48" s="3">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="62" t="s">
+      <c r="F48" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>53</v>
+      <c r="G48" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="49">
+      <c r="I48" s="51">
         <v>1980000</v>
       </c>
-      <c r="J48" s="52" t="s">
-        <v>90</v>
+      <c r="J48" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K48" s="58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="M48" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="N48" s="3">
-        <v>9200</v>
+        <v>68</v>
+      </c>
+      <c r="M48" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N48" s="4">
+        <v>9500</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -5586,17 +5559,17 @@
       <c r="S48" s="58">
         <v>16008</v>
       </c>
-      <c r="T48" s="48">
-        <v>48</v>
-      </c>
-      <c r="U48" s="48">
-        <v>0</v>
-      </c>
-      <c r="V48" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>91</v>
+      <c r="T48" s="50">
+        <v>20</v>
+      </c>
+      <c r="U48" s="50">
+        <v>0</v>
+      </c>
+      <c r="V48" t="s">
+        <v>61</v>
+      </c>
+      <c r="W48" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X48" s="3">
         <v>1</v>
@@ -5606,74 +5579,74 @@
       </c>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:25">
-      <c r="A49" s="48">
-        <v>20050012</v>
+      <c r="A49" s="50">
+        <v>20060012</v>
       </c>
       <c r="B49" s="3">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D49" s="3">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="62" t="s">
+      <c r="F49" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>53</v>
+      <c r="G49" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="49">
+      <c r="I49" s="51">
         <v>1980000</v>
       </c>
-      <c r="J49" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="K49" s="58">
-        <v>1</v>
-      </c>
-      <c r="L49" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="M49" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="N49" s="3">
-        <v>9200</v>
+      <c r="J49" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M49" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N49" s="4">
+        <v>9500</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="58">
+      <c r="P49" s="3">
         <v>180000</v>
       </c>
-      <c r="Q49" s="58">
+      <c r="Q49" s="3">
         <v>16000</v>
       </c>
-      <c r="R49" s="58">
+      <c r="R49" s="3">
         <v>15000</v>
       </c>
-      <c r="S49" s="58">
+      <c r="S49" s="3">
         <v>16008</v>
       </c>
-      <c r="T49" s="48">
-        <v>48</v>
-      </c>
-      <c r="U49" s="48">
-        <v>0</v>
-      </c>
-      <c r="V49" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>93</v>
+      <c r="T49" s="50">
+        <v>20</v>
+      </c>
+      <c r="U49" s="50">
+        <v>0</v>
+      </c>
+      <c r="V49" t="s">
+        <v>65</v>
+      </c>
+      <c r="W49" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X49" s="3">
         <v>1</v>
@@ -5683,74 +5656,74 @@
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:25">
-      <c r="A50" s="48">
-        <v>20060010</v>
+      <c r="A50" s="50">
+        <v>20070010</v>
       </c>
       <c r="B50" s="3">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D50" s="3">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="62" t="s">
+      <c r="F50" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>53</v>
+      <c r="G50" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="49">
+      <c r="I50" s="51">
         <v>1980000</v>
       </c>
-      <c r="J50" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="K50" s="58">
-        <v>0</v>
-      </c>
-      <c r="L50" s="58" t="s">
+      <c r="J50" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="K50" s="3">
+        <v>1</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="N50" s="3">
-        <v>9200</v>
+      <c r="M50" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="N50" s="4">
+        <v>9500</v>
       </c>
       <c r="O50" s="3">
-        <v>300</v>
-      </c>
-      <c r="P50" s="58">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
         <v>180000</v>
       </c>
-      <c r="Q50" s="58">
+      <c r="Q50" s="3">
         <v>16000</v>
       </c>
-      <c r="R50" s="58">
+      <c r="R50" s="3">
         <v>15000</v>
       </c>
-      <c r="S50" s="58">
+      <c r="S50" s="3">
         <v>16008</v>
       </c>
-      <c r="T50" s="48">
-        <v>20</v>
-      </c>
-      <c r="U50" s="48">
-        <v>0</v>
-      </c>
-      <c r="V50" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W50" s="3" t="s">
-        <v>89</v>
+      <c r="T50" s="50">
+        <v>30</v>
+      </c>
+      <c r="U50" s="50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>57</v>
+      </c>
+      <c r="W50" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X50" s="3">
         <v>1</v>
@@ -5760,74 +5733,74 @@
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:25">
-      <c r="A51" s="48">
-        <v>20060011</v>
+      <c r="A51" s="50">
+        <v>20070011</v>
       </c>
       <c r="B51" s="3">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D51" s="3">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="62" t="s">
+      <c r="F51" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>53</v>
+      <c r="G51" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="49">
+      <c r="I51" s="51">
         <v>1980000</v>
       </c>
-      <c r="J51" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="K51" s="58">
-        <v>0</v>
-      </c>
-      <c r="L51" s="58" t="s">
+      <c r="J51" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="K51" s="3">
+        <v>1</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="N51" s="3">
-        <v>9200</v>
+      <c r="M51" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="N51" s="4">
+        <v>9500</v>
       </c>
       <c r="O51" s="3">
-        <v>300</v>
-      </c>
-      <c r="P51" s="58">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
         <v>180000</v>
       </c>
-      <c r="Q51" s="58">
+      <c r="Q51" s="3">
         <v>16000</v>
       </c>
-      <c r="R51" s="58">
+      <c r="R51" s="3">
         <v>15000</v>
       </c>
-      <c r="S51" s="58">
+      <c r="S51" s="3">
         <v>16008</v>
       </c>
-      <c r="T51" s="48">
-        <v>20</v>
-      </c>
-      <c r="U51" s="48">
-        <v>0</v>
-      </c>
-      <c r="V51" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W51" s="3" t="s">
-        <v>91</v>
+      <c r="T51" s="50">
+        <v>30</v>
+      </c>
+      <c r="U51" s="50">
+        <v>1</v>
+      </c>
+      <c r="V51" t="s">
+        <v>61</v>
+      </c>
+      <c r="W51" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X51" s="3">
         <v>1</v>
@@ -5837,50 +5810,50 @@
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:25">
-      <c r="A52" s="48">
-        <v>20060012</v>
+      <c r="A52" s="50">
+        <v>20070012</v>
       </c>
       <c r="B52" s="3">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D52" s="3">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="62" t="s">
+      <c r="F52" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>53</v>
+      <c r="G52" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="49">
+      <c r="I52" s="51">
         <v>1980000</v>
       </c>
-      <c r="J52" s="52" t="s">
-        <v>92</v>
+      <c r="J52" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="N52" s="3">
-        <v>9200</v>
+      <c r="M52" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="N52" s="4">
+        <v>9500</v>
       </c>
       <c r="O52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>180000</v>
@@ -5894,17 +5867,17 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="48">
-        <v>20</v>
-      </c>
-      <c r="U52" s="48">
-        <v>0</v>
-      </c>
-      <c r="V52" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>93</v>
+      <c r="T52" s="50">
+        <v>30</v>
+      </c>
+      <c r="U52" s="50">
+        <v>1</v>
+      </c>
+      <c r="V52" t="s">
+        <v>65</v>
+      </c>
+      <c r="W52" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X52" s="3">
         <v>1</v>
@@ -5914,50 +5887,50 @@
       </c>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:25">
-      <c r="A53" s="48">
-        <v>20070010</v>
+      <c r="A53" s="50">
+        <v>20080010</v>
       </c>
       <c r="B53" s="3">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D53" s="3">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="62" t="s">
+      <c r="F53" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>53</v>
+      <c r="G53" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="49">
+      <c r="I53" s="51">
         <v>1980000</v>
       </c>
-      <c r="J53" s="52" t="s">
-        <v>87</v>
+      <c r="J53" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="N53" s="3">
-        <v>9200</v>
+      <c r="M53" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="N53" s="4">
+        <v>9500</v>
       </c>
       <c r="O53" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P53" s="3">
         <v>180000</v>
@@ -5971,17 +5944,17 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="48">
-        <v>30</v>
-      </c>
-      <c r="U53" s="48">
-        <v>1</v>
-      </c>
-      <c r="V53" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W53" s="3" t="s">
-        <v>89</v>
+      <c r="T53" s="50">
+        <v>20</v>
+      </c>
+      <c r="U53" s="50">
+        <v>0</v>
+      </c>
+      <c r="V53" t="s">
+        <v>57</v>
+      </c>
+      <c r="W53" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X53" s="3">
         <v>1</v>
@@ -5991,50 +5964,50 @@
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:25">
-      <c r="A54" s="48">
-        <v>20070011</v>
+      <c r="A54" s="50">
+        <v>20080011</v>
       </c>
       <c r="B54" s="3">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D54" s="3">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="62" t="s">
+      <c r="F54" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>53</v>
+      <c r="G54" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="49">
+      <c r="I54" s="51">
         <v>1980000</v>
       </c>
-      <c r="J54" s="52" t="s">
-        <v>90</v>
+      <c r="J54" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="N54" s="3">
-        <v>9200</v>
+      <c r="M54" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="N54" s="4">
+        <v>9500</v>
       </c>
       <c r="O54" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P54" s="3">
         <v>180000</v>
@@ -6048,17 +6021,17 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="48">
-        <v>30</v>
-      </c>
-      <c r="U54" s="48">
-        <v>1</v>
-      </c>
-      <c r="V54" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>91</v>
+      <c r="T54" s="50">
+        <v>20</v>
+      </c>
+      <c r="U54" s="50">
+        <v>0</v>
+      </c>
+      <c r="V54" t="s">
+        <v>61</v>
+      </c>
+      <c r="W54" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X54" s="3">
         <v>1</v>
@@ -6068,50 +6041,50 @@
       </c>
     </row>
     <row r="55" s="3" customFormat="1" spans="1:25">
-      <c r="A55" s="48">
-        <v>20070012</v>
+      <c r="A55" s="50">
+        <v>20080012</v>
       </c>
       <c r="B55" s="3">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D55" s="3">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="62" t="s">
+      <c r="F55" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>53</v>
+      <c r="G55" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="49">
+      <c r="I55" s="51">
         <v>1980000</v>
       </c>
-      <c r="J55" s="52" t="s">
-        <v>92</v>
+      <c r="J55" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="N55" s="3">
-        <v>9200</v>
+      <c r="M55" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="N55" s="4">
+        <v>9500</v>
       </c>
       <c r="O55" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P55" s="3">
         <v>180000</v>
@@ -6125,17 +6098,17 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="48">
-        <v>30</v>
-      </c>
-      <c r="U55" s="48">
-        <v>1</v>
-      </c>
-      <c r="V55" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W55" s="3" t="s">
-        <v>93</v>
+      <c r="T55" s="50">
+        <v>20</v>
+      </c>
+      <c r="U55" s="50">
+        <v>0</v>
+      </c>
+      <c r="V55" t="s">
+        <v>65</v>
+      </c>
+      <c r="W55" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X55" s="3">
         <v>1</v>
@@ -6145,35 +6118,35 @@
       </c>
     </row>
     <row r="56" s="3" customFormat="1" spans="1:25">
-      <c r="A56" s="48">
-        <v>20080010</v>
+      <c r="A56" s="50">
+        <v>20090010</v>
       </c>
       <c r="B56" s="3">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D56" s="3">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="62" t="s">
+      <c r="F56" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>53</v>
+      <c r="G56" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="49">
+      <c r="I56" s="51">
         <v>1980000</v>
       </c>
-      <c r="J56" s="52" t="s">
-        <v>87</v>
+      <c r="J56" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K56" s="3">
         <v>0</v>
@@ -6181,11 +6154,11 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="53" t="s">
+      <c r="M56" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N56" s="3">
-        <v>9200</v>
+      <c r="N56" s="4">
+        <v>9500</v>
       </c>
       <c r="O56" s="3">
         <v>300</v>
@@ -6202,17 +6175,17 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="48">
+      <c r="T56" s="50">
         <v>20</v>
       </c>
-      <c r="U56" s="48">
-        <v>0</v>
-      </c>
-      <c r="V56" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W56" s="3" t="s">
-        <v>89</v>
+      <c r="U56" s="50">
+        <v>0</v>
+      </c>
+      <c r="V56" t="s">
+        <v>57</v>
+      </c>
+      <c r="W56" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X56" s="3">
         <v>1</v>
@@ -6222,35 +6195,35 @@
       </c>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:25">
-      <c r="A57" s="48">
-        <v>20080011</v>
+      <c r="A57" s="50">
+        <v>20090011</v>
       </c>
       <c r="B57" s="3">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D57" s="3">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="62" t="s">
+      <c r="F57" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>53</v>
+      <c r="G57" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="49">
+      <c r="I57" s="51">
         <v>1980000</v>
       </c>
-      <c r="J57" s="52" t="s">
-        <v>90</v>
+      <c r="J57" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -6258,11 +6231,11 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="53" t="s">
+      <c r="M57" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N57" s="3">
-        <v>9200</v>
+      <c r="N57" s="4">
+        <v>9500</v>
       </c>
       <c r="O57" s="3">
         <v>300</v>
@@ -6279,17 +6252,17 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="48">
+      <c r="T57" s="50">
         <v>20</v>
       </c>
-      <c r="U57" s="48">
-        <v>0</v>
-      </c>
-      <c r="V57" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>91</v>
+      <c r="U57" s="50">
+        <v>0</v>
+      </c>
+      <c r="V57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W57" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X57" s="3">
         <v>1</v>
@@ -6299,35 +6272,35 @@
       </c>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:25">
-      <c r="A58" s="48">
-        <v>20080012</v>
+      <c r="A58" s="50">
+        <v>20090012</v>
       </c>
       <c r="B58" s="3">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D58" s="3">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="62" t="s">
+      <c r="F58" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>53</v>
+      <c r="G58" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="49">
+      <c r="I58" s="51">
         <v>1980000</v>
       </c>
-      <c r="J58" s="52" t="s">
-        <v>92</v>
+      <c r="J58" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -6335,11 +6308,11 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="53" t="s">
+      <c r="M58" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N58" s="3">
-        <v>9200</v>
+      <c r="N58" s="4">
+        <v>9500</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
@@ -6356,258 +6329,27 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="48">
+      <c r="T58" s="50">
         <v>20</v>
       </c>
-      <c r="U58" s="48">
-        <v>0</v>
-      </c>
-      <c r="V58" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>93</v>
+      <c r="U58" s="50">
+        <v>0</v>
+      </c>
+      <c r="V58" t="s">
+        <v>65</v>
+      </c>
+      <c r="W58" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X58" s="3">
         <v>1</v>
       </c>
       <c r="Y58" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" s="3" customFormat="1" spans="1:25">
-      <c r="A59" s="48">
-        <v>20090010</v>
-      </c>
-      <c r="B59" s="3">
-        <v>200900</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D59" s="3">
-        <v>200900001</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F59" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1</v>
-      </c>
-      <c r="I59" s="49">
-        <v>1980000</v>
-      </c>
-      <c r="J59" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M59" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="N59" s="3">
-        <v>9200</v>
-      </c>
-      <c r="O59" s="3">
-        <v>300</v>
-      </c>
-      <c r="P59" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>16008</v>
-      </c>
-      <c r="T59" s="48">
-        <v>20</v>
-      </c>
-      <c r="U59" s="48">
-        <v>0</v>
-      </c>
-      <c r="V59" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y59" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" s="3" customFormat="1" spans="1:25">
-      <c r="A60" s="48">
-        <v>20090011</v>
-      </c>
-      <c r="B60" s="3">
-        <v>200900</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="3">
-        <v>200900001</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F60" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H60" s="3">
-        <v>2</v>
-      </c>
-      <c r="I60" s="49">
-        <v>1980000</v>
-      </c>
-      <c r="J60" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M60" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="N60" s="3">
-        <v>9200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>300</v>
-      </c>
-      <c r="P60" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R60" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S60" s="3">
-        <v>16008</v>
-      </c>
-      <c r="T60" s="48">
-        <v>20</v>
-      </c>
-      <c r="U60" s="48">
-        <v>0</v>
-      </c>
-      <c r="V60" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="X60" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y60" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" s="3" customFormat="1" spans="1:25">
-      <c r="A61" s="48">
-        <v>20090012</v>
-      </c>
-      <c r="B61" s="3">
-        <v>200900</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D61" s="3">
-        <v>200900001</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F61" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H61" s="3">
-        <v>3</v>
-      </c>
-      <c r="I61" s="49">
-        <v>1980000</v>
-      </c>
-      <c r="J61" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M61" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="N61" s="3">
-        <v>9200</v>
-      </c>
-      <c r="O61" s="3">
-        <v>300</v>
-      </c>
-      <c r="P61" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>16008</v>
-      </c>
-      <c r="T61" s="48">
-        <v>20</v>
-      </c>
-      <c r="U61" s="48">
-        <v>0</v>
-      </c>
-      <c r="V61" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W61" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X61" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y61" s="57">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S61" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S58" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -330,7 +330,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="87">
   <si>
     <t>游戏ID</t>
   </si>
@@ -494,7 +494,7 @@
     <t>0:6:28|6:12:36|12:18:45|18:24:43</t>
   </si>
   <si>
-    <t>50_100_200_500_1000_2000_5000</t>
+    <t>1000_2000_5000_10000_20000_50000_100000</t>
   </si>
   <si>
     <t>组合</t>
@@ -503,34 +503,34 @@
     <t>1000,16000,8000,0</t>
   </si>
   <si>
-    <t>500000_17001</t>
-  </si>
-  <si>
-    <t>1990000_100000</t>
+    <t>5000000_17001</t>
+  </si>
+  <si>
+    <t>1990000_500000</t>
   </si>
   <si>
     <t>中级场</t>
   </si>
   <si>
-    <t>5000_10000_20000_50000_100000_200000_500000</t>
+    <t>10000_20000_50000_100000_200000_500000_1000000</t>
   </si>
   <si>
     <t>50000000_17001</t>
   </si>
   <si>
-    <t>1990000_10000000</t>
+    <t>1990000_5000000</t>
   </si>
   <si>
     <t>高级场</t>
   </si>
   <si>
-    <t>500000_1000000_2000000_5000000_10000000_20000000_50000000</t>
-  </si>
-  <si>
-    <t>5000000000_17001</t>
-  </si>
-  <si>
-    <t>1990000_100000000</t>
+    <t>100000_200000_500000_1000000_2000000_5000000_10000000</t>
+  </si>
+  <si>
+    <t>500000000_17001</t>
+  </si>
+  <si>
+    <t>1990000_50000000</t>
   </si>
   <si>
     <t>龙虎斗</t>
@@ -581,37 +581,16 @@
     <t>鱼虾蟹</t>
   </si>
   <si>
-    <t>水果机</t>
-  </si>
-  <si>
-    <t>0:24:0</t>
-  </si>
-  <si>
-    <t>0,16000,10000,4000</t>
-  </si>
-  <si>
     <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
   </si>
   <si>
-    <t>50_100_200_500_1000</t>
-  </si>
-  <si>
-    <t>5000_17001</t>
-  </si>
-  <si>
-    <t>1980000_1000</t>
-  </si>
-  <si>
-    <t>1000_2000_5000_10000_20000</t>
-  </si>
-  <si>
-    <t>1980000_100000</t>
-  </si>
-  <si>
-    <t>20000_50000_100000_200000_500000</t>
-  </si>
-  <si>
-    <t>1980000_10000000</t>
+    <t>1980000_500000</t>
+  </si>
+  <si>
+    <t>1980000_5000000</t>
+  </si>
+  <si>
+    <t>1980000_50000000</t>
   </si>
 </sst>
 </file>
@@ -1378,6 +1357,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1414,14 +1396,20 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1484,7 +1472,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1513,9 +1501,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1530,10 +1515,6 @@
     <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1543,7 +1524,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1553,9 +1533,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="center"/>
@@ -1896,10 +1873,10 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:Y58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.25" style="4"/>
+    <col min="1" max="1" width="9.375" style="4"/>
     <col min="2" max="2" width="12" style="4" customWidth="1"/>
     <col min="3" max="4" width="20.625" style="4" customWidth="1"/>
     <col min="5" max="5" width="8.625" style="4" customWidth="1"/>
@@ -1916,61 +1893,61 @@
     <col min="16" max="19" width="9.81666666666667" style="4" customWidth="1"/>
     <col min="20" max="20" width="17.2166666666667" style="6" customWidth="1"/>
     <col min="21" max="22" width="19.5" style="7" customWidth="1"/>
-    <col min="23" max="23" width="19.125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="19.125" style="8" customWidth="1"/>
     <col min="24" max="24" width="12.875" style="2" customWidth="1"/>
-    <col min="25" max="25" width="20.125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="20.125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:25">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="9"/>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="13" t="s">
+      <c r="L1" s="13"/>
+      <c r="M1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="19" t="s">
         <v>15</v>
       </c>
       <c r="T1" s="6" t="s">
@@ -1982,13 +1959,13 @@
       <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="20" t="s">
         <v>19</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="19" t="s">
+      <c r="Y1" s="21" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2000,7 +1977,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="22" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="4"/>
@@ -2050,16 +2027,16 @@
       <c r="U2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="21" t="s">
+      <c r="V2" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="24" t="s">
         <v>25</v>
       </c>
       <c r="X2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="Y2" s="25" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2124,69 +2101,71 @@
       <c r="V3" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W3" s="20" t="s">
         <v>47</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Y3" s="22" t="s">
+      <c r="Y3" s="25" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:25">
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="25"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
       <c r="T4" s="6"/>
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
+      <c r="W4" s="20"/>
+      <c r="Y4" s="20"/>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="4">
         <f t="shared" ref="A5:A34" si="0">B5*10+H5</f>
         <v>2001001</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="32">
         <v>200100</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="32">
         <v>200100038</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="32" t="s">
         <v>51</v>
       </c>
       <c r="F5" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="29">
-        <v>1</v>
-      </c>
-      <c r="I5" s="32">
+      <c r="H5" s="32">
+        <v>1</v>
+      </c>
+      <c r="I5" s="35">
         <v>1990000</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K5" s="4">
@@ -2195,11 +2174,11 @@
       <c r="L5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="M5" s="37" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O5" s="4">
         <v>300</v>
@@ -2213,27 +2192,27 @@
       <c r="R5" s="4">
         <v>15000</v>
       </c>
-      <c r="S5" s="35">
+      <c r="S5" s="38">
         <v>16008</v>
       </c>
       <c r="T5" s="6">
         <v>48</v>
       </c>
-      <c r="U5" s="36">
+      <c r="U5" s="39">
         <v>0</v>
       </c>
       <c r="V5" t="s">
         <v>57</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="W5" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X5" s="2">
         <v>0</v>
       </c>
-      <c r="Y5" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y5" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -2241,31 +2220,31 @@
         <f t="shared" si="0"/>
         <v>2001002</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="40">
         <v>200100</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="40">
         <v>200100038</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="40">
         <v>2</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="35">
         <v>1990000</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="J6" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="4">
@@ -2274,11 +2253,11 @@
       <c r="L6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="M6" s="37" t="s">
         <v>56</v>
       </c>
       <c r="N6" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O6" s="4">
         <v>300</v>
@@ -2292,27 +2271,27 @@
       <c r="R6" s="4">
         <v>15000</v>
       </c>
-      <c r="S6" s="35">
+      <c r="S6" s="38">
         <v>16008</v>
       </c>
       <c r="T6" s="6">
         <v>48</v>
       </c>
-      <c r="U6" s="36">
+      <c r="U6" s="39">
         <v>0</v>
       </c>
       <c r="V6" t="s">
         <v>61</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="W6" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X6" s="2">
         <v>0</v>
       </c>
-      <c r="Y6" s="2">
-        <f t="shared" ref="Y6:Y10" si="1">Y5*100</f>
-        <v>5000000000</v>
+      <c r="Y6" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:25">
@@ -2320,31 +2299,31 @@
         <f t="shared" si="0"/>
         <v>2001003</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="32">
         <v>200100</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="32">
         <v>200100038</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F7" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="32">
         <v>3</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="35">
         <v>1990000</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K7" s="4">
@@ -2353,11 +2332,11 @@
       <c r="L7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="34" t="s">
+      <c r="M7" s="37" t="s">
         <v>56</v>
       </c>
       <c r="N7" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O7" s="4">
         <v>300</v>
@@ -2371,27 +2350,27 @@
       <c r="R7" s="4">
         <v>15000</v>
       </c>
-      <c r="S7" s="35">
+      <c r="S7" s="38">
         <v>16008</v>
       </c>
       <c r="T7" s="6">
         <v>48</v>
       </c>
-      <c r="U7" s="36">
+      <c r="U7" s="39">
         <v>0</v>
       </c>
       <c r="V7" t="s">
         <v>65</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W7" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X7" s="2">
         <v>0</v>
       </c>
-      <c r="Y7" s="39">
-        <f t="shared" si="1"/>
-        <v>500000000000</v>
+      <c r="Y7" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:25">
@@ -2399,31 +2378,31 @@
         <f t="shared" si="0"/>
         <v>2001011</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="32">
         <v>200101</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="32">
         <v>200101001</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="43" t="s">
         <v>51</v>
       </c>
       <c r="F8" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="29">
-        <v>1</v>
-      </c>
-      <c r="I8" s="32">
+      <c r="H8" s="32">
+        <v>1</v>
+      </c>
+      <c r="I8" s="35">
         <v>1990000</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K8" s="4">
@@ -2432,11 +2411,11 @@
       <c r="L8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="M8" s="37" t="s">
         <v>69</v>
       </c>
       <c r="N8" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O8" s="4">
         <v>300</v>
@@ -2450,27 +2429,27 @@
       <c r="R8" s="4">
         <v>15000</v>
       </c>
-      <c r="S8" s="35">
+      <c r="S8" s="38">
         <v>16008</v>
       </c>
       <c r="T8" s="6">
         <v>48</v>
       </c>
-      <c r="U8" s="36">
+      <c r="U8" s="39">
         <v>0</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="W8" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X8" s="2">
         <v>0</v>
       </c>
-      <c r="Y8" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y8" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -2478,31 +2457,31 @@
         <f t="shared" si="0"/>
         <v>2001012</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="40">
         <v>200101</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="40">
         <v>200101001</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F9" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="40">
         <v>2</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="35">
         <v>1990000</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K9" s="4">
@@ -2511,11 +2490,11 @@
       <c r="L9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M9" s="34" t="s">
+      <c r="M9" s="37" t="s">
         <v>69</v>
       </c>
       <c r="N9" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O9" s="4">
         <v>300</v>
@@ -2529,27 +2508,27 @@
       <c r="R9" s="4">
         <v>15000</v>
       </c>
-      <c r="S9" s="35">
+      <c r="S9" s="38">
         <v>16008</v>
       </c>
       <c r="T9" s="6">
         <v>48</v>
       </c>
-      <c r="U9" s="36">
+      <c r="U9" s="39">
         <v>0</v>
       </c>
       <c r="V9" t="s">
         <v>61</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="W9" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X9" s="2">
         <v>0</v>
       </c>
-      <c r="Y9" s="2">
-        <f t="shared" si="1"/>
-        <v>5000000000</v>
+      <c r="Y9" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -2557,31 +2536,31 @@
         <f t="shared" si="0"/>
         <v>2001013</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="32">
         <v>200101</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="32">
         <v>200101001</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F10" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="32">
         <v>3</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="35">
         <v>1990000</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="J10" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K10" s="4">
@@ -2590,11 +2569,11 @@
       <c r="L10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="34" t="s">
+      <c r="M10" s="37" t="s">
         <v>69</v>
       </c>
       <c r="N10" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O10" s="4">
         <v>300</v>
@@ -2608,27 +2587,27 @@
       <c r="R10" s="4">
         <v>15000</v>
       </c>
-      <c r="S10" s="35">
+      <c r="S10" s="38">
         <v>16008</v>
       </c>
       <c r="T10" s="6">
         <v>48</v>
       </c>
-      <c r="U10" s="36">
+      <c r="U10" s="39">
         <v>0</v>
       </c>
       <c r="V10" t="s">
         <v>65</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="W10" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X10" s="2">
         <v>0</v>
       </c>
-      <c r="Y10" s="39">
-        <f t="shared" si="1"/>
-        <v>500000000000</v>
+      <c r="Y10" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -2636,31 +2615,31 @@
         <f t="shared" si="0"/>
         <v>2003001</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="32">
         <v>200300</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="32">
         <v>200300001</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="44" t="s">
         <v>51</v>
       </c>
       <c r="F11" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="29">
-        <v>1</v>
-      </c>
-      <c r="I11" s="32">
+      <c r="H11" s="32">
+        <v>1</v>
+      </c>
+      <c r="I11" s="35">
         <v>1990000</v>
       </c>
-      <c r="J11" s="33" t="s">
+      <c r="J11" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K11" s="4">
@@ -2669,11 +2648,11 @@
       <c r="L11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="34" t="s">
+      <c r="M11" s="37" t="s">
         <v>71</v>
       </c>
       <c r="N11" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O11" s="4">
         <v>300</v>
@@ -2687,27 +2666,27 @@
       <c r="R11" s="4">
         <v>15000</v>
       </c>
-      <c r="S11" s="35">
+      <c r="S11" s="38">
         <v>16008</v>
       </c>
       <c r="T11" s="6">
         <v>50</v>
       </c>
-      <c r="U11" s="36">
+      <c r="U11" s="39">
         <v>0</v>
       </c>
       <c r="V11" t="s">
         <v>57</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="W11" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X11" s="2">
         <v>0</v>
       </c>
-      <c r="Y11" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y11" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:25">
@@ -2715,31 +2694,31 @@
         <f t="shared" si="0"/>
         <v>2003002</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="40">
         <v>200300</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="40">
         <v>200300001</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F12" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="40">
         <v>2</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="35">
         <v>1990000</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K12" s="4">
@@ -2748,11 +2727,11 @@
       <c r="L12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="34" t="s">
+      <c r="M12" s="37" t="s">
         <v>71</v>
       </c>
       <c r="N12" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O12" s="4">
         <v>300</v>
@@ -2766,27 +2745,27 @@
       <c r="R12" s="4">
         <v>15000</v>
       </c>
-      <c r="S12" s="35">
+      <c r="S12" s="38">
         <v>16008</v>
       </c>
       <c r="T12" s="6">
         <v>50</v>
       </c>
-      <c r="U12" s="36">
+      <c r="U12" s="39">
         <v>0</v>
       </c>
       <c r="V12" t="s">
         <v>61</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="W12" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X12" s="2">
         <v>0</v>
       </c>
-      <c r="Y12" s="2">
-        <f t="shared" ref="Y12:Y16" si="2">Y11*100</f>
-        <v>5000000000</v>
+      <c r="Y12" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2794,31 +2773,31 @@
         <f t="shared" si="0"/>
         <v>2003003</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="32">
         <v>200300</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="32">
         <v>200300001</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F13" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="32">
         <v>3</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="35">
         <v>1990000</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="J13" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K13" s="4">
@@ -2827,11 +2806,11 @@
       <c r="L13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="34" t="s">
+      <c r="M13" s="37" t="s">
         <v>71</v>
       </c>
       <c r="N13" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O13" s="4">
         <v>300</v>
@@ -2845,27 +2824,27 @@
       <c r="R13" s="4">
         <v>15000</v>
       </c>
-      <c r="S13" s="35">
+      <c r="S13" s="38">
         <v>16008</v>
       </c>
       <c r="T13" s="6">
         <v>50</v>
       </c>
-      <c r="U13" s="36">
+      <c r="U13" s="39">
         <v>0</v>
       </c>
       <c r="V13" t="s">
         <v>65</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="W13" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X13" s="2">
         <v>0</v>
       </c>
-      <c r="Y13" s="39">
-        <f t="shared" si="2"/>
-        <v>500000000000</v>
+      <c r="Y13" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2873,31 +2852,31 @@
         <f t="shared" si="0"/>
         <v>2004001</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="32">
         <v>200400</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="32">
         <v>200400009</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="43" t="s">
         <v>51</v>
       </c>
       <c r="F14" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="29">
-        <v>1</v>
-      </c>
-      <c r="I14" s="32">
+      <c r="H14" s="32">
+        <v>1</v>
+      </c>
+      <c r="I14" s="35">
         <v>1990000</v>
       </c>
-      <c r="J14" s="33" t="s">
+      <c r="J14" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K14" s="4">
@@ -2906,11 +2885,11 @@
       <c r="L14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="34" t="s">
+      <c r="M14" s="37" t="s">
         <v>73</v>
       </c>
       <c r="N14" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O14" s="4">
         <v>300</v>
@@ -2924,27 +2903,27 @@
       <c r="R14" s="4">
         <v>15000</v>
       </c>
-      <c r="S14" s="35">
+      <c r="S14" s="38">
         <v>16008</v>
       </c>
       <c r="T14" s="6">
         <v>50</v>
       </c>
-      <c r="U14" s="36">
+      <c r="U14" s="39">
         <v>0</v>
       </c>
       <c r="V14" t="s">
         <v>57</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="W14" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X14" s="2">
         <v>0</v>
       </c>
-      <c r="Y14" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y14" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2952,31 +2931,31 @@
         <f t="shared" si="0"/>
         <v>2004002</v>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="40">
         <v>200400</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="40">
         <v>200400009</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F15" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="40">
         <v>2</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="35">
         <v>1990000</v>
       </c>
-      <c r="J15" s="38" t="s">
+      <c r="J15" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K15" s="4">
@@ -2985,11 +2964,11 @@
       <c r="L15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M15" s="34" t="s">
+      <c r="M15" s="37" t="s">
         <v>73</v>
       </c>
       <c r="N15" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O15" s="4">
         <v>300</v>
@@ -3003,27 +2982,27 @@
       <c r="R15" s="4">
         <v>15000</v>
       </c>
-      <c r="S15" s="35">
+      <c r="S15" s="38">
         <v>16008</v>
       </c>
       <c r="T15" s="6">
         <v>50</v>
       </c>
-      <c r="U15" s="36">
+      <c r="U15" s="39">
         <v>0</v>
       </c>
       <c r="V15" t="s">
         <v>61</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="W15" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X15" s="2">
         <v>0</v>
       </c>
-      <c r="Y15" s="2">
-        <f t="shared" si="2"/>
-        <v>5000000000</v>
+      <c r="Y15" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:25">
@@ -3031,31 +3010,31 @@
         <f t="shared" si="0"/>
         <v>2004003</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="32">
         <v>200400</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="32">
         <v>200400009</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="32">
         <v>3</v>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="35">
         <v>1990000</v>
       </c>
-      <c r="J16" s="33" t="s">
+      <c r="J16" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K16" s="4">
@@ -3064,11 +3043,11 @@
       <c r="L16" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M16" s="34" t="s">
+      <c r="M16" s="37" t="s">
         <v>73</v>
       </c>
       <c r="N16" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O16" s="4">
         <v>300</v>
@@ -3082,27 +3061,27 @@
       <c r="R16" s="4">
         <v>15000</v>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="38">
         <v>16008</v>
       </c>
       <c r="T16" s="6">
         <v>50</v>
       </c>
-      <c r="U16" s="36">
+      <c r="U16" s="39">
         <v>0</v>
       </c>
       <c r="V16" t="s">
         <v>65</v>
       </c>
-      <c r="W16" s="2" t="s">
+      <c r="W16" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X16" s="2">
         <v>0</v>
       </c>
-      <c r="Y16" s="39">
-        <f t="shared" si="2"/>
-        <v>500000000000</v>
+      <c r="Y16" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:25">
@@ -3110,31 +3089,31 @@
         <f t="shared" si="0"/>
         <v>2005001</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="32">
         <v>200500</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="32">
         <v>200500025</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="32" t="s">
         <v>51</v>
       </c>
       <c r="F17" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H17" s="29">
-        <v>1</v>
-      </c>
-      <c r="I17" s="32">
+      <c r="H17" s="32">
+        <v>1</v>
+      </c>
+      <c r="I17" s="35">
         <v>1990000</v>
       </c>
-      <c r="J17" s="33" t="s">
+      <c r="J17" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K17" s="4">
@@ -3143,11 +3122,11 @@
       <c r="L17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="34" t="s">
+      <c r="M17" s="37" t="s">
         <v>75</v>
       </c>
       <c r="N17" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O17" s="4">
         <v>300</v>
@@ -3161,27 +3140,27 @@
       <c r="R17" s="4">
         <v>15000</v>
       </c>
-      <c r="S17" s="35">
+      <c r="S17" s="38">
         <v>16008</v>
       </c>
       <c r="T17" s="6">
         <v>48</v>
       </c>
-      <c r="U17" s="36">
+      <c r="U17" s="39">
         <v>0</v>
       </c>
       <c r="V17" t="s">
         <v>57</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="W17" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
       </c>
-      <c r="Y17" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y17" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -3189,31 +3168,31 @@
         <f t="shared" si="0"/>
         <v>2005002</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="40">
         <v>200500</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="40">
         <v>200500025</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F18" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="40">
         <v>2</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="35">
         <v>1990000</v>
       </c>
-      <c r="J18" s="38" t="s">
+      <c r="J18" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K18" s="4">
@@ -3222,11 +3201,11 @@
       <c r="L18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="34" t="s">
+      <c r="M18" s="37" t="s">
         <v>75</v>
       </c>
       <c r="N18" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O18" s="4">
         <v>300</v>
@@ -3240,27 +3219,27 @@
       <c r="R18" s="4">
         <v>15000</v>
       </c>
-      <c r="S18" s="35">
+      <c r="S18" s="38">
         <v>16008</v>
       </c>
       <c r="T18" s="6">
         <v>48</v>
       </c>
-      <c r="U18" s="36">
+      <c r="U18" s="39">
         <v>0</v>
       </c>
       <c r="V18" t="s">
         <v>61</v>
       </c>
-      <c r="W18" s="2" t="s">
+      <c r="W18" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X18" s="2">
         <v>0</v>
       </c>
-      <c r="Y18" s="2">
-        <f t="shared" ref="Y18:Y22" si="3">Y17*100</f>
-        <v>5000000000</v>
+      <c r="Y18" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -3268,31 +3247,31 @@
         <f t="shared" si="0"/>
         <v>2005003</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="32">
         <v>200500</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="32">
         <v>200500025</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F19" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="32">
         <v>3</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="35">
         <v>1990000</v>
       </c>
-      <c r="J19" s="33" t="s">
+      <c r="J19" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K19" s="4">
@@ -3301,11 +3280,11 @@
       <c r="L19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="34" t="s">
+      <c r="M19" s="37" t="s">
         <v>75</v>
       </c>
       <c r="N19" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O19" s="4">
         <v>300</v>
@@ -3319,27 +3298,27 @@
       <c r="R19" s="4">
         <v>15000</v>
       </c>
-      <c r="S19" s="35">
+      <c r="S19" s="38">
         <v>16008</v>
       </c>
       <c r="T19" s="6">
         <v>48</v>
       </c>
-      <c r="U19" s="36">
+      <c r="U19" s="39">
         <v>0</v>
       </c>
       <c r="V19" t="s">
         <v>65</v>
       </c>
-      <c r="W19" s="2" t="s">
+      <c r="W19" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X19" s="2">
         <v>0</v>
       </c>
-      <c r="Y19" s="39">
-        <f t="shared" si="3"/>
-        <v>500000000000</v>
+      <c r="Y19" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -3347,31 +3326,31 @@
         <f t="shared" si="0"/>
         <v>2006001</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="32">
         <v>200600</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="32">
         <v>200600001</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="44" t="s">
         <v>51</v>
       </c>
       <c r="F20" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="29">
-        <v>1</v>
-      </c>
-      <c r="I20" s="32">
+      <c r="H20" s="32">
+        <v>1</v>
+      </c>
+      <c r="I20" s="35">
         <v>1990000</v>
       </c>
-      <c r="J20" s="33" t="s">
+      <c r="J20" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K20" s="4">
@@ -3380,11 +3359,11 @@
       <c r="L20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M20" s="37" t="s">
         <v>77</v>
       </c>
       <c r="N20" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O20" s="4">
         <v>300</v>
@@ -3398,27 +3377,27 @@
       <c r="R20" s="4">
         <v>15000</v>
       </c>
-      <c r="S20" s="35">
+      <c r="S20" s="38">
         <v>16008</v>
       </c>
       <c r="T20" s="6">
         <v>20</v>
       </c>
-      <c r="U20" s="36">
+      <c r="U20" s="39">
         <v>0</v>
       </c>
       <c r="V20" t="s">
         <v>57</v>
       </c>
-      <c r="W20" s="2" t="s">
+      <c r="W20" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X20" s="2">
         <v>0</v>
       </c>
-      <c r="Y20" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y20" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:25">
@@ -3426,31 +3405,31 @@
         <f t="shared" si="0"/>
         <v>2006002</v>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="40">
         <v>200600</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="40">
         <v>200600001</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="E21" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F21" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="37">
+      <c r="H21" s="40">
         <v>2</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="35">
         <v>1990000</v>
       </c>
-      <c r="J21" s="38" t="s">
+      <c r="J21" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K21" s="4">
@@ -3459,11 +3438,11 @@
       <c r="L21" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M21" s="34" t="s">
+      <c r="M21" s="37" t="s">
         <v>77</v>
       </c>
       <c r="N21" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O21" s="4">
         <v>300</v>
@@ -3477,27 +3456,27 @@
       <c r="R21" s="4">
         <v>15000</v>
       </c>
-      <c r="S21" s="35">
+      <c r="S21" s="38">
         <v>16008</v>
       </c>
       <c r="T21" s="6">
         <v>20</v>
       </c>
-      <c r="U21" s="36">
+      <c r="U21" s="39">
         <v>0</v>
       </c>
       <c r="V21" t="s">
         <v>61</v>
       </c>
-      <c r="W21" s="2" t="s">
+      <c r="W21" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X21" s="2">
         <v>0</v>
       </c>
-      <c r="Y21" s="2">
-        <f t="shared" si="3"/>
-        <v>5000000000</v>
+      <c r="Y21" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -3505,31 +3484,31 @@
         <f t="shared" si="0"/>
         <v>2006003</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="32">
         <v>200600</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="32">
         <v>200600001</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F22" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="32">
         <v>3</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="35">
         <v>1990000</v>
       </c>
-      <c r="J22" s="33" t="s">
+      <c r="J22" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K22" s="4">
@@ -3538,11 +3517,11 @@
       <c r="L22" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M22" s="34" t="s">
+      <c r="M22" s="37" t="s">
         <v>77</v>
       </c>
       <c r="N22" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O22" s="4">
         <v>300</v>
@@ -3556,27 +3535,27 @@
       <c r="R22" s="4">
         <v>15000</v>
       </c>
-      <c r="S22" s="35">
+      <c r="S22" s="38">
         <v>16008</v>
       </c>
       <c r="T22" s="6">
         <v>20</v>
       </c>
-      <c r="U22" s="36">
+      <c r="U22" s="39">
         <v>0</v>
       </c>
       <c r="V22" t="s">
         <v>65</v>
       </c>
-      <c r="W22" s="2" t="s">
+      <c r="W22" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X22" s="2">
         <v>0</v>
       </c>
-      <c r="Y22" s="39">
-        <f t="shared" si="3"/>
-        <v>500000000000</v>
+      <c r="Y22" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -3584,31 +3563,31 @@
         <f t="shared" si="0"/>
         <v>2007001</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="32">
         <v>200700</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="32">
         <v>200700001</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="32" t="s">
         <v>51</v>
       </c>
       <c r="F23" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H23" s="29">
-        <v>1</v>
-      </c>
-      <c r="I23" s="32">
+      <c r="H23" s="32">
+        <v>1</v>
+      </c>
+      <c r="I23" s="35">
         <v>1990000</v>
       </c>
-      <c r="J23" s="33" t="s">
+      <c r="J23" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K23" s="4">
@@ -3617,11 +3596,11 @@
       <c r="L23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M23" s="34" t="s">
+      <c r="M23" s="37" t="s">
         <v>79</v>
       </c>
       <c r="N23" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O23" s="4">
         <v>0</v>
@@ -3635,27 +3614,27 @@
       <c r="R23" s="4">
         <v>15000</v>
       </c>
-      <c r="S23" s="35">
+      <c r="S23" s="38">
         <v>16008</v>
       </c>
       <c r="T23" s="6">
         <v>30</v>
       </c>
-      <c r="U23" s="36">
+      <c r="U23" s="39">
         <v>1</v>
       </c>
       <c r="V23" t="s">
         <v>57</v>
       </c>
-      <c r="W23" s="2" t="s">
+      <c r="W23" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X23" s="2">
         <v>0</v>
       </c>
-      <c r="Y23" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y23" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -3663,31 +3642,31 @@
         <f t="shared" si="0"/>
         <v>2007002</v>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="40">
         <v>200700</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="37">
+      <c r="D24" s="40">
         <v>200700001</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="E24" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F24" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H24" s="37">
+      <c r="H24" s="40">
         <v>2</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="35">
         <v>1990000</v>
       </c>
-      <c r="J24" s="38" t="s">
+      <c r="J24" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K24" s="4">
@@ -3696,11 +3675,11 @@
       <c r="L24" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M24" s="34" t="s">
+      <c r="M24" s="37" t="s">
         <v>79</v>
       </c>
       <c r="N24" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O24" s="4">
         <v>0</v>
@@ -3714,27 +3693,27 @@
       <c r="R24" s="4">
         <v>15000</v>
       </c>
-      <c r="S24" s="35">
+      <c r="S24" s="38">
         <v>16008</v>
       </c>
       <c r="T24" s="6">
         <v>30</v>
       </c>
-      <c r="U24" s="36">
+      <c r="U24" s="39">
         <v>1</v>
       </c>
       <c r="V24" t="s">
         <v>61</v>
       </c>
-      <c r="W24" s="2" t="s">
+      <c r="W24" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X24" s="2">
         <v>0</v>
       </c>
-      <c r="Y24" s="2">
-        <f t="shared" ref="Y24:Y28" si="4">Y23*100</f>
-        <v>5000000000</v>
+      <c r="Y24" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" spans="1:25">
@@ -3742,31 +3721,31 @@
         <f t="shared" si="0"/>
         <v>2007003</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="32">
         <v>200700</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="32">
         <v>200700001</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F25" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="32">
         <v>3</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="35">
         <v>1990000</v>
       </c>
-      <c r="J25" s="33" t="s">
+      <c r="J25" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K25" s="4">
@@ -3775,11 +3754,11 @@
       <c r="L25" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M25" s="34" t="s">
+      <c r="M25" s="37" t="s">
         <v>79</v>
       </c>
       <c r="N25" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O25" s="4">
         <v>0</v>
@@ -3793,27 +3772,27 @@
       <c r="R25" s="4">
         <v>15000</v>
       </c>
-      <c r="S25" s="35">
+      <c r="S25" s="38">
         <v>16008</v>
       </c>
       <c r="T25" s="6">
         <v>30</v>
       </c>
-      <c r="U25" s="36">
+      <c r="U25" s="39">
         <v>1</v>
       </c>
       <c r="V25" t="s">
         <v>65</v>
       </c>
-      <c r="W25" s="2" t="s">
+      <c r="W25" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X25" s="2">
         <v>0</v>
       </c>
-      <c r="Y25" s="39">
-        <f t="shared" si="4"/>
-        <v>500000000000</v>
+      <c r="Y25" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="1:25">
@@ -3821,31 +3800,31 @@
         <f t="shared" si="0"/>
         <v>2008001</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="32">
         <v>200800</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="32">
         <v>200800001</v>
       </c>
-      <c r="E26" s="41" t="s">
+      <c r="E26" s="44" t="s">
         <v>51</v>
       </c>
       <c r="F26" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="29">
-        <v>1</v>
-      </c>
-      <c r="I26" s="32">
+      <c r="H26" s="32">
+        <v>1</v>
+      </c>
+      <c r="I26" s="35">
         <v>1990000</v>
       </c>
-      <c r="J26" s="33" t="s">
+      <c r="J26" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K26" s="4">
@@ -3854,11 +3833,11 @@
       <c r="L26" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M26" s="34" t="s">
+      <c r="M26" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N26" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O26" s="4">
         <v>300</v>
@@ -3872,27 +3851,27 @@
       <c r="R26" s="4">
         <v>15000</v>
       </c>
-      <c r="S26" s="35">
+      <c r="S26" s="38">
         <v>16008</v>
       </c>
       <c r="T26" s="6">
         <v>20</v>
       </c>
-      <c r="U26" s="36">
+      <c r="U26" s="39">
         <v>0</v>
       </c>
       <c r="V26" t="s">
         <v>57</v>
       </c>
-      <c r="W26" s="2" t="s">
+      <c r="W26" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X26" s="2">
         <v>0</v>
       </c>
-      <c r="Y26" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y26" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:25">
@@ -3900,31 +3879,31 @@
         <f t="shared" si="0"/>
         <v>2008002</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="32">
         <v>200800</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="32">
         <v>200800001</v>
       </c>
-      <c r="E27" s="37" t="s">
+      <c r="E27" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F27" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="37">
+      <c r="H27" s="40">
         <v>2</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="35">
         <v>1990000</v>
       </c>
-      <c r="J27" s="38" t="s">
+      <c r="J27" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K27" s="4">
@@ -3933,11 +3912,11 @@
       <c r="L27" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M27" s="34" t="s">
+      <c r="M27" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N27" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O27" s="4">
         <v>300</v>
@@ -3951,27 +3930,27 @@
       <c r="R27" s="4">
         <v>15000</v>
       </c>
-      <c r="S27" s="35">
+      <c r="S27" s="38">
         <v>16008</v>
       </c>
       <c r="T27" s="6">
         <v>20</v>
       </c>
-      <c r="U27" s="36">
+      <c r="U27" s="39">
         <v>0</v>
       </c>
       <c r="V27" t="s">
         <v>61</v>
       </c>
-      <c r="W27" s="2" t="s">
+      <c r="W27" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X27" s="2">
         <v>0</v>
       </c>
-      <c r="Y27" s="2">
-        <f t="shared" si="4"/>
-        <v>5000000000</v>
+      <c r="Y27" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" spans="1:25">
@@ -3979,31 +3958,31 @@
         <f t="shared" si="0"/>
         <v>2008003</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="32">
         <v>200800</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="32">
         <v>200800001</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F28" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="32">
         <v>3</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="35">
         <v>1990000</v>
       </c>
-      <c r="J28" s="33" t="s">
+      <c r="J28" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K28" s="4">
@@ -4012,11 +3991,11 @@
       <c r="L28" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N28" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O28" s="4">
         <v>300</v>
@@ -4030,27 +4009,27 @@
       <c r="R28" s="4">
         <v>15000</v>
       </c>
-      <c r="S28" s="35">
+      <c r="S28" s="38">
         <v>16008</v>
       </c>
       <c r="T28" s="6">
         <v>20</v>
       </c>
-      <c r="U28" s="36">
+      <c r="U28" s="39">
         <v>0</v>
       </c>
       <c r="V28" t="s">
         <v>65</v>
       </c>
-      <c r="W28" s="2" t="s">
+      <c r="W28" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X28" s="2">
         <v>0</v>
       </c>
-      <c r="Y28" s="39">
-        <f t="shared" si="4"/>
-        <v>500000000000</v>
+      <c r="Y28" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:25">
@@ -4058,44 +4037,44 @@
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="42">
+      <c r="B29" s="45">
         <v>200900</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="32">
         <v>200900001</v>
       </c>
-      <c r="E29" s="40" t="s">
+      <c r="E29" s="43" t="s">
         <v>51</v>
       </c>
       <c r="F29" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H29" s="29">
-        <v>1</v>
-      </c>
-      <c r="I29" s="32">
+      <c r="H29" s="32">
+        <v>1</v>
+      </c>
+      <c r="I29" s="35">
         <v>1990000</v>
       </c>
-      <c r="J29" s="33" t="s">
+      <c r="J29" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="43">
+      <c r="K29" s="46">
         <v>0</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M29" s="34" t="s">
+      <c r="M29" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N29" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O29" s="4">
         <v>300</v>
@@ -4109,27 +4088,27 @@
       <c r="R29" s="4">
         <v>15000</v>
       </c>
-      <c r="S29" s="35">
+      <c r="S29" s="38">
         <v>16008</v>
       </c>
       <c r="T29" s="6">
         <v>20</v>
       </c>
-      <c r="U29" s="36">
+      <c r="U29" s="39">
         <v>0</v>
       </c>
       <c r="V29" t="s">
         <v>57</v>
       </c>
-      <c r="W29" s="2" t="s">
+      <c r="W29" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X29" s="2">
         <v>0</v>
       </c>
-      <c r="Y29" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="Y29" s="8">
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -4137,44 +4116,44 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="44">
+      <c r="B30" s="47">
         <v>200900</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="40">
         <v>200900001</v>
       </c>
-      <c r="E30" s="37" t="s">
+      <c r="E30" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F30" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="31" t="s">
+      <c r="G30" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="37">
+      <c r="H30" s="40">
         <v>2</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="35">
         <v>1990000</v>
       </c>
-      <c r="J30" s="38" t="s">
+      <c r="J30" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="43">
+      <c r="K30" s="46">
         <v>0</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M30" s="34" t="s">
+      <c r="M30" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N30" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O30" s="4">
         <v>300</v>
@@ -4188,27 +4167,27 @@
       <c r="R30" s="4">
         <v>15000</v>
       </c>
-      <c r="S30" s="35">
+      <c r="S30" s="38">
         <v>16008</v>
       </c>
       <c r="T30" s="6">
         <v>20</v>
       </c>
-      <c r="U30" s="36">
+      <c r="U30" s="39">
         <v>0</v>
       </c>
       <c r="V30" t="s">
         <v>61</v>
       </c>
-      <c r="W30" s="2" t="s">
+      <c r="W30" s="8" t="s">
         <v>62</v>
       </c>
       <c r="X30" s="2">
         <v>0</v>
       </c>
-      <c r="Y30" s="2">
-        <f t="shared" ref="Y30:Y34" si="5">Y29*100</f>
-        <v>5000000000</v>
+      <c r="Y30" s="8">
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -4216,44 +4195,44 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="45">
+      <c r="B31" s="48">
         <v>200900</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="46">
+      <c r="D31" s="49">
         <v>200900001</v>
       </c>
-      <c r="E31" s="46" t="s">
+      <c r="E31" s="49" t="s">
         <v>63</v>
       </c>
       <c r="F31" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="32">
         <v>3</v>
       </c>
-      <c r="I31" s="32">
+      <c r="I31" s="35">
         <v>1990000</v>
       </c>
-      <c r="J31" s="33" t="s">
+      <c r="J31" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="43">
+      <c r="K31" s="46">
         <v>0</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="M31" s="34" t="s">
+      <c r="M31" s="37" t="s">
         <v>81</v>
       </c>
       <c r="N31" s="4">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="O31" s="4">
         <v>300</v>
@@ -4267,308 +4246,302 @@
       <c r="R31" s="4">
         <v>15000</v>
       </c>
-      <c r="S31" s="35">
+      <c r="S31" s="38">
         <v>16008</v>
       </c>
       <c r="T31" s="6">
         <v>20</v>
       </c>
-      <c r="U31" s="36">
+      <c r="U31" s="39">
         <v>0</v>
       </c>
       <c r="V31" t="s">
         <v>65</v>
       </c>
-      <c r="W31" s="2" t="s">
+      <c r="W31" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X31" s="2">
         <v>0</v>
       </c>
-      <c r="Y31" s="39">
-        <f t="shared" si="5"/>
-        <v>500000000000</v>
+      <c r="Y31" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
-      <c r="A32" s="4">
-        <f t="shared" si="0"/>
-        <v>2010001</v>
-      </c>
-      <c r="B32" s="47">
-        <v>201000</v>
-      </c>
-      <c r="C32" s="4" t="s">
+    <row r="32" s="3" customFormat="1" spans="1:25">
+      <c r="A32" s="50">
+        <v>20010010</v>
+      </c>
+      <c r="B32" s="3">
+        <v>200100</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="51">
+        <v>200100038</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="4">
-        <v>101000006</v>
-      </c>
-      <c r="E32" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="H32" s="29">
-        <v>1</v>
-      </c>
-      <c r="I32" s="32">
-        <v>1990000</v>
-      </c>
-      <c r="J32" s="33" t="s">
+      <c r="H32" s="51">
+        <v>1</v>
+      </c>
+      <c r="I32" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J32" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="43">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="M32" s="34" t="s">
-        <v>85</v>
+      <c r="K32" s="3">
+        <v>1</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M32" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N32" s="4">
-        <v>9700</v>
-      </c>
-      <c r="O32" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="4">
+      <c r="P32" s="3">
         <v>180000</v>
       </c>
-      <c r="Q32" s="4">
+      <c r="Q32" s="3">
         <v>16000</v>
       </c>
-      <c r="R32" s="4">
+      <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="35">
+      <c r="S32" s="55">
         <v>16008</v>
       </c>
-      <c r="T32" s="6">
-        <v>50</v>
-      </c>
-      <c r="U32" s="36">
+      <c r="T32" s="50">
+        <v>48</v>
+      </c>
+      <c r="U32" s="56">
         <v>0</v>
       </c>
       <c r="V32" t="s">
         <v>57</v>
       </c>
-      <c r="W32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="X32" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="2">
-        <f>5000*10000</f>
-        <v>50000000</v>
+      <c r="W32" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="X32" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="57">
+        <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
-      <c r="A33" s="4">
-        <f t="shared" si="0"/>
-        <v>2010002</v>
-      </c>
-      <c r="B33" s="47">
-        <v>201000</v>
-      </c>
-      <c r="C33" s="4" t="s">
+    <row r="33" s="3" customFormat="1" spans="1:25">
+      <c r="A33" s="50">
+        <v>20010011</v>
+      </c>
+      <c r="B33" s="3">
+        <v>200100</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="51">
+        <v>200100038</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="4">
-        <v>101000006</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="H33" s="37">
+      <c r="H33" s="51">
         <v>2</v>
       </c>
-      <c r="I33" s="32">
-        <v>1990000</v>
-      </c>
-      <c r="J33" s="38" t="s">
+      <c r="I33" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J33" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="43">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="M33" s="34" t="s">
-        <v>85</v>
+      <c r="K33" s="3">
+        <v>1</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M33" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N33" s="4">
-        <v>9700</v>
-      </c>
-      <c r="O33" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="P33" s="4">
+      <c r="P33" s="3">
         <v>180000</v>
       </c>
-      <c r="Q33" s="4">
+      <c r="Q33" s="3">
         <v>16000</v>
       </c>
-      <c r="R33" s="4">
+      <c r="R33" s="3">
         <v>15000</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="55">
         <v>16008</v>
       </c>
-      <c r="T33" s="6">
-        <v>50</v>
-      </c>
-      <c r="U33" s="36">
+      <c r="T33" s="50">
+        <v>48</v>
+      </c>
+      <c r="U33" s="56">
         <v>0</v>
       </c>
       <c r="V33" t="s">
         <v>61</v>
       </c>
-      <c r="W33" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X33" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="2">
-        <f t="shared" si="5"/>
-        <v>5000000000</v>
+      <c r="W33" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="X33" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="57">
+        <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
-      <c r="A34" s="4">
-        <f t="shared" si="0"/>
-        <v>2010003</v>
-      </c>
-      <c r="B34" s="47">
-        <v>201000</v>
-      </c>
-      <c r="C34" s="4" t="s">
+    <row r="34" s="3" customFormat="1" spans="1:25">
+      <c r="A34" s="50">
+        <v>20010012</v>
+      </c>
+      <c r="B34" s="3">
+        <v>200100</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="51">
+        <v>200100038</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="4">
-        <v>101000006</v>
-      </c>
-      <c r="E34" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="F34" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="G34" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="29">
+      <c r="H34" s="51">
         <v>3</v>
       </c>
-      <c r="I34" s="32">
-        <v>1990000</v>
-      </c>
-      <c r="J34" s="33" t="s">
+      <c r="I34" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J34" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="43">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="M34" s="34" t="s">
-        <v>85</v>
+      <c r="K34" s="3">
+        <v>1</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M34" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N34" s="4">
-        <v>9700</v>
-      </c>
-      <c r="O34" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O34" s="3">
         <v>300</v>
       </c>
-      <c r="P34" s="4">
+      <c r="P34" s="3">
         <v>180000</v>
       </c>
-      <c r="Q34" s="4">
+      <c r="Q34" s="3">
         <v>16000</v>
       </c>
-      <c r="R34" s="4">
+      <c r="R34" s="3">
         <v>15000</v>
       </c>
-      <c r="S34" s="35">
+      <c r="S34" s="55">
         <v>16008</v>
       </c>
-      <c r="T34" s="6">
-        <v>50</v>
-      </c>
-      <c r="U34" s="36">
+      <c r="T34" s="50">
+        <v>48</v>
+      </c>
+      <c r="U34" s="56">
         <v>0</v>
       </c>
       <c r="V34" t="s">
         <v>65</v>
       </c>
-      <c r="W34" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="X34" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="39">
-        <f t="shared" si="5"/>
-        <v>500000000000</v>
+      <c r="W34" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="X34" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="57">
+        <v>0</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" spans="1:25">
-      <c r="A35" s="48">
-        <v>20010010</v>
+      <c r="A35" s="50">
+        <v>20010110</v>
       </c>
       <c r="B35" s="3">
-        <v>200100</v>
-      </c>
-      <c r="C35" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="49">
-        <v>200100038</v>
-      </c>
-      <c r="E35" s="49" t="s">
+        <v>200101</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="3">
+        <v>200101001</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F35" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H35" s="49">
-        <v>1</v>
-      </c>
-      <c r="I35" s="49">
+      <c r="G35" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" s="51">
         <v>1980000</v>
       </c>
-      <c r="J35" s="52" t="s">
-        <v>87</v>
+      <c r="J35" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M35" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="N35" s="3">
-        <v>9700</v>
+        <v>68</v>
+      </c>
+      <c r="M35" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="N35" s="4">
+        <v>9500</v>
       </c>
       <c r="O35" s="3">
         <v>300</v>
@@ -4582,20 +4555,20 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="54">
+      <c r="S35" s="3">
         <v>16008</v>
       </c>
-      <c r="T35" s="48">
+      <c r="T35" s="50">
         <v>48</v>
       </c>
-      <c r="U35" s="55">
-        <v>0</v>
-      </c>
-      <c r="V35" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>89</v>
+      <c r="U35" s="56">
+        <v>0</v>
+      </c>
+      <c r="V35" t="s">
+        <v>57</v>
+      </c>
+      <c r="W35" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X35" s="3">
         <v>1</v>
@@ -4605,47 +4578,47 @@
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:25">
-      <c r="A36" s="48">
-        <v>20010011</v>
+      <c r="A36" s="50">
+        <v>20010111</v>
       </c>
       <c r="B36" s="3">
-        <v>200100</v>
-      </c>
-      <c r="C36" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="49">
-        <v>200100038</v>
-      </c>
-      <c r="E36" s="49" t="s">
+        <v>200101</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="3">
+        <v>200101001</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F36" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H36" s="49">
+      <c r="G36" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="3">
         <v>2</v>
       </c>
-      <c r="I36" s="49">
+      <c r="I36" s="51">
         <v>1980000</v>
       </c>
-      <c r="J36" s="52" t="s">
-        <v>90</v>
+      <c r="J36" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M36" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="N36" s="3">
-        <v>9700</v>
+        <v>68</v>
+      </c>
+      <c r="M36" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="N36" s="4">
+        <v>9500</v>
       </c>
       <c r="O36" s="3">
         <v>300</v>
@@ -4659,20 +4632,20 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="54">
+      <c r="S36" s="3">
         <v>16008</v>
       </c>
-      <c r="T36" s="48">
+      <c r="T36" s="50">
         <v>48</v>
       </c>
-      <c r="U36" s="55">
-        <v>0</v>
-      </c>
-      <c r="V36" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W36" s="3" t="s">
-        <v>91</v>
+      <c r="U36" s="56">
+        <v>0</v>
+      </c>
+      <c r="V36" t="s">
+        <v>61</v>
+      </c>
+      <c r="W36" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X36" s="3">
         <v>1</v>
@@ -4682,47 +4655,47 @@
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:25">
-      <c r="A37" s="48">
-        <v>20010012</v>
+      <c r="A37" s="50">
+        <v>20010112</v>
       </c>
       <c r="B37" s="3">
-        <v>200100</v>
-      </c>
-      <c r="C37" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="49">
-        <v>200100038</v>
-      </c>
-      <c r="E37" s="49" t="s">
+        <v>200101</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="3">
+        <v>200101001</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F37" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H37" s="49">
+      <c r="G37" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="3">
         <v>3</v>
       </c>
-      <c r="I37" s="49">
+      <c r="I37" s="51">
         <v>1980000</v>
       </c>
-      <c r="J37" s="52" t="s">
-        <v>92</v>
+      <c r="J37" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M37" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="N37" s="3">
-        <v>9700</v>
+        <v>68</v>
+      </c>
+      <c r="M37" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="N37" s="4">
+        <v>9500</v>
       </c>
       <c r="O37" s="3">
         <v>300</v>
@@ -4736,20 +4709,20 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="54">
+      <c r="S37" s="3">
         <v>16008</v>
       </c>
-      <c r="T37" s="48">
+      <c r="T37" s="50">
         <v>48</v>
       </c>
-      <c r="U37" s="55">
-        <v>0</v>
-      </c>
-      <c r="V37" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W37" s="3" t="s">
-        <v>93</v>
+      <c r="U37" s="56">
+        <v>0</v>
+      </c>
+      <c r="V37" t="s">
+        <v>65</v>
+      </c>
+      <c r="W37" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X37" s="3">
         <v>1</v>
@@ -4759,35 +4732,35 @@
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:25">
-      <c r="A38" s="48">
-        <v>20010110</v>
+      <c r="A38" s="50">
+        <v>20030010</v>
       </c>
       <c r="B38" s="3">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D38" s="3">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="62" t="s">
+      <c r="F38" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>53</v>
+      <c r="G38" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="49">
+      <c r="I38" s="51">
         <v>1980000</v>
       </c>
-      <c r="J38" s="52" t="s">
-        <v>87</v>
+      <c r="J38" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K38" s="3">
         <v>0</v>
@@ -4795,11 +4768,11 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="N38" s="3">
-        <v>9700</v>
+      <c r="M38" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="N38" s="4">
+        <v>9500</v>
       </c>
       <c r="O38" s="3">
         <v>300</v>
@@ -4816,17 +4789,17 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="48">
-        <v>48</v>
-      </c>
-      <c r="U38" s="55">
-        <v>0</v>
-      </c>
-      <c r="V38" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W38" s="3" t="s">
-        <v>89</v>
+      <c r="T38" s="50">
+        <v>50</v>
+      </c>
+      <c r="U38" s="56">
+        <v>0</v>
+      </c>
+      <c r="V38" t="s">
+        <v>57</v>
+      </c>
+      <c r="W38" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X38" s="3">
         <v>1</v>
@@ -4836,35 +4809,35 @@
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:25">
-      <c r="A39" s="48">
-        <v>20010111</v>
+      <c r="A39" s="50">
+        <v>20030011</v>
       </c>
       <c r="B39" s="3">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D39" s="3">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="62" t="s">
+      <c r="F39" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>53</v>
+      <c r="G39" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="49">
+      <c r="I39" s="51">
         <v>1980000</v>
       </c>
-      <c r="J39" s="52" t="s">
-        <v>90</v>
+      <c r="J39" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -4872,11 +4845,11 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="N39" s="3">
-        <v>9700</v>
+      <c r="M39" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="N39" s="4">
+        <v>9500</v>
       </c>
       <c r="O39" s="3">
         <v>300</v>
@@ -4893,17 +4866,17 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="48">
-        <v>48</v>
-      </c>
-      <c r="U39" s="55">
-        <v>0</v>
-      </c>
-      <c r="V39" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W39" s="3" t="s">
-        <v>91</v>
+      <c r="T39" s="50">
+        <v>50</v>
+      </c>
+      <c r="U39" s="56">
+        <v>0</v>
+      </c>
+      <c r="V39" t="s">
+        <v>61</v>
+      </c>
+      <c r="W39" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X39" s="3">
         <v>1</v>
@@ -4913,74 +4886,74 @@
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:25">
-      <c r="A40" s="48">
-        <v>20010112</v>
+      <c r="A40" s="50">
+        <v>20030012</v>
       </c>
       <c r="B40" s="3">
-        <v>200101</v>
+        <v>200300</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D40" s="3">
-        <v>200101001</v>
+        <v>200300001</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="62" t="s">
+      <c r="F40" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>53</v>
+      <c r="G40" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="49">
+      <c r="I40" s="51">
         <v>1980000</v>
       </c>
-      <c r="J40" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="K40" s="3">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3" t="s">
+      <c r="J40" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="K40" s="58">
+        <v>0</v>
+      </c>
+      <c r="L40" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="N40" s="3">
-        <v>9700</v>
+      <c r="M40" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="N40" s="4">
+        <v>9500</v>
       </c>
       <c r="O40" s="3">
         <v>300</v>
       </c>
-      <c r="P40" s="3">
+      <c r="P40" s="58">
         <v>180000</v>
       </c>
-      <c r="Q40" s="3">
+      <c r="Q40" s="58">
         <v>16000</v>
       </c>
-      <c r="R40" s="3">
+      <c r="R40" s="58">
         <v>15000</v>
       </c>
-      <c r="S40" s="3">
+      <c r="S40" s="58">
         <v>16008</v>
       </c>
-      <c r="T40" s="48">
-        <v>48</v>
-      </c>
-      <c r="U40" s="55">
-        <v>0</v>
-      </c>
-      <c r="V40" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W40" s="3" t="s">
-        <v>93</v>
+      <c r="T40" s="50">
+        <v>50</v>
+      </c>
+      <c r="U40" s="56">
+        <v>0</v>
+      </c>
+      <c r="V40" t="s">
+        <v>65</v>
+      </c>
+      <c r="W40" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X40" s="3">
         <v>1</v>
@@ -4990,74 +4963,74 @@
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:25">
-      <c r="A41" s="48">
-        <v>20030010</v>
+      <c r="A41" s="50">
+        <v>20040010</v>
       </c>
       <c r="B41" s="3">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D41" s="3">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="62" t="s">
+      <c r="F41" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>53</v>
+      <c r="G41" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="49">
+      <c r="I41" s="51">
         <v>1980000</v>
       </c>
-      <c r="J41" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="s">
+      <c r="J41" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="K41" s="58">
+        <v>0</v>
+      </c>
+      <c r="L41" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="N41" s="3">
-        <v>9700</v>
+      <c r="M41" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="N41" s="4">
+        <v>9500</v>
       </c>
       <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="58">
         <v>180000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="58">
         <v>16000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="58">
         <v>15000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="58">
         <v>16008</v>
       </c>
-      <c r="T41" s="48">
+      <c r="T41" s="50">
         <v>50</v>
       </c>
-      <c r="U41" s="55">
-        <v>0</v>
-      </c>
-      <c r="V41" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>89</v>
+      <c r="U41" s="56">
+        <v>0</v>
+      </c>
+      <c r="V41" t="s">
+        <v>57</v>
+      </c>
+      <c r="W41" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X41" s="3">
         <v>1</v>
@@ -5067,74 +5040,74 @@
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:25">
-      <c r="A42" s="48">
-        <v>20030011</v>
+      <c r="A42" s="50">
+        <v>20040011</v>
       </c>
       <c r="B42" s="3">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D42" s="3">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="62" t="s">
+      <c r="F42" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>53</v>
+      <c r="G42" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="49">
+      <c r="I42" s="51">
         <v>1980000</v>
       </c>
-      <c r="J42" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
+      <c r="J42" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="K42" s="58">
+        <v>0</v>
+      </c>
+      <c r="L42" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="N42" s="3">
-        <v>9700</v>
+      <c r="M42" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="N42" s="4">
+        <v>9500</v>
       </c>
       <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="P42" s="58">
         <v>180000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="Q42" s="58">
         <v>16000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="R42" s="58">
         <v>15000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="S42" s="58">
         <v>16008</v>
       </c>
-      <c r="T42" s="48">
+      <c r="T42" s="50">
         <v>50</v>
       </c>
-      <c r="U42" s="55">
-        <v>0</v>
-      </c>
-      <c r="V42" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>91</v>
+      <c r="U42" s="56">
+        <v>0</v>
+      </c>
+      <c r="V42" t="s">
+        <v>61</v>
+      </c>
+      <c r="W42" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X42" s="3">
         <v>1</v>
@@ -5144,35 +5117,35 @@
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:25">
-      <c r="A43" s="48">
-        <v>20030012</v>
+      <c r="A43" s="50">
+        <v>20040012</v>
       </c>
       <c r="B43" s="3">
-        <v>200300</v>
+        <v>200400</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D43" s="3">
-        <v>200300001</v>
+        <v>200400009</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="62" t="s">
+      <c r="F43" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>53</v>
+      <c r="G43" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="49">
+      <c r="I43" s="51">
         <v>1980000</v>
       </c>
-      <c r="J43" s="52" t="s">
-        <v>92</v>
+      <c r="J43" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K43" s="58">
         <v>0</v>
@@ -5180,11 +5153,11 @@
       <c r="L43" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="N43" s="3">
-        <v>9700</v>
+      <c r="M43" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="N43" s="4">
+        <v>9500</v>
       </c>
       <c r="O43" s="3">
         <v>300</v>
@@ -5201,17 +5174,17 @@
       <c r="S43" s="58">
         <v>16008</v>
       </c>
-      <c r="T43" s="48">
+      <c r="T43" s="50">
         <v>50</v>
       </c>
-      <c r="U43" s="55">
-        <v>0</v>
-      </c>
-      <c r="V43" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>93</v>
+      <c r="U43" s="56">
+        <v>0</v>
+      </c>
+      <c r="V43" t="s">
+        <v>65</v>
+      </c>
+      <c r="W43" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X43" s="3">
         <v>1</v>
@@ -5221,47 +5194,47 @@
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:25">
-      <c r="A44" s="48">
-        <v>20040010</v>
+      <c r="A44" s="50">
+        <v>20050010</v>
       </c>
       <c r="B44" s="3">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D44" s="3">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="62" t="s">
+      <c r="F44" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>53</v>
+      <c r="G44" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="49">
+      <c r="I44" s="51">
         <v>1980000</v>
       </c>
-      <c r="J44" s="52" t="s">
-        <v>87</v>
+      <c r="J44" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K44" s="58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="M44" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="N44" s="3">
-        <v>9700</v>
+        <v>55</v>
+      </c>
+      <c r="M44" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="N44" s="4">
+        <v>9500</v>
       </c>
       <c r="O44" s="3">
         <v>300</v>
@@ -5278,17 +5251,17 @@
       <c r="S44" s="58">
         <v>16008</v>
       </c>
-      <c r="T44" s="48">
-        <v>50</v>
-      </c>
-      <c r="U44" s="55">
-        <v>0</v>
-      </c>
-      <c r="V44" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>89</v>
+      <c r="T44" s="50">
+        <v>48</v>
+      </c>
+      <c r="U44" s="50">
+        <v>0</v>
+      </c>
+      <c r="V44" t="s">
+        <v>57</v>
+      </c>
+      <c r="W44" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X44" s="3">
         <v>1</v>
@@ -5298,47 +5271,47 @@
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:25">
-      <c r="A45" s="48">
-        <v>20040011</v>
+      <c r="A45" s="50">
+        <v>20050011</v>
       </c>
       <c r="B45" s="3">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D45" s="3">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="62" t="s">
+      <c r="F45" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>53</v>
+      <c r="G45" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="49">
+      <c r="I45" s="51">
         <v>1980000</v>
       </c>
-      <c r="J45" s="52" t="s">
-        <v>90</v>
+      <c r="J45" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K45" s="58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="M45" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="N45" s="3">
-        <v>9700</v>
+        <v>55</v>
+      </c>
+      <c r="M45" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="N45" s="4">
+        <v>9500</v>
       </c>
       <c r="O45" s="3">
         <v>300</v>
@@ -5355,17 +5328,17 @@
       <c r="S45" s="58">
         <v>16008</v>
       </c>
-      <c r="T45" s="48">
-        <v>50</v>
-      </c>
-      <c r="U45" s="55">
-        <v>0</v>
-      </c>
-      <c r="V45" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>91</v>
+      <c r="T45" s="50">
+        <v>48</v>
+      </c>
+      <c r="U45" s="50">
+        <v>0</v>
+      </c>
+      <c r="V45" t="s">
+        <v>61</v>
+      </c>
+      <c r="W45" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X45" s="3">
         <v>1</v>
@@ -5375,47 +5348,47 @@
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:25">
-      <c r="A46" s="48">
-        <v>20040012</v>
+      <c r="A46" s="50">
+        <v>20050012</v>
       </c>
       <c r="B46" s="3">
-        <v>200400</v>
+        <v>200500</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D46" s="3">
-        <v>200400009</v>
+        <v>200500025</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="62" t="s">
+      <c r="F46" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>53</v>
+      <c r="G46" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="49">
+      <c r="I46" s="51">
         <v>1980000</v>
       </c>
-      <c r="J46" s="52" t="s">
-        <v>92</v>
+      <c r="J46" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K46" s="58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="M46" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="N46" s="3">
-        <v>9700</v>
+        <v>55</v>
+      </c>
+      <c r="M46" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="N46" s="4">
+        <v>9500</v>
       </c>
       <c r="O46" s="3">
         <v>300</v>
@@ -5432,17 +5405,17 @@
       <c r="S46" s="58">
         <v>16008</v>
       </c>
-      <c r="T46" s="48">
-        <v>50</v>
-      </c>
-      <c r="U46" s="55">
-        <v>0</v>
-      </c>
-      <c r="V46" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>93</v>
+      <c r="T46" s="50">
+        <v>48</v>
+      </c>
+      <c r="U46" s="50">
+        <v>0</v>
+      </c>
+      <c r="V46" t="s">
+        <v>65</v>
+      </c>
+      <c r="W46" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X46" s="3">
         <v>1</v>
@@ -5452,47 +5425,47 @@
       </c>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:25">
-      <c r="A47" s="48">
-        <v>20050010</v>
+      <c r="A47" s="50">
+        <v>20060010</v>
       </c>
       <c r="B47" s="3">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D47" s="3">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="62" t="s">
+      <c r="F47" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>53</v>
+      <c r="G47" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="49">
+      <c r="I47" s="51">
         <v>1980000</v>
       </c>
-      <c r="J47" s="52" t="s">
-        <v>87</v>
+      <c r="J47" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K47" s="58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="M47" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="N47" s="3">
-        <v>9700</v>
+        <v>68</v>
+      </c>
+      <c r="M47" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N47" s="4">
+        <v>9500</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
@@ -5509,17 +5482,17 @@
       <c r="S47" s="58">
         <v>16008</v>
       </c>
-      <c r="T47" s="48">
-        <v>48</v>
-      </c>
-      <c r="U47" s="48">
-        <v>0</v>
-      </c>
-      <c r="V47" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>89</v>
+      <c r="T47" s="50">
+        <v>20</v>
+      </c>
+      <c r="U47" s="50">
+        <v>0</v>
+      </c>
+      <c r="V47" t="s">
+        <v>57</v>
+      </c>
+      <c r="W47" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X47" s="3">
         <v>1</v>
@@ -5529,47 +5502,47 @@
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:25">
-      <c r="A48" s="48">
-        <v>20050011</v>
+      <c r="A48" s="50">
+        <v>20060011</v>
       </c>
       <c r="B48" s="3">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D48" s="3">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="62" t="s">
+      <c r="F48" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>53</v>
+      <c r="G48" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="49">
+      <c r="I48" s="51">
         <v>1980000</v>
       </c>
-      <c r="J48" s="52" t="s">
-        <v>90</v>
+      <c r="J48" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K48" s="58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="M48" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="N48" s="3">
-        <v>9700</v>
+        <v>68</v>
+      </c>
+      <c r="M48" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N48" s="4">
+        <v>9500</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -5586,17 +5559,17 @@
       <c r="S48" s="58">
         <v>16008</v>
       </c>
-      <c r="T48" s="48">
-        <v>48</v>
-      </c>
-      <c r="U48" s="48">
-        <v>0</v>
-      </c>
-      <c r="V48" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>91</v>
+      <c r="T48" s="50">
+        <v>20</v>
+      </c>
+      <c r="U48" s="50">
+        <v>0</v>
+      </c>
+      <c r="V48" t="s">
+        <v>61</v>
+      </c>
+      <c r="W48" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X48" s="3">
         <v>1</v>
@@ -5606,74 +5579,74 @@
       </c>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:25">
-      <c r="A49" s="48">
-        <v>20050012</v>
+      <c r="A49" s="50">
+        <v>20060012</v>
       </c>
       <c r="B49" s="3">
-        <v>200500</v>
+        <v>200600</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D49" s="3">
-        <v>200500025</v>
+        <v>200600001</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="62" t="s">
+      <c r="F49" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>53</v>
+      <c r="G49" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="49">
+      <c r="I49" s="51">
         <v>1980000</v>
       </c>
-      <c r="J49" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="K49" s="58">
-        <v>1</v>
-      </c>
-      <c r="L49" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="M49" s="53" t="s">
-        <v>75</v>
-      </c>
-      <c r="N49" s="3">
-        <v>9700</v>
+      <c r="J49" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M49" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N49" s="4">
+        <v>9500</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="58">
+      <c r="P49" s="3">
         <v>180000</v>
       </c>
-      <c r="Q49" s="58">
+      <c r="Q49" s="3">
         <v>16000</v>
       </c>
-      <c r="R49" s="58">
+      <c r="R49" s="3">
         <v>15000</v>
       </c>
-      <c r="S49" s="58">
+      <c r="S49" s="3">
         <v>16008</v>
       </c>
-      <c r="T49" s="48">
-        <v>48</v>
-      </c>
-      <c r="U49" s="48">
-        <v>0</v>
-      </c>
-      <c r="V49" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>93</v>
+      <c r="T49" s="50">
+        <v>20</v>
+      </c>
+      <c r="U49" s="50">
+        <v>0</v>
+      </c>
+      <c r="V49" t="s">
+        <v>65</v>
+      </c>
+      <c r="W49" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X49" s="3">
         <v>1</v>
@@ -5683,74 +5656,74 @@
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:25">
-      <c r="A50" s="48">
-        <v>20060010</v>
+      <c r="A50" s="50">
+        <v>20070010</v>
       </c>
       <c r="B50" s="3">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D50" s="3">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="62" t="s">
+      <c r="F50" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>53</v>
+      <c r="G50" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="49">
+      <c r="I50" s="51">
         <v>1980000</v>
       </c>
-      <c r="J50" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="K50" s="58">
-        <v>0</v>
-      </c>
-      <c r="L50" s="58" t="s">
+      <c r="J50" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="K50" s="3">
+        <v>1</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="N50" s="3">
-        <v>9700</v>
+      <c r="M50" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="N50" s="4">
+        <v>9500</v>
       </c>
       <c r="O50" s="3">
-        <v>300</v>
-      </c>
-      <c r="P50" s="58">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
         <v>180000</v>
       </c>
-      <c r="Q50" s="58">
+      <c r="Q50" s="3">
         <v>16000</v>
       </c>
-      <c r="R50" s="58">
+      <c r="R50" s="3">
         <v>15000</v>
       </c>
-      <c r="S50" s="58">
+      <c r="S50" s="3">
         <v>16008</v>
       </c>
-      <c r="T50" s="48">
-        <v>20</v>
-      </c>
-      <c r="U50" s="48">
-        <v>0</v>
-      </c>
-      <c r="V50" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W50" s="3" t="s">
-        <v>89</v>
+      <c r="T50" s="50">
+        <v>30</v>
+      </c>
+      <c r="U50" s="50">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>57</v>
+      </c>
+      <c r="W50" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X50" s="3">
         <v>1</v>
@@ -5760,74 +5733,74 @@
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:25">
-      <c r="A51" s="48">
-        <v>20060011</v>
+      <c r="A51" s="50">
+        <v>20070011</v>
       </c>
       <c r="B51" s="3">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D51" s="3">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="62" t="s">
+      <c r="F51" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>53</v>
+      <c r="G51" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="49">
+      <c r="I51" s="51">
         <v>1980000</v>
       </c>
-      <c r="J51" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="K51" s="58">
-        <v>0</v>
-      </c>
-      <c r="L51" s="58" t="s">
+      <c r="J51" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="K51" s="3">
+        <v>1</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="N51" s="3">
-        <v>9700</v>
+      <c r="M51" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="N51" s="4">
+        <v>9500</v>
       </c>
       <c r="O51" s="3">
-        <v>300</v>
-      </c>
-      <c r="P51" s="58">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
         <v>180000</v>
       </c>
-      <c r="Q51" s="58">
+      <c r="Q51" s="3">
         <v>16000</v>
       </c>
-      <c r="R51" s="58">
+      <c r="R51" s="3">
         <v>15000</v>
       </c>
-      <c r="S51" s="58">
+      <c r="S51" s="3">
         <v>16008</v>
       </c>
-      <c r="T51" s="48">
-        <v>20</v>
-      </c>
-      <c r="U51" s="48">
-        <v>0</v>
-      </c>
-      <c r="V51" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W51" s="3" t="s">
-        <v>91</v>
+      <c r="T51" s="50">
+        <v>30</v>
+      </c>
+      <c r="U51" s="50">
+        <v>1</v>
+      </c>
+      <c r="V51" t="s">
+        <v>61</v>
+      </c>
+      <c r="W51" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X51" s="3">
         <v>1</v>
@@ -5837,50 +5810,50 @@
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:25">
-      <c r="A52" s="48">
-        <v>20060012</v>
+      <c r="A52" s="50">
+        <v>20070012</v>
       </c>
       <c r="B52" s="3">
-        <v>200600</v>
+        <v>200700</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D52" s="3">
-        <v>200600001</v>
+        <v>200700001</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="62" t="s">
+      <c r="F52" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>53</v>
+      <c r="G52" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="49">
+      <c r="I52" s="51">
         <v>1980000</v>
       </c>
-      <c r="J52" s="52" t="s">
-        <v>92</v>
+      <c r="J52" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="N52" s="3">
-        <v>9700</v>
+      <c r="M52" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="N52" s="4">
+        <v>9500</v>
       </c>
       <c r="O52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>180000</v>
@@ -5894,17 +5867,17 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="48">
-        <v>20</v>
-      </c>
-      <c r="U52" s="48">
-        <v>0</v>
-      </c>
-      <c r="V52" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>93</v>
+      <c r="T52" s="50">
+        <v>30</v>
+      </c>
+      <c r="U52" s="50">
+        <v>1</v>
+      </c>
+      <c r="V52" t="s">
+        <v>65</v>
+      </c>
+      <c r="W52" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X52" s="3">
         <v>1</v>
@@ -5914,50 +5887,50 @@
       </c>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:25">
-      <c r="A53" s="48">
-        <v>20070010</v>
+      <c r="A53" s="50">
+        <v>20080010</v>
       </c>
       <c r="B53" s="3">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D53" s="3">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="62" t="s">
+      <c r="F53" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>53</v>
+      <c r="G53" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="49">
+      <c r="I53" s="51">
         <v>1980000</v>
       </c>
-      <c r="J53" s="52" t="s">
-        <v>87</v>
+      <c r="J53" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="N53" s="3">
-        <v>9700</v>
+      <c r="M53" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="N53" s="4">
+        <v>9500</v>
       </c>
       <c r="O53" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P53" s="3">
         <v>180000</v>
@@ -5971,17 +5944,17 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="48">
-        <v>30</v>
-      </c>
-      <c r="U53" s="48">
-        <v>1</v>
-      </c>
-      <c r="V53" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W53" s="3" t="s">
-        <v>89</v>
+      <c r="T53" s="50">
+        <v>20</v>
+      </c>
+      <c r="U53" s="50">
+        <v>0</v>
+      </c>
+      <c r="V53" t="s">
+        <v>57</v>
+      </c>
+      <c r="W53" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X53" s="3">
         <v>1</v>
@@ -5991,50 +5964,50 @@
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:25">
-      <c r="A54" s="48">
-        <v>20070011</v>
+      <c r="A54" s="50">
+        <v>20080011</v>
       </c>
       <c r="B54" s="3">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D54" s="3">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="62" t="s">
+      <c r="F54" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>53</v>
+      <c r="G54" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="49">
+      <c r="I54" s="51">
         <v>1980000</v>
       </c>
-      <c r="J54" s="52" t="s">
-        <v>90</v>
+      <c r="J54" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="N54" s="3">
-        <v>9700</v>
+      <c r="M54" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="N54" s="4">
+        <v>9500</v>
       </c>
       <c r="O54" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P54" s="3">
         <v>180000</v>
@@ -6048,17 +6021,17 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="48">
-        <v>30</v>
-      </c>
-      <c r="U54" s="48">
-        <v>1</v>
-      </c>
-      <c r="V54" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>91</v>
+      <c r="T54" s="50">
+        <v>20</v>
+      </c>
+      <c r="U54" s="50">
+        <v>0</v>
+      </c>
+      <c r="V54" t="s">
+        <v>61</v>
+      </c>
+      <c r="W54" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X54" s="3">
         <v>1</v>
@@ -6068,50 +6041,50 @@
       </c>
     </row>
     <row r="55" s="3" customFormat="1" spans="1:25">
-      <c r="A55" s="48">
-        <v>20070012</v>
+      <c r="A55" s="50">
+        <v>20080012</v>
       </c>
       <c r="B55" s="3">
-        <v>200700</v>
+        <v>200800</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D55" s="3">
-        <v>200700001</v>
+        <v>200800001</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="62" t="s">
+      <c r="F55" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>53</v>
+      <c r="G55" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="49">
+      <c r="I55" s="51">
         <v>1980000</v>
       </c>
-      <c r="J55" s="52" t="s">
-        <v>92</v>
+      <c r="J55" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="N55" s="3">
-        <v>9700</v>
+      <c r="M55" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="N55" s="4">
+        <v>9500</v>
       </c>
       <c r="O55" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P55" s="3">
         <v>180000</v>
@@ -6125,17 +6098,17 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="48">
-        <v>30</v>
-      </c>
-      <c r="U55" s="48">
-        <v>1</v>
-      </c>
-      <c r="V55" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W55" s="3" t="s">
-        <v>93</v>
+      <c r="T55" s="50">
+        <v>20</v>
+      </c>
+      <c r="U55" s="50">
+        <v>0</v>
+      </c>
+      <c r="V55" t="s">
+        <v>65</v>
+      </c>
+      <c r="W55" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X55" s="3">
         <v>1</v>
@@ -6145,35 +6118,35 @@
       </c>
     </row>
     <row r="56" s="3" customFormat="1" spans="1:25">
-      <c r="A56" s="48">
-        <v>20080010</v>
+      <c r="A56" s="50">
+        <v>20090010</v>
       </c>
       <c r="B56" s="3">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D56" s="3">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="62" t="s">
+      <c r="F56" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>53</v>
+      <c r="G56" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="49">
+      <c r="I56" s="51">
         <v>1980000</v>
       </c>
-      <c r="J56" s="52" t="s">
-        <v>87</v>
+      <c r="J56" s="36" t="s">
+        <v>54</v>
       </c>
       <c r="K56" s="3">
         <v>0</v>
@@ -6181,11 +6154,11 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="53" t="s">
+      <c r="M56" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N56" s="3">
-        <v>9700</v>
+      <c r="N56" s="4">
+        <v>9500</v>
       </c>
       <c r="O56" s="3">
         <v>300</v>
@@ -6202,17 +6175,17 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="48">
+      <c r="T56" s="50">
         <v>20</v>
       </c>
-      <c r="U56" s="48">
-        <v>0</v>
-      </c>
-      <c r="V56" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W56" s="3" t="s">
-        <v>89</v>
+      <c r="U56" s="50">
+        <v>0</v>
+      </c>
+      <c r="V56" t="s">
+        <v>57</v>
+      </c>
+      <c r="W56" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="X56" s="3">
         <v>1</v>
@@ -6222,35 +6195,35 @@
       </c>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:25">
-      <c r="A57" s="48">
-        <v>20080011</v>
+      <c r="A57" s="50">
+        <v>20090011</v>
       </c>
       <c r="B57" s="3">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D57" s="3">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="62" t="s">
+      <c r="F57" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>53</v>
+      <c r="G57" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="49">
+      <c r="I57" s="51">
         <v>1980000</v>
       </c>
-      <c r="J57" s="52" t="s">
-        <v>90</v>
+      <c r="J57" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -6258,11 +6231,11 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="53" t="s">
+      <c r="M57" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N57" s="3">
-        <v>9700</v>
+      <c r="N57" s="4">
+        <v>9500</v>
       </c>
       <c r="O57" s="3">
         <v>300</v>
@@ -6279,17 +6252,17 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="48">
+      <c r="T57" s="50">
         <v>20</v>
       </c>
-      <c r="U57" s="48">
-        <v>0</v>
-      </c>
-      <c r="V57" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>91</v>
+      <c r="U57" s="50">
+        <v>0</v>
+      </c>
+      <c r="V57" t="s">
+        <v>61</v>
+      </c>
+      <c r="W57" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="X57" s="3">
         <v>1</v>
@@ -6299,35 +6272,35 @@
       </c>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:25">
-      <c r="A58" s="48">
-        <v>20080012</v>
+      <c r="A58" s="50">
+        <v>20090012</v>
       </c>
       <c r="B58" s="3">
-        <v>200800</v>
+        <v>200900</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D58" s="3">
-        <v>200800001</v>
+        <v>200900001</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="62" t="s">
+      <c r="F58" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>53</v>
+      <c r="G58" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="49">
+      <c r="I58" s="51">
         <v>1980000</v>
       </c>
-      <c r="J58" s="52" t="s">
-        <v>92</v>
+      <c r="J58" s="36" t="s">
+        <v>64</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -6335,11 +6308,11 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="53" t="s">
+      <c r="M58" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="N58" s="3">
-        <v>9700</v>
+      <c r="N58" s="4">
+        <v>9500</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
@@ -6356,258 +6329,27 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="48">
+      <c r="T58" s="50">
         <v>20</v>
       </c>
-      <c r="U58" s="48">
-        <v>0</v>
-      </c>
-      <c r="V58" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>93</v>
+      <c r="U58" s="50">
+        <v>0</v>
+      </c>
+      <c r="V58" t="s">
+        <v>65</v>
+      </c>
+      <c r="W58" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="X58" s="3">
         <v>1</v>
       </c>
       <c r="Y58" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" s="3" customFormat="1" spans="1:25">
-      <c r="A59" s="48">
-        <v>20090010</v>
-      </c>
-      <c r="B59" s="3">
-        <v>200900</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D59" s="3">
-        <v>200900001</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F59" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1</v>
-      </c>
-      <c r="I59" s="49">
-        <v>1980000</v>
-      </c>
-      <c r="J59" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M59" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="N59" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O59" s="3">
-        <v>300</v>
-      </c>
-      <c r="P59" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>16008</v>
-      </c>
-      <c r="T59" s="48">
-        <v>20</v>
-      </c>
-      <c r="U59" s="48">
-        <v>0</v>
-      </c>
-      <c r="V59" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y59" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" s="3" customFormat="1" spans="1:25">
-      <c r="A60" s="48">
-        <v>20090011</v>
-      </c>
-      <c r="B60" s="3">
-        <v>200900</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="3">
-        <v>200900001</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F60" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H60" s="3">
-        <v>2</v>
-      </c>
-      <c r="I60" s="49">
-        <v>1980000</v>
-      </c>
-      <c r="J60" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M60" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="N60" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O60" s="3">
-        <v>300</v>
-      </c>
-      <c r="P60" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R60" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S60" s="3">
-        <v>16008</v>
-      </c>
-      <c r="T60" s="48">
-        <v>20</v>
-      </c>
-      <c r="U60" s="48">
-        <v>0</v>
-      </c>
-      <c r="V60" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="X60" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y60" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" s="3" customFormat="1" spans="1:25">
-      <c r="A61" s="48">
-        <v>20090012</v>
-      </c>
-      <c r="B61" s="3">
-        <v>200900</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D61" s="3">
-        <v>200900001</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F61" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H61" s="3">
-        <v>3</v>
-      </c>
-      <c r="I61" s="49">
-        <v>1980000</v>
-      </c>
-      <c r="J61" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M61" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="N61" s="3">
-        <v>9700</v>
-      </c>
-      <c r="O61" s="3">
-        <v>300</v>
-      </c>
-      <c r="P61" s="3">
-        <v>180000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>15000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>16008</v>
-      </c>
-      <c r="T61" s="48">
-        <v>20</v>
-      </c>
-      <c r="U61" s="48">
-        <v>0</v>
-      </c>
-      <c r="V61" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="W61" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X61" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y61" s="57">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S61" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S58" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
+    <workbookView windowWidth="24045" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -491,7 +491,7 @@
     <t>2000,5000</t>
   </si>
   <si>
-    <t>0:6:28|6:12:36|12:18:45|18:24:43</t>
+    <t>0:6:48|6:12:42|12:18:52|18:24:62</t>
   </si>
   <si>
     <t>1000_2000_5000_10000_20000_50000_100000</t>
@@ -1334,7 +1334,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1470,9 +1470,6 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2153,7 +2150,7 @@
       <c r="E5" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G5" s="34" t="s">
@@ -2211,8 +2208,8 @@
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -2232,7 +2229,7 @@
       <c r="E6" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G6" s="34" t="s">
@@ -2290,8 +2287,8 @@
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" ref="Y6:Y10" si="1">Y5*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:25">
@@ -2311,7 +2308,7 @@
       <c r="E7" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G7" s="34" t="s">
@@ -2368,9 +2365,9 @@
       <c r="X7" s="2">
         <v>0</v>
       </c>
-      <c r="Y7" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y7" s="8">
+        <f t="shared" si="1"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:25">
@@ -2387,10 +2384,10 @@
       <c r="D8" s="32">
         <v>200101001</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="34" t="s">
@@ -2448,8 +2445,8 @@
         <v>0</v>
       </c>
       <c r="Y8" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -2469,7 +2466,7 @@
       <c r="E9" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G9" s="34" t="s">
@@ -2527,8 +2524,8 @@
         <v>0</v>
       </c>
       <c r="Y9" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" si="1"/>
+        <v>100000000</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -2548,7 +2545,7 @@
       <c r="E10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G10" s="34" t="s">
@@ -2605,9 +2602,9 @@
       <c r="X10" s="2">
         <v>0</v>
       </c>
-      <c r="Y10" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y10" s="8">
+        <f t="shared" si="1"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -2624,10 +2621,10 @@
       <c r="D11" s="32">
         <v>200300001</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G11" s="34" t="s">
@@ -2685,8 +2682,8 @@
         <v>0</v>
       </c>
       <c r="Y11" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:25">
@@ -2706,7 +2703,7 @@
       <c r="E12" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G12" s="34" t="s">
@@ -2764,8 +2761,8 @@
         <v>0</v>
       </c>
       <c r="Y12" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" ref="Y12:Y16" si="2">Y11*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2785,7 +2782,7 @@
       <c r="E13" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G13" s="34" t="s">
@@ -2842,9 +2839,9 @@
       <c r="X13" s="2">
         <v>0</v>
       </c>
-      <c r="Y13" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y13" s="8">
+        <f t="shared" si="2"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2861,10 +2858,10 @@
       <c r="D14" s="32">
         <v>200400009</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G14" s="34" t="s">
@@ -2922,8 +2919,8 @@
         <v>0</v>
       </c>
       <c r="Y14" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2943,7 +2940,7 @@
       <c r="E15" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="34" t="s">
@@ -3001,8 +2998,8 @@
         <v>0</v>
       </c>
       <c r="Y15" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" si="2"/>
+        <v>100000000</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:25">
@@ -3022,7 +3019,7 @@
       <c r="E16" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G16" s="34" t="s">
@@ -3079,9 +3076,9 @@
       <c r="X16" s="2">
         <v>0</v>
       </c>
-      <c r="Y16" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y16" s="8">
+        <f t="shared" si="2"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:25">
@@ -3101,7 +3098,7 @@
       <c r="E17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="59" t="s">
+      <c r="F17" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G17" s="34" t="s">
@@ -3159,8 +3156,8 @@
         <v>0</v>
       </c>
       <c r="Y17" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -3180,7 +3177,7 @@
       <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G18" s="34" t="s">
@@ -3238,8 +3235,8 @@
         <v>0</v>
       </c>
       <c r="Y18" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" ref="Y18:Y22" si="3">Y17*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -3259,7 +3256,7 @@
       <c r="E19" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="59" t="s">
+      <c r="F19" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G19" s="34" t="s">
@@ -3316,9 +3313,9 @@
       <c r="X19" s="2">
         <v>0</v>
       </c>
-      <c r="Y19" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y19" s="8">
+        <f t="shared" si="3"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -3335,10 +3332,10 @@
       <c r="D20" s="32">
         <v>200600001</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G20" s="34" t="s">
@@ -3396,8 +3393,8 @@
         <v>0</v>
       </c>
       <c r="Y20" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:25">
@@ -3417,7 +3414,7 @@
       <c r="E21" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="59" t="s">
+      <c r="F21" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G21" s="34" t="s">
@@ -3475,8 +3472,8 @@
         <v>0</v>
       </c>
       <c r="Y21" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" si="3"/>
+        <v>100000000</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -3496,7 +3493,7 @@
       <c r="E22" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G22" s="34" t="s">
@@ -3553,9 +3550,9 @@
       <c r="X22" s="2">
         <v>0</v>
       </c>
-      <c r="Y22" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y22" s="8">
+        <f t="shared" si="3"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -3575,7 +3572,7 @@
       <c r="E23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="34" t="s">
@@ -3633,8 +3630,8 @@
         <v>0</v>
       </c>
       <c r="Y23" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -3654,7 +3651,7 @@
       <c r="E24" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G24" s="34" t="s">
@@ -3712,8 +3709,8 @@
         <v>0</v>
       </c>
       <c r="Y24" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" ref="Y24:Y28" si="4">Y23*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" spans="1:25">
@@ -3733,7 +3730,7 @@
       <c r="E25" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="59" t="s">
+      <c r="F25" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G25" s="34" t="s">
@@ -3790,9 +3787,9 @@
       <c r="X25" s="2">
         <v>0</v>
       </c>
-      <c r="Y25" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y25" s="8">
+        <f t="shared" si="4"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="1:25">
@@ -3809,10 +3806,10 @@
       <c r="D26" s="32">
         <v>200800001</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="E26" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G26" s="34" t="s">
@@ -3870,8 +3867,8 @@
         <v>0</v>
       </c>
       <c r="Y26" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:25">
@@ -3891,7 +3888,7 @@
       <c r="E27" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="59" t="s">
+      <c r="F27" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G27" s="34" t="s">
@@ -3949,8 +3946,8 @@
         <v>0</v>
       </c>
       <c r="Y27" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" si="4"/>
+        <v>100000000</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" spans="1:25">
@@ -3970,7 +3967,7 @@
       <c r="E28" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G28" s="34" t="s">
@@ -4027,9 +4024,9 @@
       <c r="X28" s="2">
         <v>0</v>
       </c>
-      <c r="Y28" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y28" s="8">
+        <f t="shared" si="4"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:25">
@@ -4037,7 +4034,7 @@
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="45">
+      <c r="B29" s="44">
         <v>200900</v>
       </c>
       <c r="C29" s="32" t="s">
@@ -4046,10 +4043,10 @@
       <c r="D29" s="32">
         <v>200900001</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="E29" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="F29" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="34" t="s">
@@ -4064,7 +4061,7 @@
       <c r="J29" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="46">
+      <c r="K29" s="45">
         <v>0</v>
       </c>
       <c r="L29" s="4" t="s">
@@ -4107,8 +4104,8 @@
         <v>0</v>
       </c>
       <c r="Y29" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -4116,7 +4113,7 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="46">
         <v>200900</v>
       </c>
       <c r="C30" s="40" t="s">
@@ -4128,7 +4125,7 @@
       <c r="E30" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="34" t="s">
@@ -4143,7 +4140,7 @@
       <c r="J30" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="46">
+      <c r="K30" s="45">
         <v>0</v>
       </c>
       <c r="L30" s="4" t="s">
@@ -4186,8 +4183,8 @@
         <v>0</v>
       </c>
       <c r="Y30" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>Y29*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -4195,19 +4192,19 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="48">
+      <c r="B31" s="47">
         <v>200900</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="48">
         <v>200900001</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E31" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="59" t="s">
+      <c r="F31" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="34" t="s">
@@ -4222,7 +4219,7 @@
       <c r="J31" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="46">
+      <c r="K31" s="45">
         <v>0</v>
       </c>
       <c r="L31" s="4" t="s">
@@ -4264,37 +4261,37 @@
       <c r="X31" s="2">
         <v>0</v>
       </c>
-      <c r="Y31" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y31" s="8">
+        <f>Y30*10</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="32" s="3" customFormat="1" spans="1:25">
-      <c r="A32" s="50">
+      <c r="A32" s="49">
         <v>20010010</v>
       </c>
       <c r="B32" s="3">
         <v>200100</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="50">
         <v>200100038</v>
       </c>
-      <c r="E32" s="51" t="s">
+      <c r="E32" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="60" t="s">
+      <c r="F32" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="53" t="s">
+      <c r="G32" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="H32" s="51">
-        <v>1</v>
-      </c>
-      <c r="I32" s="51">
+      <c r="H32" s="50">
+        <v>1</v>
+      </c>
+      <c r="I32" s="50">
         <v>1980000</v>
       </c>
       <c r="J32" s="36" t="s">
@@ -4306,7 +4303,7 @@
       <c r="L32" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M32" s="54" t="s">
+      <c r="M32" s="53" t="s">
         <v>56</v>
       </c>
       <c r="N32" s="4">
@@ -4324,13 +4321,13 @@
       <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="55">
+      <c r="S32" s="54">
         <v>16008</v>
       </c>
-      <c r="T32" s="50">
+      <c r="T32" s="49">
         <v>48</v>
       </c>
-      <c r="U32" s="56">
+      <c r="U32" s="55">
         <v>0</v>
       </c>
       <c r="V32" t="s">
@@ -4342,36 +4339,36 @@
       <c r="X32" s="3">
         <v>1</v>
       </c>
-      <c r="Y32" s="57">
+      <c r="Y32" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:25">
-      <c r="A33" s="50">
+      <c r="A33" s="49">
         <v>20010011</v>
       </c>
       <c r="B33" s="3">
         <v>200100</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="50">
         <v>200100038</v>
       </c>
-      <c r="E33" s="51" t="s">
+      <c r="E33" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="60" t="s">
+      <c r="F33" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="53" t="s">
+      <c r="G33" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="H33" s="51">
+      <c r="H33" s="50">
         <v>2</v>
       </c>
-      <c r="I33" s="51">
+      <c r="I33" s="50">
         <v>1980000</v>
       </c>
       <c r="J33" s="41" t="s">
@@ -4383,7 +4380,7 @@
       <c r="L33" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M33" s="54" t="s">
+      <c r="M33" s="53" t="s">
         <v>56</v>
       </c>
       <c r="N33" s="4">
@@ -4401,13 +4398,13 @@
       <c r="R33" s="3">
         <v>15000</v>
       </c>
-      <c r="S33" s="55">
+      <c r="S33" s="54">
         <v>16008</v>
       </c>
-      <c r="T33" s="50">
+      <c r="T33" s="49">
         <v>48</v>
       </c>
-      <c r="U33" s="56">
+      <c r="U33" s="55">
         <v>0</v>
       </c>
       <c r="V33" t="s">
@@ -4419,36 +4416,36 @@
       <c r="X33" s="3">
         <v>1</v>
       </c>
-      <c r="Y33" s="57">
+      <c r="Y33" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" spans="1:25">
-      <c r="A34" s="50">
+      <c r="A34" s="49">
         <v>20010012</v>
       </c>
       <c r="B34" s="3">
         <v>200100</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="50">
         <v>200100038</v>
       </c>
-      <c r="E34" s="51" t="s">
+      <c r="E34" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="60" t="s">
+      <c r="F34" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="53" t="s">
+      <c r="G34" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="51">
+      <c r="H34" s="50">
         <v>3</v>
       </c>
-      <c r="I34" s="51">
+      <c r="I34" s="50">
         <v>1980000</v>
       </c>
       <c r="J34" s="36" t="s">
@@ -4460,7 +4457,7 @@
       <c r="L34" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M34" s="54" t="s">
+      <c r="M34" s="53" t="s">
         <v>56</v>
       </c>
       <c r="N34" s="4">
@@ -4478,13 +4475,13 @@
       <c r="R34" s="3">
         <v>15000</v>
       </c>
-      <c r="S34" s="55">
+      <c r="S34" s="54">
         <v>16008</v>
       </c>
-      <c r="T34" s="50">
+      <c r="T34" s="49">
         <v>48</v>
       </c>
-      <c r="U34" s="56">
+      <c r="U34" s="55">
         <v>0</v>
       </c>
       <c r="V34" t="s">
@@ -4496,12 +4493,12 @@
       <c r="X34" s="3">
         <v>1</v>
       </c>
-      <c r="Y34" s="57">
+      <c r="Y34" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" spans="1:25">
-      <c r="A35" s="50">
+      <c r="A35" s="49">
         <v>20010110</v>
       </c>
       <c r="B35" s="3">
@@ -4516,16 +4513,16 @@
       <c r="E35" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="61" t="s">
+      <c r="F35" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="53" t="s">
+      <c r="G35" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H35" s="3">
         <v>1</v>
       </c>
-      <c r="I35" s="51">
+      <c r="I35" s="50">
         <v>1980000</v>
       </c>
       <c r="J35" s="36" t="s">
@@ -4537,7 +4534,7 @@
       <c r="L35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M35" s="54" t="s">
+      <c r="M35" s="53" t="s">
         <v>69</v>
       </c>
       <c r="N35" s="4">
@@ -4558,10 +4555,10 @@
       <c r="S35" s="3">
         <v>16008</v>
       </c>
-      <c r="T35" s="50">
+      <c r="T35" s="49">
         <v>48</v>
       </c>
-      <c r="U35" s="56">
+      <c r="U35" s="55">
         <v>0</v>
       </c>
       <c r="V35" t="s">
@@ -4573,12 +4570,12 @@
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="57">
+      <c r="Y35" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:25">
-      <c r="A36" s="50">
+      <c r="A36" s="49">
         <v>20010111</v>
       </c>
       <c r="B36" s="3">
@@ -4593,16 +4590,16 @@
       <c r="E36" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="61" t="s">
+      <c r="F36" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="53" t="s">
+      <c r="G36" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H36" s="3">
         <v>2</v>
       </c>
-      <c r="I36" s="51">
+      <c r="I36" s="50">
         <v>1980000</v>
       </c>
       <c r="J36" s="41" t="s">
@@ -4614,7 +4611,7 @@
       <c r="L36" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M36" s="54" t="s">
+      <c r="M36" s="53" t="s">
         <v>69</v>
       </c>
       <c r="N36" s="4">
@@ -4635,10 +4632,10 @@
       <c r="S36" s="3">
         <v>16008</v>
       </c>
-      <c r="T36" s="50">
+      <c r="T36" s="49">
         <v>48</v>
       </c>
-      <c r="U36" s="56">
+      <c r="U36" s="55">
         <v>0</v>
       </c>
       <c r="V36" t="s">
@@ -4650,12 +4647,12 @@
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="57">
+      <c r="Y36" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:25">
-      <c r="A37" s="50">
+      <c r="A37" s="49">
         <v>20010112</v>
       </c>
       <c r="B37" s="3">
@@ -4670,16 +4667,16 @@
       <c r="E37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="61" t="s">
+      <c r="F37" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="53" t="s">
+      <c r="G37" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H37" s="3">
         <v>3</v>
       </c>
-      <c r="I37" s="51">
+      <c r="I37" s="50">
         <v>1980000</v>
       </c>
       <c r="J37" s="36" t="s">
@@ -4691,7 +4688,7 @@
       <c r="L37" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M37" s="54" t="s">
+      <c r="M37" s="53" t="s">
         <v>69</v>
       </c>
       <c r="N37" s="4">
@@ -4712,10 +4709,10 @@
       <c r="S37" s="3">
         <v>16008</v>
       </c>
-      <c r="T37" s="50">
+      <c r="T37" s="49">
         <v>48</v>
       </c>
-      <c r="U37" s="56">
+      <c r="U37" s="55">
         <v>0</v>
       </c>
       <c r="V37" t="s">
@@ -4727,12 +4724,12 @@
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="57">
+      <c r="Y37" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:25">
-      <c r="A38" s="50">
+      <c r="A38" s="49">
         <v>20030010</v>
       </c>
       <c r="B38" s="3">
@@ -4747,16 +4744,16 @@
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="61" t="s">
+      <c r="F38" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="53" t="s">
+      <c r="G38" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="51">
+      <c r="I38" s="50">
         <v>1980000</v>
       </c>
       <c r="J38" s="36" t="s">
@@ -4768,7 +4765,7 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="54" t="s">
+      <c r="M38" s="53" t="s">
         <v>71</v>
       </c>
       <c r="N38" s="4">
@@ -4789,10 +4786,10 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="50">
+      <c r="T38" s="49">
         <v>50</v>
       </c>
-      <c r="U38" s="56">
+      <c r="U38" s="55">
         <v>0</v>
       </c>
       <c r="V38" t="s">
@@ -4804,12 +4801,12 @@
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="57">
+      <c r="Y38" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:25">
-      <c r="A39" s="50">
+      <c r="A39" s="49">
         <v>20030011</v>
       </c>
       <c r="B39" s="3">
@@ -4824,16 +4821,16 @@
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="61" t="s">
+      <c r="F39" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="53" t="s">
+      <c r="G39" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="51">
+      <c r="I39" s="50">
         <v>1980000</v>
       </c>
       <c r="J39" s="41" t="s">
@@ -4845,7 +4842,7 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="54" t="s">
+      <c r="M39" s="53" t="s">
         <v>71</v>
       </c>
       <c r="N39" s="4">
@@ -4866,10 +4863,10 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="50">
+      <c r="T39" s="49">
         <v>50</v>
       </c>
-      <c r="U39" s="56">
+      <c r="U39" s="55">
         <v>0</v>
       </c>
       <c r="V39" t="s">
@@ -4881,12 +4878,12 @@
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="57">
+      <c r="Y39" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:25">
-      <c r="A40" s="50">
+      <c r="A40" s="49">
         <v>20030012</v>
       </c>
       <c r="B40" s="3">
@@ -4901,28 +4898,28 @@
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="61" t="s">
+      <c r="F40" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="53" t="s">
+      <c r="G40" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="51">
+      <c r="I40" s="50">
         <v>1980000</v>
       </c>
       <c r="J40" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K40" s="58">
-        <v>0</v>
-      </c>
-      <c r="L40" s="58" t="s">
+      <c r="K40" s="57">
+        <v>0</v>
+      </c>
+      <c r="L40" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="54" t="s">
+      <c r="M40" s="53" t="s">
         <v>71</v>
       </c>
       <c r="N40" s="4">
@@ -4931,22 +4928,22 @@
       <c r="O40" s="3">
         <v>300</v>
       </c>
-      <c r="P40" s="58">
+      <c r="P40" s="57">
         <v>180000</v>
       </c>
-      <c r="Q40" s="58">
+      <c r="Q40" s="57">
         <v>16000</v>
       </c>
-      <c r="R40" s="58">
+      <c r="R40" s="57">
         <v>15000</v>
       </c>
-      <c r="S40" s="58">
+      <c r="S40" s="57">
         <v>16008</v>
       </c>
-      <c r="T40" s="50">
+      <c r="T40" s="49">
         <v>50</v>
       </c>
-      <c r="U40" s="56">
+      <c r="U40" s="55">
         <v>0</v>
       </c>
       <c r="V40" t="s">
@@ -4958,12 +4955,12 @@
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="57">
+      <c r="Y40" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:25">
-      <c r="A41" s="50">
+      <c r="A41" s="49">
         <v>20040010</v>
       </c>
       <c r="B41" s="3">
@@ -4978,28 +4975,28 @@
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="61" t="s">
+      <c r="F41" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="53" t="s">
+      <c r="G41" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="51">
+      <c r="I41" s="50">
         <v>1980000</v>
       </c>
       <c r="J41" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K41" s="58">
-        <v>0</v>
-      </c>
-      <c r="L41" s="58" t="s">
+      <c r="K41" s="57">
+        <v>0</v>
+      </c>
+      <c r="L41" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="54" t="s">
+      <c r="M41" s="53" t="s">
         <v>73</v>
       </c>
       <c r="N41" s="4">
@@ -5008,22 +5005,22 @@
       <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="58">
+      <c r="P41" s="57">
         <v>180000</v>
       </c>
-      <c r="Q41" s="58">
+      <c r="Q41" s="57">
         <v>16000</v>
       </c>
-      <c r="R41" s="58">
+      <c r="R41" s="57">
         <v>15000</v>
       </c>
-      <c r="S41" s="58">
+      <c r="S41" s="57">
         <v>16008</v>
       </c>
-      <c r="T41" s="50">
+      <c r="T41" s="49">
         <v>50</v>
       </c>
-      <c r="U41" s="56">
+      <c r="U41" s="55">
         <v>0</v>
       </c>
       <c r="V41" t="s">
@@ -5035,12 +5032,12 @@
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="57">
+      <c r="Y41" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:25">
-      <c r="A42" s="50">
+      <c r="A42" s="49">
         <v>20040011</v>
       </c>
       <c r="B42" s="3">
@@ -5055,28 +5052,28 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="61" t="s">
+      <c r="F42" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="53" t="s">
+      <c r="G42" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="51">
+      <c r="I42" s="50">
         <v>1980000</v>
       </c>
       <c r="J42" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K42" s="58">
-        <v>0</v>
-      </c>
-      <c r="L42" s="58" t="s">
+      <c r="K42" s="57">
+        <v>0</v>
+      </c>
+      <c r="L42" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="54" t="s">
+      <c r="M42" s="53" t="s">
         <v>73</v>
       </c>
       <c r="N42" s="4">
@@ -5085,22 +5082,22 @@
       <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="58">
+      <c r="P42" s="57">
         <v>180000</v>
       </c>
-      <c r="Q42" s="58">
+      <c r="Q42" s="57">
         <v>16000</v>
       </c>
-      <c r="R42" s="58">
+      <c r="R42" s="57">
         <v>15000</v>
       </c>
-      <c r="S42" s="58">
+      <c r="S42" s="57">
         <v>16008</v>
       </c>
-      <c r="T42" s="50">
+      <c r="T42" s="49">
         <v>50</v>
       </c>
-      <c r="U42" s="56">
+      <c r="U42" s="55">
         <v>0</v>
       </c>
       <c r="V42" t="s">
@@ -5112,12 +5109,12 @@
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="57">
+      <c r="Y42" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:25">
-      <c r="A43" s="50">
+      <c r="A43" s="49">
         <v>20040012</v>
       </c>
       <c r="B43" s="3">
@@ -5132,28 +5129,28 @@
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="61" t="s">
+      <c r="F43" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="53" t="s">
+      <c r="G43" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="51">
+      <c r="I43" s="50">
         <v>1980000</v>
       </c>
       <c r="J43" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K43" s="58">
-        <v>0</v>
-      </c>
-      <c r="L43" s="58" t="s">
+      <c r="K43" s="57">
+        <v>0</v>
+      </c>
+      <c r="L43" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="54" t="s">
+      <c r="M43" s="53" t="s">
         <v>73</v>
       </c>
       <c r="N43" s="4">
@@ -5162,22 +5159,22 @@
       <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="58">
+      <c r="P43" s="57">
         <v>180000</v>
       </c>
-      <c r="Q43" s="58">
+      <c r="Q43" s="57">
         <v>16000</v>
       </c>
-      <c r="R43" s="58">
+      <c r="R43" s="57">
         <v>15000</v>
       </c>
-      <c r="S43" s="58">
+      <c r="S43" s="57">
         <v>16008</v>
       </c>
-      <c r="T43" s="50">
+      <c r="T43" s="49">
         <v>50</v>
       </c>
-      <c r="U43" s="56">
+      <c r="U43" s="55">
         <v>0</v>
       </c>
       <c r="V43" t="s">
@@ -5189,12 +5186,12 @@
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="57">
+      <c r="Y43" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:25">
-      <c r="A44" s="50">
+      <c r="A44" s="49">
         <v>20050010</v>
       </c>
       <c r="B44" s="3">
@@ -5209,28 +5206,28 @@
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="53" t="s">
+      <c r="G44" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="51">
+      <c r="I44" s="50">
         <v>1980000</v>
       </c>
       <c r="J44" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K44" s="58">
-        <v>1</v>
-      </c>
-      <c r="L44" s="58" t="s">
+      <c r="K44" s="57">
+        <v>1</v>
+      </c>
+      <c r="L44" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="M44" s="54" t="s">
+      <c r="M44" s="53" t="s">
         <v>75</v>
       </c>
       <c r="N44" s="4">
@@ -5239,22 +5236,22 @@
       <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="58">
+      <c r="P44" s="57">
         <v>180000</v>
       </c>
-      <c r="Q44" s="58">
+      <c r="Q44" s="57">
         <v>16000</v>
       </c>
-      <c r="R44" s="58">
+      <c r="R44" s="57">
         <v>15000</v>
       </c>
-      <c r="S44" s="58">
+      <c r="S44" s="57">
         <v>16008</v>
       </c>
-      <c r="T44" s="50">
+      <c r="T44" s="49">
         <v>48</v>
       </c>
-      <c r="U44" s="50">
+      <c r="U44" s="49">
         <v>0</v>
       </c>
       <c r="V44" t="s">
@@ -5266,12 +5263,12 @@
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="57">
+      <c r="Y44" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:25">
-      <c r="A45" s="50">
+      <c r="A45" s="49">
         <v>20050011</v>
       </c>
       <c r="B45" s="3">
@@ -5286,28 +5283,28 @@
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="61" t="s">
+      <c r="F45" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="53" t="s">
+      <c r="G45" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="51">
+      <c r="I45" s="50">
         <v>1980000</v>
       </c>
       <c r="J45" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K45" s="58">
-        <v>1</v>
-      </c>
-      <c r="L45" s="58" t="s">
+      <c r="K45" s="57">
+        <v>1</v>
+      </c>
+      <c r="L45" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="M45" s="54" t="s">
+      <c r="M45" s="53" t="s">
         <v>75</v>
       </c>
       <c r="N45" s="4">
@@ -5316,22 +5313,22 @@
       <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="58">
+      <c r="P45" s="57">
         <v>180000</v>
       </c>
-      <c r="Q45" s="58">
+      <c r="Q45" s="57">
         <v>16000</v>
       </c>
-      <c r="R45" s="58">
+      <c r="R45" s="57">
         <v>15000</v>
       </c>
-      <c r="S45" s="58">
+      <c r="S45" s="57">
         <v>16008</v>
       </c>
-      <c r="T45" s="50">
+      <c r="T45" s="49">
         <v>48</v>
       </c>
-      <c r="U45" s="50">
+      <c r="U45" s="49">
         <v>0</v>
       </c>
       <c r="V45" t="s">
@@ -5343,12 +5340,12 @@
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="57">
+      <c r="Y45" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:25">
-      <c r="A46" s="50">
+      <c r="A46" s="49">
         <v>20050012</v>
       </c>
       <c r="B46" s="3">
@@ -5363,28 +5360,28 @@
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="61" t="s">
+      <c r="F46" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="53" t="s">
+      <c r="G46" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="51">
+      <c r="I46" s="50">
         <v>1980000</v>
       </c>
       <c r="J46" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K46" s="58">
-        <v>1</v>
-      </c>
-      <c r="L46" s="58" t="s">
+      <c r="K46" s="57">
+        <v>1</v>
+      </c>
+      <c r="L46" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="M46" s="54" t="s">
+      <c r="M46" s="53" t="s">
         <v>75</v>
       </c>
       <c r="N46" s="4">
@@ -5393,22 +5390,22 @@
       <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="58">
+      <c r="P46" s="57">
         <v>180000</v>
       </c>
-      <c r="Q46" s="58">
+      <c r="Q46" s="57">
         <v>16000</v>
       </c>
-      <c r="R46" s="58">
+      <c r="R46" s="57">
         <v>15000</v>
       </c>
-      <c r="S46" s="58">
+      <c r="S46" s="57">
         <v>16008</v>
       </c>
-      <c r="T46" s="50">
+      <c r="T46" s="49">
         <v>48</v>
       </c>
-      <c r="U46" s="50">
+      <c r="U46" s="49">
         <v>0</v>
       </c>
       <c r="V46" t="s">
@@ -5420,12 +5417,12 @@
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="57">
+      <c r="Y46" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:25">
-      <c r="A47" s="50">
+      <c r="A47" s="49">
         <v>20060010</v>
       </c>
       <c r="B47" s="3">
@@ -5440,28 +5437,28 @@
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="61" t="s">
+      <c r="F47" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="53" t="s">
+      <c r="G47" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="51">
+      <c r="I47" s="50">
         <v>1980000</v>
       </c>
       <c r="J47" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K47" s="58">
-        <v>0</v>
-      </c>
-      <c r="L47" s="58" t="s">
+      <c r="K47" s="57">
+        <v>0</v>
+      </c>
+      <c r="L47" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M47" s="54" t="s">
+      <c r="M47" s="53" t="s">
         <v>77</v>
       </c>
       <c r="N47" s="4">
@@ -5470,22 +5467,22 @@
       <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="58">
+      <c r="P47" s="57">
         <v>180000</v>
       </c>
-      <c r="Q47" s="58">
+      <c r="Q47" s="57">
         <v>16000</v>
       </c>
-      <c r="R47" s="58">
+      <c r="R47" s="57">
         <v>15000</v>
       </c>
-      <c r="S47" s="58">
+      <c r="S47" s="57">
         <v>16008</v>
       </c>
-      <c r="T47" s="50">
+      <c r="T47" s="49">
         <v>20</v>
       </c>
-      <c r="U47" s="50">
+      <c r="U47" s="49">
         <v>0</v>
       </c>
       <c r="V47" t="s">
@@ -5497,12 +5494,12 @@
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="57">
+      <c r="Y47" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:25">
-      <c r="A48" s="50">
+      <c r="A48" s="49">
         <v>20060011</v>
       </c>
       <c r="B48" s="3">
@@ -5517,28 +5514,28 @@
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="61" t="s">
+      <c r="F48" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="53" t="s">
+      <c r="G48" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="51">
+      <c r="I48" s="50">
         <v>1980000</v>
       </c>
       <c r="J48" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K48" s="58">
-        <v>0</v>
-      </c>
-      <c r="L48" s="58" t="s">
+      <c r="K48" s="57">
+        <v>0</v>
+      </c>
+      <c r="L48" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M48" s="54" t="s">
+      <c r="M48" s="53" t="s">
         <v>77</v>
       </c>
       <c r="N48" s="4">
@@ -5547,22 +5544,22 @@
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="58">
+      <c r="P48" s="57">
         <v>180000</v>
       </c>
-      <c r="Q48" s="58">
+      <c r="Q48" s="57">
         <v>16000</v>
       </c>
-      <c r="R48" s="58">
+      <c r="R48" s="57">
         <v>15000</v>
       </c>
-      <c r="S48" s="58">
+      <c r="S48" s="57">
         <v>16008</v>
       </c>
-      <c r="T48" s="50">
+      <c r="T48" s="49">
         <v>20</v>
       </c>
-      <c r="U48" s="50">
+      <c r="U48" s="49">
         <v>0</v>
       </c>
       <c r="V48" t="s">
@@ -5574,12 +5571,12 @@
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="57">
+      <c r="Y48" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:25">
-      <c r="A49" s="50">
+      <c r="A49" s="49">
         <v>20060012</v>
       </c>
       <c r="B49" s="3">
@@ -5594,16 +5591,16 @@
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="61" t="s">
+      <c r="F49" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="53" t="s">
+      <c r="G49" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="51">
+      <c r="I49" s="50">
         <v>1980000</v>
       </c>
       <c r="J49" s="36" t="s">
@@ -5615,7 +5612,7 @@
       <c r="L49" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M49" s="54" t="s">
+      <c r="M49" s="53" t="s">
         <v>77</v>
       </c>
       <c r="N49" s="4">
@@ -5636,10 +5633,10 @@
       <c r="S49" s="3">
         <v>16008</v>
       </c>
-      <c r="T49" s="50">
+      <c r="T49" s="49">
         <v>20</v>
       </c>
-      <c r="U49" s="50">
+      <c r="U49" s="49">
         <v>0</v>
       </c>
       <c r="V49" t="s">
@@ -5651,12 +5648,12 @@
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="57">
+      <c r="Y49" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:25">
-      <c r="A50" s="50">
+      <c r="A50" s="49">
         <v>20070010</v>
       </c>
       <c r="B50" s="3">
@@ -5671,16 +5668,16 @@
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="61" t="s">
+      <c r="F50" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="53" t="s">
+      <c r="G50" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="51">
+      <c r="I50" s="50">
         <v>1980000</v>
       </c>
       <c r="J50" s="36" t="s">
@@ -5692,7 +5689,7 @@
       <c r="L50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="54" t="s">
+      <c r="M50" s="53" t="s">
         <v>79</v>
       </c>
       <c r="N50" s="4">
@@ -5713,10 +5710,10 @@
       <c r="S50" s="3">
         <v>16008</v>
       </c>
-      <c r="T50" s="50">
+      <c r="T50" s="49">
         <v>30</v>
       </c>
-      <c r="U50" s="50">
+      <c r="U50" s="49">
         <v>1</v>
       </c>
       <c r="V50" t="s">
@@ -5728,12 +5725,12 @@
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="57">
+      <c r="Y50" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:25">
-      <c r="A51" s="50">
+      <c r="A51" s="49">
         <v>20070011</v>
       </c>
       <c r="B51" s="3">
@@ -5748,16 +5745,16 @@
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="61" t="s">
+      <c r="F51" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="53" t="s">
+      <c r="G51" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="51">
+      <c r="I51" s="50">
         <v>1980000</v>
       </c>
       <c r="J51" s="41" t="s">
@@ -5769,7 +5766,7 @@
       <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="54" t="s">
+      <c r="M51" s="53" t="s">
         <v>79</v>
       </c>
       <c r="N51" s="4">
@@ -5790,10 +5787,10 @@
       <c r="S51" s="3">
         <v>16008</v>
       </c>
-      <c r="T51" s="50">
+      <c r="T51" s="49">
         <v>30</v>
       </c>
-      <c r="U51" s="50">
+      <c r="U51" s="49">
         <v>1</v>
       </c>
       <c r="V51" t="s">
@@ -5805,12 +5802,12 @@
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="57">
+      <c r="Y51" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:25">
-      <c r="A52" s="50">
+      <c r="A52" s="49">
         <v>20070012</v>
       </c>
       <c r="B52" s="3">
@@ -5825,16 +5822,16 @@
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="61" t="s">
+      <c r="F52" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="53" t="s">
+      <c r="G52" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="51">
+      <c r="I52" s="50">
         <v>1980000</v>
       </c>
       <c r="J52" s="36" t="s">
@@ -5846,7 +5843,7 @@
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="54" t="s">
+      <c r="M52" s="53" t="s">
         <v>79</v>
       </c>
       <c r="N52" s="4">
@@ -5867,10 +5864,10 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="50">
+      <c r="T52" s="49">
         <v>30</v>
       </c>
-      <c r="U52" s="50">
+      <c r="U52" s="49">
         <v>1</v>
       </c>
       <c r="V52" t="s">
@@ -5882,12 +5879,12 @@
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="57">
+      <c r="Y52" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:25">
-      <c r="A53" s="50">
+      <c r="A53" s="49">
         <v>20080010</v>
       </c>
       <c r="B53" s="3">
@@ -5902,16 +5899,16 @@
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="61" t="s">
+      <c r="F53" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="53" t="s">
+      <c r="G53" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="51">
+      <c r="I53" s="50">
         <v>1980000</v>
       </c>
       <c r="J53" s="36" t="s">
@@ -5923,7 +5920,7 @@
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="54" t="s">
+      <c r="M53" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N53" s="4">
@@ -5944,10 +5941,10 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="50">
+      <c r="T53" s="49">
         <v>20</v>
       </c>
-      <c r="U53" s="50">
+      <c r="U53" s="49">
         <v>0</v>
       </c>
       <c r="V53" t="s">
@@ -5959,12 +5956,12 @@
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="57">
+      <c r="Y53" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:25">
-      <c r="A54" s="50">
+      <c r="A54" s="49">
         <v>20080011</v>
       </c>
       <c r="B54" s="3">
@@ -5979,16 +5976,16 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="61" t="s">
+      <c r="F54" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="53" t="s">
+      <c r="G54" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="51">
+      <c r="I54" s="50">
         <v>1980000</v>
       </c>
       <c r="J54" s="41" t="s">
@@ -6000,7 +5997,7 @@
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="54" t="s">
+      <c r="M54" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N54" s="4">
@@ -6021,10 +6018,10 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="50">
+      <c r="T54" s="49">
         <v>20</v>
       </c>
-      <c r="U54" s="50">
+      <c r="U54" s="49">
         <v>0</v>
       </c>
       <c r="V54" t="s">
@@ -6036,12 +6033,12 @@
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="57">
+      <c r="Y54" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" spans="1:25">
-      <c r="A55" s="50">
+      <c r="A55" s="49">
         <v>20080012</v>
       </c>
       <c r="B55" s="3">
@@ -6056,16 +6053,16 @@
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="61" t="s">
+      <c r="F55" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="53" t="s">
+      <c r="G55" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="51">
+      <c r="I55" s="50">
         <v>1980000</v>
       </c>
       <c r="J55" s="36" t="s">
@@ -6077,7 +6074,7 @@
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="54" t="s">
+      <c r="M55" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N55" s="4">
@@ -6098,10 +6095,10 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="50">
+      <c r="T55" s="49">
         <v>20</v>
       </c>
-      <c r="U55" s="50">
+      <c r="U55" s="49">
         <v>0</v>
       </c>
       <c r="V55" t="s">
@@ -6113,12 +6110,12 @@
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="57">
+      <c r="Y55" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" spans="1:25">
-      <c r="A56" s="50">
+      <c r="A56" s="49">
         <v>20090010</v>
       </c>
       <c r="B56" s="3">
@@ -6133,16 +6130,16 @@
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="61" t="s">
+      <c r="F56" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="53" t="s">
+      <c r="G56" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="51">
+      <c r="I56" s="50">
         <v>1980000</v>
       </c>
       <c r="J56" s="36" t="s">
@@ -6154,7 +6151,7 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="54" t="s">
+      <c r="M56" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N56" s="4">
@@ -6175,10 +6172,10 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="50">
+      <c r="T56" s="49">
         <v>20</v>
       </c>
-      <c r="U56" s="50">
+      <c r="U56" s="49">
         <v>0</v>
       </c>
       <c r="V56" t="s">
@@ -6190,12 +6187,12 @@
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="57">
+      <c r="Y56" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:25">
-      <c r="A57" s="50">
+      <c r="A57" s="49">
         <v>20090011</v>
       </c>
       <c r="B57" s="3">
@@ -6210,16 +6207,16 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="61" t="s">
+      <c r="F57" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="53" t="s">
+      <c r="G57" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="51">
+      <c r="I57" s="50">
         <v>1980000</v>
       </c>
       <c r="J57" s="41" t="s">
@@ -6231,7 +6228,7 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="54" t="s">
+      <c r="M57" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N57" s="4">
@@ -6252,10 +6249,10 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="50">
+      <c r="T57" s="49">
         <v>20</v>
       </c>
-      <c r="U57" s="50">
+      <c r="U57" s="49">
         <v>0</v>
       </c>
       <c r="V57" t="s">
@@ -6267,12 +6264,12 @@
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="57">
+      <c r="Y57" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:25">
-      <c r="A58" s="50">
+      <c r="A58" s="49">
         <v>20090012</v>
       </c>
       <c r="B58" s="3">
@@ -6287,16 +6284,16 @@
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="53" t="s">
+      <c r="G58" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="51">
+      <c r="I58" s="50">
         <v>1980000</v>
       </c>
       <c r="J58" s="36" t="s">
@@ -6308,7 +6305,7 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="54" t="s">
+      <c r="M58" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N58" s="4">
@@ -6329,10 +6326,10 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="50">
+      <c r="T58" s="49">
         <v>20</v>
       </c>
-      <c r="U58" s="50">
+      <c r="U58" s="49">
         <v>0</v>
       </c>
       <c r="V58" t="s">
@@ -6344,7 +6341,7 @@
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="57">
+      <c r="Y58" s="56">
         <v>0</v>
       </c>
     </row>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27735" windowHeight="12270" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -1334,7 +1334,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1470,6 +1470,9 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2150,7 +2153,7 @@
       <c r="E5" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G5" s="34" t="s">
@@ -2208,8 +2211,8 @@
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>100*100000</f>
-        <v>10000000</v>
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -2229,7 +2232,7 @@
       <c r="E6" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="F6" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G6" s="34" t="s">
@@ -2287,8 +2290,8 @@
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f t="shared" ref="Y6:Y10" si="1">Y5*10</f>
-        <v>100000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:25">
@@ -2308,7 +2311,7 @@
       <c r="E7" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G7" s="34" t="s">
@@ -2365,9 +2368,9 @@
       <c r="X7" s="2">
         <v>0</v>
       </c>
-      <c r="Y7" s="8">
-        <f t="shared" si="1"/>
-        <v>1000000000</v>
+      <c r="Y7" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:25">
@@ -2384,10 +2387,10 @@
       <c r="D8" s="32">
         <v>200101001</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="34" t="s">
@@ -2445,8 +2448,8 @@
         <v>0</v>
       </c>
       <c r="Y8" s="8">
-        <f>100*100000</f>
-        <v>10000000</v>
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -2466,7 +2469,7 @@
       <c r="E9" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G9" s="34" t="s">
@@ -2524,8 +2527,8 @@
         <v>0</v>
       </c>
       <c r="Y9" s="8">
-        <f t="shared" si="1"/>
-        <v>100000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -2545,7 +2548,7 @@
       <c r="E10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G10" s="34" t="s">
@@ -2602,9 +2605,9 @@
       <c r="X10" s="2">
         <v>0</v>
       </c>
-      <c r="Y10" s="8">
-        <f t="shared" si="1"/>
-        <v>1000000000</v>
+      <c r="Y10" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -2621,10 +2624,10 @@
       <c r="D11" s="32">
         <v>200300001</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="58" t="s">
+      <c r="F11" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G11" s="34" t="s">
@@ -2682,8 +2685,8 @@
         <v>0</v>
       </c>
       <c r="Y11" s="8">
-        <f>100*100000</f>
-        <v>10000000</v>
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:25">
@@ -2703,7 +2706,7 @@
       <c r="E12" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G12" s="34" t="s">
@@ -2761,8 +2764,8 @@
         <v>0</v>
       </c>
       <c r="Y12" s="8">
-        <f t="shared" ref="Y12:Y16" si="2">Y11*10</f>
-        <v>100000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2782,7 +2785,7 @@
       <c r="E13" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="58" t="s">
+      <c r="F13" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G13" s="34" t="s">
@@ -2839,9 +2842,9 @@
       <c r="X13" s="2">
         <v>0</v>
       </c>
-      <c r="Y13" s="8">
-        <f t="shared" si="2"/>
-        <v>1000000000</v>
+      <c r="Y13" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2858,10 +2861,10 @@
       <c r="D14" s="32">
         <v>200400009</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G14" s="34" t="s">
@@ -2919,8 +2922,8 @@
         <v>0</v>
       </c>
       <c r="Y14" s="8">
-        <f>100*100000</f>
-        <v>10000000</v>
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2940,7 +2943,7 @@
       <c r="E15" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="34" t="s">
@@ -2998,8 +3001,8 @@
         <v>0</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" si="2"/>
-        <v>100000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:25">
@@ -3019,7 +3022,7 @@
       <c r="E16" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G16" s="34" t="s">
@@ -3076,9 +3079,9 @@
       <c r="X16" s="2">
         <v>0</v>
       </c>
-      <c r="Y16" s="8">
-        <f t="shared" si="2"/>
-        <v>1000000000</v>
+      <c r="Y16" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:25">
@@ -3098,7 +3101,7 @@
       <c r="E17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="58" t="s">
+      <c r="F17" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G17" s="34" t="s">
@@ -3156,8 +3159,8 @@
         <v>0</v>
       </c>
       <c r="Y17" s="8">
-        <f>100*100000</f>
-        <v>10000000</v>
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -3177,7 +3180,7 @@
       <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G18" s="34" t="s">
@@ -3235,8 +3238,8 @@
         <v>0</v>
       </c>
       <c r="Y18" s="8">
-        <f t="shared" ref="Y18:Y22" si="3">Y17*10</f>
-        <v>100000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -3256,7 +3259,7 @@
       <c r="E19" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="F19" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G19" s="34" t="s">
@@ -3313,9 +3316,9 @@
       <c r="X19" s="2">
         <v>0</v>
       </c>
-      <c r="Y19" s="8">
-        <f t="shared" si="3"/>
-        <v>1000000000</v>
+      <c r="Y19" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -3332,10 +3335,10 @@
       <c r="D20" s="32">
         <v>200600001</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="58" t="s">
+      <c r="F20" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G20" s="34" t="s">
@@ -3393,8 +3396,8 @@
         <v>0</v>
       </c>
       <c r="Y20" s="8">
-        <f>100*100000</f>
-        <v>10000000</v>
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:25">
@@ -3414,7 +3417,7 @@
       <c r="E21" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="58" t="s">
+      <c r="F21" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G21" s="34" t="s">
@@ -3472,8 +3475,8 @@
         <v>0</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" si="3"/>
-        <v>100000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -3493,7 +3496,7 @@
       <c r="E22" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="58" t="s">
+      <c r="F22" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G22" s="34" t="s">
@@ -3550,9 +3553,9 @@
       <c r="X22" s="2">
         <v>0</v>
       </c>
-      <c r="Y22" s="8">
-        <f t="shared" si="3"/>
-        <v>1000000000</v>
+      <c r="Y22" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -3572,7 +3575,7 @@
       <c r="E23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="58" t="s">
+      <c r="F23" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="34" t="s">
@@ -3630,8 +3633,8 @@
         <v>0</v>
       </c>
       <c r="Y23" s="8">
-        <f>100*100000</f>
-        <v>10000000</v>
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -3651,7 +3654,7 @@
       <c r="E24" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="58" t="s">
+      <c r="F24" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G24" s="34" t="s">
@@ -3709,8 +3712,8 @@
         <v>0</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" ref="Y24:Y28" si="4">Y23*10</f>
-        <v>100000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" spans="1:25">
@@ -3730,7 +3733,7 @@
       <c r="E25" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="58" t="s">
+      <c r="F25" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G25" s="34" t="s">
@@ -3787,9 +3790,9 @@
       <c r="X25" s="2">
         <v>0</v>
       </c>
-      <c r="Y25" s="8">
-        <f t="shared" si="4"/>
-        <v>1000000000</v>
+      <c r="Y25" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="1:25">
@@ -3806,10 +3809,10 @@
       <c r="D26" s="32">
         <v>200800001</v>
       </c>
-      <c r="E26" s="43" t="s">
+      <c r="E26" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="58" t="s">
+      <c r="F26" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G26" s="34" t="s">
@@ -3867,8 +3870,8 @@
         <v>0</v>
       </c>
       <c r="Y26" s="8">
-        <f>100*100000</f>
-        <v>10000000</v>
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:25">
@@ -3888,7 +3891,7 @@
       <c r="E27" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="58" t="s">
+      <c r="F27" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G27" s="34" t="s">
@@ -3946,8 +3949,8 @@
         <v>0</v>
       </c>
       <c r="Y27" s="8">
-        <f t="shared" si="4"/>
-        <v>100000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" spans="1:25">
@@ -3967,7 +3970,7 @@
       <c r="E28" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="58" t="s">
+      <c r="F28" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G28" s="34" t="s">
@@ -4024,9 +4027,9 @@
       <c r="X28" s="2">
         <v>0</v>
       </c>
-      <c r="Y28" s="8">
-        <f t="shared" si="4"/>
-        <v>1000000000</v>
+      <c r="Y28" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:25">
@@ -4034,7 +4037,7 @@
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="44">
+      <c r="B29" s="45">
         <v>200900</v>
       </c>
       <c r="C29" s="32" t="s">
@@ -4043,10 +4046,10 @@
       <c r="D29" s="32">
         <v>200900001</v>
       </c>
-      <c r="E29" s="42" t="s">
+      <c r="E29" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="58" t="s">
+      <c r="F29" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="34" t="s">
@@ -4061,7 +4064,7 @@
       <c r="J29" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="45">
+      <c r="K29" s="46">
         <v>0</v>
       </c>
       <c r="L29" s="4" t="s">
@@ -4104,8 +4107,8 @@
         <v>0</v>
       </c>
       <c r="Y29" s="8">
-        <f>100*100000</f>
-        <v>10000000</v>
+        <f>1000*100000</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -4113,7 +4116,7 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="46">
+      <c r="B30" s="47">
         <v>200900</v>
       </c>
       <c r="C30" s="40" t="s">
@@ -4125,7 +4128,7 @@
       <c r="E30" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="58" t="s">
+      <c r="F30" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="34" t="s">
@@ -4140,7 +4143,7 @@
       <c r="J30" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="45">
+      <c r="K30" s="46">
         <v>0</v>
       </c>
       <c r="L30" s="4" t="s">
@@ -4183,8 +4186,8 @@
         <v>0</v>
       </c>
       <c r="Y30" s="8">
-        <f>Y29*10</f>
-        <v>100000000</v>
+        <f>1000000*1000</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -4192,19 +4195,19 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="47">
+      <c r="B31" s="48">
         <v>200900</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="48">
+      <c r="D31" s="49">
         <v>200900001</v>
       </c>
-      <c r="E31" s="48" t="s">
+      <c r="E31" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="58" t="s">
+      <c r="F31" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="34" t="s">
@@ -4219,7 +4222,7 @@
       <c r="J31" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="45">
+      <c r="K31" s="46">
         <v>0</v>
       </c>
       <c r="L31" s="4" t="s">
@@ -4261,37 +4264,37 @@
       <c r="X31" s="2">
         <v>0</v>
       </c>
-      <c r="Y31" s="8">
-        <f>Y30*10</f>
-        <v>1000000000</v>
+      <c r="Y31" s="42">
+        <f>10000000*1000</f>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="32" s="3" customFormat="1" spans="1:25">
-      <c r="A32" s="49">
+      <c r="A32" s="50">
         <v>20010010</v>
       </c>
       <c r="B32" s="3">
         <v>200100</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="50">
+      <c r="D32" s="51">
         <v>200100038</v>
       </c>
-      <c r="E32" s="50" t="s">
+      <c r="E32" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="52" t="s">
+      <c r="G32" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="H32" s="50">
-        <v>1</v>
-      </c>
-      <c r="I32" s="50">
+      <c r="H32" s="51">
+        <v>1</v>
+      </c>
+      <c r="I32" s="51">
         <v>1980000</v>
       </c>
       <c r="J32" s="36" t="s">
@@ -4303,7 +4306,7 @@
       <c r="L32" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M32" s="53" t="s">
+      <c r="M32" s="54" t="s">
         <v>56</v>
       </c>
       <c r="N32" s="4">
@@ -4321,13 +4324,13 @@
       <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="54">
+      <c r="S32" s="55">
         <v>16008</v>
       </c>
-      <c r="T32" s="49">
+      <c r="T32" s="50">
         <v>48</v>
       </c>
-      <c r="U32" s="55">
+      <c r="U32" s="56">
         <v>0</v>
       </c>
       <c r="V32" t="s">
@@ -4339,36 +4342,36 @@
       <c r="X32" s="3">
         <v>1</v>
       </c>
-      <c r="Y32" s="56">
+      <c r="Y32" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:25">
-      <c r="A33" s="49">
+      <c r="A33" s="50">
         <v>20010011</v>
       </c>
       <c r="B33" s="3">
         <v>200100</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="50">
+      <c r="D33" s="51">
         <v>200100038</v>
       </c>
-      <c r="E33" s="50" t="s">
+      <c r="E33" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="59" t="s">
+      <c r="F33" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="52" t="s">
+      <c r="G33" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="H33" s="50">
+      <c r="H33" s="51">
         <v>2</v>
       </c>
-      <c r="I33" s="50">
+      <c r="I33" s="51">
         <v>1980000</v>
       </c>
       <c r="J33" s="41" t="s">
@@ -4380,7 +4383,7 @@
       <c r="L33" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M33" s="53" t="s">
+      <c r="M33" s="54" t="s">
         <v>56</v>
       </c>
       <c r="N33" s="4">
@@ -4398,13 +4401,13 @@
       <c r="R33" s="3">
         <v>15000</v>
       </c>
-      <c r="S33" s="54">
+      <c r="S33" s="55">
         <v>16008</v>
       </c>
-      <c r="T33" s="49">
+      <c r="T33" s="50">
         <v>48</v>
       </c>
-      <c r="U33" s="55">
+      <c r="U33" s="56">
         <v>0</v>
       </c>
       <c r="V33" t="s">
@@ -4416,36 +4419,36 @@
       <c r="X33" s="3">
         <v>1</v>
       </c>
-      <c r="Y33" s="56">
+      <c r="Y33" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" spans="1:25">
-      <c r="A34" s="49">
+      <c r="A34" s="50">
         <v>20010012</v>
       </c>
       <c r="B34" s="3">
         <v>200100</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="50">
+      <c r="D34" s="51">
         <v>200100038</v>
       </c>
-      <c r="E34" s="50" t="s">
+      <c r="E34" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="59" t="s">
+      <c r="F34" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="52" t="s">
+      <c r="G34" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="50">
+      <c r="H34" s="51">
         <v>3</v>
       </c>
-      <c r="I34" s="50">
+      <c r="I34" s="51">
         <v>1980000</v>
       </c>
       <c r="J34" s="36" t="s">
@@ -4457,7 +4460,7 @@
       <c r="L34" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M34" s="53" t="s">
+      <c r="M34" s="54" t="s">
         <v>56</v>
       </c>
       <c r="N34" s="4">
@@ -4475,13 +4478,13 @@
       <c r="R34" s="3">
         <v>15000</v>
       </c>
-      <c r="S34" s="54">
+      <c r="S34" s="55">
         <v>16008</v>
       </c>
-      <c r="T34" s="49">
+      <c r="T34" s="50">
         <v>48</v>
       </c>
-      <c r="U34" s="55">
+      <c r="U34" s="56">
         <v>0</v>
       </c>
       <c r="V34" t="s">
@@ -4493,12 +4496,12 @@
       <c r="X34" s="3">
         <v>1</v>
       </c>
-      <c r="Y34" s="56">
+      <c r="Y34" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" spans="1:25">
-      <c r="A35" s="49">
+      <c r="A35" s="50">
         <v>20010110</v>
       </c>
       <c r="B35" s="3">
@@ -4513,16 +4516,16 @@
       <c r="E35" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="60" t="s">
+      <c r="F35" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="52" t="s">
+      <c r="G35" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H35" s="3">
         <v>1</v>
       </c>
-      <c r="I35" s="50">
+      <c r="I35" s="51">
         <v>1980000</v>
       </c>
       <c r="J35" s="36" t="s">
@@ -4534,7 +4537,7 @@
       <c r="L35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M35" s="53" t="s">
+      <c r="M35" s="54" t="s">
         <v>69</v>
       </c>
       <c r="N35" s="4">
@@ -4555,10 +4558,10 @@
       <c r="S35" s="3">
         <v>16008</v>
       </c>
-      <c r="T35" s="49">
+      <c r="T35" s="50">
         <v>48</v>
       </c>
-      <c r="U35" s="55">
+      <c r="U35" s="56">
         <v>0</v>
       </c>
       <c r="V35" t="s">
@@ -4570,12 +4573,12 @@
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="56">
+      <c r="Y35" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:25">
-      <c r="A36" s="49">
+      <c r="A36" s="50">
         <v>20010111</v>
       </c>
       <c r="B36" s="3">
@@ -4590,16 +4593,16 @@
       <c r="E36" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="60" t="s">
+      <c r="F36" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="52" t="s">
+      <c r="G36" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H36" s="3">
         <v>2</v>
       </c>
-      <c r="I36" s="50">
+      <c r="I36" s="51">
         <v>1980000</v>
       </c>
       <c r="J36" s="41" t="s">
@@ -4611,7 +4614,7 @@
       <c r="L36" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M36" s="53" t="s">
+      <c r="M36" s="54" t="s">
         <v>69</v>
       </c>
       <c r="N36" s="4">
@@ -4632,10 +4635,10 @@
       <c r="S36" s="3">
         <v>16008</v>
       </c>
-      <c r="T36" s="49">
+      <c r="T36" s="50">
         <v>48</v>
       </c>
-      <c r="U36" s="55">
+      <c r="U36" s="56">
         <v>0</v>
       </c>
       <c r="V36" t="s">
@@ -4647,12 +4650,12 @@
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="56">
+      <c r="Y36" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:25">
-      <c r="A37" s="49">
+      <c r="A37" s="50">
         <v>20010112</v>
       </c>
       <c r="B37" s="3">
@@ -4667,16 +4670,16 @@
       <c r="E37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="60" t="s">
+      <c r="F37" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="52" t="s">
+      <c r="G37" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H37" s="3">
         <v>3</v>
       </c>
-      <c r="I37" s="50">
+      <c r="I37" s="51">
         <v>1980000</v>
       </c>
       <c r="J37" s="36" t="s">
@@ -4688,7 +4691,7 @@
       <c r="L37" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M37" s="53" t="s">
+      <c r="M37" s="54" t="s">
         <v>69</v>
       </c>
       <c r="N37" s="4">
@@ -4709,10 +4712,10 @@
       <c r="S37" s="3">
         <v>16008</v>
       </c>
-      <c r="T37" s="49">
+      <c r="T37" s="50">
         <v>48</v>
       </c>
-      <c r="U37" s="55">
+      <c r="U37" s="56">
         <v>0</v>
       </c>
       <c r="V37" t="s">
@@ -4724,12 +4727,12 @@
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="56">
+      <c r="Y37" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:25">
-      <c r="A38" s="49">
+      <c r="A38" s="50">
         <v>20030010</v>
       </c>
       <c r="B38" s="3">
@@ -4744,16 +4747,16 @@
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="60" t="s">
+      <c r="F38" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="52" t="s">
+      <c r="G38" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="50">
+      <c r="I38" s="51">
         <v>1980000</v>
       </c>
       <c r="J38" s="36" t="s">
@@ -4765,7 +4768,7 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="53" t="s">
+      <c r="M38" s="54" t="s">
         <v>71</v>
       </c>
       <c r="N38" s="4">
@@ -4786,10 +4789,10 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="49">
+      <c r="T38" s="50">
         <v>50</v>
       </c>
-      <c r="U38" s="55">
+      <c r="U38" s="56">
         <v>0</v>
       </c>
       <c r="V38" t="s">
@@ -4801,12 +4804,12 @@
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="56">
+      <c r="Y38" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:25">
-      <c r="A39" s="49">
+      <c r="A39" s="50">
         <v>20030011</v>
       </c>
       <c r="B39" s="3">
@@ -4821,16 +4824,16 @@
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="60" t="s">
+      <c r="F39" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="52" t="s">
+      <c r="G39" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="50">
+      <c r="I39" s="51">
         <v>1980000</v>
       </c>
       <c r="J39" s="41" t="s">
@@ -4842,7 +4845,7 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="54" t="s">
         <v>71</v>
       </c>
       <c r="N39" s="4">
@@ -4863,10 +4866,10 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="49">
+      <c r="T39" s="50">
         <v>50</v>
       </c>
-      <c r="U39" s="55">
+      <c r="U39" s="56">
         <v>0</v>
       </c>
       <c r="V39" t="s">
@@ -4878,12 +4881,12 @@
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="56">
+      <c r="Y39" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:25">
-      <c r="A40" s="49">
+      <c r="A40" s="50">
         <v>20030012</v>
       </c>
       <c r="B40" s="3">
@@ -4898,28 +4901,28 @@
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="60" t="s">
+      <c r="F40" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="52" t="s">
+      <c r="G40" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="50">
+      <c r="I40" s="51">
         <v>1980000</v>
       </c>
       <c r="J40" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K40" s="57">
-        <v>0</v>
-      </c>
-      <c r="L40" s="57" t="s">
+      <c r="K40" s="58">
+        <v>0</v>
+      </c>
+      <c r="L40" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="53" t="s">
+      <c r="M40" s="54" t="s">
         <v>71</v>
       </c>
       <c r="N40" s="4">
@@ -4928,22 +4931,22 @@
       <c r="O40" s="3">
         <v>300</v>
       </c>
-      <c r="P40" s="57">
+      <c r="P40" s="58">
         <v>180000</v>
       </c>
-      <c r="Q40" s="57">
+      <c r="Q40" s="58">
         <v>16000</v>
       </c>
-      <c r="R40" s="57">
+      <c r="R40" s="58">
         <v>15000</v>
       </c>
-      <c r="S40" s="57">
+      <c r="S40" s="58">
         <v>16008</v>
       </c>
-      <c r="T40" s="49">
+      <c r="T40" s="50">
         <v>50</v>
       </c>
-      <c r="U40" s="55">
+      <c r="U40" s="56">
         <v>0</v>
       </c>
       <c r="V40" t="s">
@@ -4955,12 +4958,12 @@
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="56">
+      <c r="Y40" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:25">
-      <c r="A41" s="49">
+      <c r="A41" s="50">
         <v>20040010</v>
       </c>
       <c r="B41" s="3">
@@ -4975,28 +4978,28 @@
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="60" t="s">
+      <c r="F41" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="52" t="s">
+      <c r="G41" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="50">
+      <c r="I41" s="51">
         <v>1980000</v>
       </c>
       <c r="J41" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K41" s="57">
-        <v>0</v>
-      </c>
-      <c r="L41" s="57" t="s">
+      <c r="K41" s="58">
+        <v>0</v>
+      </c>
+      <c r="L41" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="53" t="s">
+      <c r="M41" s="54" t="s">
         <v>73</v>
       </c>
       <c r="N41" s="4">
@@ -5005,22 +5008,22 @@
       <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="57">
+      <c r="P41" s="58">
         <v>180000</v>
       </c>
-      <c r="Q41" s="57">
+      <c r="Q41" s="58">
         <v>16000</v>
       </c>
-      <c r="R41" s="57">
+      <c r="R41" s="58">
         <v>15000</v>
       </c>
-      <c r="S41" s="57">
+      <c r="S41" s="58">
         <v>16008</v>
       </c>
-      <c r="T41" s="49">
+      <c r="T41" s="50">
         <v>50</v>
       </c>
-      <c r="U41" s="55">
+      <c r="U41" s="56">
         <v>0</v>
       </c>
       <c r="V41" t="s">
@@ -5032,12 +5035,12 @@
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="56">
+      <c r="Y41" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:25">
-      <c r="A42" s="49">
+      <c r="A42" s="50">
         <v>20040011</v>
       </c>
       <c r="B42" s="3">
@@ -5052,28 +5055,28 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="60" t="s">
+      <c r="F42" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="52" t="s">
+      <c r="G42" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="50">
+      <c r="I42" s="51">
         <v>1980000</v>
       </c>
       <c r="J42" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K42" s="57">
-        <v>0</v>
-      </c>
-      <c r="L42" s="57" t="s">
+      <c r="K42" s="58">
+        <v>0</v>
+      </c>
+      <c r="L42" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="53" t="s">
+      <c r="M42" s="54" t="s">
         <v>73</v>
       </c>
       <c r="N42" s="4">
@@ -5082,22 +5085,22 @@
       <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="57">
+      <c r="P42" s="58">
         <v>180000</v>
       </c>
-      <c r="Q42" s="57">
+      <c r="Q42" s="58">
         <v>16000</v>
       </c>
-      <c r="R42" s="57">
+      <c r="R42" s="58">
         <v>15000</v>
       </c>
-      <c r="S42" s="57">
+      <c r="S42" s="58">
         <v>16008</v>
       </c>
-      <c r="T42" s="49">
+      <c r="T42" s="50">
         <v>50</v>
       </c>
-      <c r="U42" s="55">
+      <c r="U42" s="56">
         <v>0</v>
       </c>
       <c r="V42" t="s">
@@ -5109,12 +5112,12 @@
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="56">
+      <c r="Y42" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:25">
-      <c r="A43" s="49">
+      <c r="A43" s="50">
         <v>20040012</v>
       </c>
       <c r="B43" s="3">
@@ -5129,28 +5132,28 @@
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="60" t="s">
+      <c r="F43" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="52" t="s">
+      <c r="G43" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="50">
+      <c r="I43" s="51">
         <v>1980000</v>
       </c>
       <c r="J43" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K43" s="57">
-        <v>0</v>
-      </c>
-      <c r="L43" s="57" t="s">
+      <c r="K43" s="58">
+        <v>0</v>
+      </c>
+      <c r="L43" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="53" t="s">
+      <c r="M43" s="54" t="s">
         <v>73</v>
       </c>
       <c r="N43" s="4">
@@ -5159,22 +5162,22 @@
       <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="57">
+      <c r="P43" s="58">
         <v>180000</v>
       </c>
-      <c r="Q43" s="57">
+      <c r="Q43" s="58">
         <v>16000</v>
       </c>
-      <c r="R43" s="57">
+      <c r="R43" s="58">
         <v>15000</v>
       </c>
-      <c r="S43" s="57">
+      <c r="S43" s="58">
         <v>16008</v>
       </c>
-      <c r="T43" s="49">
+      <c r="T43" s="50">
         <v>50</v>
       </c>
-      <c r="U43" s="55">
+      <c r="U43" s="56">
         <v>0</v>
       </c>
       <c r="V43" t="s">
@@ -5186,12 +5189,12 @@
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="56">
+      <c r="Y43" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:25">
-      <c r="A44" s="49">
+      <c r="A44" s="50">
         <v>20050010</v>
       </c>
       <c r="B44" s="3">
@@ -5206,28 +5209,28 @@
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="60" t="s">
+      <c r="F44" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="52" t="s">
+      <c r="G44" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="50">
+      <c r="I44" s="51">
         <v>1980000</v>
       </c>
       <c r="J44" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K44" s="57">
-        <v>1</v>
-      </c>
-      <c r="L44" s="57" t="s">
+      <c r="K44" s="58">
+        <v>1</v>
+      </c>
+      <c r="L44" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M44" s="53" t="s">
+      <c r="M44" s="54" t="s">
         <v>75</v>
       </c>
       <c r="N44" s="4">
@@ -5236,22 +5239,22 @@
       <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="57">
+      <c r="P44" s="58">
         <v>180000</v>
       </c>
-      <c r="Q44" s="57">
+      <c r="Q44" s="58">
         <v>16000</v>
       </c>
-      <c r="R44" s="57">
+      <c r="R44" s="58">
         <v>15000</v>
       </c>
-      <c r="S44" s="57">
+      <c r="S44" s="58">
         <v>16008</v>
       </c>
-      <c r="T44" s="49">
+      <c r="T44" s="50">
         <v>48</v>
       </c>
-      <c r="U44" s="49">
+      <c r="U44" s="50">
         <v>0</v>
       </c>
       <c r="V44" t="s">
@@ -5263,12 +5266,12 @@
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="56">
+      <c r="Y44" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:25">
-      <c r="A45" s="49">
+      <c r="A45" s="50">
         <v>20050011</v>
       </c>
       <c r="B45" s="3">
@@ -5283,28 +5286,28 @@
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="60" t="s">
+      <c r="F45" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="52" t="s">
+      <c r="G45" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="50">
+      <c r="I45" s="51">
         <v>1980000</v>
       </c>
       <c r="J45" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K45" s="57">
-        <v>1</v>
-      </c>
-      <c r="L45" s="57" t="s">
+      <c r="K45" s="58">
+        <v>1</v>
+      </c>
+      <c r="L45" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M45" s="53" t="s">
+      <c r="M45" s="54" t="s">
         <v>75</v>
       </c>
       <c r="N45" s="4">
@@ -5313,22 +5316,22 @@
       <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="57">
+      <c r="P45" s="58">
         <v>180000</v>
       </c>
-      <c r="Q45" s="57">
+      <c r="Q45" s="58">
         <v>16000</v>
       </c>
-      <c r="R45" s="57">
+      <c r="R45" s="58">
         <v>15000</v>
       </c>
-      <c r="S45" s="57">
+      <c r="S45" s="58">
         <v>16008</v>
       </c>
-      <c r="T45" s="49">
+      <c r="T45" s="50">
         <v>48</v>
       </c>
-      <c r="U45" s="49">
+      <c r="U45" s="50">
         <v>0</v>
       </c>
       <c r="V45" t="s">
@@ -5340,12 +5343,12 @@
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="56">
+      <c r="Y45" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:25">
-      <c r="A46" s="49">
+      <c r="A46" s="50">
         <v>20050012</v>
       </c>
       <c r="B46" s="3">
@@ -5360,28 +5363,28 @@
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="60" t="s">
+      <c r="F46" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="52" t="s">
+      <c r="G46" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="50">
+      <c r="I46" s="51">
         <v>1980000</v>
       </c>
       <c r="J46" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K46" s="57">
-        <v>1</v>
-      </c>
-      <c r="L46" s="57" t="s">
+      <c r="K46" s="58">
+        <v>1</v>
+      </c>
+      <c r="L46" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M46" s="53" t="s">
+      <c r="M46" s="54" t="s">
         <v>75</v>
       </c>
       <c r="N46" s="4">
@@ -5390,22 +5393,22 @@
       <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="57">
+      <c r="P46" s="58">
         <v>180000</v>
       </c>
-      <c r="Q46" s="57">
+      <c r="Q46" s="58">
         <v>16000</v>
       </c>
-      <c r="R46" s="57">
+      <c r="R46" s="58">
         <v>15000</v>
       </c>
-      <c r="S46" s="57">
+      <c r="S46" s="58">
         <v>16008</v>
       </c>
-      <c r="T46" s="49">
+      <c r="T46" s="50">
         <v>48</v>
       </c>
-      <c r="U46" s="49">
+      <c r="U46" s="50">
         <v>0</v>
       </c>
       <c r="V46" t="s">
@@ -5417,12 +5420,12 @@
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="56">
+      <c r="Y46" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:25">
-      <c r="A47" s="49">
+      <c r="A47" s="50">
         <v>20060010</v>
       </c>
       <c r="B47" s="3">
@@ -5437,28 +5440,28 @@
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="60" t="s">
+      <c r="F47" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="52" t="s">
+      <c r="G47" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="50">
+      <c r="I47" s="51">
         <v>1980000</v>
       </c>
       <c r="J47" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K47" s="57">
-        <v>0</v>
-      </c>
-      <c r="L47" s="57" t="s">
+      <c r="K47" s="58">
+        <v>0</v>
+      </c>
+      <c r="L47" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M47" s="53" t="s">
+      <c r="M47" s="54" t="s">
         <v>77</v>
       </c>
       <c r="N47" s="4">
@@ -5467,22 +5470,22 @@
       <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="57">
+      <c r="P47" s="58">
         <v>180000</v>
       </c>
-      <c r="Q47" s="57">
+      <c r="Q47" s="58">
         <v>16000</v>
       </c>
-      <c r="R47" s="57">
+      <c r="R47" s="58">
         <v>15000</v>
       </c>
-      <c r="S47" s="57">
+      <c r="S47" s="58">
         <v>16008</v>
       </c>
-      <c r="T47" s="49">
+      <c r="T47" s="50">
         <v>20</v>
       </c>
-      <c r="U47" s="49">
+      <c r="U47" s="50">
         <v>0</v>
       </c>
       <c r="V47" t="s">
@@ -5494,12 +5497,12 @@
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="56">
+      <c r="Y47" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:25">
-      <c r="A48" s="49">
+      <c r="A48" s="50">
         <v>20060011</v>
       </c>
       <c r="B48" s="3">
@@ -5514,28 +5517,28 @@
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="60" t="s">
+      <c r="F48" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="52" t="s">
+      <c r="G48" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="50">
+      <c r="I48" s="51">
         <v>1980000</v>
       </c>
       <c r="J48" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K48" s="57">
-        <v>0</v>
-      </c>
-      <c r="L48" s="57" t="s">
+      <c r="K48" s="58">
+        <v>0</v>
+      </c>
+      <c r="L48" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="54" t="s">
         <v>77</v>
       </c>
       <c r="N48" s="4">
@@ -5544,22 +5547,22 @@
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="57">
+      <c r="P48" s="58">
         <v>180000</v>
       </c>
-      <c r="Q48" s="57">
+      <c r="Q48" s="58">
         <v>16000</v>
       </c>
-      <c r="R48" s="57">
+      <c r="R48" s="58">
         <v>15000</v>
       </c>
-      <c r="S48" s="57">
+      <c r="S48" s="58">
         <v>16008</v>
       </c>
-      <c r="T48" s="49">
+      <c r="T48" s="50">
         <v>20</v>
       </c>
-      <c r="U48" s="49">
+      <c r="U48" s="50">
         <v>0</v>
       </c>
       <c r="V48" t="s">
@@ -5571,12 +5574,12 @@
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="56">
+      <c r="Y48" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:25">
-      <c r="A49" s="49">
+      <c r="A49" s="50">
         <v>20060012</v>
       </c>
       <c r="B49" s="3">
@@ -5591,16 +5594,16 @@
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="60" t="s">
+      <c r="F49" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="52" t="s">
+      <c r="G49" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="50">
+      <c r="I49" s="51">
         <v>1980000</v>
       </c>
       <c r="J49" s="36" t="s">
@@ -5612,7 +5615,7 @@
       <c r="L49" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M49" s="53" t="s">
+      <c r="M49" s="54" t="s">
         <v>77</v>
       </c>
       <c r="N49" s="4">
@@ -5633,10 +5636,10 @@
       <c r="S49" s="3">
         <v>16008</v>
       </c>
-      <c r="T49" s="49">
+      <c r="T49" s="50">
         <v>20</v>
       </c>
-      <c r="U49" s="49">
+      <c r="U49" s="50">
         <v>0</v>
       </c>
       <c r="V49" t="s">
@@ -5648,12 +5651,12 @@
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="56">
+      <c r="Y49" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:25">
-      <c r="A50" s="49">
+      <c r="A50" s="50">
         <v>20070010</v>
       </c>
       <c r="B50" s="3">
@@ -5668,16 +5671,16 @@
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="60" t="s">
+      <c r="F50" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="52" t="s">
+      <c r="G50" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="50">
+      <c r="I50" s="51">
         <v>1980000</v>
       </c>
       <c r="J50" s="36" t="s">
@@ -5689,7 +5692,7 @@
       <c r="L50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="53" t="s">
+      <c r="M50" s="54" t="s">
         <v>79</v>
       </c>
       <c r="N50" s="4">
@@ -5710,10 +5713,10 @@
       <c r="S50" s="3">
         <v>16008</v>
       </c>
-      <c r="T50" s="49">
+      <c r="T50" s="50">
         <v>30</v>
       </c>
-      <c r="U50" s="49">
+      <c r="U50" s="50">
         <v>1</v>
       </c>
       <c r="V50" t="s">
@@ -5725,12 +5728,12 @@
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="56">
+      <c r="Y50" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:25">
-      <c r="A51" s="49">
+      <c r="A51" s="50">
         <v>20070011</v>
       </c>
       <c r="B51" s="3">
@@ -5745,16 +5748,16 @@
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="60" t="s">
+      <c r="F51" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="52" t="s">
+      <c r="G51" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="50">
+      <c r="I51" s="51">
         <v>1980000</v>
       </c>
       <c r="J51" s="41" t="s">
@@ -5766,7 +5769,7 @@
       <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="53" t="s">
+      <c r="M51" s="54" t="s">
         <v>79</v>
       </c>
       <c r="N51" s="4">
@@ -5787,10 +5790,10 @@
       <c r="S51" s="3">
         <v>16008</v>
       </c>
-      <c r="T51" s="49">
+      <c r="T51" s="50">
         <v>30</v>
       </c>
-      <c r="U51" s="49">
+      <c r="U51" s="50">
         <v>1</v>
       </c>
       <c r="V51" t="s">
@@ -5802,12 +5805,12 @@
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="56">
+      <c r="Y51" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:25">
-      <c r="A52" s="49">
+      <c r="A52" s="50">
         <v>20070012</v>
       </c>
       <c r="B52" s="3">
@@ -5822,16 +5825,16 @@
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="60" t="s">
+      <c r="F52" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="52" t="s">
+      <c r="G52" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="50">
+      <c r="I52" s="51">
         <v>1980000</v>
       </c>
       <c r="J52" s="36" t="s">
@@ -5843,7 +5846,7 @@
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="53" t="s">
+      <c r="M52" s="54" t="s">
         <v>79</v>
       </c>
       <c r="N52" s="4">
@@ -5864,10 +5867,10 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="49">
+      <c r="T52" s="50">
         <v>30</v>
       </c>
-      <c r="U52" s="49">
+      <c r="U52" s="50">
         <v>1</v>
       </c>
       <c r="V52" t="s">
@@ -5879,12 +5882,12 @@
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="56">
+      <c r="Y52" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:25">
-      <c r="A53" s="49">
+      <c r="A53" s="50">
         <v>20080010</v>
       </c>
       <c r="B53" s="3">
@@ -5899,16 +5902,16 @@
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="60" t="s">
+      <c r="F53" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="52" t="s">
+      <c r="G53" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="50">
+      <c r="I53" s="51">
         <v>1980000</v>
       </c>
       <c r="J53" s="36" t="s">
@@ -5920,7 +5923,7 @@
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="53" t="s">
+      <c r="M53" s="54" t="s">
         <v>81</v>
       </c>
       <c r="N53" s="4">
@@ -5941,10 +5944,10 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="49">
+      <c r="T53" s="50">
         <v>20</v>
       </c>
-      <c r="U53" s="49">
+      <c r="U53" s="50">
         <v>0</v>
       </c>
       <c r="V53" t="s">
@@ -5956,12 +5959,12 @@
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="56">
+      <c r="Y53" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:25">
-      <c r="A54" s="49">
+      <c r="A54" s="50">
         <v>20080011</v>
       </c>
       <c r="B54" s="3">
@@ -5976,16 +5979,16 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="60" t="s">
+      <c r="F54" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="52" t="s">
+      <c r="G54" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="50">
+      <c r="I54" s="51">
         <v>1980000</v>
       </c>
       <c r="J54" s="41" t="s">
@@ -5997,7 +6000,7 @@
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="53" t="s">
+      <c r="M54" s="54" t="s">
         <v>81</v>
       </c>
       <c r="N54" s="4">
@@ -6018,10 +6021,10 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="49">
+      <c r="T54" s="50">
         <v>20</v>
       </c>
-      <c r="U54" s="49">
+      <c r="U54" s="50">
         <v>0</v>
       </c>
       <c r="V54" t="s">
@@ -6033,12 +6036,12 @@
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="56">
+      <c r="Y54" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" spans="1:25">
-      <c r="A55" s="49">
+      <c r="A55" s="50">
         <v>20080012</v>
       </c>
       <c r="B55" s="3">
@@ -6053,16 +6056,16 @@
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="60" t="s">
+      <c r="F55" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="52" t="s">
+      <c r="G55" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="50">
+      <c r="I55" s="51">
         <v>1980000</v>
       </c>
       <c r="J55" s="36" t="s">
@@ -6074,7 +6077,7 @@
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="53" t="s">
+      <c r="M55" s="54" t="s">
         <v>81</v>
       </c>
       <c r="N55" s="4">
@@ -6095,10 +6098,10 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="49">
+      <c r="T55" s="50">
         <v>20</v>
       </c>
-      <c r="U55" s="49">
+      <c r="U55" s="50">
         <v>0</v>
       </c>
       <c r="V55" t="s">
@@ -6110,12 +6113,12 @@
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="56">
+      <c r="Y55" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" spans="1:25">
-      <c r="A56" s="49">
+      <c r="A56" s="50">
         <v>20090010</v>
       </c>
       <c r="B56" s="3">
@@ -6130,16 +6133,16 @@
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="60" t="s">
+      <c r="F56" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="52" t="s">
+      <c r="G56" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="50">
+      <c r="I56" s="51">
         <v>1980000</v>
       </c>
       <c r="J56" s="36" t="s">
@@ -6151,7 +6154,7 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="53" t="s">
+      <c r="M56" s="54" t="s">
         <v>81</v>
       </c>
       <c r="N56" s="4">
@@ -6172,10 +6175,10 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="49">
+      <c r="T56" s="50">
         <v>20</v>
       </c>
-      <c r="U56" s="49">
+      <c r="U56" s="50">
         <v>0</v>
       </c>
       <c r="V56" t="s">
@@ -6187,12 +6190,12 @@
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="56">
+      <c r="Y56" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:25">
-      <c r="A57" s="49">
+      <c r="A57" s="50">
         <v>20090011</v>
       </c>
       <c r="B57" s="3">
@@ -6207,16 +6210,16 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="60" t="s">
+      <c r="F57" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="52" t="s">
+      <c r="G57" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="50">
+      <c r="I57" s="51">
         <v>1980000</v>
       </c>
       <c r="J57" s="41" t="s">
@@ -6228,7 +6231,7 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="53" t="s">
+      <c r="M57" s="54" t="s">
         <v>81</v>
       </c>
       <c r="N57" s="4">
@@ -6249,10 +6252,10 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="49">
+      <c r="T57" s="50">
         <v>20</v>
       </c>
-      <c r="U57" s="49">
+      <c r="U57" s="50">
         <v>0</v>
       </c>
       <c r="V57" t="s">
@@ -6264,12 +6267,12 @@
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="56">
+      <c r="Y57" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:25">
-      <c r="A58" s="49">
+      <c r="A58" s="50">
         <v>20090012</v>
       </c>
       <c r="B58" s="3">
@@ -6284,16 +6287,16 @@
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="60" t="s">
+      <c r="F58" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="52" t="s">
+      <c r="G58" s="53" t="s">
         <v>83</v>
       </c>
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="50">
+      <c r="I58" s="51">
         <v>1980000</v>
       </c>
       <c r="J58" s="36" t="s">
@@ -6305,7 +6308,7 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="53" t="s">
+      <c r="M58" s="54" t="s">
         <v>81</v>
       </c>
       <c r="N58" s="4">
@@ -6326,10 +6329,10 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="49">
+      <c r="T58" s="50">
         <v>20</v>
       </c>
-      <c r="U58" s="49">
+      <c r="U58" s="50">
         <v>0</v>
       </c>
       <c r="V58" t="s">
@@ -6341,7 +6344,7 @@
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="56">
+      <c r="Y58" s="57">
         <v>0</v>
       </c>
     </row>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27735" windowHeight="12270" tabRatio="794"/>
+    <workbookView windowWidth="24045" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -1334,7 +1334,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1470,9 +1470,6 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2153,7 +2150,7 @@
       <c r="E5" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G5" s="34" t="s">
@@ -2211,8 +2208,8 @@
         <v>0</v>
       </c>
       <c r="Y5" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -2232,7 +2229,7 @@
       <c r="E6" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G6" s="34" t="s">
@@ -2290,8 +2287,8 @@
         <v>0</v>
       </c>
       <c r="Y6" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" ref="Y6:Y10" si="1">Y5*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:25">
@@ -2311,7 +2308,7 @@
       <c r="E7" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G7" s="34" t="s">
@@ -2368,9 +2365,9 @@
       <c r="X7" s="2">
         <v>0</v>
       </c>
-      <c r="Y7" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y7" s="8">
+        <f t="shared" si="1"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:25">
@@ -2387,10 +2384,10 @@
       <c r="D8" s="32">
         <v>200101001</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="34" t="s">
@@ -2448,8 +2445,8 @@
         <v>0</v>
       </c>
       <c r="Y8" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -2469,7 +2466,7 @@
       <c r="E9" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G9" s="34" t="s">
@@ -2527,8 +2524,8 @@
         <v>0</v>
       </c>
       <c r="Y9" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" si="1"/>
+        <v>100000000</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -2548,7 +2545,7 @@
       <c r="E10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G10" s="34" t="s">
@@ -2605,9 +2602,9 @@
       <c r="X10" s="2">
         <v>0</v>
       </c>
-      <c r="Y10" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y10" s="8">
+        <f t="shared" si="1"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -2624,10 +2621,10 @@
       <c r="D11" s="32">
         <v>200300001</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G11" s="34" t="s">
@@ -2685,8 +2682,8 @@
         <v>0</v>
       </c>
       <c r="Y11" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:25">
@@ -2706,7 +2703,7 @@
       <c r="E12" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G12" s="34" t="s">
@@ -2764,8 +2761,8 @@
         <v>0</v>
       </c>
       <c r="Y12" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" ref="Y12:Y16" si="2">Y11*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2785,7 +2782,7 @@
       <c r="E13" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G13" s="34" t="s">
@@ -2842,9 +2839,9 @@
       <c r="X13" s="2">
         <v>0</v>
       </c>
-      <c r="Y13" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y13" s="8">
+        <f t="shared" si="2"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2861,10 +2858,10 @@
       <c r="D14" s="32">
         <v>200400009</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G14" s="34" t="s">
@@ -2922,8 +2919,8 @@
         <v>0</v>
       </c>
       <c r="Y14" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2943,7 +2940,7 @@
       <c r="E15" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="34" t="s">
@@ -3001,8 +2998,8 @@
         <v>0</v>
       </c>
       <c r="Y15" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" si="2"/>
+        <v>100000000</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:25">
@@ -3022,7 +3019,7 @@
       <c r="E16" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G16" s="34" t="s">
@@ -3079,9 +3076,9 @@
       <c r="X16" s="2">
         <v>0</v>
       </c>
-      <c r="Y16" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y16" s="8">
+        <f t="shared" si="2"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:25">
@@ -3101,7 +3098,7 @@
       <c r="E17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="59" t="s">
+      <c r="F17" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G17" s="34" t="s">
@@ -3159,8 +3156,8 @@
         <v>0</v>
       </c>
       <c r="Y17" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -3180,7 +3177,7 @@
       <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G18" s="34" t="s">
@@ -3238,8 +3235,8 @@
         <v>0</v>
       </c>
       <c r="Y18" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" ref="Y18:Y22" si="3">Y17*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -3259,7 +3256,7 @@
       <c r="E19" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="59" t="s">
+      <c r="F19" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G19" s="34" t="s">
@@ -3316,9 +3313,9 @@
       <c r="X19" s="2">
         <v>0</v>
       </c>
-      <c r="Y19" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y19" s="8">
+        <f t="shared" si="3"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -3335,10 +3332,10 @@
       <c r="D20" s="32">
         <v>200600001</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G20" s="34" t="s">
@@ -3396,8 +3393,8 @@
         <v>0</v>
       </c>
       <c r="Y20" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:25">
@@ -3417,7 +3414,7 @@
       <c r="E21" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="59" t="s">
+      <c r="F21" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G21" s="34" t="s">
@@ -3475,8 +3472,8 @@
         <v>0</v>
       </c>
       <c r="Y21" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" si="3"/>
+        <v>100000000</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -3496,7 +3493,7 @@
       <c r="E22" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G22" s="34" t="s">
@@ -3553,9 +3550,9 @@
       <c r="X22" s="2">
         <v>0</v>
       </c>
-      <c r="Y22" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y22" s="8">
+        <f t="shared" si="3"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -3575,7 +3572,7 @@
       <c r="E23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="34" t="s">
@@ -3633,8 +3630,8 @@
         <v>0</v>
       </c>
       <c r="Y23" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -3654,7 +3651,7 @@
       <c r="E24" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G24" s="34" t="s">
@@ -3712,8 +3709,8 @@
         <v>0</v>
       </c>
       <c r="Y24" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" ref="Y24:Y28" si="4">Y23*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" spans="1:25">
@@ -3733,7 +3730,7 @@
       <c r="E25" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="59" t="s">
+      <c r="F25" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G25" s="34" t="s">
@@ -3790,9 +3787,9 @@
       <c r="X25" s="2">
         <v>0</v>
       </c>
-      <c r="Y25" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y25" s="8">
+        <f t="shared" si="4"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="1:25">
@@ -3809,10 +3806,10 @@
       <c r="D26" s="32">
         <v>200800001</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="E26" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G26" s="34" t="s">
@@ -3870,8 +3867,8 @@
         <v>0</v>
       </c>
       <c r="Y26" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:25">
@@ -3891,7 +3888,7 @@
       <c r="E27" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="59" t="s">
+      <c r="F27" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G27" s="34" t="s">
@@ -3949,8 +3946,8 @@
         <v>0</v>
       </c>
       <c r="Y27" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f t="shared" si="4"/>
+        <v>100000000</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" spans="1:25">
@@ -3970,7 +3967,7 @@
       <c r="E28" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G28" s="34" t="s">
@@ -4027,9 +4024,9 @@
       <c r="X28" s="2">
         <v>0</v>
       </c>
-      <c r="Y28" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y28" s="8">
+        <f t="shared" si="4"/>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:25">
@@ -4037,7 +4034,7 @@
         <f t="shared" si="0"/>
         <v>2009001</v>
       </c>
-      <c r="B29" s="45">
+      <c r="B29" s="44">
         <v>200900</v>
       </c>
       <c r="C29" s="32" t="s">
@@ -4046,10 +4043,10 @@
       <c r="D29" s="32">
         <v>200900001</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="E29" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="F29" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="34" t="s">
@@ -4064,7 +4061,7 @@
       <c r="J29" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="46">
+      <c r="K29" s="45">
         <v>0</v>
       </c>
       <c r="L29" s="4" t="s">
@@ -4107,8 +4104,8 @@
         <v>0</v>
       </c>
       <c r="Y29" s="8">
-        <f>1000*100000</f>
-        <v>100000000</v>
+        <f>100*100000</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -4116,7 +4113,7 @@
         <f t="shared" si="0"/>
         <v>2009002</v>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="46">
         <v>200900</v>
       </c>
       <c r="C30" s="40" t="s">
@@ -4128,7 +4125,7 @@
       <c r="E30" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="34" t="s">
@@ -4143,7 +4140,7 @@
       <c r="J30" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="46">
+      <c r="K30" s="45">
         <v>0</v>
       </c>
       <c r="L30" s="4" t="s">
@@ -4186,8 +4183,8 @@
         <v>0</v>
       </c>
       <c r="Y30" s="8">
-        <f>1000000*1000</f>
-        <v>1000000000</v>
+        <f>Y29*10</f>
+        <v>100000000</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -4195,19 +4192,19 @@
         <f t="shared" si="0"/>
         <v>2009003</v>
       </c>
-      <c r="B31" s="48">
+      <c r="B31" s="47">
         <v>200900</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="48">
         <v>200900001</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E31" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="59" t="s">
+      <c r="F31" s="58" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="34" t="s">
@@ -4222,7 +4219,7 @@
       <c r="J31" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="46">
+      <c r="K31" s="45">
         <v>0</v>
       </c>
       <c r="L31" s="4" t="s">
@@ -4264,37 +4261,37 @@
       <c r="X31" s="2">
         <v>0</v>
       </c>
-      <c r="Y31" s="42">
-        <f>10000000*1000</f>
-        <v>10000000000</v>
+      <c r="Y31" s="8">
+        <f>Y30*10</f>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="32" s="3" customFormat="1" spans="1:25">
-      <c r="A32" s="50">
+      <c r="A32" s="49">
         <v>20010010</v>
       </c>
       <c r="B32" s="3">
         <v>200100</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="50">
         <v>200100038</v>
       </c>
-      <c r="E32" s="51" t="s">
+      <c r="E32" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="60" t="s">
+      <c r="F32" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="53" t="s">
+      <c r="G32" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="H32" s="51">
-        <v>1</v>
-      </c>
-      <c r="I32" s="51">
+      <c r="H32" s="50">
+        <v>1</v>
+      </c>
+      <c r="I32" s="50">
         <v>1980000</v>
       </c>
       <c r="J32" s="36" t="s">
@@ -4306,7 +4303,7 @@
       <c r="L32" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M32" s="54" t="s">
+      <c r="M32" s="53" t="s">
         <v>56</v>
       </c>
       <c r="N32" s="4">
@@ -4324,13 +4321,13 @@
       <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="55">
+      <c r="S32" s="54">
         <v>16008</v>
       </c>
-      <c r="T32" s="50">
+      <c r="T32" s="49">
         <v>48</v>
       </c>
-      <c r="U32" s="56">
+      <c r="U32" s="55">
         <v>0</v>
       </c>
       <c r="V32" t="s">
@@ -4342,36 +4339,36 @@
       <c r="X32" s="3">
         <v>1</v>
       </c>
-      <c r="Y32" s="57">
+      <c r="Y32" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:25">
-      <c r="A33" s="50">
+      <c r="A33" s="49">
         <v>20010011</v>
       </c>
       <c r="B33" s="3">
         <v>200100</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="50">
         <v>200100038</v>
       </c>
-      <c r="E33" s="51" t="s">
+      <c r="E33" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="60" t="s">
+      <c r="F33" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="53" t="s">
+      <c r="G33" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="H33" s="51">
+      <c r="H33" s="50">
         <v>2</v>
       </c>
-      <c r="I33" s="51">
+      <c r="I33" s="50">
         <v>1980000</v>
       </c>
       <c r="J33" s="41" t="s">
@@ -4383,7 +4380,7 @@
       <c r="L33" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M33" s="54" t="s">
+      <c r="M33" s="53" t="s">
         <v>56</v>
       </c>
       <c r="N33" s="4">
@@ -4401,13 +4398,13 @@
       <c r="R33" s="3">
         <v>15000</v>
       </c>
-      <c r="S33" s="55">
+      <c r="S33" s="54">
         <v>16008</v>
       </c>
-      <c r="T33" s="50">
+      <c r="T33" s="49">
         <v>48</v>
       </c>
-      <c r="U33" s="56">
+      <c r="U33" s="55">
         <v>0</v>
       </c>
       <c r="V33" t="s">
@@ -4419,36 +4416,36 @@
       <c r="X33" s="3">
         <v>1</v>
       </c>
-      <c r="Y33" s="57">
+      <c r="Y33" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" spans="1:25">
-      <c r="A34" s="50">
+      <c r="A34" s="49">
         <v>20010012</v>
       </c>
       <c r="B34" s="3">
         <v>200100</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="50">
         <v>200100038</v>
       </c>
-      <c r="E34" s="51" t="s">
+      <c r="E34" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="60" t="s">
+      <c r="F34" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="53" t="s">
+      <c r="G34" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="51">
+      <c r="H34" s="50">
         <v>3</v>
       </c>
-      <c r="I34" s="51">
+      <c r="I34" s="50">
         <v>1980000</v>
       </c>
       <c r="J34" s="36" t="s">
@@ -4460,7 +4457,7 @@
       <c r="L34" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M34" s="54" t="s">
+      <c r="M34" s="53" t="s">
         <v>56</v>
       </c>
       <c r="N34" s="4">
@@ -4478,13 +4475,13 @@
       <c r="R34" s="3">
         <v>15000</v>
       </c>
-      <c r="S34" s="55">
+      <c r="S34" s="54">
         <v>16008</v>
       </c>
-      <c r="T34" s="50">
+      <c r="T34" s="49">
         <v>48</v>
       </c>
-      <c r="U34" s="56">
+      <c r="U34" s="55">
         <v>0</v>
       </c>
       <c r="V34" t="s">
@@ -4496,12 +4493,12 @@
       <c r="X34" s="3">
         <v>1</v>
       </c>
-      <c r="Y34" s="57">
+      <c r="Y34" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" spans="1:25">
-      <c r="A35" s="50">
+      <c r="A35" s="49">
         <v>20010110</v>
       </c>
       <c r="B35" s="3">
@@ -4516,16 +4513,16 @@
       <c r="E35" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="61" t="s">
+      <c r="F35" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="53" t="s">
+      <c r="G35" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H35" s="3">
         <v>1</v>
       </c>
-      <c r="I35" s="51">
+      <c r="I35" s="50">
         <v>1980000</v>
       </c>
       <c r="J35" s="36" t="s">
@@ -4537,7 +4534,7 @@
       <c r="L35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M35" s="54" t="s">
+      <c r="M35" s="53" t="s">
         <v>69</v>
       </c>
       <c r="N35" s="4">
@@ -4558,10 +4555,10 @@
       <c r="S35" s="3">
         <v>16008</v>
       </c>
-      <c r="T35" s="50">
+      <c r="T35" s="49">
         <v>48</v>
       </c>
-      <c r="U35" s="56">
+      <c r="U35" s="55">
         <v>0</v>
       </c>
       <c r="V35" t="s">
@@ -4573,12 +4570,12 @@
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="57">
+      <c r="Y35" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:25">
-      <c r="A36" s="50">
+      <c r="A36" s="49">
         <v>20010111</v>
       </c>
       <c r="B36" s="3">
@@ -4593,16 +4590,16 @@
       <c r="E36" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="61" t="s">
+      <c r="F36" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="53" t="s">
+      <c r="G36" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H36" s="3">
         <v>2</v>
       </c>
-      <c r="I36" s="51">
+      <c r="I36" s="50">
         <v>1980000</v>
       </c>
       <c r="J36" s="41" t="s">
@@ -4614,7 +4611,7 @@
       <c r="L36" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M36" s="54" t="s">
+      <c r="M36" s="53" t="s">
         <v>69</v>
       </c>
       <c r="N36" s="4">
@@ -4635,10 +4632,10 @@
       <c r="S36" s="3">
         <v>16008</v>
       </c>
-      <c r="T36" s="50">
+      <c r="T36" s="49">
         <v>48</v>
       </c>
-      <c r="U36" s="56">
+      <c r="U36" s="55">
         <v>0</v>
       </c>
       <c r="V36" t="s">
@@ -4650,12 +4647,12 @@
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="57">
+      <c r="Y36" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:25">
-      <c r="A37" s="50">
+      <c r="A37" s="49">
         <v>20010112</v>
       </c>
       <c r="B37" s="3">
@@ -4670,16 +4667,16 @@
       <c r="E37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="61" t="s">
+      <c r="F37" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="53" t="s">
+      <c r="G37" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H37" s="3">
         <v>3</v>
       </c>
-      <c r="I37" s="51">
+      <c r="I37" s="50">
         <v>1980000</v>
       </c>
       <c r="J37" s="36" t="s">
@@ -4691,7 +4688,7 @@
       <c r="L37" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M37" s="54" t="s">
+      <c r="M37" s="53" t="s">
         <v>69</v>
       </c>
       <c r="N37" s="4">
@@ -4712,10 +4709,10 @@
       <c r="S37" s="3">
         <v>16008</v>
       </c>
-      <c r="T37" s="50">
+      <c r="T37" s="49">
         <v>48</v>
       </c>
-      <c r="U37" s="56">
+      <c r="U37" s="55">
         <v>0</v>
       </c>
       <c r="V37" t="s">
@@ -4727,12 +4724,12 @@
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="57">
+      <c r="Y37" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:25">
-      <c r="A38" s="50">
+      <c r="A38" s="49">
         <v>20030010</v>
       </c>
       <c r="B38" s="3">
@@ -4747,16 +4744,16 @@
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="61" t="s">
+      <c r="F38" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="53" t="s">
+      <c r="G38" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="51">
+      <c r="I38" s="50">
         <v>1980000</v>
       </c>
       <c r="J38" s="36" t="s">
@@ -4768,7 +4765,7 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="54" t="s">
+      <c r="M38" s="53" t="s">
         <v>71</v>
       </c>
       <c r="N38" s="4">
@@ -4789,10 +4786,10 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="50">
+      <c r="T38" s="49">
         <v>50</v>
       </c>
-      <c r="U38" s="56">
+      <c r="U38" s="55">
         <v>0</v>
       </c>
       <c r="V38" t="s">
@@ -4804,12 +4801,12 @@
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="57">
+      <c r="Y38" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:25">
-      <c r="A39" s="50">
+      <c r="A39" s="49">
         <v>20030011</v>
       </c>
       <c r="B39" s="3">
@@ -4824,16 +4821,16 @@
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="61" t="s">
+      <c r="F39" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="53" t="s">
+      <c r="G39" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="51">
+      <c r="I39" s="50">
         <v>1980000</v>
       </c>
       <c r="J39" s="41" t="s">
@@ -4845,7 +4842,7 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="54" t="s">
+      <c r="M39" s="53" t="s">
         <v>71</v>
       </c>
       <c r="N39" s="4">
@@ -4866,10 +4863,10 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="50">
+      <c r="T39" s="49">
         <v>50</v>
       </c>
-      <c r="U39" s="56">
+      <c r="U39" s="55">
         <v>0</v>
       </c>
       <c r="V39" t="s">
@@ -4881,12 +4878,12 @@
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="57">
+      <c r="Y39" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:25">
-      <c r="A40" s="50">
+      <c r="A40" s="49">
         <v>20030012</v>
       </c>
       <c r="B40" s="3">
@@ -4901,28 +4898,28 @@
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="61" t="s">
+      <c r="F40" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="53" t="s">
+      <c r="G40" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="51">
+      <c r="I40" s="50">
         <v>1980000</v>
       </c>
       <c r="J40" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K40" s="58">
-        <v>0</v>
-      </c>
-      <c r="L40" s="58" t="s">
+      <c r="K40" s="57">
+        <v>0</v>
+      </c>
+      <c r="L40" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="54" t="s">
+      <c r="M40" s="53" t="s">
         <v>71</v>
       </c>
       <c r="N40" s="4">
@@ -4931,22 +4928,22 @@
       <c r="O40" s="3">
         <v>300</v>
       </c>
-      <c r="P40" s="58">
+      <c r="P40" s="57">
         <v>180000</v>
       </c>
-      <c r="Q40" s="58">
+      <c r="Q40" s="57">
         <v>16000</v>
       </c>
-      <c r="R40" s="58">
+      <c r="R40" s="57">
         <v>15000</v>
       </c>
-      <c r="S40" s="58">
+      <c r="S40" s="57">
         <v>16008</v>
       </c>
-      <c r="T40" s="50">
+      <c r="T40" s="49">
         <v>50</v>
       </c>
-      <c r="U40" s="56">
+      <c r="U40" s="55">
         <v>0</v>
       </c>
       <c r="V40" t="s">
@@ -4958,12 +4955,12 @@
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="57">
+      <c r="Y40" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:25">
-      <c r="A41" s="50">
+      <c r="A41" s="49">
         <v>20040010</v>
       </c>
       <c r="B41" s="3">
@@ -4978,28 +4975,28 @@
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="61" t="s">
+      <c r="F41" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="53" t="s">
+      <c r="G41" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="51">
+      <c r="I41" s="50">
         <v>1980000</v>
       </c>
       <c r="J41" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K41" s="58">
-        <v>0</v>
-      </c>
-      <c r="L41" s="58" t="s">
+      <c r="K41" s="57">
+        <v>0</v>
+      </c>
+      <c r="L41" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="54" t="s">
+      <c r="M41" s="53" t="s">
         <v>73</v>
       </c>
       <c r="N41" s="4">
@@ -5008,22 +5005,22 @@
       <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="58">
+      <c r="P41" s="57">
         <v>180000</v>
       </c>
-      <c r="Q41" s="58">
+      <c r="Q41" s="57">
         <v>16000</v>
       </c>
-      <c r="R41" s="58">
+      <c r="R41" s="57">
         <v>15000</v>
       </c>
-      <c r="S41" s="58">
+      <c r="S41" s="57">
         <v>16008</v>
       </c>
-      <c r="T41" s="50">
+      <c r="T41" s="49">
         <v>50</v>
       </c>
-      <c r="U41" s="56">
+      <c r="U41" s="55">
         <v>0</v>
       </c>
       <c r="V41" t="s">
@@ -5035,12 +5032,12 @@
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="57">
+      <c r="Y41" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:25">
-      <c r="A42" s="50">
+      <c r="A42" s="49">
         <v>20040011</v>
       </c>
       <c r="B42" s="3">
@@ -5055,28 +5052,28 @@
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="61" t="s">
+      <c r="F42" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="53" t="s">
+      <c r="G42" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="51">
+      <c r="I42" s="50">
         <v>1980000</v>
       </c>
       <c r="J42" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K42" s="58">
-        <v>0</v>
-      </c>
-      <c r="L42" s="58" t="s">
+      <c r="K42" s="57">
+        <v>0</v>
+      </c>
+      <c r="L42" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="54" t="s">
+      <c r="M42" s="53" t="s">
         <v>73</v>
       </c>
       <c r="N42" s="4">
@@ -5085,22 +5082,22 @@
       <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="58">
+      <c r="P42" s="57">
         <v>180000</v>
       </c>
-      <c r="Q42" s="58">
+      <c r="Q42" s="57">
         <v>16000</v>
       </c>
-      <c r="R42" s="58">
+      <c r="R42" s="57">
         <v>15000</v>
       </c>
-      <c r="S42" s="58">
+      <c r="S42" s="57">
         <v>16008</v>
       </c>
-      <c r="T42" s="50">
+      <c r="T42" s="49">
         <v>50</v>
       </c>
-      <c r="U42" s="56">
+      <c r="U42" s="55">
         <v>0</v>
       </c>
       <c r="V42" t="s">
@@ -5112,12 +5109,12 @@
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="57">
+      <c r="Y42" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:25">
-      <c r="A43" s="50">
+      <c r="A43" s="49">
         <v>20040012</v>
       </c>
       <c r="B43" s="3">
@@ -5132,28 +5129,28 @@
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="61" t="s">
+      <c r="F43" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="53" t="s">
+      <c r="G43" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="51">
+      <c r="I43" s="50">
         <v>1980000</v>
       </c>
       <c r="J43" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K43" s="58">
-        <v>0</v>
-      </c>
-      <c r="L43" s="58" t="s">
+      <c r="K43" s="57">
+        <v>0</v>
+      </c>
+      <c r="L43" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="54" t="s">
+      <c r="M43" s="53" t="s">
         <v>73</v>
       </c>
       <c r="N43" s="4">
@@ -5162,22 +5159,22 @@
       <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="58">
+      <c r="P43" s="57">
         <v>180000</v>
       </c>
-      <c r="Q43" s="58">
+      <c r="Q43" s="57">
         <v>16000</v>
       </c>
-      <c r="R43" s="58">
+      <c r="R43" s="57">
         <v>15000</v>
       </c>
-      <c r="S43" s="58">
+      <c r="S43" s="57">
         <v>16008</v>
       </c>
-      <c r="T43" s="50">
+      <c r="T43" s="49">
         <v>50</v>
       </c>
-      <c r="U43" s="56">
+      <c r="U43" s="55">
         <v>0</v>
       </c>
       <c r="V43" t="s">
@@ -5189,12 +5186,12 @@
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="57">
+      <c r="Y43" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:25">
-      <c r="A44" s="50">
+      <c r="A44" s="49">
         <v>20050010</v>
       </c>
       <c r="B44" s="3">
@@ -5209,28 +5206,28 @@
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="53" t="s">
+      <c r="G44" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="51">
+      <c r="I44" s="50">
         <v>1980000</v>
       </c>
       <c r="J44" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K44" s="58">
-        <v>1</v>
-      </c>
-      <c r="L44" s="58" t="s">
+      <c r="K44" s="57">
+        <v>1</v>
+      </c>
+      <c r="L44" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="M44" s="54" t="s">
+      <c r="M44" s="53" t="s">
         <v>75</v>
       </c>
       <c r="N44" s="4">
@@ -5239,22 +5236,22 @@
       <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="58">
+      <c r="P44" s="57">
         <v>180000</v>
       </c>
-      <c r="Q44" s="58">
+      <c r="Q44" s="57">
         <v>16000</v>
       </c>
-      <c r="R44" s="58">
+      <c r="R44" s="57">
         <v>15000</v>
       </c>
-      <c r="S44" s="58">
+      <c r="S44" s="57">
         <v>16008</v>
       </c>
-      <c r="T44" s="50">
+      <c r="T44" s="49">
         <v>48</v>
       </c>
-      <c r="U44" s="50">
+      <c r="U44" s="49">
         <v>0</v>
       </c>
       <c r="V44" t="s">
@@ -5266,12 +5263,12 @@
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="57">
+      <c r="Y44" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:25">
-      <c r="A45" s="50">
+      <c r="A45" s="49">
         <v>20050011</v>
       </c>
       <c r="B45" s="3">
@@ -5286,28 +5283,28 @@
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="61" t="s">
+      <c r="F45" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="53" t="s">
+      <c r="G45" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="51">
+      <c r="I45" s="50">
         <v>1980000</v>
       </c>
       <c r="J45" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K45" s="58">
-        <v>1</v>
-      </c>
-      <c r="L45" s="58" t="s">
+      <c r="K45" s="57">
+        <v>1</v>
+      </c>
+      <c r="L45" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="M45" s="54" t="s">
+      <c r="M45" s="53" t="s">
         <v>75</v>
       </c>
       <c r="N45" s="4">
@@ -5316,22 +5313,22 @@
       <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="58">
+      <c r="P45" s="57">
         <v>180000</v>
       </c>
-      <c r="Q45" s="58">
+      <c r="Q45" s="57">
         <v>16000</v>
       </c>
-      <c r="R45" s="58">
+      <c r="R45" s="57">
         <v>15000</v>
       </c>
-      <c r="S45" s="58">
+      <c r="S45" s="57">
         <v>16008</v>
       </c>
-      <c r="T45" s="50">
+      <c r="T45" s="49">
         <v>48</v>
       </c>
-      <c r="U45" s="50">
+      <c r="U45" s="49">
         <v>0</v>
       </c>
       <c r="V45" t="s">
@@ -5343,12 +5340,12 @@
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="57">
+      <c r="Y45" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:25">
-      <c r="A46" s="50">
+      <c r="A46" s="49">
         <v>20050012</v>
       </c>
       <c r="B46" s="3">
@@ -5363,28 +5360,28 @@
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="61" t="s">
+      <c r="F46" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="53" t="s">
+      <c r="G46" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="51">
+      <c r="I46" s="50">
         <v>1980000</v>
       </c>
       <c r="J46" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K46" s="58">
-        <v>1</v>
-      </c>
-      <c r="L46" s="58" t="s">
+      <c r="K46" s="57">
+        <v>1</v>
+      </c>
+      <c r="L46" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="M46" s="54" t="s">
+      <c r="M46" s="53" t="s">
         <v>75</v>
       </c>
       <c r="N46" s="4">
@@ -5393,22 +5390,22 @@
       <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="58">
+      <c r="P46" s="57">
         <v>180000</v>
       </c>
-      <c r="Q46" s="58">
+      <c r="Q46" s="57">
         <v>16000</v>
       </c>
-      <c r="R46" s="58">
+      <c r="R46" s="57">
         <v>15000</v>
       </c>
-      <c r="S46" s="58">
+      <c r="S46" s="57">
         <v>16008</v>
       </c>
-      <c r="T46" s="50">
+      <c r="T46" s="49">
         <v>48</v>
       </c>
-      <c r="U46" s="50">
+      <c r="U46" s="49">
         <v>0</v>
       </c>
       <c r="V46" t="s">
@@ -5420,12 +5417,12 @@
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="57">
+      <c r="Y46" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:25">
-      <c r="A47" s="50">
+      <c r="A47" s="49">
         <v>20060010</v>
       </c>
       <c r="B47" s="3">
@@ -5440,28 +5437,28 @@
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="61" t="s">
+      <c r="F47" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="53" t="s">
+      <c r="G47" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="51">
+      <c r="I47" s="50">
         <v>1980000</v>
       </c>
       <c r="J47" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K47" s="58">
-        <v>0</v>
-      </c>
-      <c r="L47" s="58" t="s">
+      <c r="K47" s="57">
+        <v>0</v>
+      </c>
+      <c r="L47" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M47" s="54" t="s">
+      <c r="M47" s="53" t="s">
         <v>77</v>
       </c>
       <c r="N47" s="4">
@@ -5470,22 +5467,22 @@
       <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="58">
+      <c r="P47" s="57">
         <v>180000</v>
       </c>
-      <c r="Q47" s="58">
+      <c r="Q47" s="57">
         <v>16000</v>
       </c>
-      <c r="R47" s="58">
+      <c r="R47" s="57">
         <v>15000</v>
       </c>
-      <c r="S47" s="58">
+      <c r="S47" s="57">
         <v>16008</v>
       </c>
-      <c r="T47" s="50">
+      <c r="T47" s="49">
         <v>20</v>
       </c>
-      <c r="U47" s="50">
+      <c r="U47" s="49">
         <v>0</v>
       </c>
       <c r="V47" t="s">
@@ -5497,12 +5494,12 @@
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="57">
+      <c r="Y47" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:25">
-      <c r="A48" s="50">
+      <c r="A48" s="49">
         <v>20060011</v>
       </c>
       <c r="B48" s="3">
@@ -5517,28 +5514,28 @@
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="61" t="s">
+      <c r="F48" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="53" t="s">
+      <c r="G48" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="51">
+      <c r="I48" s="50">
         <v>1980000</v>
       </c>
       <c r="J48" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K48" s="58">
-        <v>0</v>
-      </c>
-      <c r="L48" s="58" t="s">
+      <c r="K48" s="57">
+        <v>0</v>
+      </c>
+      <c r="L48" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="M48" s="54" t="s">
+      <c r="M48" s="53" t="s">
         <v>77</v>
       </c>
       <c r="N48" s="4">
@@ -5547,22 +5544,22 @@
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="58">
+      <c r="P48" s="57">
         <v>180000</v>
       </c>
-      <c r="Q48" s="58">
+      <c r="Q48" s="57">
         <v>16000</v>
       </c>
-      <c r="R48" s="58">
+      <c r="R48" s="57">
         <v>15000</v>
       </c>
-      <c r="S48" s="58">
+      <c r="S48" s="57">
         <v>16008</v>
       </c>
-      <c r="T48" s="50">
+      <c r="T48" s="49">
         <v>20</v>
       </c>
-      <c r="U48" s="50">
+      <c r="U48" s="49">
         <v>0</v>
       </c>
       <c r="V48" t="s">
@@ -5574,12 +5571,12 @@
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="57">
+      <c r="Y48" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:25">
-      <c r="A49" s="50">
+      <c r="A49" s="49">
         <v>20060012</v>
       </c>
       <c r="B49" s="3">
@@ -5594,16 +5591,16 @@
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="61" t="s">
+      <c r="F49" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="53" t="s">
+      <c r="G49" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="51">
+      <c r="I49" s="50">
         <v>1980000</v>
       </c>
       <c r="J49" s="36" t="s">
@@ -5615,7 +5612,7 @@
       <c r="L49" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M49" s="54" t="s">
+      <c r="M49" s="53" t="s">
         <v>77</v>
       </c>
       <c r="N49" s="4">
@@ -5636,10 +5633,10 @@
       <c r="S49" s="3">
         <v>16008</v>
       </c>
-      <c r="T49" s="50">
+      <c r="T49" s="49">
         <v>20</v>
       </c>
-      <c r="U49" s="50">
+      <c r="U49" s="49">
         <v>0</v>
       </c>
       <c r="V49" t="s">
@@ -5651,12 +5648,12 @@
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="57">
+      <c r="Y49" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:25">
-      <c r="A50" s="50">
+      <c r="A50" s="49">
         <v>20070010</v>
       </c>
       <c r="B50" s="3">
@@ -5671,16 +5668,16 @@
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="61" t="s">
+      <c r="F50" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="53" t="s">
+      <c r="G50" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="51">
+      <c r="I50" s="50">
         <v>1980000</v>
       </c>
       <c r="J50" s="36" t="s">
@@ -5692,7 +5689,7 @@
       <c r="L50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="54" t="s">
+      <c r="M50" s="53" t="s">
         <v>79</v>
       </c>
       <c r="N50" s="4">
@@ -5713,10 +5710,10 @@
       <c r="S50" s="3">
         <v>16008</v>
       </c>
-      <c r="T50" s="50">
+      <c r="T50" s="49">
         <v>30</v>
       </c>
-      <c r="U50" s="50">
+      <c r="U50" s="49">
         <v>1</v>
       </c>
       <c r="V50" t="s">
@@ -5728,12 +5725,12 @@
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="57">
+      <c r="Y50" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:25">
-      <c r="A51" s="50">
+      <c r="A51" s="49">
         <v>20070011</v>
       </c>
       <c r="B51" s="3">
@@ -5748,16 +5745,16 @@
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="61" t="s">
+      <c r="F51" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="53" t="s">
+      <c r="G51" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="51">
+      <c r="I51" s="50">
         <v>1980000</v>
       </c>
       <c r="J51" s="41" t="s">
@@ -5769,7 +5766,7 @@
       <c r="L51" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="54" t="s">
+      <c r="M51" s="53" t="s">
         <v>79</v>
       </c>
       <c r="N51" s="4">
@@ -5790,10 +5787,10 @@
       <c r="S51" s="3">
         <v>16008</v>
       </c>
-      <c r="T51" s="50">
+      <c r="T51" s="49">
         <v>30</v>
       </c>
-      <c r="U51" s="50">
+      <c r="U51" s="49">
         <v>1</v>
       </c>
       <c r="V51" t="s">
@@ -5805,12 +5802,12 @@
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="57">
+      <c r="Y51" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:25">
-      <c r="A52" s="50">
+      <c r="A52" s="49">
         <v>20070012</v>
       </c>
       <c r="B52" s="3">
@@ -5825,16 +5822,16 @@
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="61" t="s">
+      <c r="F52" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="53" t="s">
+      <c r="G52" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="51">
+      <c r="I52" s="50">
         <v>1980000</v>
       </c>
       <c r="J52" s="36" t="s">
@@ -5846,7 +5843,7 @@
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="54" t="s">
+      <c r="M52" s="53" t="s">
         <v>79</v>
       </c>
       <c r="N52" s="4">
@@ -5867,10 +5864,10 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="50">
+      <c r="T52" s="49">
         <v>30</v>
       </c>
-      <c r="U52" s="50">
+      <c r="U52" s="49">
         <v>1</v>
       </c>
       <c r="V52" t="s">
@@ -5882,12 +5879,12 @@
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="57">
+      <c r="Y52" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:25">
-      <c r="A53" s="50">
+      <c r="A53" s="49">
         <v>20080010</v>
       </c>
       <c r="B53" s="3">
@@ -5902,16 +5899,16 @@
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="61" t="s">
+      <c r="F53" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="53" t="s">
+      <c r="G53" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="51">
+      <c r="I53" s="50">
         <v>1980000</v>
       </c>
       <c r="J53" s="36" t="s">
@@ -5923,7 +5920,7 @@
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="54" t="s">
+      <c r="M53" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N53" s="4">
@@ -5944,10 +5941,10 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="50">
+      <c r="T53" s="49">
         <v>20</v>
       </c>
-      <c r="U53" s="50">
+      <c r="U53" s="49">
         <v>0</v>
       </c>
       <c r="V53" t="s">
@@ -5959,12 +5956,12 @@
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="57">
+      <c r="Y53" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:25">
-      <c r="A54" s="50">
+      <c r="A54" s="49">
         <v>20080011</v>
       </c>
       <c r="B54" s="3">
@@ -5979,16 +5976,16 @@
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="61" t="s">
+      <c r="F54" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="53" t="s">
+      <c r="G54" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="51">
+      <c r="I54" s="50">
         <v>1980000</v>
       </c>
       <c r="J54" s="41" t="s">
@@ -6000,7 +5997,7 @@
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="54" t="s">
+      <c r="M54" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N54" s="4">
@@ -6021,10 +6018,10 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="50">
+      <c r="T54" s="49">
         <v>20</v>
       </c>
-      <c r="U54" s="50">
+      <c r="U54" s="49">
         <v>0</v>
       </c>
       <c r="V54" t="s">
@@ -6036,12 +6033,12 @@
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="57">
+      <c r="Y54" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" spans="1:25">
-      <c r="A55" s="50">
+      <c r="A55" s="49">
         <v>20080012</v>
       </c>
       <c r="B55" s="3">
@@ -6056,16 +6053,16 @@
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="61" t="s">
+      <c r="F55" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="53" t="s">
+      <c r="G55" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="51">
+      <c r="I55" s="50">
         <v>1980000</v>
       </c>
       <c r="J55" s="36" t="s">
@@ -6077,7 +6074,7 @@
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="54" t="s">
+      <c r="M55" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N55" s="4">
@@ -6098,10 +6095,10 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="50">
+      <c r="T55" s="49">
         <v>20</v>
       </c>
-      <c r="U55" s="50">
+      <c r="U55" s="49">
         <v>0</v>
       </c>
       <c r="V55" t="s">
@@ -6113,12 +6110,12 @@
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="57">
+      <c r="Y55" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" spans="1:25">
-      <c r="A56" s="50">
+      <c r="A56" s="49">
         <v>20090010</v>
       </c>
       <c r="B56" s="3">
@@ -6133,16 +6130,16 @@
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="61" t="s">
+      <c r="F56" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="53" t="s">
+      <c r="G56" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="51">
+      <c r="I56" s="50">
         <v>1980000</v>
       </c>
       <c r="J56" s="36" t="s">
@@ -6154,7 +6151,7 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="54" t="s">
+      <c r="M56" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N56" s="4">
@@ -6175,10 +6172,10 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="50">
+      <c r="T56" s="49">
         <v>20</v>
       </c>
-      <c r="U56" s="50">
+      <c r="U56" s="49">
         <v>0</v>
       </c>
       <c r="V56" t="s">
@@ -6190,12 +6187,12 @@
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="57">
+      <c r="Y56" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:25">
-      <c r="A57" s="50">
+      <c r="A57" s="49">
         <v>20090011</v>
       </c>
       <c r="B57" s="3">
@@ -6210,16 +6207,16 @@
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="61" t="s">
+      <c r="F57" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="53" t="s">
+      <c r="G57" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="51">
+      <c r="I57" s="50">
         <v>1980000</v>
       </c>
       <c r="J57" s="41" t="s">
@@ -6231,7 +6228,7 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="54" t="s">
+      <c r="M57" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N57" s="4">
@@ -6252,10 +6249,10 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="50">
+      <c r="T57" s="49">
         <v>20</v>
       </c>
-      <c r="U57" s="50">
+      <c r="U57" s="49">
         <v>0</v>
       </c>
       <c r="V57" t="s">
@@ -6267,12 +6264,12 @@
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="57">
+      <c r="Y57" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:25">
-      <c r="A58" s="50">
+      <c r="A58" s="49">
         <v>20090012</v>
       </c>
       <c r="B58" s="3">
@@ -6287,16 +6284,16 @@
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="53" t="s">
+      <c r="G58" s="52" t="s">
         <v>83</v>
       </c>
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="51">
+      <c r="I58" s="50">
         <v>1980000</v>
       </c>
       <c r="J58" s="36" t="s">
@@ -6308,7 +6305,7 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="54" t="s">
+      <c r="M58" s="53" t="s">
         <v>81</v>
       </c>
       <c r="N58" s="4">
@@ -6329,10 +6326,10 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="50">
+      <c r="T58" s="49">
         <v>20</v>
       </c>
-      <c r="U58" s="50">
+      <c r="U58" s="49">
         <v>0</v>
       </c>
       <c r="V58" t="s">
@@ -6344,7 +6341,7 @@
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="57">
+      <c r="Y58" s="56">
         <v>0</v>
       </c>
     </row>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -330,7 +330,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="109">
   <si>
     <t>游戏ID</t>
   </si>
@@ -584,13 +584,79 @@
     <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
   </si>
   <si>
-    <t>1980000_500000</t>
-  </si>
-  <si>
-    <t>1980000_5000000</t>
-  </si>
-  <si>
-    <t>1980000_50000000</t>
+    <t>1980000_10000</t>
+  </si>
+  <si>
+    <t>1980000_100000</t>
+  </si>
+  <si>
+    <t>1980000_1000000</t>
+  </si>
+  <si>
+    <t>1980000_8000</t>
+  </si>
+  <si>
+    <t>1980000_80000</t>
+  </si>
+  <si>
+    <t>1980000_800000</t>
+  </si>
+  <si>
+    <t>1980000_12000</t>
+  </si>
+  <si>
+    <t>1980000_120000</t>
+  </si>
+  <si>
+    <t>1980000_1200000</t>
+  </si>
+  <si>
+    <t>1980000_40000</t>
+  </si>
+  <si>
+    <t>1980000_400000</t>
+  </si>
+  <si>
+    <t>1980000_4000000</t>
+  </si>
+  <si>
+    <t>1980000_11000</t>
+  </si>
+  <si>
+    <t>1980000_110000</t>
+  </si>
+  <si>
+    <t>1980000_1100000</t>
+  </si>
+  <si>
+    <t>1980000_65000</t>
+  </si>
+  <si>
+    <t>1980000_650000</t>
+  </si>
+  <si>
+    <t>1980000_6500000</t>
+  </si>
+  <si>
+    <t>1980000_16000</t>
+  </si>
+  <si>
+    <t>1980000_160000</t>
+  </si>
+  <si>
+    <t>1980000_1600000</t>
+  </si>
+  <si>
+    <t>1980000_1000</t>
+  </si>
+  <si>
+    <t>1980000_3000</t>
+  </si>
+  <si>
+    <t>1980000_30000</t>
+  </si>
+  <si>
+    <t>1980000_300000</t>
   </si>
 </sst>
 </file>
@@ -3600,7 +3666,7 @@
         <v>9500</v>
       </c>
       <c r="O23" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P23" s="4">
         <v>180000</v>
@@ -3679,7 +3745,7 @@
         <v>9500</v>
       </c>
       <c r="O24" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P24" s="4">
         <v>180000</v>
@@ -3758,7 +3824,7 @@
         <v>9500</v>
       </c>
       <c r="O25" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P25" s="4">
         <v>180000</v>
@@ -4339,9 +4405,7 @@
       <c r="X32" s="3">
         <v>1</v>
       </c>
-      <c r="Y32" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y32" s="56"/>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:25">
       <c r="A33" s="49">
@@ -4416,9 +4480,7 @@
       <c r="X33" s="3">
         <v>1</v>
       </c>
-      <c r="Y33" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y33" s="56"/>
     </row>
     <row r="34" s="3" customFormat="1" spans="1:25">
       <c r="A34" s="49">
@@ -4493,9 +4555,7 @@
       <c r="X34" s="3">
         <v>1</v>
       </c>
-      <c r="Y34" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y34" s="56"/>
     </row>
     <row r="35" s="3" customFormat="1" spans="1:25">
       <c r="A35" s="49">
@@ -4565,14 +4625,12 @@
         <v>57</v>
       </c>
       <c r="W35" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y35" s="56"/>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:25">
       <c r="A36" s="49">
@@ -4642,14 +4700,12 @@
         <v>61</v>
       </c>
       <c r="W36" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y36" s="56"/>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:25">
       <c r="A37" s="49">
@@ -4719,14 +4775,12 @@
         <v>65</v>
       </c>
       <c r="W37" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y37" s="56"/>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:25">
       <c r="A38" s="49">
@@ -4796,14 +4850,12 @@
         <v>57</v>
       </c>
       <c r="W38" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y38" s="56"/>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:25">
       <c r="A39" s="49">
@@ -4873,14 +4925,12 @@
         <v>61</v>
       </c>
       <c r="W39" s="8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y39" s="56"/>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:25">
       <c r="A40" s="49">
@@ -4950,14 +5000,12 @@
         <v>65</v>
       </c>
       <c r="W40" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y40" s="56"/>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:25">
       <c r="A41" s="49">
@@ -5027,14 +5075,12 @@
         <v>57</v>
       </c>
       <c r="W41" s="8" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y41" s="56"/>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:25">
       <c r="A42" s="49">
@@ -5104,14 +5150,12 @@
         <v>61</v>
       </c>
       <c r="W42" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y42" s="56"/>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:25">
       <c r="A43" s="49">
@@ -5181,14 +5225,12 @@
         <v>65</v>
       </c>
       <c r="W43" s="8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y43" s="56"/>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:25">
       <c r="A44" s="49">
@@ -5258,14 +5300,12 @@
         <v>57</v>
       </c>
       <c r="W44" s="8" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y44" s="56"/>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:25">
       <c r="A45" s="49">
@@ -5335,14 +5375,12 @@
         <v>61</v>
       </c>
       <c r="W45" s="8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y45" s="56"/>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:25">
       <c r="A46" s="49">
@@ -5412,14 +5450,12 @@
         <v>65</v>
       </c>
       <c r="W46" s="8" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y46" s="56"/>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:25">
       <c r="A47" s="49">
@@ -5489,14 +5525,12 @@
         <v>57</v>
       </c>
       <c r="W47" s="8" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y47" s="56"/>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:25">
       <c r="A48" s="49">
@@ -5566,14 +5600,12 @@
         <v>61</v>
       </c>
       <c r="W48" s="8" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y48" s="56"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:25">
       <c r="A49" s="49">
@@ -5643,14 +5675,12 @@
         <v>65</v>
       </c>
       <c r="W49" s="8" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y49" s="56"/>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:25">
       <c r="A50" s="49">
@@ -5696,7 +5726,7 @@
         <v>9500</v>
       </c>
       <c r="O50" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P50" s="3">
         <v>180000</v>
@@ -5720,14 +5750,12 @@
         <v>57</v>
       </c>
       <c r="W50" s="8" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y50" s="56"/>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:25">
       <c r="A51" s="49">
@@ -5773,7 +5801,7 @@
         <v>9500</v>
       </c>
       <c r="O51" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P51" s="3">
         <v>180000</v>
@@ -5797,14 +5825,12 @@
         <v>61</v>
       </c>
       <c r="W51" s="8" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y51" s="56"/>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:25">
       <c r="A52" s="49">
@@ -5850,7 +5876,7 @@
         <v>9500</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>180000</v>
@@ -5874,14 +5900,12 @@
         <v>65</v>
       </c>
       <c r="W52" s="8" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y52" s="56"/>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:25">
       <c r="A53" s="49">
@@ -5951,14 +5975,12 @@
         <v>57</v>
       </c>
       <c r="W53" s="8" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y53" s="56"/>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:25">
       <c r="A54" s="49">
@@ -6028,14 +6050,12 @@
         <v>61</v>
       </c>
       <c r="W54" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y54" s="56"/>
     </row>
     <row r="55" s="3" customFormat="1" spans="1:25">
       <c r="A55" s="49">
@@ -6105,14 +6125,12 @@
         <v>65</v>
       </c>
       <c r="W55" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y55" s="56"/>
     </row>
     <row r="56" s="3" customFormat="1" spans="1:25">
       <c r="A56" s="49">
@@ -6182,14 +6200,12 @@
         <v>57</v>
       </c>
       <c r="W56" s="8" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y56" s="56"/>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:25">
       <c r="A57" s="49">
@@ -6259,14 +6275,12 @@
         <v>61</v>
       </c>
       <c r="W57" s="8" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y57" s="56"/>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:25">
       <c r="A58" s="49">
@@ -6336,14 +6350,12 @@
         <v>65</v>
       </c>
       <c r="W58" s="8" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="X58" s="3">
         <v>1</v>
       </c>
-      <c r="Y58" s="56">
-        <v>0</v>
-      </c>
+      <c r="Y58" s="56"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S58" etc:filterBottomFollowUsedRange="0">

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -330,7 +330,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="111">
   <si>
     <t>游戏ID</t>
   </si>
@@ -579,6 +579,12 @@
   </si>
   <si>
     <t>鱼虾蟹</t>
+  </si>
+  <si>
+    <t>俄罗斯轮盘</t>
+  </si>
+  <si>
+    <t>3000,16000,8000,0</t>
   </si>
   <si>
     <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
@@ -1400,7 +1406,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1563,6 +1569,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1936,7 +1945,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y58"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.375" style="4"/>
@@ -2216,7 +2225,7 @@
       <c r="E5" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G5" s="34" t="s">
@@ -2295,7 +2304,7 @@
       <c r="E6" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="F6" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G6" s="34" t="s">
@@ -2374,7 +2383,7 @@
       <c r="E7" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G7" s="34" t="s">
@@ -2453,7 +2462,7 @@
       <c r="E8" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="34" t="s">
@@ -2532,7 +2541,7 @@
       <c r="E9" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G9" s="34" t="s">
@@ -2611,7 +2620,7 @@
       <c r="E10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G10" s="34" t="s">
@@ -2690,7 +2699,7 @@
       <c r="E11" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="58" t="s">
+      <c r="F11" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G11" s="34" t="s">
@@ -2769,7 +2778,7 @@
       <c r="E12" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G12" s="34" t="s">
@@ -2848,7 +2857,7 @@
       <c r="E13" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="58" t="s">
+      <c r="F13" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G13" s="34" t="s">
@@ -2927,7 +2936,7 @@
       <c r="E14" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G14" s="34" t="s">
@@ -3006,7 +3015,7 @@
       <c r="E15" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="34" t="s">
@@ -3085,7 +3094,7 @@
       <c r="E16" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G16" s="34" t="s">
@@ -3164,7 +3173,7 @@
       <c r="E17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="58" t="s">
+      <c r="F17" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G17" s="34" t="s">
@@ -3243,7 +3252,7 @@
       <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G18" s="34" t="s">
@@ -3322,7 +3331,7 @@
       <c r="E19" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="F19" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G19" s="34" t="s">
@@ -3401,7 +3410,7 @@
       <c r="E20" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="58" t="s">
+      <c r="F20" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G20" s="34" t="s">
@@ -3480,7 +3489,7 @@
       <c r="E21" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="58" t="s">
+      <c r="F21" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G21" s="34" t="s">
@@ -3559,7 +3568,7 @@
       <c r="E22" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="58" t="s">
+      <c r="F22" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G22" s="34" t="s">
@@ -3638,7 +3647,7 @@
       <c r="E23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="58" t="s">
+      <c r="F23" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="34" t="s">
@@ -3717,7 +3726,7 @@
       <c r="E24" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="58" t="s">
+      <c r="F24" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G24" s="34" t="s">
@@ -3796,7 +3805,7 @@
       <c r="E25" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="58" t="s">
+      <c r="F25" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G25" s="34" t="s">
@@ -3875,7 +3884,7 @@
       <c r="E26" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="58" t="s">
+      <c r="F26" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G26" s="34" t="s">
@@ -3954,7 +3963,7 @@
       <c r="E27" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="58" t="s">
+      <c r="F27" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G27" s="34" t="s">
@@ -4033,7 +4042,7 @@
       <c r="E28" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="58" t="s">
+      <c r="F28" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G28" s="34" t="s">
@@ -4112,7 +4121,7 @@
       <c r="E29" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="58" t="s">
+      <c r="F29" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="34" t="s">
@@ -4191,7 +4200,7 @@
       <c r="E30" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="58" t="s">
+      <c r="F30" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="34" t="s">
@@ -4249,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="Y30" s="8">
-        <f>Y29*10</f>
+        <f t="shared" ref="Y30:Y34" si="5">Y29*10</f>
         <v>100000000</v>
       </c>
     </row>
@@ -4270,7 +4279,7 @@
       <c r="E31" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="58" t="s">
+      <c r="F31" s="59" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="34" t="s">
@@ -4328,274 +4337,286 @@
         <v>0</v>
       </c>
       <c r="Y31" s="8">
-        <f>Y30*10</f>
+        <f t="shared" si="5"/>
         <v>1000000000</v>
       </c>
     </row>
-    <row r="32" s="3" customFormat="1" spans="1:25">
-      <c r="A32" s="49">
-        <v>20010010</v>
-      </c>
-      <c r="B32" s="3">
-        <v>200100</v>
-      </c>
-      <c r="C32" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="50">
-        <v>200100038</v>
-      </c>
-      <c r="E32" s="50" t="s">
+    <row r="32" s="2" customFormat="1" spans="1:25">
+      <c r="A32" s="4">
+        <f t="shared" si="0"/>
+        <v>2012001</v>
+      </c>
+      <c r="B32" s="49">
+        <v>201200</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="40">
+        <v>201200001</v>
+      </c>
+      <c r="E32" s="42" t="s">
         <v>51</v>
       </c>
       <c r="F32" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="H32" s="50">
-        <v>1</v>
-      </c>
-      <c r="I32" s="50">
-        <v>1980000</v>
+      <c r="G32" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" s="32">
+        <v>1</v>
+      </c>
+      <c r="I32" s="35">
+        <v>1990000</v>
       </c>
       <c r="J32" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="3">
-        <v>1</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M32" s="53" t="s">
-        <v>56</v>
+      <c r="K32" s="45">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M32" s="37" t="s">
+        <v>84</v>
       </c>
       <c r="N32" s="4">
         <v>9500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="4">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="4">
         <v>180000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="4">
         <v>16000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="4">
         <v>15000</v>
       </c>
-      <c r="S32" s="54">
+      <c r="S32" s="38">
         <v>16008</v>
       </c>
-      <c r="T32" s="49">
-        <v>48</v>
-      </c>
-      <c r="U32" s="55">
+      <c r="T32" s="6">
+        <v>12</v>
+      </c>
+      <c r="U32" s="39">
         <v>0</v>
       </c>
       <c r="V32" t="s">
         <v>57</v>
       </c>
       <c r="W32" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="X32" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="56"/>
+        <v>58</v>
+      </c>
+      <c r="X32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="8">
+        <f>100*100000</f>
+        <v>10000000</v>
+      </c>
     </row>
-    <row r="33" s="3" customFormat="1" spans="1:25">
-      <c r="A33" s="49">
-        <v>20010011</v>
-      </c>
-      <c r="B33" s="3">
-        <v>200100</v>
-      </c>
-      <c r="C33" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="D33" s="50">
-        <v>200100038</v>
-      </c>
-      <c r="E33" s="50" t="s">
+    <row r="33" customFormat="1" spans="1:25">
+      <c r="A33" s="4">
+        <f t="shared" si="0"/>
+        <v>2012002</v>
+      </c>
+      <c r="B33" s="49">
+        <v>201200</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="40">
+        <v>201200001</v>
+      </c>
+      <c r="E33" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F33" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="H33" s="50">
+      <c r="G33" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33" s="40">
         <v>2</v>
       </c>
-      <c r="I33" s="50">
-        <v>1980000</v>
+      <c r="I33" s="35">
+        <v>1990000</v>
       </c>
       <c r="J33" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K33" s="3">
-        <v>1</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M33" s="53" t="s">
-        <v>56</v>
+      <c r="K33" s="45">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M33" s="37" t="s">
+        <v>84</v>
       </c>
       <c r="N33" s="4">
         <v>9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="4">
         <v>300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="4">
         <v>180000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="4">
         <v>16000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="4">
         <v>15000</v>
       </c>
-      <c r="S33" s="54">
+      <c r="S33" s="38">
         <v>16008</v>
       </c>
-      <c r="T33" s="49">
-        <v>48</v>
-      </c>
-      <c r="U33" s="55">
+      <c r="T33" s="6">
+        <v>12</v>
+      </c>
+      <c r="U33" s="39">
         <v>0</v>
       </c>
       <c r="V33" t="s">
         <v>61</v>
       </c>
       <c r="W33" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="X33" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y33" s="56"/>
+        <v>62</v>
+      </c>
+      <c r="X33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="8">
+        <f t="shared" si="5"/>
+        <v>100000000</v>
+      </c>
     </row>
-    <row r="34" s="3" customFormat="1" spans="1:25">
-      <c r="A34" s="49">
-        <v>20010012</v>
-      </c>
-      <c r="B34" s="3">
-        <v>200100</v>
-      </c>
-      <c r="C34" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="50">
-        <v>200100038</v>
-      </c>
-      <c r="E34" s="50" t="s">
+    <row r="34" customFormat="1" spans="1:25">
+      <c r="A34" s="4">
+        <f t="shared" si="0"/>
+        <v>2012003</v>
+      </c>
+      <c r="B34" s="49">
+        <v>201200</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="40">
+        <v>201200001</v>
+      </c>
+      <c r="E34" s="48" t="s">
         <v>63</v>
       </c>
       <c r="F34" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="G34" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" s="50">
+      <c r="G34" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="H34" s="32">
         <v>3</v>
       </c>
-      <c r="I34" s="50">
-        <v>1980000</v>
+      <c r="I34" s="35">
+        <v>1990000</v>
       </c>
       <c r="J34" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="3">
-        <v>1</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M34" s="53" t="s">
-        <v>56</v>
+      <c r="K34" s="45">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M34" s="37" t="s">
+        <v>84</v>
       </c>
       <c r="N34" s="4">
         <v>9500</v>
       </c>
-      <c r="O34" s="3">
+      <c r="O34" s="4">
         <v>300</v>
       </c>
-      <c r="P34" s="3">
+      <c r="P34" s="4">
         <v>180000</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="Q34" s="4">
         <v>16000</v>
       </c>
-      <c r="R34" s="3">
+      <c r="R34" s="4">
         <v>15000</v>
       </c>
-      <c r="S34" s="54">
+      <c r="S34" s="38">
         <v>16008</v>
       </c>
-      <c r="T34" s="49">
-        <v>48</v>
-      </c>
-      <c r="U34" s="55">
+      <c r="T34" s="6">
+        <v>12</v>
+      </c>
+      <c r="U34" s="39">
         <v>0</v>
       </c>
       <c r="V34" t="s">
         <v>65</v>
       </c>
       <c r="W34" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="X34" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="56"/>
+        <v>66</v>
+      </c>
+      <c r="X34" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="8">
+        <f t="shared" si="5"/>
+        <v>1000000000</v>
+      </c>
     </row>
     <row r="35" s="3" customFormat="1" spans="1:25">
-      <c r="A35" s="49">
-        <v>20010110</v>
+      <c r="A35" s="50">
+        <v>20010010</v>
       </c>
       <c r="B35" s="3">
-        <v>200101</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" s="3">
-        <v>200101001</v>
-      </c>
-      <c r="E35" s="3" t="s">
+        <v>200100</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="51">
+        <v>200100038</v>
+      </c>
+      <c r="E35" s="51" t="s">
         <v>51</v>
       </c>
       <c r="F35" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1</v>
-      </c>
-      <c r="I35" s="50">
+      <c r="G35" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" s="51">
+        <v>1</v>
+      </c>
+      <c r="I35" s="51">
         <v>1980000</v>
       </c>
       <c r="J35" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M35" s="53" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="M35" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N35" s="4">
         <v>9500</v>
@@ -4612,65 +4633,65 @@
       <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="S35" s="55">
         <v>16008</v>
       </c>
-      <c r="T35" s="49">
+      <c r="T35" s="50">
         <v>48</v>
       </c>
-      <c r="U35" s="55">
+      <c r="U35" s="56">
         <v>0</v>
       </c>
       <c r="V35" t="s">
         <v>57</v>
       </c>
       <c r="W35" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="X35" s="3">
         <v>1</v>
       </c>
-      <c r="Y35" s="56"/>
+      <c r="Y35" s="57"/>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:25">
-      <c r="A36" s="49">
-        <v>20010111</v>
+      <c r="A36" s="50">
+        <v>20010011</v>
       </c>
       <c r="B36" s="3">
-        <v>200101</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D36" s="3">
-        <v>200101001</v>
-      </c>
-      <c r="E36" s="3" t="s">
+        <v>200100</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="51">
+        <v>200100038</v>
+      </c>
+      <c r="E36" s="51" t="s">
         <v>59</v>
       </c>
       <c r="F36" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="3">
+      <c r="G36" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H36" s="51">
         <v>2</v>
       </c>
-      <c r="I36" s="50">
+      <c r="I36" s="51">
         <v>1980000</v>
       </c>
       <c r="J36" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M36" s="53" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="M36" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N36" s="4">
         <v>9500</v>
@@ -4687,65 +4708,65 @@
       <c r="R36" s="3">
         <v>15000</v>
       </c>
-      <c r="S36" s="3">
+      <c r="S36" s="55">
         <v>16008</v>
       </c>
-      <c r="T36" s="49">
+      <c r="T36" s="50">
         <v>48</v>
       </c>
-      <c r="U36" s="55">
+      <c r="U36" s="56">
         <v>0</v>
       </c>
       <c r="V36" t="s">
         <v>61</v>
       </c>
       <c r="W36" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X36" s="3">
         <v>1</v>
       </c>
-      <c r="Y36" s="56"/>
+      <c r="Y36" s="57"/>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:25">
-      <c r="A37" s="49">
-        <v>20010112</v>
+      <c r="A37" s="50">
+        <v>20010012</v>
       </c>
       <c r="B37" s="3">
-        <v>200101</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D37" s="3">
-        <v>200101001</v>
-      </c>
-      <c r="E37" s="3" t="s">
+        <v>200100</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="51">
+        <v>200100038</v>
+      </c>
+      <c r="E37" s="51" t="s">
         <v>63</v>
       </c>
       <c r="F37" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="3">
+      <c r="G37" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H37" s="51">
         <v>3</v>
       </c>
-      <c r="I37" s="50">
+      <c r="I37" s="51">
         <v>1980000</v>
       </c>
       <c r="J37" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M37" s="53" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="M37" s="54" t="s">
+        <v>56</v>
       </c>
       <c r="N37" s="4">
         <v>9500</v>
@@ -4762,52 +4783,52 @@
       <c r="R37" s="3">
         <v>15000</v>
       </c>
-      <c r="S37" s="3">
+      <c r="S37" s="55">
         <v>16008</v>
       </c>
-      <c r="T37" s="49">
+      <c r="T37" s="50">
         <v>48</v>
       </c>
-      <c r="U37" s="55">
+      <c r="U37" s="56">
         <v>0</v>
       </c>
       <c r="V37" t="s">
         <v>65</v>
       </c>
       <c r="W37" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="X37" s="3">
         <v>1</v>
       </c>
-      <c r="Y37" s="56"/>
+      <c r="Y37" s="57"/>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:25">
-      <c r="A38" s="49">
-        <v>20030010</v>
+      <c r="A38" s="50">
+        <v>20010110</v>
       </c>
       <c r="B38" s="3">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D38" s="3">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="60" t="s">
+      <c r="F38" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="52" t="s">
-        <v>83</v>
+      <c r="G38" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
       </c>
-      <c r="I38" s="50">
+      <c r="I38" s="51">
         <v>1980000</v>
       </c>
       <c r="J38" s="36" t="s">
@@ -4819,8 +4840,8 @@
       <c r="L38" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M38" s="53" t="s">
-        <v>71</v>
+      <c r="M38" s="54" t="s">
+        <v>69</v>
       </c>
       <c r="N38" s="4">
         <v>9500</v>
@@ -4840,49 +4861,49 @@
       <c r="S38" s="3">
         <v>16008</v>
       </c>
-      <c r="T38" s="49">
-        <v>50</v>
-      </c>
-      <c r="U38" s="55">
+      <c r="T38" s="50">
+        <v>48</v>
+      </c>
+      <c r="U38" s="56">
         <v>0</v>
       </c>
       <c r="V38" t="s">
         <v>57</v>
       </c>
       <c r="W38" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="X38" s="3">
         <v>1</v>
       </c>
-      <c r="Y38" s="56"/>
+      <c r="Y38" s="57"/>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:25">
-      <c r="A39" s="49">
-        <v>20030011</v>
+      <c r="A39" s="50">
+        <v>20010111</v>
       </c>
       <c r="B39" s="3">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D39" s="3">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="60" t="s">
+      <c r="F39" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="52" t="s">
-        <v>83</v>
+      <c r="G39" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H39" s="3">
         <v>2</v>
       </c>
-      <c r="I39" s="50">
+      <c r="I39" s="51">
         <v>1980000</v>
       </c>
       <c r="J39" s="41" t="s">
@@ -4894,8 +4915,8 @@
       <c r="L39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M39" s="53" t="s">
-        <v>71</v>
+      <c r="M39" s="54" t="s">
+        <v>69</v>
       </c>
       <c r="N39" s="4">
         <v>9500</v>
@@ -4915,62 +4936,62 @@
       <c r="S39" s="3">
         <v>16008</v>
       </c>
-      <c r="T39" s="49">
-        <v>50</v>
-      </c>
-      <c r="U39" s="55">
+      <c r="T39" s="50">
+        <v>48</v>
+      </c>
+      <c r="U39" s="56">
         <v>0</v>
       </c>
       <c r="V39" t="s">
         <v>61</v>
       </c>
       <c r="W39" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X39" s="3">
         <v>1</v>
       </c>
-      <c r="Y39" s="56"/>
+      <c r="Y39" s="57"/>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:25">
-      <c r="A40" s="49">
-        <v>20030012</v>
+      <c r="A40" s="50">
+        <v>20010112</v>
       </c>
       <c r="B40" s="3">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D40" s="3">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="60" t="s">
+      <c r="F40" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="52" t="s">
-        <v>83</v>
+      <c r="G40" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H40" s="3">
         <v>3</v>
       </c>
-      <c r="I40" s="50">
+      <c r="I40" s="51">
         <v>1980000</v>
       </c>
       <c r="J40" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K40" s="57">
-        <v>0</v>
-      </c>
-      <c r="L40" s="57" t="s">
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M40" s="53" t="s">
-        <v>71</v>
+      <c r="M40" s="54" t="s">
+        <v>69</v>
       </c>
       <c r="N40" s="4">
         <v>9500</v>
@@ -4978,74 +4999,74 @@
       <c r="O40" s="3">
         <v>300</v>
       </c>
-      <c r="P40" s="57">
+      <c r="P40" s="3">
         <v>180000</v>
       </c>
-      <c r="Q40" s="57">
+      <c r="Q40" s="3">
         <v>16000</v>
       </c>
-      <c r="R40" s="57">
+      <c r="R40" s="3">
         <v>15000</v>
       </c>
-      <c r="S40" s="57">
+      <c r="S40" s="3">
         <v>16008</v>
       </c>
-      <c r="T40" s="49">
-        <v>50</v>
-      </c>
-      <c r="U40" s="55">
+      <c r="T40" s="50">
+        <v>48</v>
+      </c>
+      <c r="U40" s="56">
         <v>0</v>
       </c>
       <c r="V40" t="s">
         <v>65</v>
       </c>
       <c r="W40" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="56"/>
+      <c r="Y40" s="57"/>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:25">
-      <c r="A41" s="49">
-        <v>20040010</v>
+      <c r="A41" s="50">
+        <v>20030010</v>
       </c>
       <c r="B41" s="3">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D41" s="3">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="60" t="s">
+      <c r="F41" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="52" t="s">
-        <v>83</v>
+      <c r="G41" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
       </c>
-      <c r="I41" s="50">
+      <c r="I41" s="51">
         <v>1980000</v>
       </c>
       <c r="J41" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K41" s="57">
-        <v>0</v>
-      </c>
-      <c r="L41" s="57" t="s">
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M41" s="53" t="s">
-        <v>73</v>
+      <c r="M41" s="54" t="s">
+        <v>71</v>
       </c>
       <c r="N41" s="4">
         <v>9500</v>
@@ -5053,74 +5074,74 @@
       <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="57">
+      <c r="P41" s="3">
         <v>180000</v>
       </c>
-      <c r="Q41" s="57">
+      <c r="Q41" s="3">
         <v>16000</v>
       </c>
-      <c r="R41" s="57">
+      <c r="R41" s="3">
         <v>15000</v>
       </c>
-      <c r="S41" s="57">
+      <c r="S41" s="3">
         <v>16008</v>
       </c>
-      <c r="T41" s="49">
+      <c r="T41" s="50">
         <v>50</v>
       </c>
-      <c r="U41" s="55">
+      <c r="U41" s="56">
         <v>0</v>
       </c>
       <c r="V41" t="s">
         <v>57</v>
       </c>
       <c r="W41" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X41" s="3">
         <v>1</v>
       </c>
-      <c r="Y41" s="56"/>
+      <c r="Y41" s="57"/>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:25">
-      <c r="A42" s="49">
-        <v>20040011</v>
+      <c r="A42" s="50">
+        <v>20030011</v>
       </c>
       <c r="B42" s="3">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D42" s="3">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="60" t="s">
+      <c r="F42" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="52" t="s">
-        <v>83</v>
+      <c r="G42" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H42" s="3">
         <v>2</v>
       </c>
-      <c r="I42" s="50">
+      <c r="I42" s="51">
         <v>1980000</v>
       </c>
       <c r="J42" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K42" s="57">
-        <v>0</v>
-      </c>
-      <c r="L42" s="57" t="s">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M42" s="53" t="s">
-        <v>73</v>
+      <c r="M42" s="54" t="s">
+        <v>71</v>
       </c>
       <c r="N42" s="4">
         <v>9500</v>
@@ -5128,74 +5149,74 @@
       <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="57">
+      <c r="P42" s="3">
         <v>180000</v>
       </c>
-      <c r="Q42" s="57">
+      <c r="Q42" s="3">
         <v>16000</v>
       </c>
-      <c r="R42" s="57">
+      <c r="R42" s="3">
         <v>15000</v>
       </c>
-      <c r="S42" s="57">
+      <c r="S42" s="3">
         <v>16008</v>
       </c>
-      <c r="T42" s="49">
+      <c r="T42" s="50">
         <v>50</v>
       </c>
-      <c r="U42" s="55">
+      <c r="U42" s="56">
         <v>0</v>
       </c>
       <c r="V42" t="s">
         <v>61</v>
       </c>
       <c r="W42" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X42" s="3">
         <v>1</v>
       </c>
-      <c r="Y42" s="56"/>
+      <c r="Y42" s="57"/>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:25">
-      <c r="A43" s="49">
-        <v>20040012</v>
+      <c r="A43" s="50">
+        <v>20030012</v>
       </c>
       <c r="B43" s="3">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D43" s="3">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="60" t="s">
+      <c r="F43" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="52" t="s">
-        <v>83</v>
+      <c r="G43" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H43" s="3">
         <v>3</v>
       </c>
-      <c r="I43" s="50">
+      <c r="I43" s="51">
         <v>1980000</v>
       </c>
       <c r="J43" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K43" s="57">
-        <v>0</v>
-      </c>
-      <c r="L43" s="57" t="s">
+      <c r="K43" s="58">
+        <v>0</v>
+      </c>
+      <c r="L43" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M43" s="53" t="s">
-        <v>73</v>
+      <c r="M43" s="54" t="s">
+        <v>71</v>
       </c>
       <c r="N43" s="4">
         <v>9500</v>
@@ -5203,74 +5224,74 @@
       <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="57">
+      <c r="P43" s="58">
         <v>180000</v>
       </c>
-      <c r="Q43" s="57">
+      <c r="Q43" s="58">
         <v>16000</v>
       </c>
-      <c r="R43" s="57">
+      <c r="R43" s="58">
         <v>15000</v>
       </c>
-      <c r="S43" s="57">
+      <c r="S43" s="58">
         <v>16008</v>
       </c>
-      <c r="T43" s="49">
+      <c r="T43" s="50">
         <v>50</v>
       </c>
-      <c r="U43" s="55">
+      <c r="U43" s="56">
         <v>0</v>
       </c>
       <c r="V43" t="s">
         <v>65</v>
       </c>
       <c r="W43" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X43" s="3">
         <v>1</v>
       </c>
-      <c r="Y43" s="56"/>
+      <c r="Y43" s="57"/>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:25">
-      <c r="A44" s="49">
-        <v>20050010</v>
+      <c r="A44" s="50">
+        <v>20040010</v>
       </c>
       <c r="B44" s="3">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D44" s="3">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="60" t="s">
+      <c r="F44" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="52" t="s">
-        <v>83</v>
+      <c r="G44" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
       </c>
-      <c r="I44" s="50">
+      <c r="I44" s="51">
         <v>1980000</v>
       </c>
       <c r="J44" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K44" s="57">
-        <v>1</v>
-      </c>
-      <c r="L44" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="M44" s="53" t="s">
-        <v>75</v>
+      <c r="K44" s="58">
+        <v>0</v>
+      </c>
+      <c r="L44" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="M44" s="54" t="s">
+        <v>73</v>
       </c>
       <c r="N44" s="4">
         <v>9500</v>
@@ -5278,74 +5299,74 @@
       <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="57">
+      <c r="P44" s="58">
         <v>180000</v>
       </c>
-      <c r="Q44" s="57">
+      <c r="Q44" s="58">
         <v>16000</v>
       </c>
-      <c r="R44" s="57">
+      <c r="R44" s="58">
         <v>15000</v>
       </c>
-      <c r="S44" s="57">
+      <c r="S44" s="58">
         <v>16008</v>
       </c>
-      <c r="T44" s="49">
-        <v>48</v>
-      </c>
-      <c r="U44" s="49">
+      <c r="T44" s="50">
+        <v>50</v>
+      </c>
+      <c r="U44" s="56">
         <v>0</v>
       </c>
       <c r="V44" t="s">
         <v>57</v>
       </c>
       <c r="W44" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X44" s="3">
         <v>1</v>
       </c>
-      <c r="Y44" s="56"/>
+      <c r="Y44" s="57"/>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:25">
-      <c r="A45" s="49">
-        <v>20050011</v>
+      <c r="A45" s="50">
+        <v>20040011</v>
       </c>
       <c r="B45" s="3">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D45" s="3">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="60" t="s">
+      <c r="F45" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="52" t="s">
-        <v>83</v>
+      <c r="G45" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H45" s="3">
         <v>2</v>
       </c>
-      <c r="I45" s="50">
+      <c r="I45" s="51">
         <v>1980000</v>
       </c>
       <c r="J45" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K45" s="57">
-        <v>1</v>
-      </c>
-      <c r="L45" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="M45" s="53" t="s">
-        <v>75</v>
+      <c r="K45" s="58">
+        <v>0</v>
+      </c>
+      <c r="L45" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="M45" s="54" t="s">
+        <v>73</v>
       </c>
       <c r="N45" s="4">
         <v>9500</v>
@@ -5353,74 +5374,74 @@
       <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="57">
+      <c r="P45" s="58">
         <v>180000</v>
       </c>
-      <c r="Q45" s="57">
+      <c r="Q45" s="58">
         <v>16000</v>
       </c>
-      <c r="R45" s="57">
+      <c r="R45" s="58">
         <v>15000</v>
       </c>
-      <c r="S45" s="57">
+      <c r="S45" s="58">
         <v>16008</v>
       </c>
-      <c r="T45" s="49">
-        <v>48</v>
-      </c>
-      <c r="U45" s="49">
+      <c r="T45" s="50">
+        <v>50</v>
+      </c>
+      <c r="U45" s="56">
         <v>0</v>
       </c>
       <c r="V45" t="s">
         <v>61</v>
       </c>
       <c r="W45" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X45" s="3">
         <v>1</v>
       </c>
-      <c r="Y45" s="56"/>
+      <c r="Y45" s="57"/>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:25">
-      <c r="A46" s="49">
-        <v>20050012</v>
+      <c r="A46" s="50">
+        <v>20040012</v>
       </c>
       <c r="B46" s="3">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D46" s="3">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="60" t="s">
+      <c r="F46" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="52" t="s">
-        <v>83</v>
+      <c r="G46" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H46" s="3">
         <v>3</v>
       </c>
-      <c r="I46" s="50">
+      <c r="I46" s="51">
         <v>1980000</v>
       </c>
       <c r="J46" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K46" s="57">
-        <v>1</v>
-      </c>
-      <c r="L46" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="M46" s="53" t="s">
-        <v>75</v>
+      <c r="K46" s="58">
+        <v>0</v>
+      </c>
+      <c r="L46" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="M46" s="54" t="s">
+        <v>73</v>
       </c>
       <c r="N46" s="4">
         <v>9500</v>
@@ -5428,74 +5449,74 @@
       <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="57">
+      <c r="P46" s="58">
         <v>180000</v>
       </c>
-      <c r="Q46" s="57">
+      <c r="Q46" s="58">
         <v>16000</v>
       </c>
-      <c r="R46" s="57">
+      <c r="R46" s="58">
         <v>15000</v>
       </c>
-      <c r="S46" s="57">
+      <c r="S46" s="58">
         <v>16008</v>
       </c>
-      <c r="T46" s="49">
-        <v>48</v>
-      </c>
-      <c r="U46" s="49">
+      <c r="T46" s="50">
+        <v>50</v>
+      </c>
+      <c r="U46" s="56">
         <v>0</v>
       </c>
       <c r="V46" t="s">
         <v>65</v>
       </c>
       <c r="W46" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X46" s="3">
         <v>1</v>
       </c>
-      <c r="Y46" s="56"/>
+      <c r="Y46" s="57"/>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:25">
-      <c r="A47" s="49">
-        <v>20060010</v>
+      <c r="A47" s="50">
+        <v>20050010</v>
       </c>
       <c r="B47" s="3">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D47" s="3">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F47" s="60" t="s">
+      <c r="F47" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="52" t="s">
-        <v>83</v>
+      <c r="G47" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="50">
+      <c r="I47" s="51">
         <v>1980000</v>
       </c>
       <c r="J47" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K47" s="57">
-        <v>0</v>
-      </c>
-      <c r="L47" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="M47" s="53" t="s">
-        <v>77</v>
+      <c r="K47" s="58">
+        <v>1</v>
+      </c>
+      <c r="L47" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="M47" s="54" t="s">
+        <v>75</v>
       </c>
       <c r="N47" s="4">
         <v>9500</v>
@@ -5503,74 +5524,74 @@
       <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="P47" s="57">
+      <c r="P47" s="58">
         <v>180000</v>
       </c>
-      <c r="Q47" s="57">
+      <c r="Q47" s="58">
         <v>16000</v>
       </c>
-      <c r="R47" s="57">
+      <c r="R47" s="58">
         <v>15000</v>
       </c>
-      <c r="S47" s="57">
+      <c r="S47" s="58">
         <v>16008</v>
       </c>
-      <c r="T47" s="49">
-        <v>20</v>
-      </c>
-      <c r="U47" s="49">
+      <c r="T47" s="50">
+        <v>48</v>
+      </c>
+      <c r="U47" s="50">
         <v>0</v>
       </c>
       <c r="V47" t="s">
         <v>57</v>
       </c>
       <c r="W47" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="X47" s="3">
         <v>1</v>
       </c>
-      <c r="Y47" s="56"/>
+      <c r="Y47" s="57"/>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:25">
-      <c r="A48" s="49">
-        <v>20060011</v>
+      <c r="A48" s="50">
+        <v>20050011</v>
       </c>
       <c r="B48" s="3">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D48" s="3">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="60" t="s">
+      <c r="F48" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="52" t="s">
-        <v>83</v>
+      <c r="G48" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H48" s="3">
         <v>2</v>
       </c>
-      <c r="I48" s="50">
+      <c r="I48" s="51">
         <v>1980000</v>
       </c>
       <c r="J48" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K48" s="57">
-        <v>0</v>
-      </c>
-      <c r="L48" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="M48" s="53" t="s">
-        <v>77</v>
+      <c r="K48" s="58">
+        <v>1</v>
+      </c>
+      <c r="L48" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="M48" s="54" t="s">
+        <v>75</v>
       </c>
       <c r="N48" s="4">
         <v>9500</v>
@@ -5578,74 +5599,74 @@
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="57">
+      <c r="P48" s="58">
         <v>180000</v>
       </c>
-      <c r="Q48" s="57">
+      <c r="Q48" s="58">
         <v>16000</v>
       </c>
-      <c r="R48" s="57">
+      <c r="R48" s="58">
         <v>15000</v>
       </c>
-      <c r="S48" s="57">
+      <c r="S48" s="58">
         <v>16008</v>
       </c>
-      <c r="T48" s="49">
-        <v>20</v>
-      </c>
-      <c r="U48" s="49">
+      <c r="T48" s="50">
+        <v>48</v>
+      </c>
+      <c r="U48" s="50">
         <v>0</v>
       </c>
       <c r="V48" t="s">
         <v>61</v>
       </c>
       <c r="W48" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="X48" s="3">
         <v>1</v>
       </c>
-      <c r="Y48" s="56"/>
+      <c r="Y48" s="57"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:25">
-      <c r="A49" s="49">
-        <v>20060012</v>
+      <c r="A49" s="50">
+        <v>20050012</v>
       </c>
       <c r="B49" s="3">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D49" s="3">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F49" s="60" t="s">
+      <c r="F49" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G49" s="52" t="s">
-        <v>83</v>
+      <c r="G49" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H49" s="3">
         <v>3</v>
       </c>
-      <c r="I49" s="50">
+      <c r="I49" s="51">
         <v>1980000</v>
       </c>
       <c r="J49" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M49" s="53" t="s">
-        <v>77</v>
+      <c r="K49" s="58">
+        <v>1</v>
+      </c>
+      <c r="L49" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="M49" s="54" t="s">
+        <v>75</v>
       </c>
       <c r="N49" s="4">
         <v>9500</v>
@@ -5653,74 +5674,74 @@
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="P49" s="58">
         <v>180000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="Q49" s="58">
         <v>16000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="R49" s="58">
         <v>15000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="S49" s="58">
         <v>16008</v>
       </c>
-      <c r="T49" s="49">
-        <v>20</v>
-      </c>
-      <c r="U49" s="49">
+      <c r="T49" s="50">
+        <v>48</v>
+      </c>
+      <c r="U49" s="50">
         <v>0</v>
       </c>
       <c r="V49" t="s">
         <v>65</v>
       </c>
       <c r="W49" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="X49" s="3">
         <v>1</v>
       </c>
-      <c r="Y49" s="56"/>
+      <c r="Y49" s="57"/>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:25">
-      <c r="A50" s="49">
-        <v>20070010</v>
+      <c r="A50" s="50">
+        <v>20060010</v>
       </c>
       <c r="B50" s="3">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D50" s="3">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F50" s="60" t="s">
+      <c r="F50" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G50" s="52" t="s">
-        <v>83</v>
+      <c r="G50" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
       </c>
-      <c r="I50" s="50">
+      <c r="I50" s="51">
         <v>1980000</v>
       </c>
       <c r="J50" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K50" s="3">
-        <v>1</v>
-      </c>
-      <c r="L50" s="3" t="s">
+      <c r="K50" s="58">
+        <v>0</v>
+      </c>
+      <c r="L50" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M50" s="53" t="s">
-        <v>79</v>
+      <c r="M50" s="54" t="s">
+        <v>77</v>
       </c>
       <c r="N50" s="4">
         <v>9500</v>
@@ -5728,74 +5749,74 @@
       <c r="O50" s="3">
         <v>300</v>
       </c>
-      <c r="P50" s="3">
+      <c r="P50" s="58">
         <v>180000</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="Q50" s="58">
         <v>16000</v>
       </c>
-      <c r="R50" s="3">
+      <c r="R50" s="58">
         <v>15000</v>
       </c>
-      <c r="S50" s="3">
+      <c r="S50" s="58">
         <v>16008</v>
       </c>
-      <c r="T50" s="49">
-        <v>30</v>
-      </c>
-      <c r="U50" s="49">
-        <v>1</v>
+      <c r="T50" s="50">
+        <v>20</v>
+      </c>
+      <c r="U50" s="50">
+        <v>0</v>
       </c>
       <c r="V50" t="s">
         <v>57</v>
       </c>
       <c r="W50" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="X50" s="3">
         <v>1</v>
       </c>
-      <c r="Y50" s="56"/>
+      <c r="Y50" s="57"/>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:25">
-      <c r="A51" s="49">
-        <v>20070011</v>
+      <c r="A51" s="50">
+        <v>20060011</v>
       </c>
       <c r="B51" s="3">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D51" s="3">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="60" t="s">
+      <c r="F51" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="52" t="s">
-        <v>83</v>
+      <c r="G51" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H51" s="3">
         <v>2</v>
       </c>
-      <c r="I51" s="50">
+      <c r="I51" s="51">
         <v>1980000</v>
       </c>
       <c r="J51" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K51" s="3">
-        <v>1</v>
-      </c>
-      <c r="L51" s="3" t="s">
+      <c r="K51" s="58">
+        <v>0</v>
+      </c>
+      <c r="L51" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="M51" s="53" t="s">
-        <v>79</v>
+      <c r="M51" s="54" t="s">
+        <v>77</v>
       </c>
       <c r="N51" s="4">
         <v>9500</v>
@@ -5803,74 +5824,74 @@
       <c r="O51" s="3">
         <v>300</v>
       </c>
-      <c r="P51" s="3">
+      <c r="P51" s="58">
         <v>180000</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="Q51" s="58">
         <v>16000</v>
       </c>
-      <c r="R51" s="3">
+      <c r="R51" s="58">
         <v>15000</v>
       </c>
-      <c r="S51" s="3">
+      <c r="S51" s="58">
         <v>16008</v>
       </c>
-      <c r="T51" s="49">
-        <v>30</v>
-      </c>
-      <c r="U51" s="49">
-        <v>1</v>
+      <c r="T51" s="50">
+        <v>20</v>
+      </c>
+      <c r="U51" s="50">
+        <v>0</v>
       </c>
       <c r="V51" t="s">
         <v>61</v>
       </c>
       <c r="W51" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X51" s="3">
         <v>1</v>
       </c>
-      <c r="Y51" s="56"/>
+      <c r="Y51" s="57"/>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:25">
-      <c r="A52" s="49">
-        <v>20070012</v>
+      <c r="A52" s="50">
+        <v>20060012</v>
       </c>
       <c r="B52" s="3">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D52" s="3">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="60" t="s">
+      <c r="F52" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="52" t="s">
-        <v>83</v>
+      <c r="G52" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="50">
+      <c r="I52" s="51">
         <v>1980000</v>
       </c>
       <c r="J52" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="53" t="s">
-        <v>79</v>
+      <c r="M52" s="54" t="s">
+        <v>77</v>
       </c>
       <c r="N52" s="4">
         <v>9500</v>
@@ -5890,62 +5911,62 @@
       <c r="S52" s="3">
         <v>16008</v>
       </c>
-      <c r="T52" s="49">
-        <v>30</v>
-      </c>
-      <c r="U52" s="49">
-        <v>1</v>
+      <c r="T52" s="50">
+        <v>20</v>
+      </c>
+      <c r="U52" s="50">
+        <v>0</v>
       </c>
       <c r="V52" t="s">
         <v>65</v>
       </c>
       <c r="W52" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="X52" s="3">
         <v>1</v>
       </c>
-      <c r="Y52" s="56"/>
+      <c r="Y52" s="57"/>
     </row>
     <row r="53" s="3" customFormat="1" spans="1:25">
-      <c r="A53" s="49">
-        <v>20080010</v>
+      <c r="A53" s="50">
+        <v>20070010</v>
       </c>
       <c r="B53" s="3">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D53" s="3">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="60" t="s">
+      <c r="F53" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="52" t="s">
-        <v>83</v>
+      <c r="G53" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
       </c>
-      <c r="I53" s="50">
+      <c r="I53" s="51">
         <v>1980000</v>
       </c>
       <c r="J53" s="36" t="s">
         <v>54</v>
       </c>
       <c r="K53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="53" t="s">
-        <v>81</v>
+      <c r="M53" s="54" t="s">
+        <v>79</v>
       </c>
       <c r="N53" s="4">
         <v>9500</v>
@@ -5965,62 +5986,62 @@
       <c r="S53" s="3">
         <v>16008</v>
       </c>
-      <c r="T53" s="49">
-        <v>20</v>
-      </c>
-      <c r="U53" s="49">
-        <v>0</v>
+      <c r="T53" s="50">
+        <v>30</v>
+      </c>
+      <c r="U53" s="50">
+        <v>1</v>
       </c>
       <c r="V53" t="s">
         <v>57</v>
       </c>
       <c r="W53" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="X53" s="3">
         <v>1</v>
       </c>
-      <c r="Y53" s="56"/>
+      <c r="Y53" s="57"/>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:25">
-      <c r="A54" s="49">
-        <v>20080011</v>
+      <c r="A54" s="50">
+        <v>20070011</v>
       </c>
       <c r="B54" s="3">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D54" s="3">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="60" t="s">
+      <c r="F54" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G54" s="52" t="s">
-        <v>83</v>
+      <c r="G54" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H54" s="3">
         <v>2</v>
       </c>
-      <c r="I54" s="50">
+      <c r="I54" s="51">
         <v>1980000</v>
       </c>
       <c r="J54" s="41" t="s">
         <v>60</v>
       </c>
       <c r="K54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M54" s="53" t="s">
-        <v>81</v>
+      <c r="M54" s="54" t="s">
+        <v>79</v>
       </c>
       <c r="N54" s="4">
         <v>9500</v>
@@ -6040,62 +6061,62 @@
       <c r="S54" s="3">
         <v>16008</v>
       </c>
-      <c r="T54" s="49">
-        <v>20</v>
-      </c>
-      <c r="U54" s="49">
-        <v>0</v>
+      <c r="T54" s="50">
+        <v>30</v>
+      </c>
+      <c r="U54" s="50">
+        <v>1</v>
       </c>
       <c r="V54" t="s">
         <v>61</v>
       </c>
       <c r="W54" s="8" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="X54" s="3">
         <v>1</v>
       </c>
-      <c r="Y54" s="56"/>
+      <c r="Y54" s="57"/>
     </row>
     <row r="55" s="3" customFormat="1" spans="1:25">
-      <c r="A55" s="49">
-        <v>20080012</v>
+      <c r="A55" s="50">
+        <v>20070012</v>
       </c>
       <c r="B55" s="3">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D55" s="3">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="60" t="s">
+      <c r="F55" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="52" t="s">
-        <v>83</v>
+      <c r="G55" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H55" s="3">
         <v>3</v>
       </c>
-      <c r="I55" s="50">
+      <c r="I55" s="51">
         <v>1980000</v>
       </c>
       <c r="J55" s="36" t="s">
         <v>64</v>
       </c>
       <c r="K55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="53" t="s">
-        <v>81</v>
+      <c r="M55" s="54" t="s">
+        <v>79</v>
       </c>
       <c r="N55" s="4">
         <v>9500</v>
@@ -6115,49 +6136,49 @@
       <c r="S55" s="3">
         <v>16008</v>
       </c>
-      <c r="T55" s="49">
-        <v>20</v>
-      </c>
-      <c r="U55" s="49">
-        <v>0</v>
+      <c r="T55" s="50">
+        <v>30</v>
+      </c>
+      <c r="U55" s="50">
+        <v>1</v>
       </c>
       <c r="V55" t="s">
         <v>65</v>
       </c>
       <c r="W55" s="8" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="X55" s="3">
         <v>1</v>
       </c>
-      <c r="Y55" s="56"/>
+      <c r="Y55" s="57"/>
     </row>
     <row r="56" s="3" customFormat="1" spans="1:25">
-      <c r="A56" s="49">
-        <v>20090010</v>
+      <c r="A56" s="50">
+        <v>20080010</v>
       </c>
       <c r="B56" s="3">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D56" s="3">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="60" t="s">
+      <c r="F56" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G56" s="52" t="s">
-        <v>83</v>
+      <c r="G56" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
       </c>
-      <c r="I56" s="50">
+      <c r="I56" s="51">
         <v>1980000</v>
       </c>
       <c r="J56" s="36" t="s">
@@ -6169,7 +6190,7 @@
       <c r="L56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M56" s="53" t="s">
+      <c r="M56" s="54" t="s">
         <v>81</v>
       </c>
       <c r="N56" s="4">
@@ -6190,49 +6211,49 @@
       <c r="S56" s="3">
         <v>16008</v>
       </c>
-      <c r="T56" s="49">
+      <c r="T56" s="50">
         <v>20</v>
       </c>
-      <c r="U56" s="49">
+      <c r="U56" s="50">
         <v>0</v>
       </c>
       <c r="V56" t="s">
         <v>57</v>
       </c>
       <c r="W56" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X56" s="3">
         <v>1</v>
       </c>
-      <c r="Y56" s="56"/>
+      <c r="Y56" s="57"/>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:25">
-      <c r="A57" s="49">
-        <v>20090011</v>
+      <c r="A57" s="50">
+        <v>20080011</v>
       </c>
       <c r="B57" s="3">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D57" s="3">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="60" t="s">
+      <c r="F57" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G57" s="52" t="s">
-        <v>83</v>
+      <c r="G57" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H57" s="3">
         <v>2</v>
       </c>
-      <c r="I57" s="50">
+      <c r="I57" s="51">
         <v>1980000</v>
       </c>
       <c r="J57" s="41" t="s">
@@ -6244,7 +6265,7 @@
       <c r="L57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M57" s="53" t="s">
+      <c r="M57" s="54" t="s">
         <v>81</v>
       </c>
       <c r="N57" s="4">
@@ -6265,49 +6286,49 @@
       <c r="S57" s="3">
         <v>16008</v>
       </c>
-      <c r="T57" s="49">
+      <c r="T57" s="50">
         <v>20</v>
       </c>
-      <c r="U57" s="49">
+      <c r="U57" s="50">
         <v>0</v>
       </c>
       <c r="V57" t="s">
         <v>61</v>
       </c>
       <c r="W57" s="8" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="X57" s="3">
         <v>1</v>
       </c>
-      <c r="Y57" s="56"/>
+      <c r="Y57" s="57"/>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:25">
-      <c r="A58" s="49">
-        <v>20090012</v>
+      <c r="A58" s="50">
+        <v>20080012</v>
       </c>
       <c r="B58" s="3">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D58" s="3">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F58" s="60" t="s">
+      <c r="F58" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G58" s="52" t="s">
-        <v>83</v>
+      <c r="G58" s="53" t="s">
+        <v>85</v>
       </c>
       <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="50">
+      <c r="I58" s="51">
         <v>1980000</v>
       </c>
       <c r="J58" s="36" t="s">
@@ -6319,7 +6340,7 @@
       <c r="L58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M58" s="53" t="s">
+      <c r="M58" s="54" t="s">
         <v>81</v>
       </c>
       <c r="N58" s="4">
@@ -6340,25 +6361,475 @@
       <c r="S58" s="3">
         <v>16008</v>
       </c>
-      <c r="T58" s="49">
+      <c r="T58" s="50">
         <v>20</v>
       </c>
-      <c r="U58" s="49">
+      <c r="U58" s="50">
         <v>0</v>
       </c>
       <c r="V58" t="s">
         <v>65</v>
       </c>
       <c r="W58" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="X58" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="57"/>
+    </row>
+    <row r="59" s="3" customFormat="1" spans="1:25">
+      <c r="A59" s="50">
+        <v>20090010</v>
+      </c>
+      <c r="B59" s="3">
+        <v>200900</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59" s="3">
+        <v>200900001</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F59" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1</v>
+      </c>
+      <c r="I59" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J59" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M59" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="N59" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O59" s="3">
+        <v>300</v>
+      </c>
+      <c r="P59" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R59" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S59" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T59" s="50">
+        <v>20</v>
+      </c>
+      <c r="U59" s="50">
+        <v>0</v>
+      </c>
+      <c r="V59" t="s">
+        <v>57</v>
+      </c>
+      <c r="W59" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="X58" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y58" s="56"/>
+      <c r="X59" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y59" s="57"/>
+    </row>
+    <row r="60" s="3" customFormat="1" spans="1:25">
+      <c r="A60" s="50">
+        <v>20090011</v>
+      </c>
+      <c r="B60" s="3">
+        <v>200900</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="3">
+        <v>200900001</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F60" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="G60" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H60" s="3">
+        <v>2</v>
+      </c>
+      <c r="I60" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J60" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="K60" s="3">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M60" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="N60" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O60" s="3">
+        <v>300</v>
+      </c>
+      <c r="P60" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R60" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S60" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T60" s="50">
+        <v>20</v>
+      </c>
+      <c r="U60" s="50">
+        <v>0</v>
+      </c>
+      <c r="V60" t="s">
+        <v>61</v>
+      </c>
+      <c r="W60" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="X60" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="57"/>
+    </row>
+    <row r="61" s="3" customFormat="1" spans="1:25">
+      <c r="A61" s="50">
+        <v>20090012</v>
+      </c>
+      <c r="B61" s="3">
+        <v>200900</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" s="3">
+        <v>200900001</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F61" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="G61" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H61" s="3">
+        <v>3</v>
+      </c>
+      <c r="I61" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J61" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M61" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="N61" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O61" s="3">
+        <v>300</v>
+      </c>
+      <c r="P61" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S61" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T61" s="50">
+        <v>20</v>
+      </c>
+      <c r="U61" s="50">
+        <v>0</v>
+      </c>
+      <c r="V61" t="s">
+        <v>65</v>
+      </c>
+      <c r="W61" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="X61" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="57"/>
+    </row>
+    <row r="62" s="3" customFormat="1" spans="1:25">
+      <c r="A62" s="50">
+        <v>20120010</v>
+      </c>
+      <c r="B62" s="49">
+        <v>201200</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" s="3">
+        <v>201200001</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F62" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="G62" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1</v>
+      </c>
+      <c r="I62" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J62" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M62" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="N62" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O62" s="3">
+        <v>300</v>
+      </c>
+      <c r="P62" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R62" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S62" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T62" s="50">
+        <v>12</v>
+      </c>
+      <c r="U62" s="50">
+        <v>0</v>
+      </c>
+      <c r="V62" t="s">
+        <v>57</v>
+      </c>
+      <c r="W62" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="X62" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y62" s="57"/>
+    </row>
+    <row r="63" s="3" customFormat="1" spans="1:25">
+      <c r="A63" s="50">
+        <v>20120011</v>
+      </c>
+      <c r="B63" s="49">
+        <v>201200</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D63" s="3">
+        <v>201200001</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="G63" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H63" s="3">
+        <v>2</v>
+      </c>
+      <c r="I63" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J63" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M63" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="N63" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O63" s="3">
+        <v>300</v>
+      </c>
+      <c r="P63" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R63" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S63" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T63" s="50">
+        <v>12</v>
+      </c>
+      <c r="U63" s="50">
+        <v>0</v>
+      </c>
+      <c r="V63" t="s">
+        <v>61</v>
+      </c>
+      <c r="W63" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="X63" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y63" s="57"/>
+    </row>
+    <row r="64" s="3" customFormat="1" spans="1:25">
+      <c r="A64" s="50">
+        <v>20120012</v>
+      </c>
+      <c r="B64" s="49">
+        <v>201200</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" s="3">
+        <v>201200001</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F64" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="G64" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="H64" s="3">
+        <v>3</v>
+      </c>
+      <c r="I64" s="51">
+        <v>1980000</v>
+      </c>
+      <c r="J64" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M64" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="N64" s="4">
+        <v>9500</v>
+      </c>
+      <c r="O64" s="3">
+        <v>300</v>
+      </c>
+      <c r="P64" s="3">
+        <v>180000</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R64" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S64" s="3">
+        <v>16008</v>
+      </c>
+      <c r="T64" s="50">
+        <v>12</v>
+      </c>
+      <c r="U64" s="50">
+        <v>0</v>
+      </c>
+      <c r="V64" t="s">
+        <v>65</v>
+      </c>
+      <c r="W64" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="X64" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y64" s="57"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S58" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S61" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Room_Bet!$A$1:$S$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -584,7 +584,7 @@
     <t>俄罗斯轮盘</t>
   </si>
   <si>
-    <t>3000,16000,8000,0</t>
+    <t>16000,8000,3000,0</t>
   </si>
   <si>
     <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
@@ -6829,7 +6829,7 @@
       <c r="Y64" s="57"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S61" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S64" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/Room_Bet.xlsx
+++ b/table/resources/sample/Room_Bet.xlsx
@@ -584,7 +584,7 @@
     <t>俄罗斯轮盘</t>
   </si>
   <si>
-    <t>16000,8000,3000,0</t>
+    <t>16000,10000,5000,0</t>
   </si>
   <si>
     <t>0:6:0|6:12:0|12:18:0|18:24:0</t>
